--- a/IPL_Fantasy_Points.xlsx
+++ b/IPL_Fantasy_Points.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player_Points" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Merged_Stats" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="No_Stats_Yet" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Possible_Mismatch" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Player_Points" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Leaderboard" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Merged_Stats" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="No_Stats_Yet" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Possible_Mismatch" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -628,19 +628,19 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>jitesh sharma</t>
+          <t>brijesh sharma</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>possible_mismatch:72.0</t>
+          <t>fuzzy:81.4814814814815</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -759,23 +759,23 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>possible_mismatch:72.0</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9">
@@ -1305,23 +1305,23 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>possible_mismatch:62.5</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
     </row>
     <row r="22">
@@ -1683,23 +1683,23 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31">
@@ -1809,23 +1809,23 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="34">
@@ -2229,23 +2229,23 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="F43" t="n">
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="44">
@@ -2481,23 +2481,23 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>possible_mismatch:66.66666666666667</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="F49" t="n">
         <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="50">
@@ -2691,23 +2691,23 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="55">
@@ -2817,7 +2817,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>possible_mismatch:78.57142857142857</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -3027,23 +3027,23 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>possible_mismatch:63.63636363636363</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I62" t="n">
         <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="63">
@@ -3363,23 +3363,23 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I70" t="n">
         <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="71">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>possible_mismatch:61.53846153846154</t>
+          <t>possible_mismatch:75.0</t>
         </is>
       </c>
       <c r="F73" t="n">
@@ -3657,23 +3657,23 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="I77" t="n">
         <v>0</v>
       </c>
       <c r="J77" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="78">
@@ -4119,23 +4119,23 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="I88" t="n">
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
     </row>
     <row r="89">
@@ -4539,23 +4539,23 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
       </c>
       <c r="H98" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I98" t="n">
         <v>0</v>
       </c>
       <c r="J98" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="99">
@@ -4833,23 +4833,23 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="F105" t="n">
         <v>0</v>
       </c>
       <c r="G105" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H105" t="n">
         <v>0</v>
       </c>
       <c r="I105" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J105" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="106">
@@ -5169,23 +5169,23 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
       </c>
       <c r="H113" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="I113" t="n">
         <v>0</v>
       </c>
       <c r="J113" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
     </row>
     <row r="114">
@@ -6807,23 +6807,23 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="F152" t="n">
         <v>0</v>
       </c>
       <c r="G152" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H152" t="n">
         <v>0</v>
       </c>
       <c r="I152" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J152" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="153">
@@ -7059,11 +7059,11 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="F158" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -7857,11 +7857,11 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="F177" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -7913,11 +7913,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>MEET11</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>219</v>
+        <v>283</v>
       </c>
     </row>
     <row r="3">
@@ -7926,11 +7926,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MEET11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>171</v>
+        <v>259</v>
       </c>
     </row>
     <row r="4">
@@ -7939,11 +7939,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>VATSAL11</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>161</v>
+        <v>212</v>
       </c>
     </row>
     <row r="5">
@@ -7952,11 +7952,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>VATSAL11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>152</v>
+        <v>187</v>
       </c>
     </row>
     <row r="6">
@@ -7965,11 +7965,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>144</v>
+        <v>161</v>
       </c>
     </row>
     <row r="7">
@@ -7982,7 +7982,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>114</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8">
@@ -7991,11 +7991,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PRATIK11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>84</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9">
@@ -8004,11 +8004,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NIRAV11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>65</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10">
@@ -8017,11 +8017,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DIPESH11</t>
+          <t>NIRAV11</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11">
@@ -8030,11 +8030,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>DIPESH11</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -8048,7 +8048,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8136,50 +8136,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>bhuvneshwar kumar</t>
+          <t>anshul kamboj</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>cameron green</t>
+          <t>bhuvneshwar kumar</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>david payne</t>
+          <t>brijesh sharma</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>devdutt padikkal</t>
+          <t>cameron green</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -8188,50 +8188,50 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>finn allen</t>
+          <t>david payne</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>hardik pandya</t>
+          <t>devdutt padikkal</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>harsh dubey</t>
+          <t>dhruv chand jurel</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>heinrich klaasen</t>
+          <t>finn allen</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
@@ -8240,76 +8240,76 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ishan kishan</t>
+          <t>hardik pandya</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>jacob duffy</t>
+          <t>harsh dubey</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>jaydev unadkat</t>
+          <t>heinrich klaasen</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>kartik tyagi</t>
+          <t>ishan kishan</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>naman dhir</t>
+          <t>jacob duffy</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>nitish kumar reddy</t>
+          <t>jamie overton</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
@@ -8318,37 +8318,37 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>philip salt</t>
+          <t>jaydev unadkat</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>rajat patidar</t>
+          <t>jofra archer</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ramandeep singh</t>
+          <t>kartik sharma</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
@@ -8357,24 +8357,24 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>rinku singh</t>
+          <t>kartik tyagi</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>rohit sharma</t>
+          <t>matt henry</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>78</v>
+        <v>5</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
@@ -8383,24 +8383,24 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>romario shepherd</t>
+          <t>matt short</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ryan rickelton</t>
+          <t>naman dhir</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>81</v>
+        <v>5</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
@@ -8409,50 +8409,50 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>salil arora</t>
+          <t>nandre burger</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>shardul thakur</t>
+          <t>nitish kumar reddy</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>sunil narine</t>
+          <t>noor ahmad</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>suryakumar yadav</t>
+          <t>philip salt</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
@@ -8461,24 +8461,24 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>suyash sharma</t>
+          <t>rajat patidar</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>tilak varma</t>
+          <t>ramandeep singh</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="C33" t="n">
         <v>0</v>
@@ -8487,52 +8487,312 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>tim david</t>
+          <t>ravi bishnoi</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>travis head</t>
+          <t>ravindra jadeja</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>vaibhav arora</t>
+          <t>rinku singh</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>riyan parag</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>14</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>rohit sharma</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>78</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>romario shepherd</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>ruturaj gaikwad</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>6</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>ryan rickelton</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>81</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>salil arora</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>9</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>sandeep sharma</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>sanju samson</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>6</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>sarfaraz khan</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>17</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>shardul thakur</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>shivam dube</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>6</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>sunil narine</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>suryakumar yadav</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>16</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>suyash sharma</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>tilak varma</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>20</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>tim david</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>16</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>travis head</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>11</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>vaibhav arora</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>vaibhav suryavanshi</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>52</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
           <t>virat kohli</t>
         </is>
       </c>
-      <c r="B37" t="n">
+      <c r="B56" t="n">
         <v>69</v>
       </c>
-      <c r="C37" t="n">
+      <c r="C56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>yashasvi jaiswal</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>38</v>
+      </c>
+      <c r="C57" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8547,7 +8807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J113"/>
+  <dimension ref="A1:J99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9277,7 +9537,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Ravi Bishnoi rr</t>
+          <t>Khaleel Ahmed csk</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -9292,7 +9552,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>ravi bishnoi</t>
+          <t>khaleel ahmed</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -9319,7 +9579,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Khaleel Ahmed csk</t>
+          <t>am ghazanfar mi</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -9334,7 +9594,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>khaleel ahmed</t>
+          <t>am ghazanfar</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -9361,7 +9621,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>am ghazanfar mi</t>
+          <t>Kuldeep sen rr</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -9376,7 +9636,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>am ghazanfar</t>
+          <t>kuldeep sen</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -9403,22 +9663,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>anshul kamboj csk</t>
+          <t>Quinton de Kock</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MEET11</t>
+          <t>VATSAL11</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>anshul kamboj</t>
+          <t>quinton de kock</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9445,22 +9705,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Kuldeep sen rr</t>
+          <t>Tom Banton</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MEET11</t>
+          <t>VATSAL11</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>kuldeep sen</t>
+          <t>tom banton</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9487,7 +9747,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Quinton de Kock</t>
+          <t>Tim Siefert</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -9502,7 +9762,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>quinton de kock</t>
+          <t>tim siefert</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9529,7 +9789,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Tom Banton</t>
+          <t>Marcus Stoinis</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -9539,12 +9799,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>tom banton</t>
+          <t>marcus stoinis</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -9571,7 +9831,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Tim Siefert</t>
+          <t>Prasidh Krishna</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -9581,12 +9841,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>tim siefert</t>
+          <t>prasidh krishna</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -9613,7 +9873,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Ravindra Jadeja</t>
+          <t>Lockie Ferguson</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -9623,12 +9883,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ravindra jadeja</t>
+          <t>lockie ferguson</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -9655,7 +9915,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Marcus Stoinis</t>
+          <t>Adam Milne</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -9665,12 +9925,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>marcus stoinis</t>
+          <t>adam milne</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -9697,7 +9957,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Prasidh Krishna</t>
+          <t>Corbin Bosch</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -9712,7 +9972,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>prasidh krishna</t>
+          <t>corbin bosch</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -9739,7 +9999,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Lockie Ferguson</t>
+          <t>Deepak Chahar</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -9754,7 +10014,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>lockie ferguson</t>
+          <t>deepak chahar</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -9781,7 +10041,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Adam Milne</t>
+          <t>Rahul Chahar</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -9796,7 +10056,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>adam milne</t>
+          <t>rahul chahar</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -9823,22 +10083,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Corbin Bosch</t>
+          <t>Jos Inglis</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>VATSAL11</t>
+          <t>BABA11</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>corbin bosch</t>
+          <t>jos inglis</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -9865,22 +10125,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Deepak Chahar</t>
+          <t>Ayush Badoni</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>VATSAL11</t>
+          <t>BABA11</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>deepak chahar</t>
+          <t>ayush badoni</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -9907,22 +10167,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Rahul Chahar</t>
+          <t>Prithvi SHaw</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>VATSAL11</t>
+          <t>BABA11</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>rahul chahar</t>
+          <t>prithvi shaw</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -9949,7 +10209,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sanju Samson</t>
+          <t>Rowman Powell</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -9964,7 +10224,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>sanju samson</t>
+          <t>rowman powell</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -9991,7 +10251,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Jos Inglis</t>
+          <t>Mitchell Starc</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -10001,12 +10261,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>jos inglis</t>
+          <t>mitchell starc</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -10033,7 +10293,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Dhruv Jurel</t>
+          <t>Varun Chakravarthy</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -10043,12 +10303,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>dhruv jurel</t>
+          <t>varun chakravarthy</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -10075,7 +10335,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Ayush Badoni</t>
+          <t>Zeeshan Ansai</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -10085,12 +10345,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>ayush badoni</t>
+          <t>zeeshan ansai</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -10117,7 +10377,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Prithvi SHaw</t>
+          <t>Mitchell Starc</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -10127,12 +10387,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>prithvi shaw</t>
+          <t>mitchell starc</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -10159,7 +10419,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Rowman Powell</t>
+          <t>Mitchel Santner</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -10169,12 +10429,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>rowman powell</t>
+          <t>mitchel santner</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -10201,22 +10461,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Mitchell Starc</t>
+          <t>Mitchel Owen</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>BABA11</t>
+          <t>DIPESH11</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>mitchell starc</t>
+          <t>mitchel owen</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -10243,22 +10503,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Varun Chakravarthy</t>
+          <t>Nehal Wadhera</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BABA11</t>
+          <t>DIPESH11</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>varun chakravarthy</t>
+          <t>nehal wadhera</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -10285,22 +10545,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Zeeshan Ansai</t>
+          <t>Tristan Stubbs</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BABA11</t>
+          <t>DIPESH11</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>zeeshan ansai</t>
+          <t>tristan stubbs</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -10327,22 +10587,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Mitchell Starc</t>
+          <t>Pat Cummins</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BABA11</t>
+          <t>DIPESH11</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>mitchell starc</t>
+          <t>pat cummins</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -10369,22 +10629,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Mitchel Santner</t>
+          <t>Aiden Markram</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>BABA11</t>
+          <t>DIPESH11</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>mitchel santner</t>
+          <t>aiden markram</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -10411,7 +10671,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Ruturaj Gaikwad</t>
+          <t>Cooper Conoly</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -10421,12 +10681,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>ruturaj gaikwad</t>
+          <t>cooper conoly</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -10453,7 +10713,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Mitchel Owen</t>
+          <t>Aqib Nabi Dar</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -10463,12 +10723,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>mitchel owen</t>
+          <t>aqib nabi dar</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -10495,7 +10755,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Nehal Wadhera</t>
+          <t>Rasik Dar Salam</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -10505,12 +10765,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>nehal wadhera</t>
+          <t>rasik dar salam</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -10537,7 +10797,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Tristan Stubbs</t>
+          <t>Xavier Bartlett</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -10547,12 +10807,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>tristan stubbs</t>
+          <t>xavier bartlett</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -10579,12 +10839,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sarfaraz Khan</t>
+          <t>KL Rahul dc</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>DIPESH11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -10594,7 +10854,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>sarfaraz khan</t>
+          <t>kl rahul</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -10621,22 +10881,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Pat Cummins</t>
+          <t>Shreyas Iyer PBKS</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>DIPESH11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>pat cummins</t>
+          <t>shreyas iyer</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -10663,22 +10923,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Aiden Markram</t>
+          <t>Jos Buttler gt</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>DIPESH11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>aiden markram</t>
+          <t>jos buttler</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -10705,22 +10965,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Cooper Conoly</t>
+          <t>Urvil Patel</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>DIPESH11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>cooper conoly</t>
+          <t>urvil patel</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -10747,22 +11007,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Aqib Nabi Dar</t>
+          <t>Arshin Kulkarni</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>DIPESH11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>aqib nabi dar</t>
+          <t>arshin kulkarni</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -10789,22 +11049,22 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Rasik Dar Salam</t>
+          <t>Jayant Yadav gt</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>DIPESH11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>rasik dar salam</t>
+          <t>jayant yadav</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -10831,22 +11091,22 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Xavier Bartlett</t>
+          <t>Ajay Mandal dc</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>DIPESH11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>xavier bartlett</t>
+          <t>ajay mandal</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -10873,7 +11133,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Yashasvi Jaiswal rr</t>
+          <t>Will Jacks mi</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -10883,12 +11143,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>yashasvi jaiswal</t>
+          <t>will jacks</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -10915,7 +11175,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>KL Rahul dc</t>
+          <t>Kagiso Rabada gt</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -10925,12 +11185,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>kl rahul</t>
+          <t>kagiso rabada</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -10957,7 +11217,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Shreyas Iyer PBKS</t>
+          <t>Josh Hazelwood rcb</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -10967,12 +11227,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>shreyas iyer</t>
+          <t>josh hazelwood</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -10999,7 +11259,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Jos Buttler gt</t>
+          <t>Kyle Jamieson dc</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -11009,12 +11269,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>jos buttler</t>
+          <t>kyle jamieson</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -11041,7 +11301,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Urvil Patel</t>
+          <t>Matheesha Pathirana kkr</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -11051,12 +11311,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>urvil patel</t>
+          <t>matheesha pathirana</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -11083,7 +11343,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Arshin Kulkarni</t>
+          <t>M Siddharth lsg</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -11093,12 +11353,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>arshin kulkarni</t>
+          <t>m siddharth</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -11125,7 +11385,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Jayant Yadav gt</t>
+          <t>Ben Dwarshuis pbks</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -11135,12 +11395,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>jayant yadav</t>
+          <t>ben dwarshuis</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -11167,22 +11427,22 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Ajay Mandal dc</t>
+          <t>Mitchel March</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>ajay mandal</t>
+          <t>mitchel march</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -11209,22 +11469,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Will Jacks mi</t>
+          <t>Shimron Hetmyer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>will jacks</t>
+          <t>shimron hetmyer</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -11251,22 +11511,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Riyan Parag rr</t>
+          <t>Pathum Nissanka</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>riyan parag</t>
+          <t>pathum nissanka</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -11293,22 +11553,22 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Kagiso Rabada gt</t>
+          <t>Donovan Ferreira rr</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>kagiso rabada</t>
+          <t>donovan ferreira</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -11335,12 +11595,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Josh Hazelwood rcb</t>
+          <t>Harshal Patel</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -11350,7 +11610,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>josh hazelwood</t>
+          <t>harshal patel</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -11377,12 +11637,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Kyle Jamieson dc</t>
+          <t>Lungi Ngidi</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -11392,7 +11652,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>kyle jamieson</t>
+          <t>lungi ngidi</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -11419,12 +11679,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Matheesha Pathirana kkr</t>
+          <t>Vyshak Vijaykumar PBKS</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -11434,7 +11694,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>matheesha pathirana</t>
+          <t>vyshak vijaykumar</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -11461,12 +11721,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>M Siddharth lsg</t>
+          <t>Mukesh Choudhary csk</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -11476,7 +11736,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>m siddharth</t>
+          <t>mukesh choudhary</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -11503,12 +11763,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Ben Dwarshuis pbks</t>
+          <t>Arjun Tendulkar</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -11518,7 +11778,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>ben dwarshuis</t>
+          <t>arjun tendulkar</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -11545,12 +11805,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Nandre Burger rr</t>
+          <t>Kwena Maphaka</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -11560,7 +11820,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>nandre burger</t>
+          <t>kwena maphaka</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -11587,7 +11847,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Mitchel March</t>
+          <t>Anrich Nortje</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -11597,12 +11857,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>mitchel march</t>
+          <t>anrich nortje</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -11629,12 +11889,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Shimron Hetmyer</t>
+          <t>Venkatesh Iyer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -11644,7 +11904,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>shimron hetmyer</t>
+          <t>venkatesh iyer</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -11671,12 +11931,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Pathum Nissanka</t>
+          <t>Sameer Rizvi</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -11686,7 +11946,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>pathum nissanka</t>
+          <t>sameer rizvi</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -11713,22 +11973,22 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Jamie Overton csk</t>
+          <t>Prashant Veer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>jamie overton</t>
+          <t>prashant veer</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -11755,12 +12015,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Donovan Ferreira rr</t>
+          <t>Washington SUndar</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -11770,7 +12030,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>donovan ferreira</t>
+          <t>washington sundar</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -11797,22 +12057,22 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Harshal Patel</t>
+          <t>Axar Patel</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>harshal patel</t>
+          <t>axar patel</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -11839,22 +12099,22 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Lungi Ngidi</t>
+          <t>Azmatullah Omarzai</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>lungi ngidi</t>
+          <t>azmatullah omarzai</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -11881,12 +12141,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Vyshak Vijaykumar PBKS</t>
+          <t>Jasprit Bumrah</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -11896,7 +12156,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>vyshak vijaykumar</t>
+          <t>jasprit bumrah</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -11923,12 +12183,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Mukesh Choudhary csk</t>
+          <t>Mohammed Shami</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -11938,7 +12198,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>mukesh choudhary</t>
+          <t>mohammed shami</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -11965,12 +12225,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Arjun Tendulkar</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -11980,7 +12240,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>arjun tendulkar</t>
+          <t>trent boult</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -12007,22 +12267,22 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Kwena Maphaka</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>kwena maphaka</t>
+          <t>nicholas pooran</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -12049,22 +12309,22 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Anrich Nortje</t>
+          <t>Nitish Rana</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>anrich nortje</t>
+          <t>nitish rana</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -12091,12 +12351,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Venkatesh Iyer</t>
+          <t>Tejasvi Singh</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -12106,7 +12366,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>venkatesh iyer</t>
+          <t>tejasvi singh</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -12133,22 +12393,22 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Sameer Rizvi</t>
+          <t>T Natarjan</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>sameer rizvi</t>
+          <t>t natarjan</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -12175,22 +12435,22 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Prashant Veer</t>
+          <t>Yuzvendra Chahal</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>prashant veer</t>
+          <t>yuzvendra chahal</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -12217,22 +12477,22 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Washington SUndar</t>
+          <t>Akash Deep</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>washington sundar</t>
+          <t>akash deep</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -12259,22 +12519,22 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Axar Patel</t>
+          <t>Ben Duckett</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>axar patel</t>
+          <t>ben duckett</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -12301,22 +12561,22 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Azmatullah Omarzai</t>
+          <t>Ayush Mhatre</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>azmatullah omarzai</t>
+          <t>ayush mhatre</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -12343,22 +12603,22 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Jasprit Bumrah</t>
+          <t>Rahul Tripathi</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>jasprit bumrah</t>
+          <t>rahul tripathi</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -12385,22 +12645,22 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Mohammed Shami</t>
+          <t>Dre Pretorius</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>mohammed shami</t>
+          <t>dre pretorius</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -12427,22 +12687,22 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Matthew Breetzke</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>trent boult</t>
+          <t>matthew breetzke</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -12469,12 +12729,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>Anuj Rawat</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -12484,7 +12744,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>nicholas pooran</t>
+          <t>anuj rawat</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -12511,22 +12771,22 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Nitish Rana</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>nitish rana</t>
+          <t>marco jansen</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -12553,22 +12813,22 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Tejasvi Singh</t>
+          <t>Wanindu Hasaranga</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>tejasvi singh</t>
+          <t>wanindu hasaranga</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -12595,22 +12855,22 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Harpreet Brar</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>jofra archer</t>
+          <t>harpreet brar</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -12637,22 +12897,22 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>T Natarjan</t>
+          <t>Digvesh Rathi</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>t natarjan</t>
+          <t>digvesh rathi</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -12679,12 +12939,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Yuzvendra Chahal</t>
+          <t>Kuldeep Yadav</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -12694,7 +12954,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>yuzvendra chahal</t>
+          <t>kuldeep yadav</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -12715,594 +12975,6 @@
         <v>0</v>
       </c>
       <c r="J99" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Matt Henry</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>AMEY11</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>BOWL</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>matt henry</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="F100" t="n">
-        <v>0</v>
-      </c>
-      <c r="G100" t="n">
-        <v>0</v>
-      </c>
-      <c r="H100" t="n">
-        <v>0</v>
-      </c>
-      <c r="I100" t="n">
-        <v>0</v>
-      </c>
-      <c r="J100" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Akash Deep</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>AMEY11</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>BOWL</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>akash deep</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="F101" t="n">
-        <v>0</v>
-      </c>
-      <c r="G101" t="n">
-        <v>0</v>
-      </c>
-      <c r="H101" t="n">
-        <v>0</v>
-      </c>
-      <c r="I101" t="n">
-        <v>0</v>
-      </c>
-      <c r="J101" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Ben Duckett</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>BAT</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>ben duckett</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="F102" t="n">
-        <v>0</v>
-      </c>
-      <c r="G102" t="n">
-        <v>0</v>
-      </c>
-      <c r="H102" t="n">
-        <v>0</v>
-      </c>
-      <c r="I102" t="n">
-        <v>0</v>
-      </c>
-      <c r="J102" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Ayush Mhatre</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>BAT</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>ayush mhatre</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="F103" t="n">
-        <v>0</v>
-      </c>
-      <c r="G103" t="n">
-        <v>0</v>
-      </c>
-      <c r="H103" t="n">
-        <v>0</v>
-      </c>
-      <c r="I103" t="n">
-        <v>0</v>
-      </c>
-      <c r="J103" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Rahul Tripathi</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>BAT</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>rahul tripathi</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="F104" t="n">
-        <v>0</v>
-      </c>
-      <c r="G104" t="n">
-        <v>0</v>
-      </c>
-      <c r="H104" t="n">
-        <v>0</v>
-      </c>
-      <c r="I104" t="n">
-        <v>0</v>
-      </c>
-      <c r="J104" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Dre Pretorius</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>BAT</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>dre pretorius</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="F105" t="n">
-        <v>0</v>
-      </c>
-      <c r="G105" t="n">
-        <v>0</v>
-      </c>
-      <c r="H105" t="n">
-        <v>0</v>
-      </c>
-      <c r="I105" t="n">
-        <v>0</v>
-      </c>
-      <c r="J105" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Matthew Breetzke</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>BAT</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>matthew breetzke</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="F106" t="n">
-        <v>0</v>
-      </c>
-      <c r="G106" t="n">
-        <v>0</v>
-      </c>
-      <c r="H106" t="n">
-        <v>0</v>
-      </c>
-      <c r="I106" t="n">
-        <v>0</v>
-      </c>
-      <c r="J106" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Anuj Rawat</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>BAT</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>anuj rawat</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="F107" t="n">
-        <v>0</v>
-      </c>
-      <c r="G107" t="n">
-        <v>0</v>
-      </c>
-      <c r="H107" t="n">
-        <v>0</v>
-      </c>
-      <c r="I107" t="n">
-        <v>0</v>
-      </c>
-      <c r="J107" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Marco Jansen</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>AR</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>marco jansen</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="F108" t="n">
-        <v>0</v>
-      </c>
-      <c r="G108" t="n">
-        <v>0</v>
-      </c>
-      <c r="H108" t="n">
-        <v>0</v>
-      </c>
-      <c r="I108" t="n">
-        <v>0</v>
-      </c>
-      <c r="J108" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Wanindu Hasaranga</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>AR</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>wanindu hasaranga</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="F109" t="n">
-        <v>0</v>
-      </c>
-      <c r="G109" t="n">
-        <v>0</v>
-      </c>
-      <c r="H109" t="n">
-        <v>0</v>
-      </c>
-      <c r="I109" t="n">
-        <v>0</v>
-      </c>
-      <c r="J109" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Harpreet Brar</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>BOWL</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>harpreet brar</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="F110" t="n">
-        <v>0</v>
-      </c>
-      <c r="G110" t="n">
-        <v>0</v>
-      </c>
-      <c r="H110" t="n">
-        <v>0</v>
-      </c>
-      <c r="I110" t="n">
-        <v>0</v>
-      </c>
-      <c r="J110" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Digvesh Rathi</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>BOWL</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>digvesh rathi</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="F111" t="n">
-        <v>0</v>
-      </c>
-      <c r="G111" t="n">
-        <v>0</v>
-      </c>
-      <c r="H111" t="n">
-        <v>0</v>
-      </c>
-      <c r="I111" t="n">
-        <v>0</v>
-      </c>
-      <c r="J111" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Kuldeep Yadav</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>BOWL</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>kuldeep yadav</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="F112" t="n">
-        <v>0</v>
-      </c>
-      <c r="G112" t="n">
-        <v>0</v>
-      </c>
-      <c r="H112" t="n">
-        <v>0</v>
-      </c>
-      <c r="I112" t="n">
-        <v>0</v>
-      </c>
-      <c r="J112" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Noor Ahmad</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>BOWL</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>noor ahmad</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="F113" t="n">
-        <v>0</v>
-      </c>
-      <c r="G113" t="n">
-        <v>0</v>
-      </c>
-      <c r="H113" t="n">
-        <v>0</v>
-      </c>
-      <c r="I113" t="n">
-        <v>0</v>
-      </c>
-      <c r="J113" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13317,7 +12989,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13417,7 +13089,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Jitesh Sharma rcb</t>
+          <t>Mohsin Khan</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -13427,17 +13099,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>jitesh sharma</t>
+          <t>mohsin khan</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>possible_mismatch:72.0</t>
+          <t>possible_mismatch:60.86956521739131</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -13459,12 +13131,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>kartik sharma</t>
+          <t>Glen Philips</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NIRAV11</t>
+          <t>VATSAL11</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -13474,12 +13146,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>kartik sharma</t>
+          <t>glen philips</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>possible_mismatch:72.0</t>
+          <t>possible_mismatch:60.86956521739131</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -13501,22 +13173,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Mohsin Khan</t>
+          <t>David Miller</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NIRAV11</t>
+          <t>BABA11</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>mohsin khan</t>
+          <t>david miller</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -13543,12 +13215,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>vaibhav suryavanshi rr</t>
+          <t>Dhruv Jurel</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MEET11</t>
+          <t>BABA11</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -13558,12 +13230,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>vaibhav suryavanshi</t>
+          <t>dhruv jurel</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>possible_mismatch:62.5</t>
+          <t>possible_mismatch:78.57142857142857</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -13585,22 +13257,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Glen Philips</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>VATSAL11</t>
+          <t>BABA11</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>glen philips</t>
+          <t>rashid khan</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -13627,27 +13299,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sandeep Sharma</t>
+          <t>Sai Sudharsan</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>VATSAL11</t>
+          <t>DIPESH11</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>sandeep sharma</t>
+          <t>sai sudharsan</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>possible_mismatch:66.66666666666667</t>
+          <t>possible_mismatch:61.53846153846154</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -13669,12 +13341,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>David Miller</t>
+          <t>Prabhsimran Singh</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BABA11</t>
+          <t>DIPESH11</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -13684,12 +13356,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>david miller</t>
+          <t>prabhsimran singh</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>possible_mismatch:60.86956521739131</t>
+          <t>possible_mismatch:72.72727272727273</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -13711,12 +13383,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Shivam Dube</t>
+          <t>Priyansh Arya</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BABA11</t>
+          <t>DIPESH11</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -13726,12 +13398,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>shivam dube</t>
+          <t>priyansh arya</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>possible_mismatch:63.63636363636363</t>
+          <t>possible_mismatch:75.0</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -13753,27 +13425,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Arshdeep Singh</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BABA11</t>
+          <t>DIPESH11</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>rashid khan</t>
+          <t>arshdeep singh</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>possible_mismatch:60.86956521739131</t>
+          <t>possible_mismatch:75.86206896551724</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -13795,7 +13467,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sai Sudharsan</t>
+          <t>Avesh Khan</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -13805,17 +13477,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>sai sudharsan</t>
+          <t>avesh khan</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>possible_mismatch:61.53846153846154</t>
+          <t>possible_mismatch:63.63636363636363</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -13837,7 +13509,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Prabhsimran Singh</t>
+          <t>Mukesh Kumar</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -13847,17 +13519,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>prabhsimran singh</t>
+          <t>mukesh kumar</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>possible_mismatch:72.72727272727273</t>
+          <t>possible_mismatch:68.96551724137932</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -13879,22 +13551,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Priyansh Arya</t>
+          <t>Nishant Sindhu gt</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DIPESH11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>priyansh arya</t>
+          <t>nishant sindhu</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -13921,27 +13593,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Arshdeep Singh</t>
+          <t>Manish Pandey</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DIPESH11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>arshdeep singh</t>
+          <t>manish pandey</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>possible_mismatch:75.86206896551724</t>
+          <t>possible_mismatch:61.53846153846154</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -13963,12 +13635,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Avesh Khan</t>
+          <t>Gurjapneet Singh</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DIPESH11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -13978,12 +13650,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>avesh khan</t>
+          <t>gurjapneet singh</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>possible_mismatch:63.63636363636363</t>
+          <t>possible_mismatch:70.96774193548387</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -14005,27 +13677,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Mukesh Kumar</t>
+          <t>Ramkrishna Ghosh</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DIPESH11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>mukesh kumar</t>
+          <t>ramkrishna ghosh</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>possible_mismatch:68.96551724137932</t>
+          <t>possible_mismatch:61.111111111111114</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -14047,27 +13719,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Nishant Sindhu gt</t>
+          <t>Shahrukh Khan</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>nishant sindhu</t>
+          <t>shahrukh khan</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>possible_mismatch:61.53846153846154</t>
+          <t>possible_mismatch:64.0</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -14089,12 +13761,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Manish Pandey</t>
+          <t>Ashutosh Sharma</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -14104,12 +13776,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>manish pandey</t>
+          <t>ashutosh sharma</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>possible_mismatch:61.53846153846154</t>
+          <t>possible_mismatch:78.57142857142857</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -14131,27 +13803,27 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gurjapneet Singh</t>
+          <t>Shashank Singh</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>gurjapneet singh</t>
+          <t>shashank singh</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>possible_mismatch:70.96774193548387</t>
+          <t>possible_mismatch:66.66666666666667</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -14173,12 +13845,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ramkrishna Ghosh</t>
+          <t>Himmat Singh</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -14188,12 +13860,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ramkrishna ghosh</t>
+          <t>himmat singh</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>possible_mismatch:61.111111111111114</t>
+          <t>possible_mismatch:64.28571428571428</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -14215,12 +13887,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Shahrukh Khan</t>
+          <t>Suryansh Shegde</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -14230,12 +13902,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>shahrukh khan</t>
+          <t>suryansh shegde</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>possible_mismatch:64.0</t>
+          <t>possible_mismatch:64.28571428571428</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -14257,27 +13929,27 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ashutosh Sharma</t>
+          <t>Krunal Pandya</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ashutosh sharma</t>
+          <t>krunal pandya</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>possible_mismatch:78.57142857142857</t>
+          <t>possible_mismatch:61.53846153846154</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -14299,27 +13971,27 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Shashank Singh</t>
+          <t>Sai Kishor</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>shashank singh</t>
+          <t>sai kishor</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>possible_mismatch:66.66666666666667</t>
+          <t>possible_mismatch:63.63636363636363</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -14341,12 +14013,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Himmat Singh</t>
+          <t>Abhishek Porel</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -14356,12 +14028,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>himmat singh</t>
+          <t>abhishek porel</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>possible_mismatch:64.28571428571428</t>
+          <t>possible_mismatch:68.96551724137932</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -14383,22 +14055,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Suryansh Shegde</t>
+          <t>Mayank Yadav</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>suryansh shegde</t>
+          <t>mayank yadav</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -14419,174 +14091,6 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Krunal Pandya</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>AMEY11</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>AR</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>krunal pandya</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>possible_mismatch:61.53846153846154</t>
-        </is>
-      </c>
-      <c r="F27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Sai Kishor</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>AMEY11</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>BOWL</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>sai kishor</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>possible_mismatch:63.63636363636363</t>
-        </is>
-      </c>
-      <c r="F28" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Abhishek Porel</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>BAT</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>abhishek porel</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>possible_mismatch:68.96551724137932</t>
-        </is>
-      </c>
-      <c r="F29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Mayank Yadav</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>BOWL</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>mayank yadav</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>possible_mismatch:64.28571428571428</t>
-        </is>
-      </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" t="n">
         <v>0</v>
       </c>
     </row>

--- a/IPL_Fantasy_Points.xlsx
+++ b/IPL_Fantasy_Points.xlsx
@@ -1,17 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Player_Points" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Leaderboard" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Merged_Stats" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="No_Stats_Yet" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Possible_Mismatch" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player_Points" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Merged_Stats" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="No_Stats_Yet" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Possible_Mismatch" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI_Matches" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -507,7 +508,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>possible_mismatch:61.111111111111114</t>
+          <t>no_stats_yet</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -613,7 +614,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Jitesh Sharma rcb</t>
+          <t>Jitesh Sharma</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -628,19 +629,19 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>brijesh sharma</t>
+          <t>jitesh sharma</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>fuzzy:81.4814814814815</t>
+          <t>possible_mismatch:81.4814814814815</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -655,7 +656,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>rajat patidar rcb</t>
+          <t>rajat patidar</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1011,7 +1012,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>possible_mismatch:60.86956521739131</t>
+          <t>no_stats_yet</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -2145,7 +2146,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>possible_mismatch:60.86956521739131</t>
+          <t>no_stats_yet</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -2775,7 +2776,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>possible_mismatch:60.86956521739131</t>
+          <t>no_stats_yet</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -2812,28 +2813,28 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>dhruv jurel</t>
+          <t>dhruv chand jurel</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>possible_mismatch:78.57142857142857</t>
+          <t>ai_structured</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I57" t="n">
         <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="58">
@@ -2938,28 +2939,28 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>ryan rickelton</t>
+          <t>ryan rickleton</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>fuzzy:92.85714285714286</t>
+          <t>possible_mismatch:92.85714285714286</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="I60" t="n">
         <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3111,7 +3112,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>possible_mismatch:60.86956521739131</t>
+          <t>no_stats_yet</t>
         </is>
       </c>
       <c r="F64" t="n">
@@ -3405,7 +3406,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>possible_mismatch:61.53846153846154</t>
+          <t>no_stats_yet</t>
         </is>
       </c>
       <c r="F71" t="n">
@@ -3447,7 +3448,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>possible_mismatch:72.72727272727273</t>
+          <t>no_stats_yet</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -3909,7 +3910,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>possible_mismatch:63.63636363636363</t>
+          <t>no_stats_yet</t>
         </is>
       </c>
       <c r="F83" t="n">
@@ -3951,7 +3952,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>possible_mismatch:68.96551724137932</t>
+          <t>no_stats_yet</t>
         </is>
       </c>
       <c r="F84" t="n">
@@ -4371,7 +4372,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>possible_mismatch:61.53846153846154</t>
+          <t>no_stats_yet</t>
         </is>
       </c>
       <c r="F94" t="n">
@@ -4870,28 +4871,28 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>philip salt</t>
+          <t>phil salt</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>fuzzy:90.0</t>
+          <t>possible_mismatch:90.0</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
       </c>
       <c r="H106" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I106" t="n">
         <v>0</v>
       </c>
       <c r="J106" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -5043,7 +5044,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>possible_mismatch:61.53846153846154</t>
+          <t>no_stats_yet</t>
         </is>
       </c>
       <c r="F110" t="n">
@@ -5463,7 +5464,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>possible_mismatch:70.96774193548387</t>
+          <t>no_stats_yet</t>
         </is>
       </c>
       <c r="F120" t="n">
@@ -5673,7 +5674,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>possible_mismatch:61.111111111111114</t>
+          <t>no_stats_yet</t>
         </is>
       </c>
       <c r="F125" t="n">
@@ -5757,7 +5758,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>possible_mismatch:64.0</t>
+          <t>no_stats_yet</t>
         </is>
       </c>
       <c r="F127" t="n">
@@ -5883,7 +5884,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>possible_mismatch:66.66666666666667</t>
+          <t>no_stats_yet</t>
         </is>
       </c>
       <c r="F130" t="n">
@@ -6577,7 +6578,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Akshat Raghuvanshi</t>
+          <t>Akshat Raghuwanshi</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -6592,28 +6593,28 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>angkrish raghuvanshi</t>
+          <t>akshat raghuwanshi</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>fuzzy:84.21052631578947</t>
+          <t>possible_mismatch:78.94736842105263</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
       </c>
       <c r="H147" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="I147" t="n">
         <v>0</v>
       </c>
       <c r="J147" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148">
@@ -6639,7 +6640,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>possible_mismatch:64.28571428571428</t>
+          <t>no_stats_yet</t>
         </is>
       </c>
       <c r="F148" t="n">
@@ -6681,7 +6682,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>possible_mismatch:64.28571428571428</t>
+          <t>no_stats_yet</t>
         </is>
       </c>
       <c r="F149" t="n">
@@ -6765,7 +6766,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>possible_mismatch:61.53846153846154</t>
+          <t>no_stats_yet</t>
         </is>
       </c>
       <c r="F151" t="n">
@@ -6933,7 +6934,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>fuzzy:97.14285714285714</t>
+          <t>ai_structured</t>
         </is>
       </c>
       <c r="F155" t="n">
@@ -7017,7 +7018,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>possible_mismatch:63.63636363636363</t>
+          <t>no_stats_yet</t>
         </is>
       </c>
       <c r="F157" t="n">
@@ -7227,7 +7228,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>possible_mismatch:68.96551724137932</t>
+          <t>no_stats_yet</t>
         </is>
       </c>
       <c r="F162" t="n">
@@ -7689,7 +7690,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>possible_mismatch:64.28571428571428</t>
+          <t>no_stats_yet</t>
         </is>
       </c>
       <c r="F173" t="n">
@@ -7926,11 +7927,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>VATSAL11</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>259</v>
+        <v>212</v>
       </c>
     </row>
     <row r="4">
@@ -7939,11 +7940,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>VATSAL11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="5">
@@ -7956,7 +7957,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>187</v>
+        <v>179</v>
       </c>
     </row>
     <row r="6">
@@ -7978,11 +7979,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BABA11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>126</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8">
@@ -7991,11 +7992,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>92</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9">
@@ -8004,11 +8005,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PRATIK11</t>
+          <t>NIRAV11</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10">
@@ -8017,11 +8018,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NIRAV11</t>
+          <t>BABA11</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>83</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11">
@@ -8807,7 +8808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J99"/>
+  <dimension ref="A1:J120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8865,7 +8866,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Rishabh Pant LSG</t>
+          <t>MS Dhoni CSK</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -8880,7 +8881,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>rishabh pant</t>
+          <t>mahendra singh dhoni</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -8907,7 +8908,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Dewald Brevis</t>
+          <t>Rishabh Pant LSG</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -8922,7 +8923,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>dewald brevis</t>
+          <t>rishabh pant</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -8949,7 +8950,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Akeal Hosein</t>
+          <t>Dewald Brevis</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -8959,12 +8960,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>akeal hosein</t>
+          <t>dewald brevis</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -8991,7 +8992,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Anukul Roy</t>
+          <t>Akeal Hosein</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -9006,7 +9007,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>anukul roy</t>
+          <t>akeal hosein</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -9033,7 +9034,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Mohammed Siraj</t>
+          <t>Anukul Roy</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -9043,12 +9044,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>mohammed siraj</t>
+          <t>anukul roy</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -9075,7 +9076,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Brydon Carse</t>
+          <t>Mohammed Siraj</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -9090,7 +9091,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>brydon carse</t>
+          <t>mohammed siraj</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -9117,7 +9118,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Mayank Markande</t>
+          <t>Mohsin Khan</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -9132,7 +9133,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>mayank markande</t>
+          <t>mohsin khan</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -9159,7 +9160,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Umran Malik</t>
+          <t>Brydon Carse</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -9174,7 +9175,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>umran malik</t>
+          <t>brydon carse</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -9201,22 +9202,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Shubman Gill gt</t>
+          <t>Mayank Markande</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MEET11</t>
+          <t>NIRAV11</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>shubman gill</t>
+          <t>mayank markande</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -9243,22 +9244,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>karun nair dc</t>
+          <t>Umran Malik</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MEET11</t>
+          <t>NIRAV11</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>karun nair</t>
+          <t>umran malik</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -9285,7 +9286,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>jacob bethel rcb</t>
+          <t>Shubman Gill gt</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -9295,12 +9296,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>jacob bethel</t>
+          <t>shubman gill</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -9327,7 +9328,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>vipraj nigam dc</t>
+          <t>karun nair dc</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -9337,12 +9338,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>vipraj nigam</t>
+          <t>karun nair</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -9369,7 +9370,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Rahul Tewatia gt</t>
+          <t>jacob bethel rcb</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -9384,7 +9385,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>rahul tewatia</t>
+          <t>jacob bethel</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -9411,7 +9412,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Jason Holder gt</t>
+          <t>vipraj nigam dc</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -9426,7 +9427,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>jason holder</t>
+          <t>vipraj nigam</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -9453,7 +9454,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>kamindu mendis srh</t>
+          <t>Rahul Tewatia gt</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -9463,12 +9464,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>kamindu mendis</t>
+          <t>rahul tewatia</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -9495,7 +9496,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>tushar deshpande rr</t>
+          <t>Jason Holder gt</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -9505,12 +9506,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>tushar deshpande</t>
+          <t>jason holder</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -9537,7 +9538,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Khaleel Ahmed csk</t>
+          <t>kamindu mendis srh</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -9552,7 +9553,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>khaleel ahmed</t>
+          <t>kamindu mendis</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -9579,7 +9580,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>am ghazanfar mi</t>
+          <t>tushar deshpande rr</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -9594,7 +9595,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>am ghazanfar</t>
+          <t>tushar deshpande</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -9621,7 +9622,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Kuldeep sen rr</t>
+          <t>Khaleel Ahmed csk</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -9636,7 +9637,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>kuldeep sen</t>
+          <t>khaleel ahmed</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -9663,22 +9664,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Quinton de Kock</t>
+          <t>am ghazanfar mi</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>VATSAL11</t>
+          <t>MEET11</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>quinton de kock</t>
+          <t>am ghazanfar</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9705,22 +9706,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Tom Banton</t>
+          <t>Kuldeep sen rr</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>VATSAL11</t>
+          <t>MEET11</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>tom banton</t>
+          <t>kuldeep sen</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9747,7 +9748,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Tim Siefert</t>
+          <t>Quinton de Kock</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -9762,7 +9763,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>tim siefert</t>
+          <t>quinton de kock</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9789,7 +9790,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Marcus Stoinis</t>
+          <t>Tom Banton</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -9799,12 +9800,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>marcus stoinis</t>
+          <t>tom banton</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -9831,7 +9832,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Prasidh Krishna</t>
+          <t>Tim Siefert</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -9841,12 +9842,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>prasidh krishna</t>
+          <t>tim siefert</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -9873,7 +9874,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Lockie Ferguson</t>
+          <t>Glen Philips</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -9883,12 +9884,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>lockie ferguson</t>
+          <t>glen philips</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -9915,7 +9916,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Adam Milne</t>
+          <t>Marcus Stoinis</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -9925,12 +9926,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>adam milne</t>
+          <t>marcus stoinis</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -9957,7 +9958,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Corbin Bosch</t>
+          <t>Prasidh Krishna</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -9972,7 +9973,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>corbin bosch</t>
+          <t>prasidh krishna</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -9999,7 +10000,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Deepak Chahar</t>
+          <t>Lockie Ferguson</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -10014,7 +10015,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>deepak chahar</t>
+          <t>lockie ferguson</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -10041,7 +10042,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Rahul Chahar</t>
+          <t>Adam Milne</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -10056,7 +10057,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>rahul chahar</t>
+          <t>adam milne</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -10083,22 +10084,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Jos Inglis</t>
+          <t>Corbin Bosch</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BABA11</t>
+          <t>VATSAL11</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>jos inglis</t>
+          <t>corbin bosch</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -10125,22 +10126,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Ayush Badoni</t>
+          <t>Deepak Chahar</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BABA11</t>
+          <t>VATSAL11</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ayush badoni</t>
+          <t>deepak chahar</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -10167,22 +10168,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Prithvi SHaw</t>
+          <t>Rahul Chahar</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BABA11</t>
+          <t>VATSAL11</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>prithvi shaw</t>
+          <t>rahul chahar</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -10209,7 +10210,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Rowman Powell</t>
+          <t>Jos Inglis</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -10224,7 +10225,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>rowman powell</t>
+          <t>jos inglis</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -10251,7 +10252,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Mitchell Starc</t>
+          <t>David Miller</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -10261,12 +10262,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>mitchell starc</t>
+          <t>david miller</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -10293,7 +10294,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Varun Chakravarthy</t>
+          <t>Ayush Badoni</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -10303,12 +10304,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>varun chakravarthy</t>
+          <t>ayush badoni</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -10335,7 +10336,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Zeeshan Ansai</t>
+          <t>Prithvi SHaw</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -10345,12 +10346,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>zeeshan ansai</t>
+          <t>prithvi shaw</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -10377,7 +10378,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Mitchell Starc</t>
+          <t>Rowman Powell</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -10387,12 +10388,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>mitchell starc</t>
+          <t>rowman powell</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -10419,7 +10420,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Mitchel Santner</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -10429,12 +10430,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>mitchel santner</t>
+          <t>rashid khan</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -10461,22 +10462,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Mitchel Owen</t>
+          <t>Mitchell Starc</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>DIPESH11</t>
+          <t>BABA11</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>mitchel owen</t>
+          <t>mitchell starc</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -10503,22 +10504,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Nehal Wadhera</t>
+          <t>Varun Chakravarthy</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>DIPESH11</t>
+          <t>BABA11</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>nehal wadhera</t>
+          <t>varun chakravarthy</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -10545,22 +10546,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Tristan Stubbs</t>
+          <t>Zeeshan Ansai</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>DIPESH11</t>
+          <t>BABA11</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>tristan stubbs</t>
+          <t>zeeshan ansai</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -10587,22 +10588,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Pat Cummins</t>
+          <t>Mitchell Starc</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>DIPESH11</t>
+          <t>BABA11</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>pat cummins</t>
+          <t>mitchell starc</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -10629,22 +10630,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Aiden Markram</t>
+          <t>Mitchel Santner</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>DIPESH11</t>
+          <t>BABA11</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>aiden markram</t>
+          <t>mitchel santner</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -10671,7 +10672,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Cooper Conoly</t>
+          <t>Sai Sudharsan</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -10681,12 +10682,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>cooper conoly</t>
+          <t>sai sudharsan</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -10713,7 +10714,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Aqib Nabi Dar</t>
+          <t>Prabhsimran Singh</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -10723,12 +10724,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>aqib nabi dar</t>
+          <t>prabhsimran singh</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -10755,7 +10756,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Rasik Dar Salam</t>
+          <t>Mitchel Owen</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -10765,12 +10766,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>rasik dar salam</t>
+          <t>mitchel owen</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -10797,7 +10798,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Xavier Bartlett</t>
+          <t>Nehal Wadhera</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -10807,12 +10808,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>xavier bartlett</t>
+          <t>nehal wadhera</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -10839,12 +10840,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>KL Rahul dc</t>
+          <t>Tristan Stubbs</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>DIPESH11</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -10854,7 +10855,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>kl rahul</t>
+          <t>tristan stubbs</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -10881,22 +10882,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Shreyas Iyer PBKS</t>
+          <t>Pat Cummins</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>DIPESH11</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>shreyas iyer</t>
+          <t>pat cummins</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -10923,22 +10924,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Jos Buttler gt</t>
+          <t>Aiden Markram</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>DIPESH11</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>jos buttler</t>
+          <t>aiden markram</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -10965,22 +10966,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Urvil Patel</t>
+          <t>Cooper Conoly</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>DIPESH11</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>urvil patel</t>
+          <t>cooper conoly</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -11007,22 +11008,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Arshin Kulkarni</t>
+          <t>Avesh Khan</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>DIPESH11</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>arshin kulkarni</t>
+          <t>avesh khan</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -11049,22 +11050,22 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Jayant Yadav gt</t>
+          <t>Mukesh Kumar</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>DIPESH11</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>jayant yadav</t>
+          <t>mukesh kumar</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -11091,22 +11092,22 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Ajay Mandal dc</t>
+          <t>Aqib Nabi Dar</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>DIPESH11</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ajay mandal</t>
+          <t>aqib nabi dar</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -11133,22 +11134,22 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Will Jacks mi</t>
+          <t>Rasik Dar Salam</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>DIPESH11</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>will jacks</t>
+          <t>rasik dar salam</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -11175,12 +11176,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Kagiso Rabada gt</t>
+          <t>Xavier Bartlett</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>DIPESH11</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -11190,7 +11191,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>kagiso rabada</t>
+          <t>xavier bartlett</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -11217,7 +11218,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Josh Hazelwood rcb</t>
+          <t>KL Rahul dc</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -11227,12 +11228,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>josh hazelwood</t>
+          <t>kl rahul</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -11259,7 +11260,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Kyle Jamieson dc</t>
+          <t>Shreyas Iyer PBKS</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -11269,12 +11270,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>kyle jamieson</t>
+          <t>shreyas iyer</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -11301,7 +11302,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Matheesha Pathirana kkr</t>
+          <t>Jos Buttler gt</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -11311,12 +11312,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>matheesha pathirana</t>
+          <t>jos buttler</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -11343,7 +11344,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>M Siddharth lsg</t>
+          <t>Urvil Patel</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -11353,12 +11354,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>m siddharth</t>
+          <t>urvil patel</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -11385,7 +11386,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Ben Dwarshuis pbks</t>
+          <t>Arshin Kulkarni</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -11395,12 +11396,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>ben dwarshuis</t>
+          <t>arshin kulkarni</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -11427,22 +11428,22 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Mitchel March</t>
+          <t>Nishant Sindhu gt</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>mitchel march</t>
+          <t>nishant sindhu</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -11469,22 +11470,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Shimron Hetmyer</t>
+          <t>Jayant Yadav gt</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>shimron hetmyer</t>
+          <t>jayant yadav</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -11511,22 +11512,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Pathum Nissanka</t>
+          <t>Ajay Mandal dc</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>pathum nissanka</t>
+          <t>ajay mandal</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -11553,12 +11554,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Donovan Ferreira rr</t>
+          <t>Will Jacks mi</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -11568,7 +11569,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>donovan ferreira</t>
+          <t>will jacks</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -11595,12 +11596,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Harshal Patel</t>
+          <t>Kagiso Rabada gt</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -11610,7 +11611,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>harshal patel</t>
+          <t>kagiso rabada</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -11637,12 +11638,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Lungi Ngidi</t>
+          <t>Josh Hazelwood rcb</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -11652,7 +11653,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>lungi ngidi</t>
+          <t>josh hazelwood</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -11679,12 +11680,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Vyshak Vijaykumar PBKS</t>
+          <t>Kyle Jamieson dc</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -11694,7 +11695,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>vyshak vijaykumar</t>
+          <t>kyle jamieson</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -11721,12 +11722,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Mukesh Choudhary csk</t>
+          <t>Matheesha Pathirana kkr</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -11736,7 +11737,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>mukesh choudhary</t>
+          <t>matheesha pathirana</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -11763,12 +11764,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Arjun Tendulkar</t>
+          <t>M Siddharth lsg</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -11778,7 +11779,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>arjun tendulkar</t>
+          <t>m siddharth</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -11805,12 +11806,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Kwena Maphaka</t>
+          <t>Ben Dwarshuis pbks</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -11820,7 +11821,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>kwena maphaka</t>
+          <t>ben dwarshuis</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -11847,7 +11848,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Anrich Nortje</t>
+          <t>Mitchel March</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -11857,12 +11858,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>anrich nortje</t>
+          <t>mitchel march</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -11889,12 +11890,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Venkatesh Iyer</t>
+          <t>Shimron Hetmyer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -11904,7 +11905,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>venkatesh iyer</t>
+          <t>shimron hetmyer</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -11931,12 +11932,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sameer Rizvi</t>
+          <t>Manish Pandey</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -11946,7 +11947,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>sameer rizvi</t>
+          <t>manish pandey</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -11973,12 +11974,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Prashant Veer</t>
+          <t>Pathum Nissanka</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -11988,7 +11989,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>prashant veer</t>
+          <t>pathum nissanka</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -12015,12 +12016,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Washington SUndar</t>
+          <t>Donovan Ferreira rr</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -12030,7 +12031,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>washington sundar</t>
+          <t>donovan ferreira</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -12057,22 +12058,22 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Axar Patel</t>
+          <t>Harshal Patel</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>axar patel</t>
+          <t>harshal patel</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -12099,22 +12100,22 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Azmatullah Omarzai</t>
+          <t>Lungi Ngidi</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>azmatullah omarzai</t>
+          <t>lungi ngidi</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -12141,12 +12142,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Jasprit Bumrah</t>
+          <t>Vyshak Vijaykumar PBKS</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -12156,7 +12157,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>jasprit bumrah</t>
+          <t>vyshak vijaykumar</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -12183,12 +12184,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Mohammed Shami</t>
+          <t>Mukesh Choudhary csk</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -12198,7 +12199,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>mohammed shami</t>
+          <t>mukesh choudhary</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -12225,12 +12226,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Gurjapneet Singh</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -12240,7 +12241,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>trent boult</t>
+          <t>gurjapneet singh</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -12267,22 +12268,22 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>Arjun Tendulkar</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>nicholas pooran</t>
+          <t>arjun tendulkar</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -12309,22 +12310,22 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Nitish Rana</t>
+          <t>Kwena Maphaka</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>nitish rana</t>
+          <t>kwena maphaka</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -12351,22 +12352,22 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Tejasvi Singh</t>
+          <t>Anrich Nortje</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>tejasvi singh</t>
+          <t>anrich nortje</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -12393,22 +12394,22 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>T Natarjan</t>
+          <t>Ramkrishna Ghosh</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>t natarjan</t>
+          <t>ramkrishna ghosh</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -12435,22 +12436,22 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Yuzvendra Chahal</t>
+          <t>Venkatesh Iyer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>yuzvendra chahal</t>
+          <t>venkatesh iyer</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -12477,22 +12478,22 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Akash Deep</t>
+          <t>Shahrukh Khan</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>akash deep</t>
+          <t>shahrukh khan</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -12519,12 +12520,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Ben Duckett</t>
+          <t>Shashank Singh</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>PRATIK11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -12534,7 +12535,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>ben duckett</t>
+          <t>shashank singh</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -12561,12 +12562,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Ayush Mhatre</t>
+          <t>Sameer Rizvi</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>PRATIK11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -12576,7 +12577,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>ayush mhatre</t>
+          <t>sameer rizvi</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -12603,12 +12604,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Rahul Tripathi</t>
+          <t>Prashant Veer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>PRATIK11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -12618,7 +12619,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>rahul tripathi</t>
+          <t>prashant veer</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -12645,22 +12646,22 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Dre Pretorius</t>
+          <t>Washington SUndar</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>PRATIK11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>dre pretorius</t>
+          <t>washington sundar</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -12687,22 +12688,22 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Matthew Breetzke</t>
+          <t>Axar Patel</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>PRATIK11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>matthew breetzke</t>
+          <t>axar patel</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -12729,22 +12730,22 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Anuj Rawat</t>
+          <t>Azmatullah Omarzai</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>PRATIK11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>anuj rawat</t>
+          <t>azmatullah omarzai</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -12771,22 +12772,22 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Jasprit Bumrah</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>PRATIK11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>marco jansen</t>
+          <t>jasprit bumrah</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -12813,22 +12814,22 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Wanindu Hasaranga</t>
+          <t>Mohammed Shami</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>PRATIK11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>wanindu hasaranga</t>
+          <t>mohammed shami</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -12855,12 +12856,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Harpreet Brar</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>PRATIK11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -12870,7 +12871,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>harpreet brar</t>
+          <t>trent boult</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -12897,22 +12898,22 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Digvesh Rathi</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>PRATIK11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>digvesh rathi</t>
+          <t>nicholas pooran</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -12939,42 +12940,924 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
+          <t>Nitish Rana</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>AMEY11</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>BAT</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>nitish rana</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>no_stats_yet</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>0</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Himmat Singh</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>AMEY11</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>BAT</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>himmat singh</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>no_stats_yet</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Suryansh Shegde</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>AMEY11</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>BAT</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>suryansh shegde</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>no_stats_yet</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Tejasvi Singh</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>AMEY11</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>BAT</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>tejasvi singh</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>no_stats_yet</t>
+        </is>
+      </c>
+      <c r="F102" t="n">
+        <v>0</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Krunal Pandya</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>AMEY11</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>krunal pandya</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>no_stats_yet</t>
+        </is>
+      </c>
+      <c r="F103" t="n">
+        <v>0</v>
+      </c>
+      <c r="G103" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>T Natarjan</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>AMEY11</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>t natarjan</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>no_stats_yet</t>
+        </is>
+      </c>
+      <c r="F104" t="n">
+        <v>0</v>
+      </c>
+      <c r="G104" t="n">
+        <v>0</v>
+      </c>
+      <c r="H104" t="n">
+        <v>0</v>
+      </c>
+      <c r="I104" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Yuzvendra Chahal</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>AMEY11</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>BOWL</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>yuzvendra chahal</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>no_stats_yet</t>
+        </is>
+      </c>
+      <c r="F105" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Sai Kishor</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>AMEY11</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>BOWL</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>sai kishor</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>no_stats_yet</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
+        <v>0</v>
+      </c>
+      <c r="G106" t="n">
+        <v>0</v>
+      </c>
+      <c r="H106" t="n">
+        <v>0</v>
+      </c>
+      <c r="I106" t="n">
+        <v>0</v>
+      </c>
+      <c r="J106" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Akash Deep</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>AMEY11</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>BOWL</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>akash deep</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>no_stats_yet</t>
+        </is>
+      </c>
+      <c r="F107" t="n">
+        <v>0</v>
+      </c>
+      <c r="G107" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" t="n">
+        <v>0</v>
+      </c>
+      <c r="I107" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Ben Duckett</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>PRATIK11</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>BAT</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>ben duckett</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>no_stats_yet</t>
+        </is>
+      </c>
+      <c r="F108" t="n">
+        <v>0</v>
+      </c>
+      <c r="G108" t="n">
+        <v>0</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0</v>
+      </c>
+      <c r="I108" t="n">
+        <v>0</v>
+      </c>
+      <c r="J108" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Abhishek Porel</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>PRATIK11</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>BAT</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>abhishek porel</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>no_stats_yet</t>
+        </is>
+      </c>
+      <c r="F109" t="n">
+        <v>0</v>
+      </c>
+      <c r="G109" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" t="n">
+        <v>0</v>
+      </c>
+      <c r="I109" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Ayush Mhatre</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>PRATIK11</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>BAT</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>ayush mhatre</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>no_stats_yet</t>
+        </is>
+      </c>
+      <c r="F110" t="n">
+        <v>0</v>
+      </c>
+      <c r="G110" t="n">
+        <v>0</v>
+      </c>
+      <c r="H110" t="n">
+        <v>0</v>
+      </c>
+      <c r="I110" t="n">
+        <v>0</v>
+      </c>
+      <c r="J110" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Rahul Tripathi</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>PRATIK11</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>BAT</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>rahul tripathi</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>no_stats_yet</t>
+        </is>
+      </c>
+      <c r="F111" t="n">
+        <v>0</v>
+      </c>
+      <c r="G111" t="n">
+        <v>0</v>
+      </c>
+      <c r="H111" t="n">
+        <v>0</v>
+      </c>
+      <c r="I111" t="n">
+        <v>0</v>
+      </c>
+      <c r="J111" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Dre Pretorius</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>PRATIK11</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>BAT</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>dre pretorius</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>no_stats_yet</t>
+        </is>
+      </c>
+      <c r="F112" t="n">
+        <v>0</v>
+      </c>
+      <c r="G112" t="n">
+        <v>0</v>
+      </c>
+      <c r="H112" t="n">
+        <v>0</v>
+      </c>
+      <c r="I112" t="n">
+        <v>0</v>
+      </c>
+      <c r="J112" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Matthew Breetzke</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>PRATIK11</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>BAT</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>matthew breetzke</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>no_stats_yet</t>
+        </is>
+      </c>
+      <c r="F113" t="n">
+        <v>0</v>
+      </c>
+      <c r="G113" t="n">
+        <v>0</v>
+      </c>
+      <c r="H113" t="n">
+        <v>0</v>
+      </c>
+      <c r="I113" t="n">
+        <v>0</v>
+      </c>
+      <c r="J113" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Anuj Rawat</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>PRATIK11</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>BAT</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>anuj rawat</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>no_stats_yet</t>
+        </is>
+      </c>
+      <c r="F114" t="n">
+        <v>0</v>
+      </c>
+      <c r="G114" t="n">
+        <v>0</v>
+      </c>
+      <c r="H114" t="n">
+        <v>0</v>
+      </c>
+      <c r="I114" t="n">
+        <v>0</v>
+      </c>
+      <c r="J114" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Marco Jansen</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>PRATIK11</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>marco jansen</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>no_stats_yet</t>
+        </is>
+      </c>
+      <c r="F115" t="n">
+        <v>0</v>
+      </c>
+      <c r="G115" t="n">
+        <v>0</v>
+      </c>
+      <c r="H115" t="n">
+        <v>0</v>
+      </c>
+      <c r="I115" t="n">
+        <v>0</v>
+      </c>
+      <c r="J115" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Wanindu Hasaranga</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>PRATIK11</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>wanindu hasaranga</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>no_stats_yet</t>
+        </is>
+      </c>
+      <c r="F116" t="n">
+        <v>0</v>
+      </c>
+      <c r="G116" t="n">
+        <v>0</v>
+      </c>
+      <c r="H116" t="n">
+        <v>0</v>
+      </c>
+      <c r="I116" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Harpreet Brar</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>PRATIK11</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>BOWL</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>harpreet brar</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>no_stats_yet</t>
+        </is>
+      </c>
+      <c r="F117" t="n">
+        <v>0</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Mayank Yadav</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>PRATIK11</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>BOWL</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>mayank yadav</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>no_stats_yet</t>
+        </is>
+      </c>
+      <c r="F118" t="n">
+        <v>0</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Digvesh Rathi</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>PRATIK11</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>BOWL</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>digvesh rathi</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>no_stats_yet</t>
+        </is>
+      </c>
+      <c r="F119" t="n">
+        <v>0</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
           <t>Kuldeep Yadav</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
+      <c r="B120" t="inlineStr">
         <is>
           <t>PRATIK11</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
+      <c r="C120" t="inlineStr">
         <is>
           <t>BOWL</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
+      <c r="D120" t="inlineStr">
         <is>
           <t>kuldeep yadav</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="F99" t="n">
-        <v>0</v>
-      </c>
-      <c r="G99" t="n">
-        <v>0</v>
-      </c>
-      <c r="H99" t="n">
-        <v>0</v>
-      </c>
-      <c r="I99" t="n">
-        <v>0</v>
-      </c>
-      <c r="J99" t="n">
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>no_stats_yet</t>
+        </is>
+      </c>
+      <c r="F120" t="n">
+        <v>0</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0</v>
+      </c>
+      <c r="J120" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12989,7 +13872,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13047,7 +13930,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MS Dhoni CSK</t>
+          <t>Jitesh Sharma</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -13062,12 +13945,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>mahendra singh dhoni</t>
+          <t>jitesh sharma</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>possible_mismatch:61.111111111111114</t>
+          <t>possible_mismatch:81.4814814814815</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -13089,27 +13972,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Mohsin Khan</t>
+          <t>Ryan Rickleton</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NIRAV11</t>
+          <t>BABA11</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>mohsin khan</t>
+          <t>ryan rickleton</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>possible_mismatch:60.86956521739131</t>
+          <t>possible_mismatch:92.85714285714286</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -13131,12 +14014,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Glen Philips</t>
+          <t>Priyansh Arya</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>VATSAL11</t>
+          <t>DIPESH11</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -13146,12 +14029,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>glen philips</t>
+          <t>priyansh arya</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>possible_mismatch:60.86956521739131</t>
+          <t>possible_mismatch:75.0</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -13173,27 +14056,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>David Miller</t>
+          <t>Arshdeep Singh</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BABA11</t>
+          <t>DIPESH11</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>david miller</t>
+          <t>arshdeep singh</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>possible_mismatch:60.86956521739131</t>
+          <t>possible_mismatch:75.86206896551724</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -13215,12 +14098,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Dhruv Jurel</t>
+          <t>Phil Salt</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BABA11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -13230,12 +14113,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>dhruv jurel</t>
+          <t>phil salt</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>possible_mismatch:78.57142857142857</t>
+          <t>possible_mismatch:90.0</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -13257,27 +14140,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Ashutosh Sharma</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BABA11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>rashid khan</t>
+          <t>ashutosh sharma</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>possible_mismatch:60.86956521739131</t>
+          <t>possible_mismatch:78.57142857142857</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -13299,12 +14182,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sai Sudharsan</t>
+          <t>Akshat Raghuwanshi</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DIPESH11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -13314,12 +14197,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>sai sudharsan</t>
+          <t>akshat raghuwanshi</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>possible_mismatch:61.53846153846154</t>
+          <t>possible_mismatch:78.94736842105263</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -13338,760 +14221,154 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Prabhsimran Singh</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>DIPESH11</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Player</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Matched_Player</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Match_Type</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Wkts</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Batting_Points</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Bowling_Points</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Points</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Dhruv Jurel</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BABA11</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
         <is>
           <t>BAT</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>prabhsimran singh</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>possible_mismatch:72.72727272727273</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Priyansh Arya</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>DIPESH11</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>BAT</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>priyansh arya</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>possible_mismatch:75.0</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Arshdeep Singh</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>DIPESH11</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>dhruv chand jurel</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>ai_structured</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>18</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>18</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Bhuvaneshwar Kumar</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>AMEY11</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>BOWL</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>arshdeep singh</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>possible_mismatch:75.86206896551724</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Avesh Khan</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>DIPESH11</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>BOWL</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>avesh khan</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>possible_mismatch:63.63636363636363</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Mukesh Kumar</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>DIPESH11</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>BOWL</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>mukesh kumar</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>possible_mismatch:68.96551724137932</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Nishant Sindhu gt</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>NAKUL11</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>AR</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>nishant sindhu</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>possible_mismatch:61.53846153846154</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Manish Pandey</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>SKY11</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>BAT</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>manish pandey</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>possible_mismatch:61.53846153846154</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Gurjapneet Singh</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>SKY11</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>BOWL</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>gurjapneet singh</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>possible_mismatch:70.96774193548387</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Ramkrishna Ghosh</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>HARSH11</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>BAT</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>ramkrishna ghosh</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>possible_mismatch:61.111111111111114</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Shahrukh Khan</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>HARSH11</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>BAT</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>shahrukh khan</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>possible_mismatch:64.0</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Ashutosh Sharma</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>HARSH11</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>BAT</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>ashutosh sharma</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>possible_mismatch:78.57142857142857</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Shashank Singh</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>HARSH11</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>BAT</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>shashank singh</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>possible_mismatch:66.66666666666667</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Himmat Singh</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>AMEY11</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>BAT</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>himmat singh</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>possible_mismatch:64.28571428571428</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Suryansh Shegde</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>AMEY11</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>BAT</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>suryansh shegde</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>possible_mismatch:64.28571428571428</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Krunal Pandya</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>AMEY11</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>AR</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>krunal pandya</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>possible_mismatch:61.53846153846154</t>
-        </is>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Sai Kishor</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>AMEY11</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>BOWL</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>sai kishor</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>possible_mismatch:63.63636363636363</t>
-        </is>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Abhishek Porel</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>BAT</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>abhishek porel</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>possible_mismatch:68.96551724137932</t>
-        </is>
-      </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Mayank Yadav</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>BOWL</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>mayank yadav</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>possible_mismatch:64.28571428571428</t>
-        </is>
-      </c>
-      <c r="F26" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>bhuvneshwar kumar</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ai_structured</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>20</v>
+      </c>
+      <c r="J3" t="n">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/IPL_Fantasy_Points.xlsx
+++ b/IPL_Fantasy_Points.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player_Points" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Merged_Stats" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="No_Stats_Yet" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Possible_Mismatch" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI_Matches" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Player_Points" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Leaderboard" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Merged_Stats" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="No_Stats_Yet" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Possible_Mismatch" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="AI_Matches" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/IPL_Fantasy_Points.xlsx
+++ b/IPL_Fantasy_Points.xlsx
@@ -2882,7 +2882,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Prithvi SHaw</t>
+          <t>Prithvi Shaw</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2924,7 +2924,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Ryan Rickleton</t>
+          <t>Ryan Rickelton</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2939,28 +2939,28 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>ryan rickleton</t>
+          <t>ryan rickelton</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>possible_mismatch:92.85714285714286</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="I60" t="n">
         <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
     </row>
     <row r="61">
@@ -7979,11 +7979,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>BABA11</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>92</v>
+        <v>144</v>
       </c>
     </row>
     <row r="8">
@@ -7992,11 +7992,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PRATIK11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>84</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9">
@@ -8005,11 +8005,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NIRAV11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10">
@@ -8018,11 +8018,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BABA11</t>
+          <t>NIRAV11</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>63</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11">
@@ -10336,7 +10336,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Prithvi SHaw</t>
+          <t>Prithvi Shaw</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -13872,7 +13872,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13972,12 +13972,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Ryan Rickleton</t>
+          <t>Priyansh Arya</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BABA11</t>
+          <t>DIPESH11</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -13987,12 +13987,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ryan rickleton</t>
+          <t>priyansh arya</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>possible_mismatch:92.85714285714286</t>
+          <t>possible_mismatch:75.0</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -14014,7 +14014,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Priyansh Arya</t>
+          <t>Arshdeep Singh</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -14024,17 +14024,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>priyansh arya</t>
+          <t>arshdeep singh</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>possible_mismatch:75.0</t>
+          <t>possible_mismatch:75.86206896551724</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -14056,27 +14056,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Arshdeep Singh</t>
+          <t>Phil Salt</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DIPESH11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>arshdeep singh</t>
+          <t>phil salt</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>possible_mismatch:75.86206896551724</t>
+          <t>possible_mismatch:90.0</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -14098,12 +14098,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Phil Salt</t>
+          <t>Ashutosh Sharma</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -14113,12 +14113,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>phil salt</t>
+          <t>ashutosh sharma</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>possible_mismatch:90.0</t>
+          <t>possible_mismatch:78.57142857142857</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -14140,12 +14140,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ashutosh Sharma</t>
+          <t>Akshat Raghuwanshi</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -14155,12 +14155,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ashutosh sharma</t>
+          <t>akshat raghuwanshi</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>possible_mismatch:78.57142857142857</t>
+          <t>possible_mismatch:78.94736842105263</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -14176,48 +14176,6 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Akshat Raghuwanshi</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>AMEY11</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>BAT</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>akshat raghuwanshi</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>possible_mismatch:78.94736842105263</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
         <v>0</v>
       </c>
     </row>

--- a/IPL_Fantasy_Points.xlsx
+++ b/IPL_Fantasy_Points.xlsx
@@ -2924,7 +2924,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Ryan Rickelton</t>
+          <t>ryan rickelton</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">

--- a/IPL_Fantasy_Points.xlsx
+++ b/IPL_Fantasy_Points.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J177"/>
+  <dimension ref="A1:J179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -614,7 +614,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Jitesh Sharma</t>
+          <t>jitesh sharma</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3134,7 +3134,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Mitchell Starc</t>
+          <t>liam livingston</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>mitchell starc</t>
+          <t>liam livingston</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3176,7 +3176,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Varun Chakravarthy</t>
+          <t>rachin ravindra</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>varun chakravarthy</t>
+          <t>rachin ravindra</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3218,7 +3218,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Zeeshan Ansai</t>
+          <t>sherfane rutherford</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3228,12 +3228,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>zeeshan ansai</t>
+          <t>sherfane rutherford</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -3260,7 +3260,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Mitchell Starc</t>
+          <t>Varun Chakravarthy</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3275,7 +3275,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>mitchell starc</t>
+          <t>varun chakravarthy</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3302,7 +3302,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Mitchel Santner</t>
+          <t>Zeeshan Ansari</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3317,7 +3317,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>mitchel santner</t>
+          <t>zeeshan ansari</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -3344,64 +3344,64 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Ruturaj Gaikwad</t>
+          <t>Mitchell Starc</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>DIPESH11</t>
+          <t>BABA11</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>ruturaj gaikwad</t>
+          <t>mitchell starc</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>exact/alias</t>
+          <t>no_stats_yet</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I70" t="n">
         <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sai Sudharsan</t>
+          <t>Mitchel Santner</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>DIPESH11</t>
+          <t>BABA11</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>sai sudharsan</t>
+          <t>mitchel santner</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -3428,7 +3428,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Prabhsimran Singh</t>
+          <t>Ruturaj Gaikwad</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3443,34 +3443,34 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>prabhsimran singh</t>
+          <t>ruturaj gaikwad</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I72" t="n">
         <v>0</v>
       </c>
       <c r="J72" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Priyansh Arya</t>
+          <t>Sai Sudharsan</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>priyansh arya</t>
+          <t>sai sudharsan</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>possible_mismatch:75.0</t>
+          <t>no_stats_yet</t>
         </is>
       </c>
       <c r="F73" t="n">
@@ -3512,7 +3512,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Mitchel Owen</t>
+          <t>Prabhsimran Singh</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>mitchel owen</t>
+          <t>prabhsimran singh</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -3554,7 +3554,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Nehal Wadhera</t>
+          <t>priyansh arya</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3569,12 +3569,12 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>nehal wadhera</t>
+          <t>priyansh arya</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>possible_mismatch:75.0</t>
         </is>
       </c>
       <c r="F75" t="n">
@@ -3596,7 +3596,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Tristan Stubbs</t>
+          <t>Mitchel Owen</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>tristan stubbs</t>
+          <t>mitchel owen</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -3638,7 +3638,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Sarfaraz Khan</t>
+          <t>Nehal Wadhera</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3653,34 +3653,34 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>sarfaraz khan</t>
+          <t>nehal wadhera</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>exact/alias</t>
+          <t>no_stats_yet</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="I77" t="n">
         <v>0</v>
       </c>
       <c r="J77" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Pat Cummins</t>
+          <t>Tristan Stubbs</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3690,12 +3690,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>pat cummins</t>
+          <t>tristan stubbs</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -3722,7 +3722,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Aiden Markram</t>
+          <t>Sarfaraz Khan</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3732,39 +3732,39 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>aiden markram</t>
+          <t>sarfaraz khan</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="I79" t="n">
         <v>0</v>
       </c>
       <c r="J79" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Tim David</t>
+          <t>Pat Cummins</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3779,34 +3779,34 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>tim david</t>
+          <t>pat cummins</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>exact/alias</t>
+          <t>no_stats_yet</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I80" t="n">
         <v>0</v>
       </c>
       <c r="J80" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Cooper Conoly</t>
+          <t>Aiden Markram</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>cooper conoly</t>
+          <t>aiden markram</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -3848,7 +3848,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Arshdeep Singh</t>
+          <t>Tim David</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3858,39 +3858,39 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>arshdeep singh</t>
+          <t>tim david</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>possible_mismatch:75.86206896551724</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I82" t="n">
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Avesh Khan</t>
+          <t>Cooper Conoly</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3900,12 +3900,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>avesh khan</t>
+          <t>cooper conoly</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -3932,7 +3932,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Mukesh Kumar</t>
+          <t>arshdeep singh</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>mukesh kumar</t>
+          <t>arshdeep singh</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>possible_mismatch:75.86206896551724</t>
         </is>
       </c>
       <c r="F84" t="n">
@@ -3974,7 +3974,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Aqib Nabi Dar</t>
+          <t>Avesh Khan</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3989,7 +3989,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>aqib nabi dar</t>
+          <t>avesh khan</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -4016,7 +4016,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Rasik Dar Salam</t>
+          <t>Mukesh Kumar</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>rasik dar salam</t>
+          <t>mukesh kumar</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -4058,7 +4058,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Xavier Bartlett</t>
+          <t>Aqib Nabi Dar</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4073,7 +4073,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>xavier bartlett</t>
+          <t>aqib nabi dar</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -4100,64 +4100,64 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Yashasvi Jaiswal rr</t>
+          <t>Rasik Dar Salam</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>DIPESH11</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>yashasvi jaiswal</t>
+          <t>rasik dar salam</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>exact/alias</t>
+          <t>no_stats_yet</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="I88" t="n">
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>KL Rahul dc</t>
+          <t>Xavier Bartlett</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>DIPESH11</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>kl rahul</t>
+          <t>xavier bartlett</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -4184,7 +4184,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Shreyas Iyer PBKS</t>
+          <t>Yashasvi Jaiswal rr</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4199,34 +4199,34 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>shreyas iyer</t>
+          <t>yashasvi jaiswal</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="I90" t="n">
         <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Jos Buttler gt</t>
+          <t>KL Rahul dc</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>jos buttler</t>
+          <t>kl rahul</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -4268,7 +4268,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Urvil Patel</t>
+          <t>Shreyas Iyer PBKS</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4283,7 +4283,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>urvil patel</t>
+          <t>shreyas iyer</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -4310,7 +4310,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Arshin Kulkarni</t>
+          <t>Jos Buttler gt</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>arshin kulkarni</t>
+          <t>jos buttler</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -4352,7 +4352,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Nishant Sindhu gt</t>
+          <t>Urvil Patel</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4362,12 +4362,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>nishant sindhu</t>
+          <t>urvil patel</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -4394,7 +4394,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Jayant Yadav gt</t>
+          <t>Arshin Kulkarni</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4404,12 +4404,12 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>jayant yadav</t>
+          <t>arshin kulkarni</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -4436,7 +4436,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Ajay Mandal dc</t>
+          <t>Nishant Sindhu gt</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>ajay mandal</t>
+          <t>nishant sindhu</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -4478,7 +4478,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Will Jacks mi</t>
+          <t>Jayant Yadav gt</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4493,7 +4493,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>will jacks</t>
+          <t>jayant yadav</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -4520,7 +4520,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Riyan Parag rr</t>
+          <t>Ajay Mandal dc</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4535,34 +4535,34 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>riyan parag</t>
+          <t>ajay mandal</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>exact/alias</t>
+          <t>no_stats_yet</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
       </c>
       <c r="H98" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="I98" t="n">
         <v>0</v>
       </c>
       <c r="J98" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Kagiso Rabada gt</t>
+          <t>Will Jacks mi</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>kagiso rabada</t>
+          <t>will jacks</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -4604,7 +4604,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Josh Hazelwood rcb</t>
+          <t>Riyan Parag rr</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4614,39 +4614,39 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>josh hazelwood</t>
+          <t>riyan parag</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
       </c>
       <c r="H100" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I100" t="n">
         <v>0</v>
       </c>
       <c r="J100" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Kyle Jamieson dc</t>
+          <t>Kagiso Rabada gt</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>kyle jamieson</t>
+          <t>kagiso rabada</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -4688,7 +4688,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Matheesha Pathirana kkr</t>
+          <t>Josh Hazelwood rcb</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>matheesha pathirana</t>
+          <t>josh hazelwood</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -4730,7 +4730,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>M Siddharth lsg</t>
+          <t>Kyle Jamieson dc</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4745,7 +4745,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>m siddharth</t>
+          <t>kyle jamieson</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -4772,7 +4772,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Ben Dwarshuis pbks</t>
+          <t>Matheesha Pathirana kkr</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4787,7 +4787,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>ben dwarshuis</t>
+          <t>matheesha pathirana</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -4814,7 +4814,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Nandre Burger rr</t>
+          <t>M Siddharth lsg</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4829,54 +4829,54 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>nandre burger</t>
+          <t>m siddharth</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>exact/alias</t>
+          <t>no_stats_yet</t>
         </is>
       </c>
       <c r="F105" t="n">
         <v>0</v>
       </c>
       <c r="G105" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H105" t="n">
         <v>0</v>
       </c>
       <c r="I105" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="J105" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Phil Salt</t>
+          <t>Ben Dwarshuis pbks</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>phil salt</t>
+          <t>ben dwarshuis</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>possible_mismatch:90.0</t>
+          <t>no_stats_yet</t>
         </is>
       </c>
       <c r="F106" t="n">
@@ -4898,49 +4898,49 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Mitchel March</t>
+          <t>Nandre Burger rr</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>mitchel march</t>
+          <t>nandre burger</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="F107" t="n">
         <v>0</v>
       </c>
       <c r="G107" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
       </c>
       <c r="I107" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J107" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Rohit Sharma</t>
+          <t>phil salt</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4955,34 +4955,34 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>rohit sharma</t>
+          <t>phil salt</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>exact/alias</t>
+          <t>possible_mismatch:90.0</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
       </c>
       <c r="H108" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="I108" t="n">
         <v>0</v>
       </c>
       <c r="J108" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Shimron Hetmyer</t>
+          <t>Mitchel March</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>shimron hetmyer</t>
+          <t>mitchel march</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -5024,7 +5024,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Manish Pandey</t>
+          <t>Rohit Sharma</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -5039,34 +5039,34 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>manish pandey</t>
+          <t>rohit sharma</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
       </c>
       <c r="H110" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="I110" t="n">
         <v>0</v>
       </c>
       <c r="J110" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Pathum Nissanka</t>
+          <t>Shimron Hetmyer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>pathum nissanka</t>
+          <t>shimron hetmyer</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -5108,7 +5108,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Hardik Pandya</t>
+          <t>Manish Pandey</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -5118,39 +5118,39 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>hardik pandya</t>
+          <t>manish pandey</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>exact/alias</t>
+          <t>no_stats_yet</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="G112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H112" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="I112" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J112" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Jamie Overton csk</t>
+          <t>Pathum Nissanka</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -5160,39 +5160,39 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>jamie overton</t>
+          <t>pathum nissanka</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>exact/alias</t>
+          <t>no_stats_yet</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
       </c>
       <c r="H113" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="I113" t="n">
         <v>0</v>
       </c>
       <c r="J113" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Donovan Ferreira rr</t>
+          <t>Hardik Pandya</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -5207,34 +5207,34 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>donovan ferreira</t>
+          <t>hardik pandya</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H114" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I114" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J114" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Harshal Patel</t>
+          <t>Jamie Overton csk</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -5244,39 +5244,39 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>harshal patel</t>
+          <t>jamie overton</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
       </c>
       <c r="H115" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="I115" t="n">
         <v>0</v>
       </c>
       <c r="J115" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Kartik Tyagi</t>
+          <t>Donovan Ferreira rr</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -5286,39 +5286,39 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>kartik tyagi</t>
+          <t>donovan ferreira</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>exact/alias</t>
+          <t>no_stats_yet</t>
         </is>
       </c>
       <c r="F116" t="n">
         <v>0</v>
       </c>
       <c r="G116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H116" t="n">
         <v>0</v>
       </c>
       <c r="I116" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J116" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Lungi Ngidi</t>
+          <t>Harshal Patel</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -5333,7 +5333,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>lungi ngidi</t>
+          <t>harshal patel</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -5360,7 +5360,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Vyshak Vijaykumar PBKS</t>
+          <t>Kartik Tyagi</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -5375,34 +5375,34 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>vyshak vijaykumar</t>
+          <t>kartik tyagi</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="F118" t="n">
         <v>0</v>
       </c>
       <c r="G118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H118" t="n">
         <v>0</v>
       </c>
       <c r="I118" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J118" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Mukesh Choudhary csk</t>
+          <t>Lungi Ngidi</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -5417,7 +5417,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>mukesh choudhary</t>
+          <t>lungi ngidi</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -5444,7 +5444,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Gurjapneet Singh</t>
+          <t>Vyshak Vijaykumar PBKS</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5459,7 +5459,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>gurjapneet singh</t>
+          <t>vyshak vijaykumar</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -5486,7 +5486,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Arjun Tendulkar</t>
+          <t>Mukesh Choudhary csk</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>arjun tendulkar</t>
+          <t>mukesh choudhary</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -5528,7 +5528,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Kwena Maphaka</t>
+          <t>Gurjapneet Singh</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5543,7 +5543,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>kwena maphaka</t>
+          <t>gurjapneet singh</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -5570,7 +5570,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Anrich Nortje</t>
+          <t>Arjun Tendulkar</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5585,7 +5585,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>anrich nortje</t>
+          <t>arjun tendulkar</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -5612,64 +5612,64 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Devdutt Padikkal</t>
+          <t>Kwena Maphaka</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>devdutt padikkal</t>
+          <t>kwena maphaka</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>exact/alias</t>
+          <t>no_stats_yet</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
       </c>
       <c r="H124" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="I124" t="n">
         <v>0</v>
       </c>
       <c r="J124" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Ramkrishna Ghosh</t>
+          <t>Anrich Nortje</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>ramkrishna ghosh</t>
+          <t>anrich nortje</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -5696,7 +5696,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Venkatesh Iyer</t>
+          <t>Devdutt Padikkal</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5711,34 +5711,34 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>venkatesh iyer</t>
+          <t>devdutt padikkal</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="F126" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
       </c>
       <c r="H126" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="I126" t="n">
         <v>0</v>
       </c>
       <c r="J126" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Shahrukh Khan</t>
+          <t>Ramkrishna Ghosh</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5753,7 +5753,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>shahrukh khan</t>
+          <t>ramkrishna ghosh</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -5780,7 +5780,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Ashutosh Sharma</t>
+          <t>Venkatesh Iyer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5795,12 +5795,12 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>ashutosh sharma</t>
+          <t>venkatesh iyer</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>possible_mismatch:78.57142857142857</t>
+          <t>no_stats_yet</t>
         </is>
       </c>
       <c r="F128" t="n">
@@ -5822,7 +5822,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Tilak Varma</t>
+          <t>Shahrukh Khan</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -5837,34 +5837,34 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>tilak varma</t>
+          <t>shahrukh khan</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>exact/alias</t>
+          <t>no_stats_yet</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
       </c>
       <c r="H129" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I129" t="n">
         <v>0</v>
       </c>
       <c r="J129" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Shashank Singh</t>
+          <t>ashutosh sharma</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -5879,12 +5879,12 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>shashank singh</t>
+          <t>ashutosh sharma</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>possible_mismatch:78.57142857142857</t>
         </is>
       </c>
       <c r="F130" t="n">
@@ -5906,7 +5906,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Sameer Rizvi</t>
+          <t>Tilak Varma</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -5921,34 +5921,34 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>sameer rizvi</t>
+          <t>tilak varma</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
       </c>
       <c r="H131" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I131" t="n">
         <v>0</v>
       </c>
       <c r="J131" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Angkrish Raghuvanshi</t>
+          <t>Shashank Singh</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -5963,34 +5963,34 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>angkrish raghuvanshi</t>
+          <t>shashank singh</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>exact/alias</t>
+          <t>no_stats_yet</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
       </c>
       <c r="H132" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="I132" t="n">
         <v>0</v>
       </c>
       <c r="J132" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Prashant Veer</t>
+          <t>Sameer Rizvi</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -6005,7 +6005,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>prashant veer</t>
+          <t>sameer rizvi</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -6032,7 +6032,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Washington SUndar</t>
+          <t>Angkrish Raghuvanshi</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -6042,39 +6042,39 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>washington sundar</t>
+          <t>angkrish raghuvanshi</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
       </c>
       <c r="H134" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="I134" t="n">
         <v>0</v>
       </c>
       <c r="J134" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Axar Patel</t>
+          <t>Prashant Veer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>axar patel</t>
+          <t>prashant veer</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -6116,7 +6116,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Azmatullah Omarzai</t>
+          <t>Washington SUndar</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>azmatullah omarzai</t>
+          <t>washington sundar</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -6158,7 +6158,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Salil Arora</t>
+          <t>Axar Patel</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -6173,34 +6173,34 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>salil arora</t>
+          <t>axar patel</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>exact/alias</t>
+          <t>no_stats_yet</t>
         </is>
       </c>
       <c r="F137" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
       </c>
       <c r="H137" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I137" t="n">
         <v>0</v>
       </c>
       <c r="J137" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Jasprit Bumrah</t>
+          <t>Azmatullah Omarzai</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -6210,12 +6210,12 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>jasprit bumrah</t>
+          <t>azmatullah omarzai</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -6242,7 +6242,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Jaydev Unadkat</t>
+          <t>Salil Arora</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -6252,12 +6252,12 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>jaydev unadkat</t>
+          <t>salil arora</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -6266,25 +6266,25 @@
         </is>
       </c>
       <c r="F139" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H139" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I139" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J139" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Mohammed Shami</t>
+          <t>Jasprit Bumrah</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -6299,7 +6299,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>mohammed shami</t>
+          <t>jasprit bumrah</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -6326,7 +6326,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Jaydev Unadkat</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -6341,118 +6341,118 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>trent boult</t>
+          <t>jaydev unadkat</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="F141" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
       </c>
       <c r="I141" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J141" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Virat Kohli</t>
+          <t>Mohammed Shami</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>virat kohli</t>
+          <t>mohammed shami</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>exact/alias</t>
+          <t>no_stats_yet</t>
         </is>
       </c>
       <c r="F142" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
       </c>
       <c r="H142" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="I142" t="n">
         <v>0</v>
       </c>
       <c r="J142" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Suryakumar Yadav</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>suryakumar yadav</t>
+          <t>trent boult</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>exact/alias</t>
+          <t>no_stats_yet</t>
         </is>
       </c>
       <c r="F143" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
       </c>
       <c r="H143" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I143" t="n">
         <v>0</v>
       </c>
       <c r="J143" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>Virat Kohli</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -6467,34 +6467,34 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>nicholas pooran</t>
+          <t>virat kohli</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="F144" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
       </c>
       <c r="H144" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="I144" t="n">
         <v>0</v>
       </c>
       <c r="J144" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Nitish Rana</t>
+          <t>Suryakumar Yadav</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -6509,34 +6509,34 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>nitish rana</t>
+          <t>suryakumar yadav</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="F145" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
       </c>
       <c r="H145" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I145" t="n">
         <v>0</v>
       </c>
       <c r="J145" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Aniket Verma</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -6551,34 +6551,34 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>aniket verma</t>
+          <t>nicholas pooran</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>exact/alias</t>
+          <t>no_stats_yet</t>
         </is>
       </c>
       <c r="F146" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
       </c>
       <c r="H146" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="I146" t="n">
         <v>0</v>
       </c>
       <c r="J146" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Akshat Raghuwanshi</t>
+          <t>Nitish Rana</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -6593,12 +6593,12 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>akshat raghuwanshi</t>
+          <t>nitish rana</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>possible_mismatch:78.94736842105263</t>
+          <t>no_stats_yet</t>
         </is>
       </c>
       <c r="F147" t="n">
@@ -6620,7 +6620,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Himmat Singh</t>
+          <t>Aniket Verma</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -6635,34 +6635,34 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>himmat singh</t>
+          <t>aniket verma</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
       </c>
       <c r="H148" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="I148" t="n">
         <v>0</v>
       </c>
       <c r="J148" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Suryansh Shegde</t>
+          <t>akshat raghuwanshi</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -6677,12 +6677,12 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>suryansh shegde</t>
+          <t>akshat raghuwanshi</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>possible_mismatch:78.94736842105263</t>
         </is>
       </c>
       <c r="F149" t="n">
@@ -6704,7 +6704,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Tejasvi Singh</t>
+          <t>Himmat Singh</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -6719,7 +6719,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>tejasvi singh</t>
+          <t>himmat singh</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -6746,7 +6746,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Krunal Pandya</t>
+          <t>Suryansh Shegde</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -6756,12 +6756,12 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>krunal pandya</t>
+          <t>suryansh shegde</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -6788,7 +6788,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Tejasvi Singh</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -6798,39 +6798,39 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>jofra archer</t>
+          <t>tejasvi singh</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>exact/alias</t>
+          <t>no_stats_yet</t>
         </is>
       </c>
       <c r="F152" t="n">
         <v>0</v>
       </c>
       <c r="G152" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H152" t="n">
         <v>0</v>
       </c>
       <c r="I152" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="J152" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>T Natarjan</t>
+          <t>Krunal Pandya</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>t natarjan</t>
+          <t>krunal pandya</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -6872,7 +6872,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Yuzvendra Chahal</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -6882,39 +6882,39 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>yuzvendra chahal</t>
+          <t>jofra archer</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="F154" t="n">
         <v>0</v>
       </c>
       <c r="G154" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H154" t="n">
         <v>0</v>
       </c>
       <c r="I154" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J154" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Bhuvaneshwar Kumar</t>
+          <t>T Natarjan</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -6924,39 +6924,39 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>bhuvneshwar kumar</t>
+          <t>t natarjan</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>ai_structured</t>
+          <t>no_stats_yet</t>
         </is>
       </c>
       <c r="F155" t="n">
         <v>0</v>
       </c>
       <c r="G155" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H155" t="n">
         <v>0</v>
       </c>
       <c r="I155" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J155" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Vaibhav Arora</t>
+          <t>Yuzvendra Chahal</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -6971,34 +6971,34 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>vaibhav arora</t>
+          <t>yuzvendra chahal</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>exact/alias</t>
+          <t>no_stats_yet</t>
         </is>
       </c>
       <c r="F156" t="n">
         <v>0</v>
       </c>
       <c r="G156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H156" t="n">
         <v>0</v>
       </c>
       <c r="I156" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J156" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Sai Kishor</t>
+          <t>Bhuvaneshwar Kumar</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -7013,34 +7013,34 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>sai kishor</t>
+          <t>bhuvneshwar kumar</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>ai_structured</t>
         </is>
       </c>
       <c r="F157" t="n">
         <v>0</v>
       </c>
       <c r="G157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
       </c>
       <c r="I157" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J157" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Vaibhav Arora</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -7055,7 +7055,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>matt henry</t>
+          <t>vaibhav arora</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -7064,25 +7064,25 @@
         </is>
       </c>
       <c r="F158" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
       </c>
       <c r="I158" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J158" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Akash Deep</t>
+          <t>Sai Kishor</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -7097,7 +7097,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>akash deep</t>
+          <t>sai kishor</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -7124,22 +7124,22 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Abhishek Sharma</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>PRATIK11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>abhishek sharma</t>
+          <t>matt henry</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -7148,40 +7148,40 @@
         </is>
       </c>
       <c r="F160" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
       </c>
       <c r="H160" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I160" t="n">
         <v>0</v>
       </c>
       <c r="J160" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Ben Duckett</t>
+          <t>Akash Deep</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>PRATIK11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>ben duckett</t>
+          <t>akash deep</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -7208,7 +7208,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Abhishek Porel</t>
+          <t>Abhishek Sharma</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -7223,34 +7223,34 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>abhishek porel</t>
+          <t>abhishek sharma</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="F162" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
       </c>
       <c r="H162" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I162" t="n">
         <v>0</v>
       </c>
       <c r="J162" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Ayush Mhatre</t>
+          <t>Ben Duckett</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -7265,7 +7265,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>ayush mhatre</t>
+          <t>ben duckett</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -7292,7 +7292,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Finn Allen</t>
+          <t>Abhishek Porel</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -7307,34 +7307,34 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>finn allen</t>
+          <t>abhishek porel</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>exact/alias</t>
+          <t>no_stats_yet</t>
         </is>
       </c>
       <c r="F164" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
       </c>
       <c r="H164" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="I164" t="n">
         <v>0</v>
       </c>
       <c r="J164" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Rahul Tripathi</t>
+          <t>Ayush Mhatre</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -7349,7 +7349,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>rahul tripathi</t>
+          <t>ayush mhatre</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -7376,7 +7376,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Dre Pretorius</t>
+          <t>Finn Allen</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -7391,34 +7391,34 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>dre pretorius</t>
+          <t>finn allen</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="F166" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
       </c>
       <c r="H166" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="I166" t="n">
         <v>0</v>
       </c>
       <c r="J166" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Matthew Breetzke</t>
+          <t>Rahul Tripathi</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>matthew breetzke</t>
+          <t>rahul tripathi</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -7460,7 +7460,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Anuj Rawat</t>
+          <t>Dre Pretorius</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -7475,7 +7475,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>anuj rawat</t>
+          <t>dre pretorius</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -7502,7 +7502,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Matthew Breetzke</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>marco jansen</t>
+          <t>matthew breetzke</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -7544,7 +7544,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Sunil Narine</t>
+          <t>Anuj Rawat</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -7554,39 +7554,39 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>sunil narine</t>
+          <t>anuj rawat</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>exact/alias</t>
+          <t>no_stats_yet</t>
         </is>
       </c>
       <c r="F170" t="n">
         <v>0</v>
       </c>
       <c r="G170" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H170" t="n">
         <v>0</v>
       </c>
       <c r="I170" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J170" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Wanindu Hasaranga</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>wanindu hasaranga</t>
+          <t>marco jansen</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -7628,7 +7628,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Harpreet Brar</t>
+          <t>Sunil Narine</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -7638,39 +7638,39 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>harpreet brar</t>
+          <t>sunil narine</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="F172" t="n">
         <v>0</v>
       </c>
       <c r="G172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H172" t="n">
         <v>0</v>
       </c>
       <c r="I172" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J172" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Mayank Yadav</t>
+          <t>Wanindu Hasaranga</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -7680,12 +7680,12 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>mayank yadav</t>
+          <t>wanindu hasaranga</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -7712,7 +7712,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Suyash Sharma</t>
+          <t>Harpreet Brar</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -7727,34 +7727,34 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>suyash sharma</t>
+          <t>harpreet brar</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>exact/alias</t>
+          <t>no_stats_yet</t>
         </is>
       </c>
       <c r="F174" t="n">
         <v>0</v>
       </c>
       <c r="G174" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H174" t="n">
         <v>0</v>
       </c>
       <c r="I174" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J174" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Digvesh Rathi</t>
+          <t>Mayank Yadav</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -7769,7 +7769,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>digvesh rathi</t>
+          <t>mayank yadav</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -7796,7 +7796,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Kuldeep Yadav</t>
+          <t>Suyash Sharma</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -7811,69 +7811,153 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>kuldeep yadav</t>
+          <t>suyash sharma</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="F176" t="n">
         <v>0</v>
       </c>
       <c r="G176" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H176" t="n">
         <v>0</v>
       </c>
       <c r="I176" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J176" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
+          <t>Digvesh Rathi</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>PRATIK11</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>BOWL</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>digvesh rathi</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>no_stats_yet</t>
+        </is>
+      </c>
+      <c r="F177" t="n">
+        <v>0</v>
+      </c>
+      <c r="G177" t="n">
+        <v>0</v>
+      </c>
+      <c r="H177" t="n">
+        <v>0</v>
+      </c>
+      <c r="I177" t="n">
+        <v>0</v>
+      </c>
+      <c r="J177" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Kuldeep Yadav</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>PRATIK11</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>BOWL</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>kuldeep yadav</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>no_stats_yet</t>
+        </is>
+      </c>
+      <c r="F178" t="n">
+        <v>0</v>
+      </c>
+      <c r="G178" t="n">
+        <v>0</v>
+      </c>
+      <c r="H178" t="n">
+        <v>0</v>
+      </c>
+      <c r="I178" t="n">
+        <v>0</v>
+      </c>
+      <c r="J178" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
           <t>Noor Ahmad</t>
         </is>
       </c>
-      <c r="B177" t="inlineStr">
+      <c r="B179" t="inlineStr">
         <is>
           <t>PRATIK11</t>
         </is>
       </c>
-      <c r="C177" t="inlineStr">
+      <c r="C179" t="inlineStr">
         <is>
           <t>BOWL</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr">
+      <c r="D179" t="inlineStr">
         <is>
           <t>noor ahmad</t>
         </is>
       </c>
-      <c r="E177" t="inlineStr">
+      <c r="E179" t="inlineStr">
         <is>
           <t>exact/alias</t>
         </is>
       </c>
-      <c r="F177" t="n">
+      <c r="F179" t="n">
         <v>1</v>
       </c>
-      <c r="G177" t="n">
-        <v>0</v>
-      </c>
-      <c r="H177" t="n">
-        <v>0</v>
-      </c>
-      <c r="I177" t="n">
-        <v>0</v>
-      </c>
-      <c r="J177" t="n">
+      <c r="G179" t="n">
+        <v>0</v>
+      </c>
+      <c r="H179" t="n">
+        <v>0</v>
+      </c>
+      <c r="I179" t="n">
+        <v>0</v>
+      </c>
+      <c r="J179" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8808,7 +8892,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J120"/>
+  <dimension ref="A1:J122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10462,7 +10546,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Mitchell Starc</t>
+          <t>liam livingston</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -10477,7 +10561,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>mitchell starc</t>
+          <t>liam livingston</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -10504,7 +10588,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Varun Chakravarthy</t>
+          <t>rachin ravindra</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -10514,12 +10598,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>varun chakravarthy</t>
+          <t>rachin ravindra</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -10546,7 +10630,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Zeeshan Ansai</t>
+          <t>sherfane rutherford</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -10556,12 +10640,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>zeeshan ansai</t>
+          <t>sherfane rutherford</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -10588,7 +10672,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Mitchell Starc</t>
+          <t>Varun Chakravarthy</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -10603,7 +10687,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>mitchell starc</t>
+          <t>varun chakravarthy</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -10630,7 +10714,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Mitchel Santner</t>
+          <t>Zeeshan Ansari</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -10645,7 +10729,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>mitchel santner</t>
+          <t>zeeshan ansari</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -10672,22 +10756,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sai Sudharsan</t>
+          <t>Mitchell Starc</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>DIPESH11</t>
+          <t>BABA11</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>sai sudharsan</t>
+          <t>mitchell starc</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -10714,22 +10798,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Prabhsimran Singh</t>
+          <t>Mitchel Santner</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>DIPESH11</t>
+          <t>BABA11</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>prabhsimran singh</t>
+          <t>mitchel santner</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -10756,7 +10840,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Mitchel Owen</t>
+          <t>Sai Sudharsan</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -10771,7 +10855,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>mitchel owen</t>
+          <t>sai sudharsan</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -10798,7 +10882,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Nehal Wadhera</t>
+          <t>Prabhsimran Singh</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -10813,7 +10897,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>nehal wadhera</t>
+          <t>prabhsimran singh</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -10840,7 +10924,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Tristan Stubbs</t>
+          <t>Mitchel Owen</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -10855,7 +10939,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>tristan stubbs</t>
+          <t>mitchel owen</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -10882,7 +10966,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Pat Cummins</t>
+          <t>Nehal Wadhera</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -10892,12 +10976,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>pat cummins</t>
+          <t>nehal wadhera</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -10924,7 +11008,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Aiden Markram</t>
+          <t>Tristan Stubbs</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -10934,12 +11018,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>aiden markram</t>
+          <t>tristan stubbs</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -10966,7 +11050,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Cooper Conoly</t>
+          <t>Pat Cummins</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -10981,7 +11065,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>cooper conoly</t>
+          <t>pat cummins</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -11008,7 +11092,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Avesh Khan</t>
+          <t>Aiden Markram</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -11018,12 +11102,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>avesh khan</t>
+          <t>aiden markram</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -11050,7 +11134,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Mukesh Kumar</t>
+          <t>Cooper Conoly</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -11060,12 +11144,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>mukesh kumar</t>
+          <t>cooper conoly</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -11092,7 +11176,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Aqib Nabi Dar</t>
+          <t>Avesh Khan</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -11107,7 +11191,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>aqib nabi dar</t>
+          <t>avesh khan</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -11134,7 +11218,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Rasik Dar Salam</t>
+          <t>Mukesh Kumar</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -11149,7 +11233,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>rasik dar salam</t>
+          <t>mukesh kumar</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -11176,7 +11260,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Xavier Bartlett</t>
+          <t>Aqib Nabi Dar</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -11191,7 +11275,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>xavier bartlett</t>
+          <t>aqib nabi dar</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -11218,22 +11302,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>KL Rahul dc</t>
+          <t>Rasik Dar Salam</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>DIPESH11</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>kl rahul</t>
+          <t>rasik dar salam</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -11260,22 +11344,22 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Shreyas Iyer PBKS</t>
+          <t>Xavier Bartlett</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>DIPESH11</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>shreyas iyer</t>
+          <t>xavier bartlett</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -11302,7 +11386,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Jos Buttler gt</t>
+          <t>KL Rahul dc</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -11317,7 +11401,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>jos buttler</t>
+          <t>kl rahul</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -11344,7 +11428,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Urvil Patel</t>
+          <t>Shreyas Iyer PBKS</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -11359,7 +11443,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>urvil patel</t>
+          <t>shreyas iyer</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -11386,7 +11470,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Arshin Kulkarni</t>
+          <t>Jos Buttler gt</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -11401,7 +11485,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>arshin kulkarni</t>
+          <t>jos buttler</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -11428,7 +11512,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Nishant Sindhu gt</t>
+          <t>Urvil Patel</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -11438,12 +11522,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>nishant sindhu</t>
+          <t>urvil patel</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -11470,7 +11554,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Jayant Yadav gt</t>
+          <t>Arshin Kulkarni</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -11480,12 +11564,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>jayant yadav</t>
+          <t>arshin kulkarni</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -11512,7 +11596,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Ajay Mandal dc</t>
+          <t>Nishant Sindhu gt</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -11527,7 +11611,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>ajay mandal</t>
+          <t>nishant sindhu</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -11554,7 +11638,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Will Jacks mi</t>
+          <t>Jayant Yadav gt</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -11569,7 +11653,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>will jacks</t>
+          <t>jayant yadav</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -11596,7 +11680,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Kagiso Rabada gt</t>
+          <t>Ajay Mandal dc</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -11606,12 +11690,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>kagiso rabada</t>
+          <t>ajay mandal</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -11638,7 +11722,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Josh Hazelwood rcb</t>
+          <t>Will Jacks mi</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -11648,12 +11732,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>josh hazelwood</t>
+          <t>will jacks</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -11680,7 +11764,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Kyle Jamieson dc</t>
+          <t>Kagiso Rabada gt</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -11695,7 +11779,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>kyle jamieson</t>
+          <t>kagiso rabada</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -11722,7 +11806,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Matheesha Pathirana kkr</t>
+          <t>Josh Hazelwood rcb</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -11737,7 +11821,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>matheesha pathirana</t>
+          <t>josh hazelwood</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -11764,7 +11848,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>M Siddharth lsg</t>
+          <t>Kyle Jamieson dc</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -11779,7 +11863,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>m siddharth</t>
+          <t>kyle jamieson</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -11806,7 +11890,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Ben Dwarshuis pbks</t>
+          <t>Matheesha Pathirana kkr</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -11821,7 +11905,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>ben dwarshuis</t>
+          <t>matheesha pathirana</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -11848,22 +11932,22 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Mitchel March</t>
+          <t>M Siddharth lsg</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>mitchel march</t>
+          <t>m siddharth</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -11890,22 +11974,22 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Shimron Hetmyer</t>
+          <t>Ben Dwarshuis pbks</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>shimron hetmyer</t>
+          <t>ben dwarshuis</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -11932,7 +12016,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Manish Pandey</t>
+          <t>Mitchel March</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -11947,7 +12031,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>manish pandey</t>
+          <t>mitchel march</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -11974,7 +12058,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Pathum Nissanka</t>
+          <t>Shimron Hetmyer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -11989,7 +12073,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>pathum nissanka</t>
+          <t>shimron hetmyer</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -12016,7 +12100,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Donovan Ferreira rr</t>
+          <t>Manish Pandey</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -12026,12 +12110,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>donovan ferreira</t>
+          <t>manish pandey</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -12058,7 +12142,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Harshal Patel</t>
+          <t>Pathum Nissanka</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -12068,12 +12152,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>harshal patel</t>
+          <t>pathum nissanka</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -12100,7 +12184,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Lungi Ngidi</t>
+          <t>Donovan Ferreira rr</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -12110,12 +12194,12 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>lungi ngidi</t>
+          <t>donovan ferreira</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -12142,7 +12226,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Vyshak Vijaykumar PBKS</t>
+          <t>Harshal Patel</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -12157,7 +12241,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>vyshak vijaykumar</t>
+          <t>harshal patel</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -12184,7 +12268,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Mukesh Choudhary csk</t>
+          <t>Lungi Ngidi</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -12199,7 +12283,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>mukesh choudhary</t>
+          <t>lungi ngidi</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -12226,7 +12310,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Gurjapneet Singh</t>
+          <t>Vyshak Vijaykumar PBKS</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -12241,7 +12325,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>gurjapneet singh</t>
+          <t>vyshak vijaykumar</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -12268,7 +12352,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Arjun Tendulkar</t>
+          <t>Mukesh Choudhary csk</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -12283,7 +12367,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>arjun tendulkar</t>
+          <t>mukesh choudhary</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -12310,7 +12394,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Kwena Maphaka</t>
+          <t>Gurjapneet Singh</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -12325,7 +12409,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>kwena maphaka</t>
+          <t>gurjapneet singh</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -12352,7 +12436,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Anrich Nortje</t>
+          <t>Arjun Tendulkar</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -12367,7 +12451,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>anrich nortje</t>
+          <t>arjun tendulkar</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -12394,22 +12478,22 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Ramkrishna Ghosh</t>
+          <t>Kwena Maphaka</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>ramkrishna ghosh</t>
+          <t>kwena maphaka</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -12436,22 +12520,22 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Venkatesh Iyer</t>
+          <t>Anrich Nortje</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>venkatesh iyer</t>
+          <t>anrich nortje</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -12478,7 +12562,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Shahrukh Khan</t>
+          <t>Ramkrishna Ghosh</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -12493,7 +12577,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>shahrukh khan</t>
+          <t>ramkrishna ghosh</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -12520,7 +12604,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Shashank Singh</t>
+          <t>Venkatesh Iyer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -12535,7 +12619,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>shashank singh</t>
+          <t>venkatesh iyer</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -12562,7 +12646,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Sameer Rizvi</t>
+          <t>Shahrukh Khan</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -12577,7 +12661,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>sameer rizvi</t>
+          <t>shahrukh khan</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -12604,7 +12688,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Prashant Veer</t>
+          <t>Shashank Singh</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -12619,7 +12703,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>prashant veer</t>
+          <t>shashank singh</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -12646,7 +12730,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Washington SUndar</t>
+          <t>Sameer Rizvi</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -12656,12 +12740,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>washington sundar</t>
+          <t>sameer rizvi</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -12688,7 +12772,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Axar Patel</t>
+          <t>Prashant Veer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -12698,12 +12782,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>axar patel</t>
+          <t>prashant veer</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -12730,7 +12814,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Azmatullah Omarzai</t>
+          <t>Washington SUndar</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -12745,7 +12829,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>azmatullah omarzai</t>
+          <t>washington sundar</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -12772,7 +12856,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Jasprit Bumrah</t>
+          <t>Axar Patel</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -12782,12 +12866,12 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>jasprit bumrah</t>
+          <t>axar patel</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -12814,7 +12898,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Mohammed Shami</t>
+          <t>Azmatullah Omarzai</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -12824,12 +12908,12 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>mohammed shami</t>
+          <t>azmatullah omarzai</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -12856,7 +12940,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Jasprit Bumrah</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -12871,7 +12955,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>trent boult</t>
+          <t>jasprit bumrah</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -12898,22 +12982,22 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>Mohammed Shami</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>nicholas pooran</t>
+          <t>mohammed shami</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -12940,22 +13024,22 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Nitish Rana</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>nitish rana</t>
+          <t>trent boult</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -12982,7 +13066,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Himmat Singh</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -12997,7 +13081,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>himmat singh</t>
+          <t>nicholas pooran</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -13024,7 +13108,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Suryansh Shegde</t>
+          <t>Nitish Rana</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -13039,7 +13123,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>suryansh shegde</t>
+          <t>nitish rana</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -13066,7 +13150,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Tejasvi Singh</t>
+          <t>Himmat Singh</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -13081,7 +13165,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>tejasvi singh</t>
+          <t>himmat singh</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -13108,7 +13192,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Krunal Pandya</t>
+          <t>Suryansh Shegde</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -13118,12 +13202,12 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>krunal pandya</t>
+          <t>suryansh shegde</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -13150,7 +13234,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>T Natarjan</t>
+          <t>Tejasvi Singh</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -13160,12 +13244,12 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>t natarjan</t>
+          <t>tejasvi singh</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -13192,7 +13276,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Yuzvendra Chahal</t>
+          <t>Krunal Pandya</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -13202,12 +13286,12 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>yuzvendra chahal</t>
+          <t>krunal pandya</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -13234,7 +13318,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Sai Kishor</t>
+          <t>T Natarjan</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -13244,12 +13328,12 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>sai kishor</t>
+          <t>t natarjan</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -13276,7 +13360,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Akash Deep</t>
+          <t>Yuzvendra Chahal</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -13291,7 +13375,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>akash deep</t>
+          <t>yuzvendra chahal</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -13318,22 +13402,22 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Ben Duckett</t>
+          <t>Sai Kishor</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>PRATIK11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>ben duckett</t>
+          <t>sai kishor</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -13360,22 +13444,22 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Abhishek Porel</t>
+          <t>Akash Deep</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>PRATIK11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>abhishek porel</t>
+          <t>akash deep</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -13402,7 +13486,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Ayush Mhatre</t>
+          <t>Ben Duckett</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -13417,7 +13501,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>ayush mhatre</t>
+          <t>ben duckett</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -13444,7 +13528,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Rahul Tripathi</t>
+          <t>Abhishek Porel</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -13459,7 +13543,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>rahul tripathi</t>
+          <t>abhishek porel</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -13486,7 +13570,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Dre Pretorius</t>
+          <t>Ayush Mhatre</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -13501,7 +13585,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>dre pretorius</t>
+          <t>ayush mhatre</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -13528,7 +13612,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Matthew Breetzke</t>
+          <t>Rahul Tripathi</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -13543,7 +13627,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>matthew breetzke</t>
+          <t>rahul tripathi</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -13570,7 +13654,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Anuj Rawat</t>
+          <t>Dre Pretorius</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -13585,7 +13669,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>anuj rawat</t>
+          <t>dre pretorius</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -13612,7 +13696,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Matthew Breetzke</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -13622,12 +13706,12 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>marco jansen</t>
+          <t>matthew breetzke</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -13654,7 +13738,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Wanindu Hasaranga</t>
+          <t>Anuj Rawat</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -13664,12 +13748,12 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>wanindu hasaranga</t>
+          <t>anuj rawat</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -13696,7 +13780,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Harpreet Brar</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -13706,12 +13790,12 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>harpreet brar</t>
+          <t>marco jansen</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -13738,7 +13822,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Mayank Yadav</t>
+          <t>Wanindu Hasaranga</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -13748,12 +13832,12 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>mayank yadav</t>
+          <t>wanindu hasaranga</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -13780,7 +13864,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Digvesh Rathi</t>
+          <t>Harpreet Brar</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -13795,7 +13879,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>digvesh rathi</t>
+          <t>harpreet brar</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -13822,42 +13906,126 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
+          <t>Mayank Yadav</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>PRATIK11</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>BOWL</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>mayank yadav</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>no_stats_yet</t>
+        </is>
+      </c>
+      <c r="F120" t="n">
+        <v>0</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Digvesh Rathi</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>PRATIK11</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>BOWL</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>digvesh rathi</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>no_stats_yet</t>
+        </is>
+      </c>
+      <c r="F121" t="n">
+        <v>0</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
           <t>Kuldeep Yadav</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr">
+      <c r="B122" t="inlineStr">
         <is>
           <t>PRATIK11</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr">
+      <c r="C122" t="inlineStr">
         <is>
           <t>BOWL</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr">
+      <c r="D122" t="inlineStr">
         <is>
           <t>kuldeep yadav</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="F120" t="n">
-        <v>0</v>
-      </c>
-      <c r="G120" t="n">
-        <v>0</v>
-      </c>
-      <c r="H120" t="n">
-        <v>0</v>
-      </c>
-      <c r="I120" t="n">
-        <v>0</v>
-      </c>
-      <c r="J120" t="n">
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>no_stats_yet</t>
+        </is>
+      </c>
+      <c r="F122" t="n">
+        <v>0</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0</v>
+      </c>
+      <c r="J122" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13930,7 +14098,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Jitesh Sharma</t>
+          <t>jitesh sharma</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -13972,7 +14140,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Priyansh Arya</t>
+          <t>priyansh arya</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -14014,7 +14182,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Arshdeep Singh</t>
+          <t>arshdeep singh</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -14056,7 +14224,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Phil Salt</t>
+          <t>phil salt</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -14098,7 +14266,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ashutosh Sharma</t>
+          <t>ashutosh sharma</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -14140,7 +14308,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Akshat Raghuwanshi</t>
+          <t>akshat raghuwanshi</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">

--- a/IPL_Fantasy_Points.xlsx
+++ b/IPL_Fantasy_Points.xlsx
@@ -1222,23 +1222,23 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -1516,23 +1516,23 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>possible_mismatch:92.3076923076923</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -2356,23 +2356,23 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="F46" t="n">
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="47">
@@ -3112,23 +3112,23 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="F64" t="n">
         <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J64" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="65">
@@ -3490,7 +3490,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>possible_mismatch:89.65517241379311</t>
         </is>
       </c>
       <c r="F73" t="n">
@@ -3532,23 +3532,23 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="I74" t="n">
         <v>0</v>
       </c>
       <c r="J74" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
     </row>
     <row r="75">
@@ -3574,23 +3574,23 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>possible_mismatch:75.0</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I75" t="n">
         <v>0</v>
       </c>
       <c r="J75" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="76">
@@ -3658,23 +3658,23 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I77" t="n">
         <v>0</v>
       </c>
       <c r="J77" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>possible_mismatch:92.85714285714286</t>
         </is>
       </c>
       <c r="F83" t="n">
@@ -3994,7 +3994,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>possible_mismatch:76.19047619047619</t>
         </is>
       </c>
       <c r="F85" t="n">
@@ -4162,11 +4162,11 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -4288,23 +4288,23 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
       </c>
       <c r="H92" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I92" t="n">
         <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="93">
@@ -4330,23 +4330,23 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
       </c>
       <c r="H93" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="I93" t="n">
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
     </row>
     <row r="94">
@@ -4666,23 +4666,23 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="F101" t="n">
         <v>0</v>
       </c>
       <c r="G101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H101" t="n">
         <v>0</v>
       </c>
       <c r="I101" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J101" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="102">
@@ -5842,23 +5842,23 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
       </c>
       <c r="H129" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I129" t="n">
         <v>0</v>
       </c>
       <c r="J129" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="130">
@@ -5884,7 +5884,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>possible_mismatch:78.57142857142857</t>
+          <t>possible_mismatch:81.4814814814815</t>
         </is>
       </c>
       <c r="F130" t="n">
@@ -5968,23 +5968,23 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
       </c>
       <c r="H132" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I132" t="n">
         <v>0</v>
       </c>
       <c r="J132" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="133">
@@ -6136,23 +6136,23 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="F136" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H136" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I136" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J136" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
     </row>
     <row r="137">
@@ -6976,23 +6976,23 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="F156" t="n">
         <v>0</v>
       </c>
       <c r="G156" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H156" t="n">
         <v>0</v>
       </c>
       <c r="I156" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J156" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="157">
@@ -7606,23 +7606,23 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="F171" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H171" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I171" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J171" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="172">
@@ -8002,7 +8002,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>283</v>
+        <v>333</v>
       </c>
     </row>
     <row r="3">
@@ -8015,7 +8015,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>212</v>
+        <v>272</v>
       </c>
     </row>
     <row r="4">
@@ -8028,7 +8028,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>208</v>
+        <v>248</v>
       </c>
     </row>
     <row r="5">
@@ -8037,11 +8037,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>179</v>
+        <v>207</v>
       </c>
     </row>
     <row r="6">
@@ -8050,11 +8050,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>161</v>
+        <v>179</v>
       </c>
     </row>
     <row r="7">
@@ -8063,11 +8063,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BABA11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>144</v>
+        <v>168</v>
       </c>
     </row>
     <row r="8">
@@ -8076,11 +8076,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>BABA11</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>92</v>
+        <v>164</v>
       </c>
     </row>
     <row r="9">
@@ -8093,7 +8093,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>84</v>
+        <v>113</v>
       </c>
     </row>
     <row r="10">
@@ -8102,11 +8102,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NIRAV11</t>
+          <t>DIPESH11</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11">
@@ -8115,11 +8115,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DIPESH11</t>
+          <t>NIRAV11</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>39</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -8133,7 +8133,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C57"/>
+  <dimension ref="A1:C78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8234,7 +8234,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>bhuvneshwar kumar</t>
+          <t>ashok sharma</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -8247,50 +8247,50 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>brijesh sharma</t>
+          <t>b sai sudharshan</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>cameron green</t>
+          <t>bhuvneshwar kumar</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>david payne</t>
+          <t>brijesh sharma</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>devdutt padikkal</t>
+          <t>cameron green</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
@@ -8299,11 +8299,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>dhruv chand jurel</t>
+          <t>cooper connolly</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>72</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -8312,50 +8312,50 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>finn allen</t>
+          <t>david payne</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>hardik pandya</t>
+          <t>devdutt padikkal</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>harsh dubey</t>
+          <t>dhruv chand jurel</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>heinrich klaasen</t>
+          <t>finn allen</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -8364,11 +8364,11 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ishan kishan</t>
+          <t>glenn phillips</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>80</v>
+        <v>25</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -8377,115 +8377,115 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>jacob duffy</t>
+          <t>hardik pandya</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>jamie overton</t>
+          <t>harsh dubey</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>jaydev unadkat</t>
+          <t>heinrich klaasen</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>jofra archer</t>
+          <t>ishan kishan</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="C22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>kartik sharma</t>
+          <t>jacob duffy</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>kartik tyagi</t>
+          <t>jamie overton</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>matt henry</t>
+          <t>jaydev unadkat</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>matt short</t>
+          <t>jofra archer</t>
         </is>
       </c>
       <c r="B26" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" t="n">
         <v>2</v>
-      </c>
-      <c r="C26" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>naman dhir</t>
+          <t>jos buttler</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
@@ -8494,24 +8494,24 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>nandre burger</t>
+          <t>kagiso rabada</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>nitish kumar reddy</t>
+          <t>kartik sharma</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
@@ -8520,37 +8520,37 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>noor ahmad</t>
+          <t>kartik tyagi</t>
         </is>
       </c>
       <c r="B30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" t="n">
         <v>1</v>
-      </c>
-      <c r="C30" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>philip salt</t>
+          <t>marco jansen</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>rajat patidar</t>
+          <t>matt henry</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
@@ -8559,11 +8559,11 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ramandeep singh</t>
+          <t>matt short</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C33" t="n">
         <v>0</v>
@@ -8572,20 +8572,20 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ravi bishnoi</t>
+          <t>naman dhir</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ravindra jadeja</t>
+          <t>nandre burger</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -8598,11 +8598,11 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>rinku singh</t>
+          <t>nehal wadhera</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
@@ -8611,11 +8611,11 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>riyan parag</t>
+          <t>nitish kumar reddy</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="C37" t="n">
         <v>0</v>
@@ -8624,11 +8624,11 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>rohit sharma</t>
+          <t>noor ahmad</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>78</v>
+        <v>1</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -8637,24 +8637,24 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>romario shepherd</t>
+          <t>philip salt</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ruturaj gaikwad</t>
+          <t>prabhsimran singh</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="C40" t="n">
         <v>0</v>
@@ -8663,24 +8663,24 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ryan rickelton</t>
+          <t>prasidh krishna</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>salil arora</t>
+          <t>priyansh arya</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
@@ -8689,24 +8689,24 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>sandeep sharma</t>
+          <t>rahul tewatia</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>sanju samson</t>
+          <t>rajat patidar</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
@@ -8715,11 +8715,11 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>sarfaraz khan</t>
+          <t>ramandeep singh</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="C45" t="n">
         <v>0</v>
@@ -8728,50 +8728,50 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>shardul thakur</t>
+          <t>rashid khan</t>
         </is>
       </c>
       <c r="B46" t="n">
         <v>0</v>
       </c>
       <c r="C46" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>shivam dube</t>
+          <t>ravi bishnoi</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>sunil narine</t>
+          <t>ravindra jadeja</t>
         </is>
       </c>
       <c r="B48" t="n">
         <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>suryakumar yadav</t>
+          <t>rinku singh</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="C49" t="n">
         <v>0</v>
@@ -8780,24 +8780,24 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>suyash sharma</t>
+          <t>riyan parag</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="C50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>tilak varma</t>
+          <t>rohit sharma</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>20</v>
+        <v>78</v>
       </c>
       <c r="C51" t="n">
         <v>0</v>
@@ -8806,24 +8806,24 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>tim david</t>
+          <t>romario shepherd</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="C52" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>travis head</t>
+          <t>ruturaj gaikwad</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C53" t="n">
         <v>0</v>
@@ -8832,24 +8832,24 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>vaibhav arora</t>
+          <t>ryan rickelton</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="C54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>vaibhav suryavanshi</t>
+          <t>salil arora</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="C55" t="n">
         <v>0</v>
@@ -8858,27 +8858,300 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>virat kohli</t>
+          <t>sandeep sharma</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="C56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
+          <t>sanju samson</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>6</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>sarfaraz khan</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>17</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>shahrukh khan</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>4</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>shardul thakur</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>0</v>
+      </c>
+      <c r="C60" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>shashank singh</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>4</v>
+      </c>
+      <c r="C61" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>shivam dube</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>6</v>
+      </c>
+      <c r="C62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>shreyas iyer</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>18</v>
+      </c>
+      <c r="C63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>shubman gill</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>39</v>
+      </c>
+      <c r="C64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>sunil narine</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>0</v>
+      </c>
+      <c r="C65" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>suryakumar yadav</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>16</v>
+      </c>
+      <c r="C66" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>suyash sharma</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>0</v>
+      </c>
+      <c r="C67" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>tilak varma</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>20</v>
+      </c>
+      <c r="C68" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>tim david</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>16</v>
+      </c>
+      <c r="C69" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>travis head</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>11</v>
+      </c>
+      <c r="C70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>vaibhav arora</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>0</v>
+      </c>
+      <c r="C71" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>vaibhav suryavanshi</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>52</v>
+      </c>
+      <c r="C72" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>vijaykumar vyshak</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>0</v>
+      </c>
+      <c r="C73" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>virat kohli</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>69</v>
+      </c>
+      <c r="C74" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>washington sundar</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>18</v>
+      </c>
+      <c r="C75" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>xavier bartlett</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>11</v>
+      </c>
+      <c r="C76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
           <t>yashasvi jaiswal</t>
         </is>
       </c>
-      <c r="B57" t="n">
+      <c r="B77" t="n">
         <v>38</v>
       </c>
-      <c r="C57" t="n">
-        <v>0</v>
+      <c r="C77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>yuzvendra chahal</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>0</v>
+      </c>
+      <c r="C78" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -8892,7 +9165,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J122"/>
+  <dimension ref="A1:J103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9370,7 +9643,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Shubman Gill gt</t>
+          <t>karun nair dc</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -9385,7 +9658,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>shubman gill</t>
+          <t>karun nair</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -9412,7 +9685,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>karun nair dc</t>
+          <t>jacob bethel rcb</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -9422,12 +9695,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>karun nair</t>
+          <t>jacob bethel</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -9454,7 +9727,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>jacob bethel rcb</t>
+          <t>vipraj nigam dc</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -9469,7 +9742,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>jacob bethel</t>
+          <t>vipraj nigam</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -9496,7 +9769,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>vipraj nigam dc</t>
+          <t>Jason Holder gt</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -9511,7 +9784,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>vipraj nigam</t>
+          <t>jason holder</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -9538,7 +9811,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Rahul Tewatia gt</t>
+          <t>kamindu mendis srh</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -9548,12 +9821,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>rahul tewatia</t>
+          <t>kamindu mendis</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -9580,7 +9853,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Jason Holder gt</t>
+          <t>tushar deshpande rr</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -9590,12 +9863,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>jason holder</t>
+          <t>tushar deshpande</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -9622,7 +9895,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>kamindu mendis srh</t>
+          <t>Khaleel Ahmed csk</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -9637,7 +9910,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>kamindu mendis</t>
+          <t>khaleel ahmed</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -9664,7 +9937,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>tushar deshpande rr</t>
+          <t>am ghazanfar mi</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -9679,7 +9952,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>tushar deshpande</t>
+          <t>am ghazanfar</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -9706,7 +9979,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Khaleel Ahmed csk</t>
+          <t>Kuldeep sen rr</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -9721,7 +9994,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>khaleel ahmed</t>
+          <t>kuldeep sen</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -9748,22 +10021,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>am ghazanfar mi</t>
+          <t>Quinton de Kock</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MEET11</t>
+          <t>VATSAL11</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>am ghazanfar</t>
+          <t>quinton de kock</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9790,22 +10063,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Kuldeep sen rr</t>
+          <t>Tom Banton</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MEET11</t>
+          <t>VATSAL11</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>kuldeep sen</t>
+          <t>tom banton</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9832,7 +10105,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Quinton de Kock</t>
+          <t>Tim Siefert</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -9847,7 +10120,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>quinton de kock</t>
+          <t>tim siefert</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9874,7 +10147,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Tom Banton</t>
+          <t>Marcus Stoinis</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -9884,12 +10157,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>tom banton</t>
+          <t>marcus stoinis</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -9916,7 +10189,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Tim Siefert</t>
+          <t>Lockie Ferguson</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -9926,12 +10199,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>tim siefert</t>
+          <t>lockie ferguson</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -9958,7 +10231,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Glen Philips</t>
+          <t>Adam Milne</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -9968,12 +10241,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>glen philips</t>
+          <t>adam milne</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -10000,7 +10273,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Marcus Stoinis</t>
+          <t>Corbin Bosch</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -10010,12 +10283,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>marcus stoinis</t>
+          <t>corbin bosch</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -10042,7 +10315,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Prasidh Krishna</t>
+          <t>Deepak Chahar</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -10057,7 +10330,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>prasidh krishna</t>
+          <t>deepak chahar</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -10084,7 +10357,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Lockie Ferguson</t>
+          <t>Rahul Chahar</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -10099,7 +10372,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>lockie ferguson</t>
+          <t>rahul chahar</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -10126,22 +10399,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Adam Milne</t>
+          <t>Jos Inglis</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>VATSAL11</t>
+          <t>BABA11</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>adam milne</t>
+          <t>jos inglis</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -10168,22 +10441,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Corbin Bosch</t>
+          <t>David Miller</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>VATSAL11</t>
+          <t>BABA11</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>corbin bosch</t>
+          <t>david miller</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -10210,22 +10483,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Deepak Chahar</t>
+          <t>Ayush Badoni</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>VATSAL11</t>
+          <t>BABA11</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>deepak chahar</t>
+          <t>ayush badoni</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -10252,22 +10525,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Rahul Chahar</t>
+          <t>Prithvi Shaw</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>VATSAL11</t>
+          <t>BABA11</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>rahul chahar</t>
+          <t>prithvi shaw</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -10294,7 +10567,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Jos Inglis</t>
+          <t>Rowman Powell</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -10309,7 +10582,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>jos inglis</t>
+          <t>rowman powell</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -10336,7 +10609,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>David Miller</t>
+          <t>liam livingston</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -10346,12 +10619,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>david miller</t>
+          <t>liam livingston</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -10378,7 +10651,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Ayush Badoni</t>
+          <t>rachin ravindra</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -10388,12 +10661,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ayush badoni</t>
+          <t>rachin ravindra</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -10420,7 +10693,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Prithvi Shaw</t>
+          <t>sherfane rutherford</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -10430,12 +10703,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>prithvi shaw</t>
+          <t>sherfane rutherford</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -10462,7 +10735,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Rowman Powell</t>
+          <t>Varun Chakravarthy</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -10472,12 +10745,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>rowman powell</t>
+          <t>varun chakravarthy</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -10504,7 +10777,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Zeeshan Ansari</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -10514,12 +10787,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>rashid khan</t>
+          <t>zeeshan ansari</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -10546,7 +10819,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>liam livingston</t>
+          <t>Mitchell Starc</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -10556,12 +10829,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>liam livingston</t>
+          <t>mitchell starc</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -10588,7 +10861,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>rachin ravindra</t>
+          <t>Mitchel Santner</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -10598,12 +10871,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>rachin ravindra</t>
+          <t>mitchel santner</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -10630,22 +10903,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>sherfane rutherford</t>
+          <t>Mitchel Owen</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BABA11</t>
+          <t>DIPESH11</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>sherfane rutherford</t>
+          <t>mitchel owen</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -10672,22 +10945,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Varun Chakravarthy</t>
+          <t>Tristan Stubbs</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BABA11</t>
+          <t>DIPESH11</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>varun chakravarthy</t>
+          <t>tristan stubbs</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -10714,22 +10987,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Zeeshan Ansari</t>
+          <t>Pat Cummins</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>BABA11</t>
+          <t>DIPESH11</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>zeeshan ansari</t>
+          <t>pat cummins</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -10756,22 +11029,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Mitchell Starc</t>
+          <t>Aiden Markram</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BABA11</t>
+          <t>DIPESH11</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>mitchell starc</t>
+          <t>aiden markram</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -10798,12 +11071,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Mitchel Santner</t>
+          <t>Mukesh Kumar</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>BABA11</t>
+          <t>DIPESH11</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -10813,7 +11086,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>mitchel santner</t>
+          <t>mukesh kumar</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -10840,7 +11113,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sai Sudharsan</t>
+          <t>Aqib Nabi Dar</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -10850,12 +11123,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>sai sudharsan</t>
+          <t>aqib nabi dar</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -10882,7 +11155,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Prabhsimran Singh</t>
+          <t>Rasik Dar Salam</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -10892,12 +11165,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>prabhsimran singh</t>
+          <t>rasik dar salam</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -10924,12 +11197,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Mitchel Owen</t>
+          <t>KL Rahul dc</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>DIPESH11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -10939,7 +11212,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>mitchel owen</t>
+          <t>kl rahul</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -10966,12 +11239,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Nehal Wadhera</t>
+          <t>Urvil Patel</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>DIPESH11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -10981,7 +11254,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>nehal wadhera</t>
+          <t>urvil patel</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -11008,12 +11281,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Tristan Stubbs</t>
+          <t>Arshin Kulkarni</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>DIPESH11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -11023,7 +11296,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>tristan stubbs</t>
+          <t>arshin kulkarni</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -11050,12 +11323,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Pat Cummins</t>
+          <t>Nishant Sindhu gt</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>DIPESH11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -11065,7 +11338,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>pat cummins</t>
+          <t>nishant sindhu</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -11092,12 +11365,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Aiden Markram</t>
+          <t>Jayant Yadav gt</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>DIPESH11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -11107,7 +11380,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>aiden markram</t>
+          <t>jayant yadav</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -11134,12 +11407,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Cooper Conoly</t>
+          <t>Ajay Mandal dc</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>DIPESH11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -11149,7 +11422,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>cooper conoly</t>
+          <t>ajay mandal</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -11176,22 +11449,22 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Avesh Khan</t>
+          <t>Will Jacks mi</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>DIPESH11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>avesh khan</t>
+          <t>will jacks</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -11218,12 +11491,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Mukesh Kumar</t>
+          <t>Josh Hazelwood rcb</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>DIPESH11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -11233,7 +11506,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>mukesh kumar</t>
+          <t>josh hazelwood</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -11260,12 +11533,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Aqib Nabi Dar</t>
+          <t>Kyle Jamieson dc</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>DIPESH11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -11275,7 +11548,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>aqib nabi dar</t>
+          <t>kyle jamieson</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -11302,12 +11575,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Rasik Dar Salam</t>
+          <t>Matheesha Pathirana kkr</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>DIPESH11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -11317,7 +11590,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>rasik dar salam</t>
+          <t>matheesha pathirana</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -11344,12 +11617,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Xavier Bartlett</t>
+          <t>M Siddharth lsg</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>DIPESH11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -11359,7 +11632,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>xavier bartlett</t>
+          <t>m siddharth</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -11386,7 +11659,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>KL Rahul dc</t>
+          <t>Ben Dwarshuis pbks</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -11396,12 +11669,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>kl rahul</t>
+          <t>ben dwarshuis</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -11428,12 +11701,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Shreyas Iyer PBKS</t>
+          <t>Mitchel March</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -11443,7 +11716,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>shreyas iyer</t>
+          <t>mitchel march</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -11470,12 +11743,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Jos Buttler gt</t>
+          <t>Shimron Hetmyer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -11485,7 +11758,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>jos buttler</t>
+          <t>shimron hetmyer</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -11512,12 +11785,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Urvil Patel</t>
+          <t>Manish Pandey</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -11527,7 +11800,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>urvil patel</t>
+          <t>manish pandey</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -11554,12 +11827,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Arshin Kulkarni</t>
+          <t>Pathum Nissanka</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -11569,7 +11842,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>arshin kulkarni</t>
+          <t>pathum nissanka</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -11596,12 +11869,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Nishant Sindhu gt</t>
+          <t>Donovan Ferreira rr</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -11611,7 +11884,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>nishant sindhu</t>
+          <t>donovan ferreira</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -11638,22 +11911,22 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Jayant Yadav gt</t>
+          <t>Harshal Patel</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>jayant yadav</t>
+          <t>harshal patel</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -11680,22 +11953,22 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Ajay Mandal dc</t>
+          <t>Lungi Ngidi</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>ajay mandal</t>
+          <t>lungi ngidi</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -11722,22 +11995,22 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Will Jacks mi</t>
+          <t>Vyshak Vijaykumar PBKS</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>will jacks</t>
+          <t>vyshak vijaykumar</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -11764,12 +12037,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Kagiso Rabada gt</t>
+          <t>Mukesh Choudhary csk</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -11779,7 +12052,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>kagiso rabada</t>
+          <t>mukesh choudhary</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -11806,12 +12079,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Josh Hazelwood rcb</t>
+          <t>Gurjapneet Singh</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -11821,7 +12094,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>josh hazelwood</t>
+          <t>gurjapneet singh</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -11848,12 +12121,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Kyle Jamieson dc</t>
+          <t>Arjun Tendulkar</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -11863,7 +12136,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>kyle jamieson</t>
+          <t>arjun tendulkar</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -11890,12 +12163,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Matheesha Pathirana kkr</t>
+          <t>Kwena Maphaka</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -11905,7 +12178,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>matheesha pathirana</t>
+          <t>kwena maphaka</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -11932,12 +12205,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>M Siddharth lsg</t>
+          <t>Anrich Nortje</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -11947,7 +12220,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>m siddharth</t>
+          <t>anrich nortje</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -11974,22 +12247,22 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Ben Dwarshuis pbks</t>
+          <t>Ramkrishna Ghosh</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>ben dwarshuis</t>
+          <t>ramkrishna ghosh</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -12016,12 +12289,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Mitchel March</t>
+          <t>Venkatesh Iyer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -12031,7 +12304,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>mitchel march</t>
+          <t>venkatesh iyer</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -12058,12 +12331,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Shimron Hetmyer</t>
+          <t>Sameer Rizvi</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -12073,7 +12346,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>shimron hetmyer</t>
+          <t>sameer rizvi</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -12100,12 +12373,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Manish Pandey</t>
+          <t>Prashant Veer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -12115,7 +12388,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>manish pandey</t>
+          <t>prashant veer</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -12142,22 +12415,22 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Pathum Nissanka</t>
+          <t>Axar Patel</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>pathum nissanka</t>
+          <t>axar patel</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -12184,12 +12457,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Donovan Ferreira rr</t>
+          <t>Azmatullah Omarzai</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -12199,7 +12472,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>donovan ferreira</t>
+          <t>azmatullah omarzai</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -12226,12 +12499,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Harshal Patel</t>
+          <t>Jasprit Bumrah</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -12241,7 +12514,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>harshal patel</t>
+          <t>jasprit bumrah</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -12268,12 +12541,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Lungi Ngidi</t>
+          <t>Mohammed Shami</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -12283,7 +12556,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>lungi ngidi</t>
+          <t>mohammed shami</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -12310,12 +12583,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Vyshak Vijaykumar PBKS</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -12325,7 +12598,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>vyshak vijaykumar</t>
+          <t>trent boult</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -12352,22 +12625,22 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Mukesh Choudhary csk</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>mukesh choudhary</t>
+          <t>nicholas pooran</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -12394,22 +12667,22 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Gurjapneet Singh</t>
+          <t>Nitish Rana</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>gurjapneet singh</t>
+          <t>nitish rana</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -12436,22 +12709,22 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Arjun Tendulkar</t>
+          <t>Himmat Singh</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>arjun tendulkar</t>
+          <t>himmat singh</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -12478,22 +12751,22 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Kwena Maphaka</t>
+          <t>Suryansh Shegde</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>kwena maphaka</t>
+          <t>suryansh shegde</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -12520,22 +12793,22 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Anrich Nortje</t>
+          <t>Tejasvi Singh</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>anrich nortje</t>
+          <t>tejasvi singh</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -12562,22 +12835,22 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Ramkrishna Ghosh</t>
+          <t>Krunal Pandya</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>ramkrishna ghosh</t>
+          <t>krunal pandya</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -12604,22 +12877,22 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Venkatesh Iyer</t>
+          <t>T Natarjan</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>venkatesh iyer</t>
+          <t>t natarjan</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -12646,22 +12919,22 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Shahrukh Khan</t>
+          <t>Sai Kishor</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>shahrukh khan</t>
+          <t>sai kishor</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -12688,22 +12961,22 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Shashank Singh</t>
+          <t>Akash Deep</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>shashank singh</t>
+          <t>akash deep</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -12730,12 +13003,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Sameer Rizvi</t>
+          <t>Ben Duckett</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -12745,7 +13018,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>sameer rizvi</t>
+          <t>ben duckett</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -12772,12 +13045,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Prashant Veer</t>
+          <t>Abhishek Porel</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -12787,7 +13060,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>prashant veer</t>
+          <t>abhishek porel</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -12814,22 +13087,22 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Washington SUndar</t>
+          <t>Ayush Mhatre</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>washington sundar</t>
+          <t>ayush mhatre</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -12856,22 +13129,22 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Axar Patel</t>
+          <t>Rahul Tripathi</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>axar patel</t>
+          <t>rahul tripathi</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -12898,22 +13171,22 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Azmatullah Omarzai</t>
+          <t>Dre Pretorius</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>azmatullah omarzai</t>
+          <t>dre pretorius</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -12940,22 +13213,22 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Jasprit Bumrah</t>
+          <t>Matthew Breetzke</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>jasprit bumrah</t>
+          <t>matthew breetzke</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -12982,22 +13255,22 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Mohammed Shami</t>
+          <t>Anuj Rawat</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>mohammed shami</t>
+          <t>anuj rawat</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -13024,22 +13297,22 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Wanindu Hasaranga</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>trent boult</t>
+          <t>wanindu hasaranga</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -13066,22 +13339,22 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>Harpreet Brar</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>nicholas pooran</t>
+          <t>harpreet brar</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -13108,22 +13381,22 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Nitish Rana</t>
+          <t>Mayank Yadav</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>nitish rana</t>
+          <t>mayank yadav</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -13150,22 +13423,22 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Himmat Singh</t>
+          <t>Digvesh Rathi</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>himmat singh</t>
+          <t>digvesh rathi</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -13192,22 +13465,22 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Suryansh Shegde</t>
+          <t>Kuldeep Yadav</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>suryansh shegde</t>
+          <t>kuldeep yadav</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -13228,804 +13501,6 @@
         <v>0</v>
       </c>
       <c r="J103" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Tejasvi Singh</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>AMEY11</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>BAT</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>tejasvi singh</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="F104" t="n">
-        <v>0</v>
-      </c>
-      <c r="G104" t="n">
-        <v>0</v>
-      </c>
-      <c r="H104" t="n">
-        <v>0</v>
-      </c>
-      <c r="I104" t="n">
-        <v>0</v>
-      </c>
-      <c r="J104" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Krunal Pandya</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>AMEY11</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>AR</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>krunal pandya</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="F105" t="n">
-        <v>0</v>
-      </c>
-      <c r="G105" t="n">
-        <v>0</v>
-      </c>
-      <c r="H105" t="n">
-        <v>0</v>
-      </c>
-      <c r="I105" t="n">
-        <v>0</v>
-      </c>
-      <c r="J105" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>T Natarjan</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>AMEY11</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>AR</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>t natarjan</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="F106" t="n">
-        <v>0</v>
-      </c>
-      <c r="G106" t="n">
-        <v>0</v>
-      </c>
-      <c r="H106" t="n">
-        <v>0</v>
-      </c>
-      <c r="I106" t="n">
-        <v>0</v>
-      </c>
-      <c r="J106" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Yuzvendra Chahal</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>AMEY11</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>BOWL</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>yuzvendra chahal</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="F107" t="n">
-        <v>0</v>
-      </c>
-      <c r="G107" t="n">
-        <v>0</v>
-      </c>
-      <c r="H107" t="n">
-        <v>0</v>
-      </c>
-      <c r="I107" t="n">
-        <v>0</v>
-      </c>
-      <c r="J107" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Sai Kishor</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>AMEY11</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>BOWL</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>sai kishor</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="F108" t="n">
-        <v>0</v>
-      </c>
-      <c r="G108" t="n">
-        <v>0</v>
-      </c>
-      <c r="H108" t="n">
-        <v>0</v>
-      </c>
-      <c r="I108" t="n">
-        <v>0</v>
-      </c>
-      <c r="J108" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Akash Deep</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>AMEY11</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>BOWL</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>akash deep</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="F109" t="n">
-        <v>0</v>
-      </c>
-      <c r="G109" t="n">
-        <v>0</v>
-      </c>
-      <c r="H109" t="n">
-        <v>0</v>
-      </c>
-      <c r="I109" t="n">
-        <v>0</v>
-      </c>
-      <c r="J109" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Ben Duckett</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>BAT</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>ben duckett</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="F110" t="n">
-        <v>0</v>
-      </c>
-      <c r="G110" t="n">
-        <v>0</v>
-      </c>
-      <c r="H110" t="n">
-        <v>0</v>
-      </c>
-      <c r="I110" t="n">
-        <v>0</v>
-      </c>
-      <c r="J110" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Abhishek Porel</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>BAT</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>abhishek porel</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="F111" t="n">
-        <v>0</v>
-      </c>
-      <c r="G111" t="n">
-        <v>0</v>
-      </c>
-      <c r="H111" t="n">
-        <v>0</v>
-      </c>
-      <c r="I111" t="n">
-        <v>0</v>
-      </c>
-      <c r="J111" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Ayush Mhatre</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>BAT</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>ayush mhatre</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="F112" t="n">
-        <v>0</v>
-      </c>
-      <c r="G112" t="n">
-        <v>0</v>
-      </c>
-      <c r="H112" t="n">
-        <v>0</v>
-      </c>
-      <c r="I112" t="n">
-        <v>0</v>
-      </c>
-      <c r="J112" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Rahul Tripathi</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>BAT</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>rahul tripathi</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="F113" t="n">
-        <v>0</v>
-      </c>
-      <c r="G113" t="n">
-        <v>0</v>
-      </c>
-      <c r="H113" t="n">
-        <v>0</v>
-      </c>
-      <c r="I113" t="n">
-        <v>0</v>
-      </c>
-      <c r="J113" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Dre Pretorius</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>BAT</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>dre pretorius</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="F114" t="n">
-        <v>0</v>
-      </c>
-      <c r="G114" t="n">
-        <v>0</v>
-      </c>
-      <c r="H114" t="n">
-        <v>0</v>
-      </c>
-      <c r="I114" t="n">
-        <v>0</v>
-      </c>
-      <c r="J114" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Matthew Breetzke</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>BAT</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>matthew breetzke</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="F115" t="n">
-        <v>0</v>
-      </c>
-      <c r="G115" t="n">
-        <v>0</v>
-      </c>
-      <c r="H115" t="n">
-        <v>0</v>
-      </c>
-      <c r="I115" t="n">
-        <v>0</v>
-      </c>
-      <c r="J115" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Anuj Rawat</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>BAT</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>anuj rawat</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="F116" t="n">
-        <v>0</v>
-      </c>
-      <c r="G116" t="n">
-        <v>0</v>
-      </c>
-      <c r="H116" t="n">
-        <v>0</v>
-      </c>
-      <c r="I116" t="n">
-        <v>0</v>
-      </c>
-      <c r="J116" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Marco Jansen</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>AR</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>marco jansen</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="F117" t="n">
-        <v>0</v>
-      </c>
-      <c r="G117" t="n">
-        <v>0</v>
-      </c>
-      <c r="H117" t="n">
-        <v>0</v>
-      </c>
-      <c r="I117" t="n">
-        <v>0</v>
-      </c>
-      <c r="J117" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Wanindu Hasaranga</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>AR</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>wanindu hasaranga</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="F118" t="n">
-        <v>0</v>
-      </c>
-      <c r="G118" t="n">
-        <v>0</v>
-      </c>
-      <c r="H118" t="n">
-        <v>0</v>
-      </c>
-      <c r="I118" t="n">
-        <v>0</v>
-      </c>
-      <c r="J118" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Harpreet Brar</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>BOWL</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>harpreet brar</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="F119" t="n">
-        <v>0</v>
-      </c>
-      <c r="G119" t="n">
-        <v>0</v>
-      </c>
-      <c r="H119" t="n">
-        <v>0</v>
-      </c>
-      <c r="I119" t="n">
-        <v>0</v>
-      </c>
-      <c r="J119" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Mayank Yadav</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>BOWL</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>mayank yadav</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="F120" t="n">
-        <v>0</v>
-      </c>
-      <c r="G120" t="n">
-        <v>0</v>
-      </c>
-      <c r="H120" t="n">
-        <v>0</v>
-      </c>
-      <c r="I120" t="n">
-        <v>0</v>
-      </c>
-      <c r="J120" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Digvesh Rathi</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>BOWL</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>digvesh rathi</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="F121" t="n">
-        <v>0</v>
-      </c>
-      <c r="G121" t="n">
-        <v>0</v>
-      </c>
-      <c r="H121" t="n">
-        <v>0</v>
-      </c>
-      <c r="I121" t="n">
-        <v>0</v>
-      </c>
-      <c r="J121" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Kuldeep Yadav</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>BOWL</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>kuldeep yadav</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="F122" t="n">
-        <v>0</v>
-      </c>
-      <c r="G122" t="n">
-        <v>0</v>
-      </c>
-      <c r="H122" t="n">
-        <v>0</v>
-      </c>
-      <c r="I122" t="n">
-        <v>0</v>
-      </c>
-      <c r="J122" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14040,7 +13515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14140,12 +13615,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>priyansh arya</t>
+          <t>Glen Philips</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DIPESH11</t>
+          <t>VATSAL11</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -14155,12 +13630,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>priyansh arya</t>
+          <t>glen philips</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>possible_mismatch:75.0</t>
+          <t>possible_mismatch:92.3076923076923</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -14182,7 +13657,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>arshdeep singh</t>
+          <t>Sai Sudharsan</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -14192,17 +13667,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>arshdeep singh</t>
+          <t>sai sudharsan</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>possible_mismatch:75.86206896551724</t>
+          <t>possible_mismatch:89.65517241379311</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -14224,27 +13699,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>phil salt</t>
+          <t>Cooper Conoly</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>DIPESH11</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>phil salt</t>
+          <t>cooper conoly</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>possible_mismatch:90.0</t>
+          <t>possible_mismatch:92.85714285714286</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -14266,27 +13741,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ashutosh sharma</t>
+          <t>arshdeep singh</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>DIPESH11</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ashutosh sharma</t>
+          <t>arshdeep singh</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>possible_mismatch:78.57142857142857</t>
+          <t>possible_mismatch:75.86206896551724</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -14308,42 +13783,168 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Avesh Khan</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>DIPESH11</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>BOWL</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>avesh khan</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>possible_mismatch:76.19047619047619</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>phil salt</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>SKY11</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>BAT</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>phil salt</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>possible_mismatch:90.0</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ashutosh sharma</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>HARSH11</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>BAT</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>ashutosh sharma</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>possible_mismatch:81.4814814814815</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>akshat raghuwanshi</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>AMEY11</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>BAT</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>akshat raghuwanshi</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>possible_mismatch:78.94736842105263</t>
         </is>
       </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
         <v>0</v>
       </c>
     </row>

--- a/IPL_Fantasy_Points.xlsx
+++ b/IPL_Fantasy_Points.xlsx
@@ -3546,7 +3546,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sai Sudharsan</t>
+          <t>b sai sudharsan</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>possible_mismatch:89.65517241379311</t>
+          <t>possible_mismatch:96.7741935483871</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -5051,7 +5051,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>phil salt</t>
+          <t>philip salt</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -5064,31 +5064,31 @@
           <t>BAT</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
-      <c r="E108" t="inlineStr">
+      <c r="D108" t="inlineStr">
         <is>
           <t>philip salt</t>
         </is>
       </c>
+      <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
-          <t>possible_mismatch:90.0</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="G108" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H108" t="n">
         <v>0</v>
       </c>
       <c r="I108" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
       </c>
       <c r="K108" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="109">
@@ -5567,7 +5567,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Vyshak Vijaykumar PBKS</t>
+          <t>vijaykumar vyshak</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5580,31 +5580,31 @@
           <t>BOWL</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>bhuvneshwar kumar</t>
-        </is>
-      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>vijaykumar vyshak</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="G120" t="n">
         <v>0</v>
       </c>
       <c r="H120" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I120" t="n">
         <v>0</v>
       </c>
       <c r="J120" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="K120" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="121">
@@ -8220,11 +8220,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>207</v>
+        <v>247</v>
       </c>
     </row>
     <row r="6">
@@ -8233,11 +8233,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>179</v>
+        <v>207</v>
       </c>
     </row>
     <row r="7">
@@ -9582,7 +9582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K88"/>
+  <dimension ref="A1:K87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12053,7 +12053,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Vyshak Vijaykumar PBKS</t>
+          <t>Mukesh Choudhary csk</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -12069,7 +12069,7 @@
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>bhuvneshwar kumar</t>
+          <t>ayush mhatre</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -12096,7 +12096,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Mukesh Choudhary csk</t>
+          <t>Gurjapneet Singh</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -12112,7 +12112,7 @@
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>ayush mhatre</t>
+          <t>ramandeep singh</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -12139,7 +12139,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Gurjapneet Singh</t>
+          <t>Arjun Tendulkar</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -12155,7 +12155,7 @@
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>ramandeep singh</t>
+          <t>krunal pandya</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -12182,7 +12182,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Arjun Tendulkar</t>
+          <t>Kwena Maphaka</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -12225,7 +12225,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Kwena Maphaka</t>
+          <t>Anrich Nortje</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -12241,7 +12241,7 @@
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>krunal pandya</t>
+          <t>heinrich klaasen</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -12268,23 +12268,23 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Anrich Nortje</t>
+          <t>Ramkrishna Ghosh</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>heinrich klaasen</t>
+          <t>angkrish raghuvanshi</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -12311,7 +12311,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Ramkrishna Ghosh</t>
+          <t>Venkatesh Iyer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -12327,7 +12327,7 @@
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>angkrish raghuvanshi</t>
+          <t>shreyas iyer</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -12354,7 +12354,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Venkatesh Iyer</t>
+          <t>Sameer Rizvi</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -12370,7 +12370,7 @@
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>shreyas iyer</t>
+          <t>cameron green</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -12397,7 +12397,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sameer Rizvi</t>
+          <t>Prashant Veer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -12413,7 +12413,7 @@
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>cameron green</t>
+          <t>aniket verma</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -12440,7 +12440,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Prashant Veer</t>
+          <t>Axar Patel</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -12450,13 +12450,13 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>aniket verma</t>
+          <t>harshal patel</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -12483,7 +12483,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Axar Patel</t>
+          <t>Azmatullah Omarzai</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -12499,7 +12499,7 @@
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>harshal patel</t>
+          <t>mayank markande</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -12526,23 +12526,23 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Azmatullah Omarzai</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>mayank markande</t>
+          <t>heinrich klaasen</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -12569,7 +12569,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>Nitish Rana</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -12585,7 +12585,7 @@
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>heinrich klaasen</t>
+          <t>jitesh sharma</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -12612,7 +12612,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Nitish Rana</t>
+          <t>Himmat Singh</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -12628,7 +12628,7 @@
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>jitesh sharma</t>
+          <t>prabhsimran singh</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -12655,7 +12655,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Himmat Singh</t>
+          <t>Suryansh Shegde</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -12671,7 +12671,7 @@
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>prabhsimran singh</t>
+          <t>suyash sharma</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -12698,7 +12698,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Suryansh Shegde</t>
+          <t>Tejasvi Singh</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -12714,7 +12714,7 @@
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>suyash sharma</t>
+          <t>prabhsimran singh</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -12741,7 +12741,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Tejasvi Singh</t>
+          <t>T Natarjan</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -12751,13 +12751,13 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>prabhsimran singh</t>
+          <t>rajat patidar</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -12784,7 +12784,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>T Natarjan</t>
+          <t>Sai Kishor</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -12794,13 +12794,13 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>rajat patidar</t>
+          <t>ishan kishan</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -12827,7 +12827,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sai Kishor</t>
+          <t>Akash Deep</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -12843,7 +12843,7 @@
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>ishan kishan</t>
+          <t>arshdeep singh</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -12870,23 +12870,23 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Akash Deep</t>
+          <t>Ben Duckett</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>arshdeep singh</t>
+          <t>ryan rickelton</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -12913,7 +12913,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Ben Duckett</t>
+          <t>Abhishek Porel</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -12929,7 +12929,7 @@
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>ryan rickelton</t>
+          <t>abhishek sharma</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -12956,7 +12956,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Abhishek Porel</t>
+          <t>Rahul Tripathi</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -12972,7 +12972,7 @@
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>abhishek sharma</t>
+          <t>rahul tewatia</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -12999,7 +12999,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Rahul Tripathi</t>
+          <t>Dre Pretorius</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -13015,7 +13015,7 @@
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>rahul tewatia</t>
+          <t>nandre burger</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -13042,7 +13042,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Dre Pretorius</t>
+          <t>Matthew Breetzke</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -13058,7 +13058,7 @@
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>nandre burger</t>
+          <t>matt henry</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -13085,7 +13085,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Matthew Breetzke</t>
+          <t>Anuj Rawat</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -13101,7 +13101,7 @@
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>matt henry</t>
+          <t>rahul tewatia</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -13128,7 +13128,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Anuj Rawat</t>
+          <t>Wanindu Hasaranga</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -13138,13 +13138,13 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>rahul tewatia</t>
+          <t>sandeep sharma</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -13171,7 +13171,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Wanindu Hasaranga</t>
+          <t>Harpreet Brar</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -13181,13 +13181,13 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>sandeep sharma</t>
+          <t>jasprit bumrah</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -13214,7 +13214,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Harpreet Brar</t>
+          <t>Mayank Yadav</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -13230,7 +13230,7 @@
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>jasprit bumrah</t>
+          <t>mayank markande</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -13257,7 +13257,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Mayank Yadav</t>
+          <t>Digvesh Rathi</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -13273,7 +13273,7 @@
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>mayank markande</t>
+          <t>jitesh sharma</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -13300,7 +13300,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Digvesh Rathi</t>
+          <t>Kuldeep Yadav</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -13316,7 +13316,7 @@
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>jitesh sharma</t>
+          <t>suryakumar yadav</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -13337,49 +13337,6 @@
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Kuldeep Yadav</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>BOWL</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>suryakumar yadav</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="G88" t="n">
-        <v>0</v>
-      </c>
-      <c r="H88" t="n">
-        <v>0</v>
-      </c>
-      <c r="I88" t="n">
-        <v>0</v>
-      </c>
-      <c r="J88" t="n">
-        <v>0</v>
-      </c>
-      <c r="K88" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13394,7 +13351,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13457,7 +13414,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sai Sudharsan</t>
+          <t>b sai sudharsan</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -13478,7 +13435,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>possible_mismatch:89.65517241379311</t>
+          <t>possible_mismatch:96.7741935483871</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -13543,12 +13500,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>phil salt</t>
+          <t>ashutosh sharma</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -13559,12 +13516,12 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>philip salt</t>
+          <t>ashok sharma</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>possible_mismatch:90.0</t>
+          <t>possible_mismatch:81.4814814814815</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -13586,7 +13543,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ashutosh sharma</t>
+          <t>Mohammed Shami</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -13596,18 +13553,18 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ashok sharma</t>
+          <t>mohammed siraj</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>possible_mismatch:81.4814814814815</t>
+          <t>possible_mismatch:78.57142857142857</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -13629,28 +13586,28 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Mohammed Shami</t>
+          <t>akshat raghuwanshi</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>mohammed siraj</t>
+          <t>angkrish raghuvanshi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>possible_mismatch:78.57142857142857</t>
+          <t>possible_mismatch:78.94736842105263</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -13666,49 +13623,6 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>akshat raghuwanshi</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>AMEY11</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>BAT</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>angkrish raghuvanshi</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>possible_mismatch:78.94736842105263</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
         <v>0</v>
       </c>
     </row>

--- a/IPL_Fantasy_Points.xlsx
+++ b/IPL_Fantasy_Points.xlsx
@@ -3546,7 +3546,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>b sai sudharsan</t>
+          <t>b sai sudharshan</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3559,31 +3559,31 @@
           <t>BAT</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr">
+      <c r="D73" t="inlineStr">
         <is>
           <t>b sai sudharshan</t>
         </is>
       </c>
+      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
-          <t>possible_mismatch:96.7741935483871</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="74">
@@ -8246,11 +8246,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>DIPESH11</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>168</v>
+        <v>171</v>
       </c>
     </row>
     <row r="8">
@@ -8259,11 +8259,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BABA11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>164</v>
+        <v>168</v>
       </c>
     </row>
     <row r="9">
@@ -8272,11 +8272,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DIPESH11</t>
+          <t>BABA11</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>158</v>
+        <v>164</v>
       </c>
     </row>
     <row r="10">
@@ -13351,7 +13351,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13414,7 +13414,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>b sai sudharsan</t>
+          <t>Avesh Khan</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -13424,18 +13424,18 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>b sai sudharshan</t>
+          <t>rashid khan</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>possible_mismatch:96.7741935483871</t>
+          <t>possible_mismatch:76.19047619047619</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -13457,28 +13457,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Avesh Khan</t>
+          <t>ashutosh sharma</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DIPESH11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>rashid khan</t>
+          <t>ashok sharma</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>possible_mismatch:76.19047619047619</t>
+          <t>possible_mismatch:81.4814814814815</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -13500,7 +13500,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ashutosh sharma</t>
+          <t>Mohammed Shami</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -13510,18 +13510,18 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ashok sharma</t>
+          <t>mohammed siraj</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>possible_mismatch:81.4814814814815</t>
+          <t>possible_mismatch:78.57142857142857</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -13543,28 +13543,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Mohammed Shami</t>
+          <t>akshat raghuwanshi</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>mohammed siraj</t>
+          <t>angkrish raghuvanshi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>possible_mismatch:78.57142857142857</t>
+          <t>possible_mismatch:78.94736842105263</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -13580,49 +13580,6 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>akshat raghuwanshi</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>AMEY11</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>BAT</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>angkrish raghuvanshi</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>possible_mismatch:78.94736842105263</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
         <v>0</v>
       </c>
     </row>

--- a/IPL_Fantasy_Points.xlsx
+++ b/IPL_Fantasy_Points.xlsx
@@ -493,7 +493,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MS Dhoni CSK</t>
+          <t>MS Dhoni</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -536,7 +536,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Rishabh Pant LSG</t>
+          <t>Rishabh Pant</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -549,37 +549,37 @@
           <t>BAT</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>harshal patel</t>
-        </is>
-      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>rishabh pant</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Travis Head srh</t>
+          <t>Travis Head</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1022,31 +1022,31 @@
           <t>BOWL</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>rashid khan</t>
-        </is>
-      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>mohsin khan</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15">
@@ -1181,7 +1181,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Ishan Kishan srh</t>
+          <t>Ishan Kishan</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1224,7 +1224,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Shubman Gill gt</t>
+          <t>Shubman Gill</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1267,7 +1267,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ajinkya Rahane kkr</t>
+          <t>Ajinkya Rahane</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1310,7 +1310,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>vaibhav suryavanshi rr</t>
+          <t>vaibhav suryavanshi</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1353,7 +1353,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ramandeep singh kkr</t>
+          <t>ramandeep singh</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1396,7 +1396,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>karun nair dc</t>
+          <t>karun nair</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1439,7 +1439,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>jacob bethel rcb</t>
+          <t>jacob bethel</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1482,7 +1482,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>vipraj nigam dc</t>
+          <t>vipraj nigam</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1495,15 +1495,15 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>virat kohli</t>
-        </is>
-      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>vipraj nigam</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -1525,7 +1525,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rahul Tewatia gt</t>
+          <t>Rahul Tewatia</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1568,7 +1568,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Jason Holder gt</t>
+          <t>Jason Holder</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1611,7 +1611,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>kamindu mendis srh</t>
+          <t>kamindu mendis</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1654,7 +1654,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>tushar deshpande rr</t>
+          <t>tushar deshpande</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1697,7 +1697,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Ravi Bishnoi rr</t>
+          <t>Ravi Bishnoi</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1740,7 +1740,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Khaleel Ahmed csk</t>
+          <t>Khaleel Ahmed</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1783,7 +1783,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>am ghazanfar mi</t>
+          <t>am ghazanfar</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1826,7 +1826,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>anshul kamboj csk</t>
+          <t>anshul kamboj</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1869,7 +1869,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Harsh Dubey srh</t>
+          <t>Harsh Dubey</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1912,7 +1912,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Kuldeep sen rr</t>
+          <t>Kuldeep sen</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1928,7 +1928,7 @@
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>arshdeep singh</t>
+          <t>kuldeep yadav</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2057,7 +2057,7 @@
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>marco jansen</t>
+          <t>t natarajan</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2444,7 +2444,7 @@
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>jamie overton</t>
+          <t>lokesh rahul</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2573,7 +2573,7 @@
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>mayank markande</t>
+          <t>david miller</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2828,15 +2828,15 @@
           <t>BAT</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>david payne</t>
-        </is>
-      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>david miller</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -2858,7 +2858,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Dhruv Jurel</t>
+          <t>dhruv chand jurel</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2879,7 +2879,7 @@
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>ai_structured</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -2914,15 +2914,15 @@
           <t>BAT</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>ayush mhatre</t>
-        </is>
-      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>ayush badoni</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -3433,7 +3433,7 @@
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>jitesh sharma</t>
+          <t>mitchell marsh</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3476,7 +3476,7 @@
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>jitesh sharma</t>
+          <t>mitchell marsh</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3691,7 +3691,7 @@
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>jamie overton</t>
+          <t>mitchell marsh</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3774,31 +3774,31 @@
           <t>BAT</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>ishan kishan</t>
-        </is>
-      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>tristan stubbs</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
     </row>
     <row r="79">
@@ -3863,7 +3863,7 @@
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>marcus stoinis</t>
+          <t>pathum nissanka</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3903,31 +3903,31 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>salil arora</t>
-        </is>
-      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>aiden markram</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="G81" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="82">
@@ -4062,7 +4062,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Avesh Khan</t>
+          <t>avesh khan</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4083,7 +4083,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>possible_mismatch:76.19047619047619</t>
+          <t>no_stats_yet</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -4118,15 +4118,15 @@
           <t>BOWL</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>bhuvneshwar kumar</t>
-        </is>
-      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>mukesh kumar</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -4277,7 +4277,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Yashasvi Jaiswal rr</t>
+          <t>Yashasvi Jaiswal</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4320,7 +4320,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>KL Rahul dc</t>
+          <t>KL Rahul</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4336,7 +4336,7 @@
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>khaleel ahmed</t>
+          <t>lokesh rahul</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -4363,7 +4363,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Shreyas Iyer PBKS</t>
+          <t>Shreyas Iyer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4406,7 +4406,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Jos Buttler gt</t>
+          <t>Jos Buttler</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4465,7 +4465,7 @@
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>harshal patel</t>
+          <t>axar patel</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -4535,7 +4535,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Nishant Sindhu gt</t>
+          <t>Nishant Sindhu</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4578,7 +4578,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Jayant Yadav gt</t>
+          <t>Jayant Yadav</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4594,7 +4594,7 @@
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>suryakumar yadav</t>
+          <t>prince yadav</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -4621,7 +4621,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Ajay Mandal dc</t>
+          <t>Ajay Mandal</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4664,7 +4664,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Will Jacks mi</t>
+          <t>Will Jacks</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4680,7 +4680,7 @@
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>yashasvi jaiswal</t>
+          <t>mitchell marsh</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -4707,7 +4707,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Riyan Parag rr</t>
+          <t>Riyan Parag</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4750,7 +4750,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Kagiso Rabada gt</t>
+          <t>Kagiso Rabada</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4793,7 +4793,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Josh Hazelwood rcb</t>
+          <t>Josh Hazelwood</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4809,7 +4809,7 @@
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>ayush mhatre</t>
+          <t>shahbaz ahmed</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -4836,7 +4836,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Kyle Jamieson dc</t>
+          <t>Kyle Jamieson</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4879,7 +4879,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Matheesha Pathirana kkr</t>
+          <t>Matheesha Pathirana</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4922,7 +4922,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>M Siddharth lsg</t>
+          <t>M Siddharth</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4965,7 +4965,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Ben Dwarshuis pbks</t>
+          <t>Ben Dwarshuis</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -5008,7 +5008,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Nandre Burger rr</t>
+          <t>Nandre Burger</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -5094,7 +5094,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Mitchel March</t>
+          <t>Mitchel Marsh</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -5107,31 +5107,31 @@
           <t>BAT</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>jitesh sharma</t>
-        </is>
-      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>mitchell marsh</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>ai_structured</t>
         </is>
       </c>
       <c r="G109" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H109" t="n">
         <v>0</v>
       </c>
       <c r="I109" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
       </c>
       <c r="K109" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="110">
@@ -5279,31 +5279,31 @@
           <t>BAT</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr"/>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>prasidh krishna</t>
-        </is>
-      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>pathum nissanka</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="G113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H113" t="n">
         <v>0</v>
       </c>
       <c r="I113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
       </c>
       <c r="K113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114">
@@ -5352,7 +5352,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Jamie Overton csk</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -5395,7 +5395,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Donovan Ferreira rr</t>
+          <t>Donovan Ferreira</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -5537,31 +5537,31 @@
           <t>BOWL</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>sunil narine</t>
-        </is>
-      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>lungi ngidi</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="G119" t="n">
         <v>0</v>
       </c>
       <c r="H119" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I119" t="n">
         <v>0</v>
       </c>
       <c r="J119" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="K119" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="120">
@@ -5610,7 +5610,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Mukesh Choudhary csk</t>
+          <t>Mukesh Choudhary</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5626,7 +5626,7 @@
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr">
         <is>
-          <t>ayush mhatre</t>
+          <t>mukul choudhary</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -5755,7 +5755,7 @@
       <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr">
         <is>
-          <t>krunal pandya</t>
+          <t>aiden markram</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -5795,15 +5795,15 @@
           <t>BOWL</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>heinrich klaasen</t>
-        </is>
-      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>anrich nortje</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>possible_mismatch:81.4814814814815</t>
+          <t>no_stats_yet</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -6139,37 +6139,37 @@
           <t>BAT</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr"/>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>cameron green</t>
-        </is>
-      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>sameer rizvi</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="G133" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H133" t="n">
         <v>0</v>
       </c>
       <c r="I133" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
       </c>
       <c r="K133" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Angkrish Raghuvanshi</t>
+          <t>angkrish raghuvanshi</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -6255,7 +6255,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Washington SUndar</t>
+          <t>Washington Sundar</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -6311,31 +6311,31 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>harshal patel</t>
-        </is>
-      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>axar patel</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="G137" t="n">
         <v>0</v>
       </c>
       <c r="H137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I137" t="n">
         <v>0</v>
       </c>
       <c r="J137" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K137" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="138">
@@ -6357,7 +6357,7 @@
       <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr">
         <is>
-          <t>mayank markande</t>
+          <t>mitchell marsh</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -6513,7 +6513,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Mohammed Shami</t>
+          <t>mohammed shami</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -6526,31 +6526,31 @@
           <t>BOWL</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr"/>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>mohammed siraj</t>
-        </is>
-      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>mohammed shami</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
-          <t>possible_mismatch:78.57142857142857</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="G142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I142" t="n">
         <v>0</v>
       </c>
       <c r="J142" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K142" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="143">
@@ -6698,31 +6698,31 @@
           <t>BAT</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr"/>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>heinrich klaasen</t>
-        </is>
-      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>nicholas pooran</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="G146" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H146" t="n">
         <v>0</v>
       </c>
       <c r="I146" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
       </c>
       <c r="K146" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="147">
@@ -6741,31 +6741,31 @@
           <t>BAT</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr"/>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>jitesh sharma</t>
-        </is>
-      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>nitish rana</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="G147" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H147" t="n">
         <v>0</v>
       </c>
       <c r="I147" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
       </c>
       <c r="K147" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="148">
@@ -6835,7 +6835,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>possible_mismatch:78.94736842105263</t>
+          <t>no_stats_yet</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -7072,7 +7072,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>T Natarjan</t>
+          <t>T Natarajan</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -7085,31 +7085,31 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr"/>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>rajat patidar</t>
-        </is>
-      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>t natarajan</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="G155" t="n">
         <v>0</v>
       </c>
       <c r="H155" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I155" t="n">
         <v>0</v>
       </c>
       <c r="J155" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="K155" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="156">
@@ -7158,7 +7158,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Bhuvaneshwar Kumar</t>
+          <t>bhuvneshwar kumar</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -7179,7 +7179,7 @@
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr">
         <is>
-          <t>ai_structured</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -8034,7 +8034,7 @@
       <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr">
         <is>
-          <t>jitesh sharma</t>
+          <t>lokesh rahul</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -8074,31 +8074,31 @@
           <t>BOWL</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr"/>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>suryakumar yadav</t>
-        </is>
-      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>kuldeep yadav</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="G178" t="n">
         <v>0</v>
       </c>
       <c r="H178" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I178" t="n">
         <v>0</v>
       </c>
       <c r="J178" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="K178" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="179">
@@ -8181,11 +8181,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MEET11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>333</v>
+        <v>343</v>
       </c>
     </row>
     <row r="3">
@@ -8194,11 +8194,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>VATSAL11</t>
+          <t>MEET11</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>297</v>
+        <v>333</v>
       </c>
     </row>
     <row r="4">
@@ -8211,7 +8211,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>248</v>
+        <v>331</v>
       </c>
     </row>
     <row r="5">
@@ -8220,11 +8220,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>247</v>
+        <v>317</v>
       </c>
     </row>
     <row r="6">
@@ -8233,11 +8233,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>VATSAL11</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>207</v>
+        <v>297</v>
       </c>
     </row>
     <row r="7">
@@ -8250,7 +8250,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>171</v>
+        <v>221</v>
       </c>
     </row>
     <row r="8">
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>113</v>
+        <v>153</v>
       </c>
     </row>
     <row r="11">
@@ -8302,7 +8302,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>83</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -8316,7 +8316,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C96"/>
+  <dimension ref="A1:C120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8339,37 +8339,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>abhinandan singh</t>
+          <t>abdul samad</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>abhishek sharma</t>
+          <t>abhinandan singh</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ajinkya rahane</t>
+          <t>abhishek sharma</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>67</v>
+        <v>7</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -8378,11 +8378,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>am ghazanfar</t>
+          <t>aiden markram</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -8391,11 +8391,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>angkrish raghuvanshi</t>
+          <t>ajinkya rahane</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -8404,11 +8404,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>aniket verma</t>
+          <t>am ghazanfar</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -8417,24 +8417,24 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>anshul kamboj</t>
+          <t>angkrish raghuvanshi</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>anukul roy</t>
+          <t>aniket verma</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -8443,7 +8443,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>arshdeep singh</t>
+          <t>anrich nortje</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -8456,20 +8456,20 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ashok sharma</t>
+          <t>anshul kamboj</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ayush mhatre</t>
+          <t>anukul roy</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -8482,11 +8482,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>b sai sudharshan</t>
+          <t>arshdeep singh</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -8495,7 +8495,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>bhuvneshwar kumar</t>
+          <t>ashok sharma</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -8508,37 +8508,37 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>blessing muzarabani</t>
+          <t>axar patel</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>brijesh sharma</t>
+          <t>ayush badoni</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>cameron green</t>
+          <t>ayush mhatre</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -8547,11 +8547,11 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>cooper connolly</t>
+          <t>b sai sudharshan</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>72</v>
+        <v>13</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -8560,24 +8560,24 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>david payne</t>
+          <t>bhuvneshwar kumar</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>devdutt padikkal</t>
+          <t>blessing muzarabani</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
@@ -8586,24 +8586,24 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>dhruv chand jurel</t>
+          <t>brijesh sharma</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>eshan malinga</t>
+          <t>cameron green</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
@@ -8612,11 +8612,11 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>finn allen</t>
+          <t>cooper connolly</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>37</v>
+        <v>72</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
@@ -8625,11 +8625,11 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>glenn phillips</t>
+          <t>david miller</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
@@ -8638,37 +8638,37 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>hardik pandya</t>
+          <t>david payne</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>harsh dubey</t>
+          <t>devdutt padikkal</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3</v>
+        <v>61</v>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>harshal patel</t>
+          <t>dhruv chand jurel</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
@@ -8677,11 +8677,11 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>heinrich klaasen</t>
+          <t>eshan malinga</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
@@ -8690,11 +8690,11 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ishan kishan</t>
+          <t>finn allen</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>80</v>
+        <v>37</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
@@ -8703,63 +8703,63 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>jacob duffy</t>
+          <t>glenn phillips</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="C30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>jamie overton</t>
+          <t>hardik pandya</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>jasprit bumrah</t>
+          <t>harsh dubey</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>jaydev unadkat</t>
+          <t>harshal patel</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>jitesh sharma</t>
+          <t>heinrich klaasen</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="C34" t="n">
         <v>0</v>
@@ -8768,50 +8768,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>jofra archer</t>
+          <t>ishan kishan</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="C35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>jos buttler</t>
+          <t>jacob duffy</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>kagiso rabada</t>
+          <t>jamie overton</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="C37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>kartik sharma</t>
+          <t>jasprit bumrah</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -8820,11 +8820,11 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>kartik tyagi</t>
+          <t>jaydev unadkat</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C39" t="n">
         <v>1</v>
@@ -8833,7 +8833,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>khaleel ahmed</t>
+          <t>jitesh sharma</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -8846,50 +8846,50 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>krunal pandya</t>
+          <t>jofra archer</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>marco jansen</t>
+          <t>jos buttler</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="C42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>marcus stoinis</t>
+          <t>kagiso rabada</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>0</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>matt henry</t>
+          <t>kartik sharma</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
@@ -8898,20 +8898,20 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>matt short</t>
+          <t>kartik tyagi</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>mayank markande</t>
+          <t>khaleel ahmed</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -8924,7 +8924,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>mohammed siraj</t>
+          <t>krunal pandya</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -8937,63 +8937,63 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>naman dhir</t>
+          <t>kuldeep yadav</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>nandre burger</t>
+          <t>lokesh rahul</t>
         </is>
       </c>
       <c r="B49" t="n">
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>nehal wadhera</t>
+          <t>lungi ngidi</t>
         </is>
       </c>
       <c r="B50" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" t="n">
         <v>3</v>
-      </c>
-      <c r="C50" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>nitish kumar reddy</t>
+          <t>marco jansen</t>
         </is>
       </c>
       <c r="B51" t="n">
+        <v>9</v>
+      </c>
+      <c r="C51" t="n">
         <v>1</v>
-      </c>
-      <c r="C51" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>noor ahmad</t>
+          <t>marcus stoinis</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C52" t="n">
         <v>0</v>
@@ -9002,11 +9002,11 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>philip salt</t>
+          <t>matt henry</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C53" t="n">
         <v>0</v>
@@ -9015,11 +9015,11 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>prabhsimran singh</t>
+          <t>matt short</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="C54" t="n">
         <v>0</v>
@@ -9028,24 +9028,24 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>prasidh krishna</t>
+          <t>mayank markande</t>
         </is>
       </c>
       <c r="B55" t="n">
         <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>priyansh arya</t>
+          <t>mitchell marsh</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
@@ -9054,24 +9054,24 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>rahul tewatia</t>
+          <t>mohammed shami</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>rajat patidar</t>
+          <t>mohammed siraj</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="C58" t="n">
         <v>0</v>
@@ -9080,76 +9080,76 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ramandeep singh</t>
+          <t>mohsin khan</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>rashid khan</t>
+          <t>mukesh kumar</t>
         </is>
       </c>
       <c r="B60" t="n">
         <v>0</v>
       </c>
       <c r="C60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ravi bishnoi</t>
+          <t>mukul choudhary</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="C61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ravindra jadeja</t>
+          <t>naman dhir</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C62" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>rinku singh</t>
+          <t>nandre burger</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="C63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>riyan parag</t>
+          <t>nehal wadhera</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C64" t="n">
         <v>0</v>
@@ -9158,11 +9158,11 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>rohit sharma</t>
+          <t>nicholas pooran</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>78</v>
+        <v>8</v>
       </c>
       <c r="C65" t="n">
         <v>0</v>
@@ -9171,24 +9171,24 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>romario shepherd</t>
+          <t>nitish kumar reddy</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C66" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ruturaj gaikwad</t>
+          <t>nitish rana</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C67" t="n">
         <v>0</v>
@@ -9197,11 +9197,11 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ryan rickelton</t>
+          <t>noor ahmad</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>81</v>
+        <v>1</v>
       </c>
       <c r="C68" t="n">
         <v>0</v>
@@ -9210,11 +9210,11 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>salil arora</t>
+          <t>pathum nissanka</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C69" t="n">
         <v>0</v>
@@ -9223,24 +9223,24 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>sandeep sharma</t>
+          <t>philip salt</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>sanju samson</t>
+          <t>prabhsimran singh</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="C71" t="n">
         <v>0</v>
@@ -9249,50 +9249,50 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>sarfaraz khan</t>
+          <t>prasidh krishna</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="C72" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>shahrukh khan</t>
+          <t>prince yadav</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>shardul thakur</t>
+          <t>priyansh arya</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C74" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>shashank singh</t>
+          <t>rahul tewatia</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C75" t="n">
         <v>0</v>
@@ -9301,11 +9301,11 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>sherfane rutherford</t>
+          <t>rajat patidar</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="C76" t="n">
         <v>0</v>
@@ -9314,11 +9314,11 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>shimron hetmyer</t>
+          <t>ramandeep singh</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C77" t="n">
         <v>0</v>
@@ -9327,63 +9327,63 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>shivam dube</t>
+          <t>rashid khan</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>shreyas iyer</t>
+          <t>ravi bishnoi</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="C79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>shubman gill</t>
+          <t>ravindra jadeja</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C80" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>sunil narine</t>
+          <t>rinku singh</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="C81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>suryakumar yadav</t>
+          <t>rishabh pant</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
@@ -9392,24 +9392,24 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>suyash sharma</t>
+          <t>riyan parag</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="C83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>tilak varma</t>
+          <t>rohit sharma</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>20</v>
+        <v>78</v>
       </c>
       <c r="C84" t="n">
         <v>0</v>
@@ -9418,24 +9418,24 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>tim david</t>
+          <t>romario shepherd</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="C85" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>travis head</t>
+          <t>ruturaj gaikwad</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
@@ -9444,11 +9444,11 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>trent boult</t>
+          <t>ryan rickelton</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
@@ -9457,24 +9457,24 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>vaibhav arora</t>
+          <t>salil arora</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>vaibhav suryavanshi</t>
+          <t>sameer rizvi</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
@@ -9483,37 +9483,37 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>varun chakravarthy</t>
+          <t>sandeep sharma</t>
         </is>
       </c>
       <c r="B90" t="n">
         <v>0</v>
       </c>
       <c r="C90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>vijaykumar vyshak</t>
+          <t>sanju samson</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C91" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>virat kohli</t>
+          <t>sarfaraz khan</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>69</v>
+        <v>17</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
@@ -9522,24 +9522,24 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>washington sundar</t>
+          <t>shahbaz ahmed</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>xavier bartlett</t>
+          <t>shahrukh khan</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
@@ -9548,26 +9548,338 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>yashasvi jaiswal</t>
+          <t>shardul thakur</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C95" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
+          <t>shashank singh</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>4</v>
+      </c>
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>sherfane rutherford</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>0</v>
+      </c>
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>shimron hetmyer</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>0</v>
+      </c>
+      <c r="C98" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>shivam dube</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>6</v>
+      </c>
+      <c r="C99" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>shreyas iyer</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>18</v>
+      </c>
+      <c r="C100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>shubman gill</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>39</v>
+      </c>
+      <c r="C101" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>sunil narine</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>0</v>
+      </c>
+      <c r="C102" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>suryakumar yadav</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>16</v>
+      </c>
+      <c r="C103" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>suyash sharma</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>0</v>
+      </c>
+      <c r="C104" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>t natarajan</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>0</v>
+      </c>
+      <c r="C105" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>tilak varma</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>20</v>
+      </c>
+      <c r="C106" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>tim david</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>16</v>
+      </c>
+      <c r="C107" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>travis head</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>11</v>
+      </c>
+      <c r="C108" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>trent boult</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>0</v>
+      </c>
+      <c r="C109" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>tristan stubbs</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>39</v>
+      </c>
+      <c r="C110" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>vaibhav arora</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>0</v>
+      </c>
+      <c r="C111" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>vaibhav suryavanshi</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>52</v>
+      </c>
+      <c r="C112" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>varun chakravarthy</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>0</v>
+      </c>
+      <c r="C113" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>vijaykumar vyshak</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>0</v>
+      </c>
+      <c r="C114" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>vipraj nigam</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>0</v>
+      </c>
+      <c r="C115" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>virat kohli</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>69</v>
+      </c>
+      <c r="C116" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>washington sundar</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>18</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>xavier bartlett</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>11</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>yashasvi jaiswal</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>38</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
           <t>yuzvendra chahal</t>
         </is>
       </c>
-      <c r="B96" t="n">
-        <v>0</v>
-      </c>
-      <c r="C96" t="n">
+      <c r="B120" t="n">
+        <v>0</v>
+      </c>
+      <c r="C120" t="n">
         <v>2</v>
       </c>
     </row>
@@ -9582,7 +9894,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K87"/>
+  <dimension ref="A1:K72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9645,7 +9957,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MS Dhoni CSK</t>
+          <t>MS Dhoni</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -9688,7 +10000,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Rishabh Pant LSG</t>
+          <t>Dewald Brevis</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -9704,7 +10016,7 @@
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>harshal patel</t>
+          <t>nandre burger</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -9731,7 +10043,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Dewald Brevis</t>
+          <t>Akeal Hosein</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -9741,13 +10053,13 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>nandre burger</t>
+          <t>jamie overton</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -9774,7 +10086,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Akeal Hosein</t>
+          <t>Brydon Carse</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -9784,13 +10096,13 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>jamie overton</t>
+          <t>riyan parag</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -9817,7 +10129,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Mohsin Khan</t>
+          <t>Umran Malik</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -9833,7 +10145,7 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>rashid khan</t>
+          <t>eshan malinga</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -9860,23 +10172,23 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Brydon Carse</t>
+          <t>karun nair</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NIRAV11</t>
+          <t>MEET11</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>riyan parag</t>
+          <t>krunal pandya</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -9903,23 +10215,23 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Umran Malik</t>
+          <t>jacob bethel</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NIRAV11</t>
+          <t>MEET11</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>eshan malinga</t>
+          <t>jacob duffy</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -9946,7 +10258,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>karun nair dc</t>
+          <t>Jason Holder</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -9956,13 +10268,13 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>krunal pandya</t>
+          <t>jos buttler</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -9989,7 +10301,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>jacob bethel rcb</t>
+          <t>kamindu mendis</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -9999,13 +10311,13 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>jacob duffy</t>
+          <t>naman dhir</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -10032,7 +10344,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>vipraj nigam dc</t>
+          <t>tushar deshpande</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -10042,13 +10354,13 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>virat kohli</t>
+          <t>ishan kishan</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -10075,7 +10387,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Jason Holder gt</t>
+          <t>Kuldeep sen</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -10085,13 +10397,13 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>jos buttler</t>
+          <t>kuldeep yadav</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -10118,23 +10430,23 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>kamindu mendis srh</t>
+          <t>Quinton de Kock</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MEET11</t>
+          <t>VATSAL11</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>naman dhir</t>
+          <t>washington sundar</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -10161,23 +10473,23 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>tushar deshpande rr</t>
+          <t>Tom Banton</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MEET11</t>
+          <t>VATSAL11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ishan kishan</t>
+          <t>t natarajan</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -10204,23 +10516,23 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Kuldeep sen rr</t>
+          <t>Tim Siefert</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MEET11</t>
+          <t>VATSAL11</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>arshdeep singh</t>
+          <t>jamie overton</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -10247,7 +10559,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Quinton de Kock</t>
+          <t>Lockie Ferguson</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -10257,13 +10569,13 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>washington sundar</t>
+          <t>lokesh rahul</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -10290,7 +10602,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Tom Banton</t>
+          <t>Adam Milne</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -10300,13 +10612,13 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>marco jansen</t>
+          <t>david miller</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -10333,7 +10645,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Tim Siefert</t>
+          <t>Corbin Bosch</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -10343,13 +10655,13 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>jamie overton</t>
+          <t>rinku singh</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -10376,7 +10688,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Lockie Ferguson</t>
+          <t>Deepak Chahar</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -10392,7 +10704,7 @@
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>jamie overton</t>
+          <t>sandeep sharma</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -10419,7 +10731,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Adam Milne</t>
+          <t>Rahul Chahar</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -10435,7 +10747,7 @@
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>mayank markande</t>
+          <t>rahul tewatia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -10462,23 +10774,23 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Corbin Bosch</t>
+          <t>Jos Inglis</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>VATSAL11</t>
+          <t>BABA11</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>rinku singh</t>
+          <t>marcus stoinis</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -10505,23 +10817,23 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Deepak Chahar</t>
+          <t>Prithvi Shaw</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>VATSAL11</t>
+          <t>BABA11</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>sandeep sharma</t>
+          <t>prasidh krishna</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -10548,23 +10860,23 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rahul Chahar</t>
+          <t>Rowman Powell</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>VATSAL11</t>
+          <t>BABA11</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>rahul tewatia</t>
+          <t>romario shepherd</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -10591,7 +10903,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Jos Inglis</t>
+          <t>liam livingston</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10601,13 +10913,13 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>marcus stoinis</t>
+          <t>jamie overton</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -10634,7 +10946,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>David Miller</t>
+          <t>rachin ravindra</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -10644,13 +10956,13 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>david payne</t>
+          <t>rashid khan</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -10677,7 +10989,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Ayush Badoni</t>
+          <t>Zeeshan Ansari</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -10687,13 +10999,13 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ayush mhatre</t>
+          <t>eshan malinga</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -10720,7 +11032,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Prithvi Shaw</t>
+          <t>Mitchell Starc</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -10730,13 +11042,13 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>prasidh krishna</t>
+          <t>mitchell marsh</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -10763,7 +11075,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rowman Powell</t>
+          <t>Mitchel Santner</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -10773,13 +11085,13 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>romario shepherd</t>
+          <t>mitchell marsh</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -10806,23 +11118,23 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>liam livingston</t>
+          <t>Mitchel Owen</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BABA11</t>
+          <t>DIPESH11</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>jamie overton</t>
+          <t>mitchell marsh</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -10849,12 +11161,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>rachin ravindra</t>
+          <t>Pat Cummins</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>BABA11</t>
+          <t>DIPESH11</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -10865,7 +11177,7 @@
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>rashid khan</t>
+          <t>pathum nissanka</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -10892,12 +11204,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Zeeshan Ansari</t>
+          <t>avesh khan</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BABA11</t>
+          <t>DIPESH11</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -10908,7 +11220,7 @@
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>eshan malinga</t>
+          <t>rashid khan</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -10935,12 +11247,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Mitchell Starc</t>
+          <t>Aqib Nabi Dar</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BABA11</t>
+          <t>DIPESH11</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -10951,7 +11263,7 @@
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>jitesh sharma</t>
+          <t>b sai sudharshan</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -10978,12 +11290,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Mitchel Santner</t>
+          <t>Rasik Dar Salam</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BABA11</t>
+          <t>DIPESH11</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -10994,7 +11306,7 @@
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>jitesh sharma</t>
+          <t>rashid khan</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -11021,12 +11333,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Mitchel Owen</t>
+          <t>KL Rahul</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>DIPESH11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -11037,7 +11349,7 @@
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>jamie overton</t>
+          <t>lokesh rahul</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -11064,12 +11376,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Tristan Stubbs</t>
+          <t>Urvil Patel</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>DIPESH11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -11080,7 +11392,7 @@
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>ishan kishan</t>
+          <t>axar patel</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -11107,23 +11419,23 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Pat Cummins</t>
+          <t>Arshin Kulkarni</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>DIPESH11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>marcus stoinis</t>
+          <t>rashid khan</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -11150,12 +11462,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Aiden Markram</t>
+          <t>Nishant Sindhu</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>DIPESH11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -11166,7 +11478,7 @@
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>salil arora</t>
+          <t>shashank singh</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -11193,23 +11505,23 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Mukesh Kumar</t>
+          <t>Jayant Yadav</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>DIPESH11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>bhuvneshwar kumar</t>
+          <t>prince yadav</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -11236,23 +11548,23 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Aqib Nabi Dar</t>
+          <t>Ajay Mandal</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>DIPESH11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>b sai sudharshan</t>
+          <t>rajat patidar</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -11279,23 +11591,23 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rasik Dar Salam</t>
+          <t>Will Jacks</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>DIPESH11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>rashid khan</t>
+          <t>mitchell marsh</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -11322,7 +11634,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>KL Rahul dc</t>
+          <t>Josh Hazelwood</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -11332,13 +11644,13 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>khaleel ahmed</t>
+          <t>shahbaz ahmed</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -11365,7 +11677,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Urvil Patel</t>
+          <t>Kyle Jamieson</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -11375,13 +11687,13 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>harshal patel</t>
+          <t>jamie overton</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -11408,7 +11720,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Arshin Kulkarni</t>
+          <t>Matheesha Pathirana</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -11418,13 +11730,13 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>rashid khan</t>
+          <t>eshan malinga</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -11451,7 +11763,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Nishant Sindhu gt</t>
+          <t>M Siddharth</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -11461,13 +11773,13 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>shashank singh</t>
+          <t>b sai sudharshan</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -11494,7 +11806,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Jayant Yadav gt</t>
+          <t>Ben Dwarshuis</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -11504,13 +11816,13 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>suryakumar yadav</t>
+          <t>b sai sudharshan</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -11537,23 +11849,23 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Ajay Mandal dc</t>
+          <t>Manish Pandey</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>rajat patidar</t>
+          <t>hardik pandya</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -11580,12 +11892,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Will Jacks mi</t>
+          <t>Donovan Ferreira</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -11596,7 +11908,7 @@
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>yashasvi jaiswal</t>
+          <t>nandre burger</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -11623,12 +11935,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Josh Hazelwood rcb</t>
+          <t>Mukesh Choudhary</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -11639,7 +11951,7 @@
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>ayush mhatre</t>
+          <t>mukul choudhary</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -11666,12 +11978,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Kyle Jamieson dc</t>
+          <t>Gurjapneet Singh</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -11682,7 +11994,7 @@
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>jamie overton</t>
+          <t>ramandeep singh</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -11709,12 +12021,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Matheesha Pathirana kkr</t>
+          <t>Arjun Tendulkar</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -11725,7 +12037,7 @@
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>eshan malinga</t>
+          <t>krunal pandya</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -11752,12 +12064,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>M Siddharth lsg</t>
+          <t>Kwena Maphaka</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -11768,7 +12080,7 @@
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>b sai sudharshan</t>
+          <t>aiden markram</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -11795,23 +12107,23 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Ben Dwarshuis pbks</t>
+          <t>Ramkrishna Ghosh</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>b sai sudharshan</t>
+          <t>angkrish raghuvanshi</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -11838,12 +12150,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Mitchel March</t>
+          <t>Venkatesh Iyer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -11854,7 +12166,7 @@
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>jitesh sharma</t>
+          <t>shreyas iyer</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -11881,12 +12193,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Manish Pandey</t>
+          <t>ashutosh sharma</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -11897,7 +12209,7 @@
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>hardik pandya</t>
+          <t>ashok sharma</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -11924,12 +12236,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Pathum Nissanka</t>
+          <t>Prashant Veer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -11940,7 +12252,7 @@
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>prasidh krishna</t>
+          <t>aniket verma</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -11967,12 +12279,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Donovan Ferreira rr</t>
+          <t>Azmatullah Omarzai</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -11983,7 +12295,7 @@
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>nandre burger</t>
+          <t>mitchell marsh</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -12010,23 +12322,23 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Lungi Ngidi</t>
+          <t>akshat raghuwanshi</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>sunil narine</t>
+          <t>angkrish raghuvanshi</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -12053,23 +12365,23 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Mukesh Choudhary csk</t>
+          <t>Himmat Singh</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>ayush mhatre</t>
+          <t>prabhsimran singh</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -12096,23 +12408,23 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Gurjapneet Singh</t>
+          <t>Suryansh Shegde</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>ramandeep singh</t>
+          <t>suyash sharma</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -12139,23 +12451,23 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Arjun Tendulkar</t>
+          <t>Tejasvi Singh</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>krunal pandya</t>
+          <t>prabhsimran singh</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -12182,12 +12494,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Kwena Maphaka</t>
+          <t>Sai Kishor</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -12198,7 +12510,7 @@
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>krunal pandya</t>
+          <t>ishan kishan</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -12225,12 +12537,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Anrich Nortje</t>
+          <t>Akash Deep</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -12241,7 +12553,7 @@
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>heinrich klaasen</t>
+          <t>arshdeep singh</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -12268,12 +12580,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Ramkrishna Ghosh</t>
+          <t>Ben Duckett</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -12284,7 +12596,7 @@
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>angkrish raghuvanshi</t>
+          <t>ryan rickelton</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -12311,12 +12623,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Venkatesh Iyer</t>
+          <t>Abhishek Porel</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -12327,7 +12639,7 @@
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>shreyas iyer</t>
+          <t>abhishek sharma</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -12354,12 +12666,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sameer Rizvi</t>
+          <t>Rahul Tripathi</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -12370,7 +12682,7 @@
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>cameron green</t>
+          <t>rahul tewatia</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -12397,12 +12709,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Prashant Veer</t>
+          <t>Dre Pretorius</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -12413,7 +12725,7 @@
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>aniket verma</t>
+          <t>nandre burger</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -12440,23 +12752,23 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Axar Patel</t>
+          <t>Matthew Breetzke</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>harshal patel</t>
+          <t>matt henry</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -12483,23 +12795,23 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Azmatullah Omarzai</t>
+          <t>Anuj Rawat</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>mayank markande</t>
+          <t>rahul tewatia</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -12526,23 +12838,23 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>Wanindu Hasaranga</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>heinrich klaasen</t>
+          <t>sandeep sharma</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -12569,23 +12881,23 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Nitish Rana</t>
+          <t>Harpreet Brar</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>jitesh sharma</t>
+          <t>jasprit bumrah</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -12612,23 +12924,23 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Himmat Singh</t>
+          <t>Mayank Yadav</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>prabhsimran singh</t>
+          <t>mayank markande</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -12655,23 +12967,23 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Suryansh Shegde</t>
+          <t>Digvesh Rathi</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>suyash sharma</t>
+          <t>lokesh rahul</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -12692,651 +13004,6 @@
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Tejasvi Singh</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>AMEY11</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>BAT</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>prabhsimran singh</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="G73" t="n">
-        <v>0</v>
-      </c>
-      <c r="H73" t="n">
-        <v>0</v>
-      </c>
-      <c r="I73" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" t="n">
-        <v>0</v>
-      </c>
-      <c r="K73" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>T Natarjan</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>AMEY11</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>AR</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>rajat patidar</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="G74" t="n">
-        <v>0</v>
-      </c>
-      <c r="H74" t="n">
-        <v>0</v>
-      </c>
-      <c r="I74" t="n">
-        <v>0</v>
-      </c>
-      <c r="J74" t="n">
-        <v>0</v>
-      </c>
-      <c r="K74" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Sai Kishor</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>AMEY11</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>BOWL</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>ishan kishan</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="G75" t="n">
-        <v>0</v>
-      </c>
-      <c r="H75" t="n">
-        <v>0</v>
-      </c>
-      <c r="I75" t="n">
-        <v>0</v>
-      </c>
-      <c r="J75" t="n">
-        <v>0</v>
-      </c>
-      <c r="K75" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Akash Deep</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>AMEY11</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>BOWL</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>arshdeep singh</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="G76" t="n">
-        <v>0</v>
-      </c>
-      <c r="H76" t="n">
-        <v>0</v>
-      </c>
-      <c r="I76" t="n">
-        <v>0</v>
-      </c>
-      <c r="J76" t="n">
-        <v>0</v>
-      </c>
-      <c r="K76" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Ben Duckett</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>BAT</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>ryan rickelton</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="G77" t="n">
-        <v>0</v>
-      </c>
-      <c r="H77" t="n">
-        <v>0</v>
-      </c>
-      <c r="I77" t="n">
-        <v>0</v>
-      </c>
-      <c r="J77" t="n">
-        <v>0</v>
-      </c>
-      <c r="K77" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Abhishek Porel</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>BAT</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>abhishek sharma</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="G78" t="n">
-        <v>0</v>
-      </c>
-      <c r="H78" t="n">
-        <v>0</v>
-      </c>
-      <c r="I78" t="n">
-        <v>0</v>
-      </c>
-      <c r="J78" t="n">
-        <v>0</v>
-      </c>
-      <c r="K78" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Rahul Tripathi</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>BAT</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr"/>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>rahul tewatia</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="G79" t="n">
-        <v>0</v>
-      </c>
-      <c r="H79" t="n">
-        <v>0</v>
-      </c>
-      <c r="I79" t="n">
-        <v>0</v>
-      </c>
-      <c r="J79" t="n">
-        <v>0</v>
-      </c>
-      <c r="K79" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Dre Pretorius</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>BAT</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>nandre burger</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="G80" t="n">
-        <v>0</v>
-      </c>
-      <c r="H80" t="n">
-        <v>0</v>
-      </c>
-      <c r="I80" t="n">
-        <v>0</v>
-      </c>
-      <c r="J80" t="n">
-        <v>0</v>
-      </c>
-      <c r="K80" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Matthew Breetzke</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>BAT</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>matt henry</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="G81" t="n">
-        <v>0</v>
-      </c>
-      <c r="H81" t="n">
-        <v>0</v>
-      </c>
-      <c r="I81" t="n">
-        <v>0</v>
-      </c>
-      <c r="J81" t="n">
-        <v>0</v>
-      </c>
-      <c r="K81" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Anuj Rawat</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>BAT</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>rahul tewatia</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="G82" t="n">
-        <v>0</v>
-      </c>
-      <c r="H82" t="n">
-        <v>0</v>
-      </c>
-      <c r="I82" t="n">
-        <v>0</v>
-      </c>
-      <c r="J82" t="n">
-        <v>0</v>
-      </c>
-      <c r="K82" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Wanindu Hasaranga</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>AR</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>sandeep sharma</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="G83" t="n">
-        <v>0</v>
-      </c>
-      <c r="H83" t="n">
-        <v>0</v>
-      </c>
-      <c r="I83" t="n">
-        <v>0</v>
-      </c>
-      <c r="J83" t="n">
-        <v>0</v>
-      </c>
-      <c r="K83" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Harpreet Brar</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>BOWL</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>jasprit bumrah</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="G84" t="n">
-        <v>0</v>
-      </c>
-      <c r="H84" t="n">
-        <v>0</v>
-      </c>
-      <c r="I84" t="n">
-        <v>0</v>
-      </c>
-      <c r="J84" t="n">
-        <v>0</v>
-      </c>
-      <c r="K84" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Mayank Yadav</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>BOWL</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>mayank markande</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="G85" t="n">
-        <v>0</v>
-      </c>
-      <c r="H85" t="n">
-        <v>0</v>
-      </c>
-      <c r="I85" t="n">
-        <v>0</v>
-      </c>
-      <c r="J85" t="n">
-        <v>0</v>
-      </c>
-      <c r="K85" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Digvesh Rathi</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>BOWL</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>jitesh sharma</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="G86" t="n">
-        <v>0</v>
-      </c>
-      <c r="H86" t="n">
-        <v>0</v>
-      </c>
-      <c r="I86" t="n">
-        <v>0</v>
-      </c>
-      <c r="J86" t="n">
-        <v>0</v>
-      </c>
-      <c r="K86" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Kuldeep Yadav</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>BOWL</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>suryakumar yadav</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="G87" t="n">
-        <v>0</v>
-      </c>
-      <c r="H87" t="n">
-        <v>0</v>
-      </c>
-      <c r="I87" t="n">
-        <v>0</v>
-      </c>
-      <c r="J87" t="n">
-        <v>0</v>
-      </c>
-      <c r="K87" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13351,7 +13018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13409,178 +13076,6 @@
         <is>
           <t>Points</t>
         </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Avesh Khan</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>DIPESH11</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>BOWL</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>rashid khan</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>possible_mismatch:76.19047619047619</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>ashutosh sharma</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>HARSH11</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>BAT</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>ashok sharma</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>possible_mismatch:81.4814814814815</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Mohammed Shami</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>HARSH11</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>BOWL</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>mohammed siraj</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>possible_mismatch:78.57142857142857</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>akshat raghuwanshi</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>AMEY11</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>BAT</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>angkrish raghuvanshi</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>possible_mismatch:78.94736842105263</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -13594,7 +13089,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13657,12 +13152,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Dhruv Jurel</t>
+          <t>Mitchel Marsh</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BABA11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -13672,7 +13167,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>dhruv chand jurel</t>
+          <t>mitchell marsh</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -13682,62 +13177,19 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Bhuvaneshwar Kumar</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>AMEY11</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>BOWL</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>bhuvneshwar kumar</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>ai_structured</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>20</v>
-      </c>
-      <c r="K3" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/IPL_Fantasy_Points.xlsx
+++ b/IPL_Fantasy_Points.xlsx
@@ -604,19 +604,19 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>11</v>
+        <v>57</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>11</v>
+        <v>57</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>11</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5">
@@ -862,19 +862,19 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11">
@@ -951,16 +951,16 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
@@ -1206,19 +1206,19 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>80</v>
+        <v>94</v>
       </c>
     </row>
     <row r="19">
@@ -1292,19 +1292,19 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21">
@@ -1378,19 +1378,19 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23">
@@ -1894,19 +1894,19 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="K34" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="35">
@@ -2023,19 +2023,19 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>31</v>
+        <v>83</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>31</v>
+        <v>83</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>31</v>
+        <v>83</v>
       </c>
     </row>
     <row r="38">
@@ -2109,19 +2109,19 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
     </row>
     <row r="40">
@@ -3055,19 +3055,19 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>33</v>
+        <v>68</v>
       </c>
     </row>
     <row r="62">
@@ -4508,7 +4508,7 @@
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>rashid khan</t>
+          <t>shivang kumar</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -5094,7 +5094,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Mitchel Marsh</t>
+          <t>mitchell marsh</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -5115,7 +5115,7 @@
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
-          <t>ai_structured</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -5506,19 +5506,19 @@
         </is>
       </c>
       <c r="G118" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H118" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I118" t="n">
         <v>0</v>
       </c>
       <c r="J118" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="K118" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="119">
@@ -6194,19 +6194,19 @@
         </is>
       </c>
       <c r="G134" t="n">
-        <v>51</v>
+        <v>103</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
       </c>
       <c r="I134" t="n">
-        <v>51</v>
+        <v>103</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
       </c>
       <c r="K134" t="n">
-        <v>51</v>
+        <v>103</v>
       </c>
     </row>
     <row r="135">
@@ -6498,16 +6498,16 @@
         <v>4</v>
       </c>
       <c r="H141" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I141" t="n">
         <v>0</v>
       </c>
       <c r="J141" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="K141" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
     </row>
     <row r="142">
@@ -6796,19 +6796,19 @@
         </is>
       </c>
       <c r="G148" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H148" t="n">
         <v>0</v>
       </c>
       <c r="I148" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
       </c>
       <c r="K148" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="149">
@@ -7226,19 +7226,19 @@
         </is>
       </c>
       <c r="G158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H158" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I158" t="n">
         <v>0</v>
       </c>
       <c r="J158" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="K158" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
     </row>
     <row r="159">
@@ -7398,19 +7398,19 @@
         </is>
       </c>
       <c r="G162" t="n">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="H162" t="n">
         <v>0</v>
       </c>
       <c r="I162" t="n">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
       </c>
       <c r="K162" t="n">
-        <v>7</v>
+        <v>55</v>
       </c>
     </row>
     <row r="163">
@@ -7570,19 +7570,19 @@
         </is>
       </c>
       <c r="G166" t="n">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="H166" t="n">
         <v>0</v>
       </c>
       <c r="I166" t="n">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
       </c>
       <c r="K166" t="n">
-        <v>37</v>
+        <v>65</v>
       </c>
     </row>
     <row r="167">
@@ -7828,19 +7828,19 @@
         </is>
       </c>
       <c r="G172" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H172" t="n">
         <v>1</v>
       </c>
       <c r="I172" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J172" t="n">
         <v>20</v>
       </c>
       <c r="K172" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="173">
@@ -8181,11 +8181,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>343</v>
+        <v>429</v>
       </c>
     </row>
     <row r="3">
@@ -8194,11 +8194,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MEET11</t>
+          <t>VATSAL11</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>333</v>
+        <v>388</v>
       </c>
     </row>
     <row r="4">
@@ -8207,11 +8207,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>MEET11</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>331</v>
+        <v>385</v>
       </c>
     </row>
     <row r="5">
@@ -8220,11 +8220,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>317</v>
+        <v>372</v>
       </c>
     </row>
     <row r="6">
@@ -8233,11 +8233,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>VATSAL11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>297</v>
+        <v>363</v>
       </c>
     </row>
     <row r="7">
@@ -8246,11 +8246,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DIPESH11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>221</v>
+        <v>241</v>
       </c>
     </row>
     <row r="8">
@@ -8259,11 +8259,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>DIPESH11</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>168</v>
+        <v>221</v>
       </c>
     </row>
     <row r="9">
@@ -8276,7 +8276,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>164</v>
+        <v>199</v>
       </c>
     </row>
     <row r="10">
@@ -8285,11 +8285,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PRATIK11</t>
+          <t>NIRAV11</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>153</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11">
@@ -8298,11 +8298,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NIRAV11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>110</v>
+        <v>168</v>
       </c>
     </row>
   </sheetData>
@@ -8316,7 +8316,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C120"/>
+  <dimension ref="A1:C121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8369,7 +8369,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -8395,7 +8395,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -8421,7 +8421,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>51</v>
+        <v>103</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -8434,7 +8434,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -8476,7 +8476,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -8580,7 +8580,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -8603,7 +8603,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
@@ -8684,7 +8684,7 @@
         <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -8694,7 +8694,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
@@ -8733,10 +8733,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -8759,7 +8759,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>31</v>
+        <v>83</v>
       </c>
       <c r="C34" t="n">
         <v>0</v>
@@ -8772,7 +8772,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="C35" t="n">
         <v>0</v>
@@ -8827,7 +8827,7 @@
         <v>4</v>
       </c>
       <c r="C39" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40">
@@ -8902,10 +8902,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -9175,10 +9175,10 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="C66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
@@ -9318,7 +9318,7 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C77" t="n">
         <v>0</v>
@@ -9370,7 +9370,7 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c r="C81" t="n">
         <v>0</v>
@@ -9613,11 +9613,11 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>shreyas iyer</t>
+          <t>shivang kumar</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C100" t="n">
         <v>0</v>
@@ -9626,11 +9626,11 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>shubman gill</t>
+          <t>shreyas iyer</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="C101" t="n">
         <v>0</v>
@@ -9639,76 +9639,76 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>sunil narine</t>
+          <t>shubman gill</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>suryakumar yadav</t>
+          <t>sunil narine</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>suyash sharma</t>
+          <t>suryakumar yadav</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="C104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>t natarajan</t>
+          <t>suyash sharma</t>
         </is>
       </c>
       <c r="B105" t="n">
         <v>0</v>
       </c>
       <c r="C105" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>tilak varma</t>
+          <t>t natarajan</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="C106" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>tim david</t>
+          <t>tilak varma</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C107" t="n">
         <v>0</v>
@@ -9717,11 +9717,11 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>travis head</t>
+          <t>tim david</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C108" t="n">
         <v>0</v>
@@ -9730,11 +9730,11 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>trent boult</t>
+          <t>travis head</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="C109" t="n">
         <v>0</v>
@@ -9743,11 +9743,11 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>tristan stubbs</t>
+          <t>trent boult</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C110" t="n">
         <v>0</v>
@@ -9756,37 +9756,37 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>vaibhav arora</t>
+          <t>tristan stubbs</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>vaibhav suryavanshi</t>
+          <t>vaibhav arora</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="C112" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>varun chakravarthy</t>
+          <t>vaibhav suryavanshi</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="C113" t="n">
         <v>0</v>
@@ -9795,37 +9795,37 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>vijaykumar vyshak</t>
+          <t>varun chakravarthy</t>
         </is>
       </c>
       <c r="B114" t="n">
         <v>0</v>
       </c>
       <c r="C114" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>vipraj nigam</t>
+          <t>vijaykumar vyshak</t>
         </is>
       </c>
       <c r="B115" t="n">
         <v>0</v>
       </c>
       <c r="C115" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>virat kohli</t>
+          <t>vipraj nigam</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="C116" t="n">
         <v>0</v>
@@ -9834,37 +9834,37 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>washington sundar</t>
+          <t>virat kohli</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>18</v>
+        <v>69</v>
       </c>
       <c r="C117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>xavier bartlett</t>
+          <t>washington sundar</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>yashasvi jaiswal</t>
+          <t>xavier bartlett</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="C119" t="n">
         <v>0</v>
@@ -9873,13 +9873,26 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
+          <t>yashasvi jaiswal</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>38</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
           <t>yuzvendra chahal</t>
         </is>
       </c>
-      <c r="B120" t="n">
-        <v>0</v>
-      </c>
-      <c r="C120" t="n">
+      <c r="B121" t="n">
+        <v>0</v>
+      </c>
+      <c r="C121" t="n">
         <v>2</v>
       </c>
     </row>
@@ -11435,7 +11448,7 @@
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>rashid khan</t>
+          <t>shivang kumar</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -13089,7 +13102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13149,49 +13162,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Mitchel Marsh</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>SKY11</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>BAT</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>mitchell marsh</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>ai_structured</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>35</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>35</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>35</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/IPL_Fantasy_Points.xlsx
+++ b/IPL_Fantasy_Points.xlsx
@@ -561,19 +561,19 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>7</v>
+        <v>75</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>7</v>
+        <v>75</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>7</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4">
@@ -604,19 +604,19 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9">
@@ -819,19 +819,19 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>5</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10">
@@ -994,16 +994,16 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14">
@@ -1206,19 +1206,19 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="19">
@@ -1335,19 +1335,19 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>52</v>
+        <v>83</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>52</v>
+        <v>83</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>52</v>
+        <v>83</v>
       </c>
     </row>
     <row r="22">
@@ -1510,16 +1510,16 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26">
@@ -1550,19 +1550,19 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="27">
@@ -1667,31 +1667,31 @@
           <t>BOWL</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>ishan kishan</t>
-        </is>
-      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>tushar deshpande</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30">
@@ -1725,16 +1725,16 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="K30" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31">
@@ -1854,16 +1854,16 @@
         <v>7</v>
       </c>
       <c r="H33" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="K33" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
     </row>
     <row r="34">
@@ -1897,16 +1897,16 @@
         <v>12</v>
       </c>
       <c r="H34" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="K34" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
     </row>
     <row r="35">
@@ -2023,19 +2023,19 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>83</v>
+        <v>145</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>83</v>
+        <v>145</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>83</v>
+        <v>145</v>
       </c>
     </row>
     <row r="38">
@@ -2109,19 +2109,19 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>40</v>
+        <v>96</v>
       </c>
       <c r="H39" t="n">
         <v>2</v>
       </c>
       <c r="I39" t="n">
-        <v>40</v>
+        <v>96</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>40</v>
+        <v>96</v>
       </c>
     </row>
     <row r="40">
@@ -2195,19 +2195,19 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="42">
@@ -2281,19 +2281,19 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H43" t="n">
         <v>2</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J43" t="n">
         <v>40</v>
       </c>
       <c r="K43" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
     </row>
     <row r="44">
@@ -2367,19 +2367,19 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="46">
@@ -2413,16 +2413,16 @@
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="K46" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
     </row>
     <row r="47">
@@ -2613,31 +2613,31 @@
           <t>BOWL</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>rinku singh</t>
-        </is>
-      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>corbin bosch</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K51" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="52">
@@ -2656,31 +2656,31 @@
           <t>BOWL</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>sandeep sharma</t>
-        </is>
-      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>deepak chahar</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K52" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="53">
@@ -2699,15 +2699,15 @@
           <t>BOWL</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>rahul tewatia</t>
-        </is>
-      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>rahul chahar</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -2754,19 +2754,19 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="55">
@@ -2840,19 +2840,19 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="57">
@@ -2883,19 +2883,19 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>18</v>
+        <v>93</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>18</v>
+        <v>93</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>18</v>
+        <v>93</v>
       </c>
     </row>
     <row r="58">
@@ -2926,19 +2926,19 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="59">
@@ -3012,19 +3012,19 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>81</v>
+        <v>90</v>
       </c>
     </row>
     <row r="61">
@@ -3098,19 +3098,19 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>6</v>
+        <v>51</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>6</v>
+        <v>51</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>6</v>
+        <v>51</v>
       </c>
     </row>
     <row r="63">
@@ -3184,19 +3184,19 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="H64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I64" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="J64" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="K64" t="n">
-        <v>20</v>
+        <v>64</v>
       </c>
     </row>
     <row r="65">
@@ -3218,7 +3218,7 @@
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>jamie overton</t>
+          <t>liam livingstone</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3313,19 +3313,19 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="68">
@@ -3433,7 +3433,7 @@
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>mitchell marsh</t>
+          <t>mitchell santner</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3473,31 +3473,31 @@
           <t>BOWL</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>mitchell marsh</t>
-        </is>
-      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>mitchell santner</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>ai_structured</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I71" t="n">
         <v>0</v>
       </c>
       <c r="J71" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K71" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="72">
@@ -3528,19 +3528,19 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
     </row>
     <row r="73">
@@ -3571,19 +3571,19 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>13</v>
+        <v>86</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>13</v>
+        <v>86</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>13</v>
+        <v>86</v>
       </c>
     </row>
     <row r="74">
@@ -3614,19 +3614,19 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>37</v>
+        <v>80</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>37</v>
+        <v>80</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>37</v>
+        <v>80</v>
       </c>
     </row>
     <row r="75">
@@ -3657,19 +3657,19 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>7</v>
+        <v>46</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>7</v>
+        <v>46</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>7</v>
+        <v>46</v>
       </c>
     </row>
     <row r="76">
@@ -3691,7 +3691,7 @@
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>mitchell marsh</t>
+          <t>mitchell santner</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3743,19 +3743,19 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="78">
@@ -3786,19 +3786,19 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="79">
@@ -3829,19 +3829,19 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="H79" t="n">
         <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>17</v>
+        <v>49</v>
       </c>
     </row>
     <row r="80">
@@ -3915,19 +3915,19 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>11</v>
+        <v>56</v>
       </c>
     </row>
     <row r="82">
@@ -4001,19 +4001,19 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>72</v>
+        <v>108</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>72</v>
+        <v>108</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>72</v>
+        <v>108</v>
       </c>
     </row>
     <row r="84">
@@ -4075,31 +4075,31 @@
           <t>BOWL</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>rashid khan</t>
-        </is>
-      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>avesh khan</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="G85" t="n">
         <v>0</v>
       </c>
       <c r="H85" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I85" t="n">
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="K85" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="86">
@@ -4133,16 +4133,16 @@
         <v>0</v>
       </c>
       <c r="H86" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I86" t="n">
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="K86" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="87">
@@ -4262,16 +4262,16 @@
         <v>11</v>
       </c>
       <c r="H89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I89" t="n">
         <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K89" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="90">
@@ -4302,19 +4302,19 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>38</v>
+        <v>93</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>38</v>
+        <v>93</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>38</v>
+        <v>93</v>
       </c>
     </row>
     <row r="91">
@@ -4388,19 +4388,19 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>18</v>
+        <v>68</v>
       </c>
     </row>
     <row r="93">
@@ -4431,19 +4431,19 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>38</v>
+        <v>64</v>
       </c>
     </row>
     <row r="94">
@@ -4732,19 +4732,19 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="H100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I100" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="J100" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K100" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
     </row>
     <row r="101">
@@ -4775,19 +4775,19 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="H101" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I101" t="n">
         <v>0</v>
       </c>
       <c r="J101" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="K101" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
     </row>
     <row r="102">
@@ -4938,7 +4938,7 @@
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>b sai sudharshan</t>
+          <t>manimaran siddharth</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -5036,16 +5036,16 @@
         <v>0</v>
       </c>
       <c r="H107" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I107" t="n">
         <v>0</v>
       </c>
       <c r="J107" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="K107" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="108">
@@ -5119,19 +5119,19 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="H109" t="n">
         <v>0</v>
       </c>
       <c r="I109" t="n">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
       </c>
       <c r="K109" t="n">
-        <v>35</v>
+        <v>49</v>
       </c>
     </row>
     <row r="110">
@@ -5162,19 +5162,19 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
       </c>
       <c r="I110" t="n">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
       </c>
       <c r="K110" t="n">
-        <v>78</v>
+        <v>113</v>
       </c>
     </row>
     <row r="111">
@@ -5205,19 +5205,19 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
       </c>
       <c r="I111" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
       </c>
       <c r="K111" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="112">
@@ -5291,19 +5291,19 @@
         </is>
       </c>
       <c r="G113" t="n">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="H113" t="n">
         <v>0</v>
       </c>
       <c r="I113" t="n">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
       </c>
       <c r="K113" t="n">
-        <v>1</v>
+        <v>45</v>
       </c>
     </row>
     <row r="114">
@@ -5411,7 +5411,7 @@
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>nandre burger</t>
+          <t>donavon ferreira</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -5463,7 +5463,7 @@
         </is>
       </c>
       <c r="G117" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
@@ -5552,16 +5552,16 @@
         <v>0</v>
       </c>
       <c r="H119" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I119" t="n">
         <v>0</v>
       </c>
       <c r="J119" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="K119" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
     </row>
     <row r="120">
@@ -5595,16 +5595,16 @@
         <v>0</v>
       </c>
       <c r="H120" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I120" t="n">
         <v>0</v>
       </c>
       <c r="J120" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="K120" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
     </row>
     <row r="121">
@@ -5979,19 +5979,19 @@
         </is>
       </c>
       <c r="G129" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
       </c>
       <c r="I129" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
       </c>
       <c r="K129" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="130">
@@ -6108,19 +6108,19 @@
         </is>
       </c>
       <c r="G132" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="H132" t="n">
         <v>0</v>
       </c>
       <c r="I132" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
       </c>
       <c r="K132" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
     </row>
     <row r="133">
@@ -6151,19 +6151,19 @@
         </is>
       </c>
       <c r="G133" t="n">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="H133" t="n">
         <v>0</v>
       </c>
       <c r="I133" t="n">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
       </c>
       <c r="K133" t="n">
-        <v>70</v>
+        <v>160</v>
       </c>
     </row>
     <row r="134">
@@ -6225,31 +6225,31 @@
           <t>BAT</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr"/>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>aniket verma</t>
-        </is>
-      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>prashant veer</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="G135" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H135" t="n">
         <v>0</v>
       </c>
       <c r="I135" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
       </c>
       <c r="K135" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="136">
@@ -6280,19 +6280,19 @@
         </is>
       </c>
       <c r="G136" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H136" t="n">
         <v>1</v>
       </c>
       <c r="I136" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J136" t="n">
         <v>20</v>
       </c>
       <c r="K136" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="137">
@@ -6326,16 +6326,16 @@
         <v>0</v>
       </c>
       <c r="H137" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I137" t="n">
         <v>0</v>
       </c>
       <c r="J137" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="K137" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="138">
@@ -6541,16 +6541,16 @@
         <v>1</v>
       </c>
       <c r="H142" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I142" t="n">
         <v>0</v>
       </c>
       <c r="J142" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="K142" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
     </row>
     <row r="143">
@@ -6667,19 +6667,19 @@
         </is>
       </c>
       <c r="G145" t="n">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
       </c>
       <c r="I145" t="n">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
       </c>
       <c r="K145" t="n">
-        <v>16</v>
+        <v>67</v>
       </c>
     </row>
     <row r="146">
@@ -6710,19 +6710,19 @@
         </is>
       </c>
       <c r="G146" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H146" t="n">
         <v>0</v>
       </c>
       <c r="I146" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
       </c>
       <c r="K146" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="147">
@@ -6796,19 +6796,19 @@
         </is>
       </c>
       <c r="G148" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H148" t="n">
         <v>0</v>
       </c>
       <c r="I148" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
       </c>
       <c r="K148" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="149">
@@ -7054,19 +7054,19 @@
         </is>
       </c>
       <c r="G154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H154" t="n">
         <v>2</v>
       </c>
       <c r="I154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J154" t="n">
         <v>40</v>
       </c>
       <c r="K154" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="155">
@@ -7100,16 +7100,16 @@
         <v>0</v>
       </c>
       <c r="H155" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I155" t="n">
         <v>0</v>
       </c>
       <c r="J155" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="K155" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
     </row>
     <row r="156">
@@ -7143,16 +7143,16 @@
         <v>0</v>
       </c>
       <c r="H156" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I156" t="n">
         <v>0</v>
       </c>
       <c r="J156" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="K156" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="157">
@@ -7315,16 +7315,16 @@
         <v>5</v>
       </c>
       <c r="H160" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I160" t="n">
         <v>0</v>
       </c>
       <c r="J160" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="K160" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="161">
@@ -7527,19 +7527,19 @@
         </is>
       </c>
       <c r="G165" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="H165" t="n">
         <v>0</v>
       </c>
       <c r="I165" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
       </c>
       <c r="K165" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
     </row>
     <row r="166">
@@ -7788,16 +7788,16 @@
         <v>9</v>
       </c>
       <c r="H171" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I171" t="n">
         <v>9</v>
       </c>
       <c r="J171" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="K171" t="n">
-        <v>29</v>
+        <v>49</v>
       </c>
     </row>
     <row r="172">
@@ -8031,31 +8031,31 @@
           <t>BOWL</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr"/>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>lokesh rahul</t>
-        </is>
-      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>digvesh rathi</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr"/>
       <c r="F177" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="G177" t="n">
         <v>0</v>
       </c>
       <c r="H177" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I177" t="n">
         <v>0</v>
       </c>
       <c r="J177" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K177" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="178">
@@ -8181,11 +8181,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>DIPESH11</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>429</v>
+        <v>630</v>
       </c>
     </row>
     <row r="3">
@@ -8194,11 +8194,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>VATSAL11</t>
+          <t>MEET11</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>388</v>
+        <v>629</v>
       </c>
     </row>
     <row r="4">
@@ -8207,11 +8207,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MEET11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>385</v>
+        <v>614</v>
       </c>
     </row>
     <row r="5">
@@ -8220,11 +8220,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>VATSAL11</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>372</v>
+        <v>585</v>
       </c>
     </row>
     <row r="6">
@@ -8237,7 +8237,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>363</v>
+        <v>534</v>
       </c>
     </row>
     <row r="7">
@@ -8246,11 +8246,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PRATIK11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>241</v>
+        <v>507</v>
       </c>
     </row>
     <row r="8">
@@ -8259,11 +8259,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DIPESH11</t>
+          <t>BABA11</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>221</v>
+        <v>437</v>
       </c>
     </row>
     <row r="9">
@@ -8272,11 +8272,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BABA11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>199</v>
+        <v>387</v>
       </c>
     </row>
     <row r="10">
@@ -8285,11 +8285,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NIRAV11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>178</v>
+        <v>354</v>
       </c>
     </row>
     <row r="11">
@@ -8298,11 +8298,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>NIRAV11</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>168</v>
+        <v>302</v>
       </c>
     </row>
   </sheetData>
@@ -8316,7 +8316,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C121"/>
+  <dimension ref="A1:C133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8343,7 +8343,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -8382,7 +8382,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -8434,7 +8434,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -8463,7 +8463,7 @@
         <v>7</v>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -8502,43 +8502,43 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>axar patel</t>
+          <t>avesh khan</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ayush badoni</t>
+          <t>axar patel</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ayush mhatre</t>
+          <t>ayush badoni</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -8547,11 +8547,11 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>b sai sudharshan</t>
+          <t>ayush mhatre</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>73</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -8560,63 +8560,63 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>bhuvneshwar kumar</t>
+          <t>b sai sudharshan</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>blessing muzarabani</t>
+          <t>bhuvneshwar kumar</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>brijesh sharma</t>
+          <t>blessing muzarabani</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>cameron green</t>
+          <t>brijesh sharma</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>cooper connolly</t>
+          <t>cameron green</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>72</v>
+        <v>20</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
@@ -8625,11 +8625,11 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>david miller</t>
+          <t>cooper connolly</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
@@ -8638,24 +8638,24 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>david payne</t>
+          <t>corbin bosch</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>devdutt padikkal</t>
+          <t>david miller</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>61</v>
+        <v>21</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
@@ -8664,37 +8664,37 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>dhruv chand jurel</t>
+          <t>david payne</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>eshan malinga</t>
+          <t>deepak chahar</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>finn allen</t>
+          <t>devdutt padikkal</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
@@ -8703,11 +8703,11 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>glenn phillips</t>
+          <t>dhruv chand jurel</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>25</v>
+        <v>93</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
@@ -8716,11 +8716,11 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>hardik pandya</t>
+          <t>digvesh rathi</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="C31" t="n">
         <v>1</v>
@@ -8729,37 +8729,37 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>harsh dubey</t>
+          <t>donavon ferreira</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>harshal patel</t>
+          <t>eshan malinga</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>heinrich klaasen</t>
+          <t>finn allen</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="C34" t="n">
         <v>0</v>
@@ -8768,11 +8768,11 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ishan kishan</t>
+          <t>glenn phillips</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>94</v>
+        <v>28</v>
       </c>
       <c r="C35" t="n">
         <v>0</v>
@@ -8781,37 +8781,37 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>jacob duffy</t>
+          <t>hardik pandya</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C36" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>jamie overton</t>
+          <t>harsh dubey</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>jasprit bumrah</t>
+          <t>harshal patel</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -8820,24 +8820,24 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>jaydev unadkat</t>
+          <t>heinrich klaasen</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4</v>
+        <v>145</v>
       </c>
       <c r="C39" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>jitesh sharma</t>
+          <t>ishan kishan</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="C40" t="n">
         <v>0</v>
@@ -8846,24 +8846,24 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>jofra archer</t>
+          <t>jacob duffy</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>jos buttler</t>
+          <t>jamie overton</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
@@ -8872,63 +8872,63 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>kagiso rabada</t>
+          <t>jasprit bumrah</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>0</v>
       </c>
       <c r="C43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>kartik sharma</t>
+          <t>jaydev unadkat</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>kartik tyagi</t>
+          <t>jitesh sharma</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>khaleel ahmed</t>
+          <t>jofra archer</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>krunal pandya</t>
+          <t>jos buttler</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="C47" t="n">
         <v>0</v>
@@ -8937,24 +8937,24 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>kuldeep yadav</t>
+          <t>kagiso rabada</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="C48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>lokesh rahul</t>
+          <t>kartik sharma</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="C49" t="n">
         <v>0</v>
@@ -8963,33 +8963,33 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>lungi ngidi</t>
+          <t>kartik tyagi</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>marco jansen</t>
+          <t>khaleel ahmed</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>marcus stoinis</t>
+          <t>krunal pandya</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -9002,24 +9002,24 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>matt henry</t>
+          <t>kuldeep yadav</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>matt short</t>
+          <t>kumar kushagra</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="C54" t="n">
         <v>0</v>
@@ -9028,11 +9028,11 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>mayank markande</t>
+          <t>liam livingstone</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="C55" t="n">
         <v>0</v>
@@ -9041,11 +9041,11 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>mitchell marsh</t>
+          <t>lokesh rahul</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
@@ -9054,50 +9054,50 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>mohammed shami</t>
+          <t>lungi ngidi</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C57" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>mohammed siraj</t>
+          <t>manimaran siddharth</t>
         </is>
       </c>
       <c r="B58" t="n">
         <v>0</v>
       </c>
       <c r="C58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>mohsin khan</t>
+          <t>marco jansen</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>mukesh kumar</t>
+          <t>marcus stoinis</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C60" t="n">
         <v>0</v>
@@ -9106,24 +9106,24 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>mukul choudhary</t>
+          <t>matt henry</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="C61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>naman dhir</t>
+          <t>matt short</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C62" t="n">
         <v>0</v>
@@ -9132,24 +9132,24 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>nandre burger</t>
+          <t>mayank markande</t>
         </is>
       </c>
       <c r="B63" t="n">
         <v>0</v>
       </c>
       <c r="C63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>nehal wadhera</t>
+          <t>mitchell marsh</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>3</v>
+        <v>49</v>
       </c>
       <c r="C64" t="n">
         <v>0</v>
@@ -9158,76 +9158,76 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>nicholas pooran</t>
+          <t>mitchell santner</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>nitish kumar reddy</t>
+          <t>mohammed shami</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="C66" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>nitish rana</t>
+          <t>mohammed siraj</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="C67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>noor ahmad</t>
+          <t>mohsin khan</t>
         </is>
       </c>
       <c r="B68" t="n">
+        <v>0</v>
+      </c>
+      <c r="C68" t="n">
         <v>1</v>
-      </c>
-      <c r="C68" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>pathum nissanka</t>
+          <t>mukesh kumar</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>philip salt</t>
+          <t>mukul choudhary</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C70" t="n">
         <v>0</v>
@@ -9236,11 +9236,11 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>prabhsimran singh</t>
+          <t>naman dhir</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C71" t="n">
         <v>0</v>
@@ -9249,7 +9249,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>prasidh krishna</t>
+          <t>nandre burger</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -9262,24 +9262,24 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>prince yadav</t>
+          <t>nehal wadhera</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="C73" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>priyansh arya</t>
+          <t>nicholas pooran</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C74" t="n">
         <v>0</v>
@@ -9288,24 +9288,24 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>rahul tewatia</t>
+          <t>nitish kumar reddy</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>11</v>
+        <v>96</v>
       </c>
       <c r="C75" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>rajat patidar</t>
+          <t>nitish rana</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="C76" t="n">
         <v>0</v>
@@ -9314,11 +9314,11 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ramandeep singh</t>
+          <t>noor ahmad</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="C77" t="n">
         <v>0</v>
@@ -9327,50 +9327,50 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>rashid khan</t>
+          <t>pathum nissanka</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="C78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ravi bishnoi</t>
+          <t>philip salt</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ravindra jadeja</t>
+          <t>prabhsimran singh</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="C80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>rinku singh</t>
+          <t>prashant veer</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>68</v>
+        <v>6</v>
       </c>
       <c r="C81" t="n">
         <v>0</v>
@@ -9379,37 +9379,37 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>rishabh pant</t>
+          <t>prasidh krishna</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C82" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>riyan parag</t>
+          <t>prince yadav</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C83" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>rohit sharma</t>
+          <t>priyansh arya</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="C84" t="n">
         <v>0</v>
@@ -9418,24 +9418,24 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>romario shepherd</t>
+          <t>rahul chahar</t>
         </is>
       </c>
       <c r="B85" t="n">
         <v>0</v>
       </c>
       <c r="C85" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ruturaj gaikwad</t>
+          <t>rahul tewatia</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
@@ -9444,11 +9444,11 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ryan rickelton</t>
+          <t>rajat patidar</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>81</v>
+        <v>31</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
@@ -9457,11 +9457,11 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>salil arora</t>
+          <t>ramandeep singh</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
@@ -9470,50 +9470,50 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>sameer rizvi</t>
+          <t>rashid khan</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>70</v>
+        <v>24</v>
       </c>
       <c r="C89" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>sandeep sharma</t>
+          <t>ravi bishnoi</t>
         </is>
       </c>
       <c r="B90" t="n">
         <v>0</v>
       </c>
       <c r="C90" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>sanju samson</t>
+          <t>ravindra jadeja</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C91" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>sarfaraz khan</t>
+          <t>rinku singh</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
@@ -9522,11 +9522,11 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>shahbaz ahmed</t>
+          <t>rishabh pant</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
@@ -9535,50 +9535,50 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>shahrukh khan</t>
+          <t>riyan parag</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="C94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>shardul thakur</t>
+          <t>rohit sharma</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0</v>
+        <v>113</v>
       </c>
       <c r="C95" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>shashank singh</t>
+          <t>romario shepherd</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C96" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>sherfane rutherford</t>
+          <t>ruturaj gaikwad</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="C97" t="n">
         <v>0</v>
@@ -9587,11 +9587,11 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>shimron hetmyer</t>
+          <t>ryan rickelton</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="C98" t="n">
         <v>0</v>
@@ -9600,11 +9600,11 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>shivam dube</t>
+          <t>salil arora</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C99" t="n">
         <v>0</v>
@@ -9613,11 +9613,11 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>shivang kumar</t>
+          <t>sameer rizvi</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>4</v>
+        <v>160</v>
       </c>
       <c r="C100" t="n">
         <v>0</v>
@@ -9626,24 +9626,24 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>shreyas iyer</t>
+          <t>sandeep sharma</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="C101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>shubman gill</t>
+          <t>sanju samson</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="C102" t="n">
         <v>0</v>
@@ -9652,24 +9652,24 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>sunil narine</t>
+          <t>sarfaraz khan</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="C103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>suryakumar yadav</t>
+          <t>shahbaz ahmed</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C104" t="n">
         <v>0</v>
@@ -9678,20 +9678,20 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>suyash sharma</t>
+          <t>shahrukh khan</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>t natarajan</t>
+          <t>shardul thakur</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -9704,11 +9704,11 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>tilak varma</t>
+          <t>shashank singh</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C107" t="n">
         <v>0</v>
@@ -9717,11 +9717,11 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>tim david</t>
+          <t>sherfane rutherford</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C108" t="n">
         <v>0</v>
@@ -9730,11 +9730,11 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>travis head</t>
+          <t>shimron hetmyer</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>57</v>
+        <v>18</v>
       </c>
       <c r="C109" t="n">
         <v>0</v>
@@ -9743,11 +9743,11 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>trent boult</t>
+          <t>shivam dube</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="C110" t="n">
         <v>0</v>
@@ -9756,37 +9756,37 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>tristan stubbs</t>
+          <t>shivang kumar</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="C111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>vaibhav arora</t>
+          <t>shreyas iyer</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="C112" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>vaibhav suryavanshi</t>
+          <t>shubman gill</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="C113" t="n">
         <v>0</v>
@@ -9795,76 +9795,76 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>varun chakravarthy</t>
+          <t>sunil narine</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>vijaykumar vyshak</t>
+          <t>suryakumar yadav</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="C115" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>vipraj nigam</t>
+          <t>suyash sharma</t>
         </is>
       </c>
       <c r="B116" t="n">
         <v>0</v>
       </c>
       <c r="C116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>virat kohli</t>
+          <t>t natarajan</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="C117" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>washington sundar</t>
+          <t>tilak varma</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>xavier bartlett</t>
+          <t>tim david</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C119" t="n">
         <v>0</v>
@@ -9873,11 +9873,11 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>yashasvi jaiswal</t>
+          <t>travis head</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="C120" t="n">
         <v>0</v>
@@ -9886,14 +9886,170 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
+          <t>trent boult</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>0</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>tristan stubbs</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>42</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>tushar deshpande</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>0</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>vaibhav arora</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>1</v>
+      </c>
+      <c r="C124" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>vaibhav suryavanshi</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>83</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>varun chakravarthy</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>0</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>vijaykumar vyshak</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>0</v>
+      </c>
+      <c r="C127" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>vipraj nigam</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>0</v>
+      </c>
+      <c r="C128" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>virat kohli</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>69</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>washington sundar</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>22</v>
+      </c>
+      <c r="C130" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>xavier bartlett</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>11</v>
+      </c>
+      <c r="C131" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>yashasvi jaiswal</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>93</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
           <t>yuzvendra chahal</t>
         </is>
       </c>
-      <c r="B121" t="n">
-        <v>0</v>
-      </c>
-      <c r="C121" t="n">
-        <v>2</v>
+      <c r="B133" t="n">
+        <v>0</v>
+      </c>
+      <c r="C133" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -9907,7 +10063,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K72"/>
+  <dimension ref="A1:K64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10357,7 +10513,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>tushar deshpande</t>
+          <t>Kuldeep sen</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -10373,7 +10529,7 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ishan kishan</t>
+          <t>kuldeep yadav</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -10400,23 +10556,23 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Kuldeep sen</t>
+          <t>Quinton de Kock</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MEET11</t>
+          <t>VATSAL11</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>kuldeep yadav</t>
+          <t>washington sundar</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -10443,7 +10599,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Quinton de Kock</t>
+          <t>Tom Banton</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -10459,7 +10615,7 @@
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>washington sundar</t>
+          <t>t natarajan</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -10486,7 +10642,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Tom Banton</t>
+          <t>Tim Siefert</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -10502,7 +10658,7 @@
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>t natarajan</t>
+          <t>jamie overton</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -10529,7 +10685,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Tim Siefert</t>
+          <t>Lockie Ferguson</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -10539,13 +10695,13 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>jamie overton</t>
+          <t>lokesh rahul</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -10572,7 +10728,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Lockie Ferguson</t>
+          <t>Adam Milne</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -10588,7 +10744,7 @@
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>lokesh rahul</t>
+          <t>david miller</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -10615,23 +10771,23 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Adam Milne</t>
+          <t>Jos Inglis</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>VATSAL11</t>
+          <t>BABA11</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>david miller</t>
+          <t>marcus stoinis</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -10658,23 +10814,23 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Corbin Bosch</t>
+          <t>Prithvi Shaw</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>VATSAL11</t>
+          <t>BABA11</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>rinku singh</t>
+          <t>prasidh krishna</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -10701,23 +10857,23 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Deepak Chahar</t>
+          <t>Rowman Powell</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>VATSAL11</t>
+          <t>BABA11</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>sandeep sharma</t>
+          <t>romario shepherd</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -10744,23 +10900,23 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Rahul Chahar</t>
+          <t>liam livingston</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>VATSAL11</t>
+          <t>BABA11</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>rahul tewatia</t>
+          <t>liam livingstone</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -10787,7 +10943,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Jos Inglis</t>
+          <t>rachin ravindra</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -10797,13 +10953,13 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>marcus stoinis</t>
+          <t>rashid khan</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -10830,7 +10986,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Prithvi Shaw</t>
+          <t>Zeeshan Ansari</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -10840,13 +10996,13 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>prasidh krishna</t>
+          <t>eshan malinga</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -10873,7 +11029,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rowman Powell</t>
+          <t>Mitchell Starc</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10883,13 +11039,13 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>romario shepherd</t>
+          <t>mitchell santner</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -10916,23 +11072,23 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>liam livingston</t>
+          <t>Mitchel Owen</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BABA11</t>
+          <t>DIPESH11</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>jamie overton</t>
+          <t>mitchell santner</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -10959,12 +11115,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>rachin ravindra</t>
+          <t>Pat Cummins</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BABA11</t>
+          <t>DIPESH11</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -10975,7 +11131,7 @@
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>rashid khan</t>
+          <t>pathum nissanka</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -11002,12 +11158,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Zeeshan Ansari</t>
+          <t>Aqib Nabi Dar</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BABA11</t>
+          <t>DIPESH11</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -11018,7 +11174,7 @@
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>eshan malinga</t>
+          <t>b sai sudharshan</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -11045,12 +11201,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Mitchell Starc</t>
+          <t>Rasik Dar Salam</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BABA11</t>
+          <t>DIPESH11</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -11061,7 +11217,7 @@
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>mitchell marsh</t>
+          <t>rashid khan</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -11088,23 +11244,23 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Mitchel Santner</t>
+          <t>KL Rahul</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BABA11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>mitchell marsh</t>
+          <t>lokesh rahul</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -11131,12 +11287,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Mitchel Owen</t>
+          <t>Urvil Patel</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>DIPESH11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -11147,7 +11303,7 @@
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>mitchell marsh</t>
+          <t>axar patel</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -11174,23 +11330,23 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Pat Cummins</t>
+          <t>Arshin Kulkarni</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>DIPESH11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>pathum nissanka</t>
+          <t>shivang kumar</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -11217,23 +11373,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>avesh khan</t>
+          <t>Nishant Sindhu</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>DIPESH11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>rashid khan</t>
+          <t>shashank singh</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -11260,23 +11416,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Aqib Nabi Dar</t>
+          <t>Jayant Yadav</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>DIPESH11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>b sai sudharshan</t>
+          <t>prince yadav</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -11303,23 +11459,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Rasik Dar Salam</t>
+          <t>Ajay Mandal</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>DIPESH11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>rashid khan</t>
+          <t>rajat patidar</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -11346,7 +11502,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>KL Rahul</t>
+          <t>Will Jacks</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -11356,13 +11512,13 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>lokesh rahul</t>
+          <t>mitchell marsh</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -11389,7 +11545,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Urvil Patel</t>
+          <t>Josh Hazelwood</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -11399,13 +11555,13 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>axar patel</t>
+          <t>shahbaz ahmed</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -11432,7 +11588,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Arshin Kulkarni</t>
+          <t>Kyle Jamieson</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -11442,13 +11598,13 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>shivang kumar</t>
+          <t>jamie overton</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -11475,7 +11631,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Nishant Sindhu</t>
+          <t>Matheesha Pathirana</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -11485,13 +11641,13 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>shashank singh</t>
+          <t>eshan malinga</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -11518,7 +11674,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Jayant Yadav</t>
+          <t>M Siddharth</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -11528,13 +11684,13 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>prince yadav</t>
+          <t>manimaran siddharth</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -11561,7 +11717,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Ajay Mandal</t>
+          <t>Ben Dwarshuis</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -11571,13 +11727,13 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>rajat patidar</t>
+          <t>b sai sudharshan</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -11604,23 +11760,23 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Will Jacks</t>
+          <t>Manish Pandey</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>mitchell marsh</t>
+          <t>hardik pandya</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -11647,23 +11803,23 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Josh Hazelwood</t>
+          <t>Donovan Ferreira</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>shahbaz ahmed</t>
+          <t>donavon ferreira</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -11690,12 +11846,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Kyle Jamieson</t>
+          <t>Mukesh Choudhary</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -11706,7 +11862,7 @@
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>jamie overton</t>
+          <t>mukul choudhary</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -11733,12 +11889,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Matheesha Pathirana</t>
+          <t>Gurjapneet Singh</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -11749,7 +11905,7 @@
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>eshan malinga</t>
+          <t>ramandeep singh</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -11776,12 +11932,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>M Siddharth</t>
+          <t>Arjun Tendulkar</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -11792,7 +11948,7 @@
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>b sai sudharshan</t>
+          <t>krunal pandya</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -11819,12 +11975,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Ben Dwarshuis</t>
+          <t>Kwena Maphaka</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -11835,7 +11991,7 @@
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>b sai sudharshan</t>
+          <t>aiden markram</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -11862,12 +12018,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Manish Pandey</t>
+          <t>Ramkrishna Ghosh</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -11878,7 +12034,7 @@
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>hardik pandya</t>
+          <t>angkrish raghuvanshi</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -11905,23 +12061,23 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Donovan Ferreira</t>
+          <t>Venkatesh Iyer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>nandre burger</t>
+          <t>shreyas iyer</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -11948,23 +12104,23 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mukesh Choudhary</t>
+          <t>ashutosh sharma</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>mukul choudhary</t>
+          <t>ashok sharma</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -11991,23 +12147,23 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Gurjapneet Singh</t>
+          <t>Azmatullah Omarzai</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>ramandeep singh</t>
+          <t>mitchell marsh</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -12034,23 +12190,23 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Arjun Tendulkar</t>
+          <t>akshat raghuwanshi</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>krunal pandya</t>
+          <t>angkrish raghuvanshi</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -12077,23 +12233,23 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Kwena Maphaka</t>
+          <t>Himmat Singh</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>aiden markram</t>
+          <t>prabhsimran singh</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -12120,12 +12276,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Ramkrishna Ghosh</t>
+          <t>Suryansh Shegde</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -12136,7 +12292,7 @@
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>angkrish raghuvanshi</t>
+          <t>suyash sharma</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -12163,12 +12319,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Venkatesh Iyer</t>
+          <t>Tejasvi Singh</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -12179,7 +12335,7 @@
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>shreyas iyer</t>
+          <t>prabhsimran singh</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -12206,23 +12362,23 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ashutosh sharma</t>
+          <t>Sai Kishor</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>ashok sharma</t>
+          <t>ishan kishan</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -12249,23 +12405,23 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Prashant Veer</t>
+          <t>Akash Deep</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>aniket verma</t>
+          <t>arshdeep singh</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -12292,23 +12448,23 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Azmatullah Omarzai</t>
+          <t>Ben Duckett</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>mitchell marsh</t>
+          <t>ryan rickelton</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -12335,12 +12491,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>akshat raghuwanshi</t>
+          <t>Abhishek Porel</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -12351,7 +12507,7 @@
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>angkrish raghuvanshi</t>
+          <t>abhishek sharma</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -12378,12 +12534,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Himmat Singh</t>
+          <t>Rahul Tripathi</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -12394,7 +12550,7 @@
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>prabhsimran singh</t>
+          <t>rahul tewatia</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -12421,12 +12577,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Suryansh Shegde</t>
+          <t>Dre Pretorius</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -12437,7 +12593,7 @@
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>suyash sharma</t>
+          <t>nandre burger</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -12464,12 +12620,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Tejasvi Singh</t>
+          <t>Matthew Breetzke</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -12480,7 +12636,7 @@
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>prabhsimran singh</t>
+          <t>matt henry</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -12507,23 +12663,23 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sai Kishor</t>
+          <t>Anuj Rawat</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>ishan kishan</t>
+          <t>rahul tewatia</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -12550,23 +12706,23 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Akash Deep</t>
+          <t>Wanindu Hasaranga</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>arshdeep singh</t>
+          <t>sandeep sharma</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -12593,7 +12749,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Ben Duckett</t>
+          <t>Harpreet Brar</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -12603,13 +12759,13 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>ryan rickelton</t>
+          <t>jasprit bumrah</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -12636,7 +12792,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Abhishek Porel</t>
+          <t>Mayank Yadav</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -12646,13 +12802,13 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>abhishek sharma</t>
+          <t>mayank markande</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -12673,350 +12829,6 @@
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Rahul Tripathi</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>BAT</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>rahul tewatia</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="G65" t="n">
-        <v>0</v>
-      </c>
-      <c r="H65" t="n">
-        <v>0</v>
-      </c>
-      <c r="I65" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" t="n">
-        <v>0</v>
-      </c>
-      <c r="K65" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Dre Pretorius</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>BAT</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>nandre burger</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="G66" t="n">
-        <v>0</v>
-      </c>
-      <c r="H66" t="n">
-        <v>0</v>
-      </c>
-      <c r="I66" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" t="n">
-        <v>0</v>
-      </c>
-      <c r="K66" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Matthew Breetzke</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>BAT</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>matt henry</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="G67" t="n">
-        <v>0</v>
-      </c>
-      <c r="H67" t="n">
-        <v>0</v>
-      </c>
-      <c r="I67" t="n">
-        <v>0</v>
-      </c>
-      <c r="J67" t="n">
-        <v>0</v>
-      </c>
-      <c r="K67" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Anuj Rawat</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>BAT</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>rahul tewatia</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="G68" t="n">
-        <v>0</v>
-      </c>
-      <c r="H68" t="n">
-        <v>0</v>
-      </c>
-      <c r="I68" t="n">
-        <v>0</v>
-      </c>
-      <c r="J68" t="n">
-        <v>0</v>
-      </c>
-      <c r="K68" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Wanindu Hasaranga</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>AR</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>sandeep sharma</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="G69" t="n">
-        <v>0</v>
-      </c>
-      <c r="H69" t="n">
-        <v>0</v>
-      </c>
-      <c r="I69" t="n">
-        <v>0</v>
-      </c>
-      <c r="J69" t="n">
-        <v>0</v>
-      </c>
-      <c r="K69" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Harpreet Brar</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>BOWL</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>jasprit bumrah</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="G70" t="n">
-        <v>0</v>
-      </c>
-      <c r="H70" t="n">
-        <v>0</v>
-      </c>
-      <c r="I70" t="n">
-        <v>0</v>
-      </c>
-      <c r="J70" t="n">
-        <v>0</v>
-      </c>
-      <c r="K70" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Mayank Yadav</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>BOWL</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>mayank markande</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="G71" t="n">
-        <v>0</v>
-      </c>
-      <c r="H71" t="n">
-        <v>0</v>
-      </c>
-      <c r="I71" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" t="n">
-        <v>0</v>
-      </c>
-      <c r="K71" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Digvesh Rathi</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>BOWL</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>lokesh rahul</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="G72" t="n">
-        <v>0</v>
-      </c>
-      <c r="H72" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" t="n">
-        <v>0</v>
-      </c>
-      <c r="J72" t="n">
-        <v>0</v>
-      </c>
-      <c r="K72" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13102,7 +12914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13162,6 +12974,49 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Mitchel Santner</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BABA11</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>BOWL</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>mitchell santner</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>ai_structured</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>18</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>20</v>
+      </c>
+      <c r="K2" t="n">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/IPL_Fantasy_Points.xlsx
+++ b/IPL_Fantasy_Points.xlsx
@@ -690,19 +690,19 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>31</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9">
@@ -1851,19 +1851,19 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="H33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="K33" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="34">
@@ -2499,16 +2499,16 @@
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I48" t="n">
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="K48" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
     </row>
     <row r="49">
@@ -2754,19 +2754,19 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="55">
@@ -3098,19 +3098,19 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="H62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I62" t="n">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>51</v>
+        <v>69</v>
       </c>
     </row>
     <row r="63">
@@ -3528,19 +3528,19 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="73">
@@ -3829,19 +3829,19 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>49</v>
+        <v>99</v>
       </c>
       <c r="H79" t="n">
         <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>49</v>
+        <v>99</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>49</v>
+        <v>99</v>
       </c>
     </row>
     <row r="80">
@@ -3958,19 +3958,19 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>16</v>
+        <v>86</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>16</v>
+        <v>86</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>16</v>
+        <v>86</v>
       </c>
     </row>
     <row r="83">
@@ -5076,19 +5076,19 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="H108" t="n">
         <v>0</v>
       </c>
       <c r="I108" t="n">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
       </c>
       <c r="K108" t="n">
-        <v>8</v>
+        <v>54</v>
       </c>
     </row>
     <row r="109">
@@ -5377,19 +5377,19 @@
         </is>
       </c>
       <c r="G115" t="n">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="H115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I115" t="n">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="J115" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K115" t="n">
-        <v>43</v>
+        <v>100</v>
       </c>
     </row>
     <row r="116">
@@ -5850,19 +5850,19 @@
         </is>
       </c>
       <c r="G126" t="n">
-        <v>61</v>
+        <v>111</v>
       </c>
       <c r="H126" t="n">
         <v>0</v>
       </c>
       <c r="I126" t="n">
-        <v>61</v>
+        <v>111</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
       </c>
       <c r="K126" t="n">
-        <v>61</v>
+        <v>111</v>
       </c>
     </row>
     <row r="127">
@@ -6237,19 +6237,19 @@
         </is>
       </c>
       <c r="G135" t="n">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="H135" t="n">
         <v>0</v>
       </c>
       <c r="I135" t="n">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
       </c>
       <c r="K135" t="n">
-        <v>6</v>
+        <v>49</v>
       </c>
     </row>
     <row r="136">
@@ -6624,19 +6624,19 @@
         </is>
       </c>
       <c r="G144" t="n">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
       </c>
       <c r="I144" t="n">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
       </c>
       <c r="K144" t="n">
-        <v>69</v>
+        <v>97</v>
       </c>
     </row>
     <row r="145">
@@ -7014,16 +7014,16 @@
         <v>0</v>
       </c>
       <c r="H153" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I153" t="n">
         <v>0</v>
       </c>
       <c r="J153" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="K153" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="154">
@@ -7186,16 +7186,16 @@
         <v>0</v>
       </c>
       <c r="H157" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I157" t="n">
         <v>0</v>
       </c>
       <c r="J157" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="K157" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
     </row>
     <row r="158">
@@ -7312,7 +7312,7 @@
         </is>
       </c>
       <c r="G160" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H160" t="n">
         <v>2</v>
@@ -7527,19 +7527,19 @@
         </is>
       </c>
       <c r="G165" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H165" t="n">
         <v>0</v>
       </c>
       <c r="I165" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
       </c>
       <c r="K165" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="166">
@@ -8003,16 +8003,16 @@
         <v>0</v>
       </c>
       <c r="H176" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I176" t="n">
         <v>0</v>
       </c>
       <c r="J176" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="K176" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="177">
@@ -8129,7 +8129,7 @@
         </is>
       </c>
       <c r="G179" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H179" t="n">
         <v>0</v>
@@ -8185,7 +8185,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>630</v>
+        <v>757</v>
       </c>
     </row>
     <row r="3">
@@ -8194,11 +8194,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MEET11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>629</v>
+        <v>707</v>
       </c>
     </row>
     <row r="4">
@@ -8207,11 +8207,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>MEET11</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>614</v>
+        <v>649</v>
       </c>
     </row>
     <row r="5">
@@ -8220,11 +8220,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>VATSAL11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>585</v>
+        <v>637</v>
       </c>
     </row>
     <row r="6">
@@ -8233,11 +8233,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>534</v>
+        <v>635</v>
       </c>
     </row>
     <row r="7">
@@ -8246,11 +8246,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>VATSAL11</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>507</v>
+        <v>625</v>
       </c>
     </row>
     <row r="8">
@@ -8263,7 +8263,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>437</v>
+        <v>464</v>
       </c>
     </row>
     <row r="9">
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>354</v>
+        <v>375</v>
       </c>
     </row>
     <row r="11">
@@ -8302,7 +8302,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>302</v>
+        <v>356</v>
       </c>
     </row>
   </sheetData>
@@ -8359,7 +8359,7 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -8460,10 +8460,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -8551,7 +8551,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -8580,7 +8580,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -8694,7 +8694,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>61</v>
+        <v>111</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
@@ -8853,7 +8853,7 @@
         <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42">
@@ -8863,10 +8863,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -8954,7 +8954,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C49" t="n">
         <v>0</v>
@@ -8996,7 +8996,7 @@
         <v>0</v>
       </c>
       <c r="C52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -9110,7 +9110,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C61" t="n">
         <v>2</v>
@@ -9318,7 +9318,7 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C77" t="n">
         <v>0</v>
@@ -9344,7 +9344,7 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="C79" t="n">
         <v>0</v>
@@ -9370,7 +9370,7 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="C81" t="n">
         <v>0</v>
@@ -9448,7 +9448,7 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
@@ -9578,7 +9578,7 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C97" t="n">
         <v>0</v>
@@ -9643,7 +9643,7 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C102" t="n">
         <v>0</v>
@@ -9656,7 +9656,7 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>49</v>
+        <v>99</v>
       </c>
       <c r="C103" t="n">
         <v>0</v>
@@ -9747,10 +9747,10 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="C110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111">
@@ -9828,7 +9828,7 @@
         <v>0</v>
       </c>
       <c r="C116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="117">
@@ -9864,7 +9864,7 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>16</v>
+        <v>86</v>
       </c>
       <c r="C119" t="n">
         <v>0</v>
@@ -9994,7 +9994,7 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="C129" t="n">
         <v>0</v>

--- a/IPL_Fantasy_Points.xlsx
+++ b/IPL_Fantasy_Points.xlsx
@@ -819,19 +819,19 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>33</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10">
@@ -862,19 +862,19 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11">
@@ -1292,19 +1292,19 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
     </row>
     <row r="21">
@@ -1335,19 +1335,19 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>83</v>
+        <v>122</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>83</v>
+        <v>122</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>83</v>
+        <v>122</v>
       </c>
     </row>
     <row r="22">
@@ -1682,16 +1682,16 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="K29" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="30">
@@ -1725,16 +1725,16 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="K30" t="n">
-        <v>100</v>
+        <v>140</v>
       </c>
     </row>
     <row r="31">
@@ -1811,16 +1811,16 @@
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="33">
@@ -2324,19 +2324,19 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H44" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J44" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="K44" t="n">
-        <v>60</v>
+        <v>88</v>
       </c>
     </row>
     <row r="45">
@@ -2542,16 +2542,16 @@
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="K49" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
     </row>
     <row r="50">
@@ -2668,7 +2668,7 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H52" t="n">
         <v>1</v>
@@ -2883,19 +2883,19 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="58">
@@ -3012,19 +3012,19 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
     </row>
     <row r="61">
@@ -3132,7 +3132,7 @@
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>romario shepherd</t>
+          <t>rovman powell</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3313,19 +3313,19 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="68">
@@ -3460,7 +3460,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Mitchel Santner</t>
+          <t>mitchell santner</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3481,7 +3481,7 @@
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>ai_structured</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -4262,16 +4262,16 @@
         <v>11</v>
       </c>
       <c r="H89" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I89" t="n">
         <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="K89" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
     </row>
     <row r="90">
@@ -4302,19 +4302,19 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>93</v>
+        <v>170</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>93</v>
+        <v>170</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>93</v>
+        <v>170</v>
       </c>
     </row>
     <row r="91">
@@ -4732,19 +4732,19 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="H100" t="n">
         <v>1</v>
       </c>
       <c r="I100" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="J100" t="n">
         <v>20</v>
       </c>
       <c r="K100" t="n">
-        <v>42</v>
+        <v>62</v>
       </c>
     </row>
     <row r="101">
@@ -5036,16 +5036,16 @@
         <v>0</v>
       </c>
       <c r="H107" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I107" t="n">
         <v>0</v>
       </c>
       <c r="J107" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="K107" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
     </row>
     <row r="108">
@@ -5162,19 +5162,19 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
       </c>
       <c r="I110" t="n">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
       </c>
       <c r="K110" t="n">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="111">
@@ -5205,19 +5205,19 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
       </c>
       <c r="I111" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
       </c>
       <c r="K111" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="112">
@@ -5334,19 +5334,19 @@
         </is>
       </c>
       <c r="G114" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="H114" t="n">
         <v>1</v>
       </c>
       <c r="I114" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J114" t="n">
         <v>20</v>
       </c>
       <c r="K114" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
     </row>
     <row r="115">
@@ -6065,19 +6065,19 @@
         </is>
       </c>
       <c r="G131" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="H131" t="n">
         <v>0</v>
       </c>
       <c r="I131" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
       </c>
       <c r="K131" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
     </row>
     <row r="132">
@@ -6194,19 +6194,19 @@
         </is>
       </c>
       <c r="G134" t="n">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
       </c>
       <c r="I134" t="n">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
       </c>
       <c r="K134" t="n">
-        <v>103</v>
+        <v>110</v>
       </c>
     </row>
     <row r="135">
@@ -6452,7 +6452,7 @@
         </is>
       </c>
       <c r="G140" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H140" t="n">
         <v>0</v>
@@ -6581,7 +6581,7 @@
         </is>
       </c>
       <c r="G143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H143" t="n">
         <v>0</v>
@@ -6667,19 +6667,19 @@
         </is>
       </c>
       <c r="G145" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
       </c>
       <c r="I145" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
       </c>
       <c r="K145" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
     </row>
     <row r="146">
@@ -7057,16 +7057,16 @@
         <v>1</v>
       </c>
       <c r="H154" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I154" t="n">
         <v>1</v>
       </c>
       <c r="J154" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="K154" t="n">
-        <v>41</v>
+        <v>61</v>
       </c>
     </row>
     <row r="155">
@@ -7570,19 +7570,19 @@
         </is>
       </c>
       <c r="G166" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="H166" t="n">
         <v>0</v>
       </c>
       <c r="I166" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
       </c>
       <c r="K166" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
     </row>
     <row r="167">
@@ -8185,7 +8185,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>757</v>
+        <v>797</v>
       </c>
     </row>
     <row r="3">
@@ -8194,11 +8194,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>MEET11</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>707</v>
+        <v>796</v>
       </c>
     </row>
     <row r="4">
@@ -8207,11 +8207,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MEET11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>649</v>
+        <v>728</v>
       </c>
     </row>
     <row r="5">
@@ -8220,11 +8220,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>VATSAL11</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>637</v>
+        <v>693</v>
       </c>
     </row>
     <row r="6">
@@ -8237,7 +8237,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>635</v>
+        <v>661</v>
       </c>
     </row>
     <row r="7">
@@ -8246,11 +8246,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>VATSAL11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>625</v>
+        <v>657</v>
       </c>
     </row>
     <row r="8">
@@ -8259,11 +8259,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BABA11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>464</v>
+        <v>524</v>
       </c>
     </row>
     <row r="9">
@@ -8272,11 +8272,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>BABA11</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>387</v>
+        <v>499</v>
       </c>
     </row>
     <row r="10">
@@ -8285,11 +8285,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PRATIK11</t>
+          <t>NIRAV11</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>375</v>
+        <v>385</v>
       </c>
     </row>
     <row r="11">
@@ -8298,11 +8298,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NIRAV11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>356</v>
+        <v>381</v>
       </c>
     </row>
   </sheetData>
@@ -8316,7 +8316,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C133"/>
+  <dimension ref="A1:C135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8395,7 +8395,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -8411,7 +8411,7 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -8421,7 +8421,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -8616,7 +8616,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
@@ -8681,7 +8681,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C28" t="n">
         <v>1</v>
@@ -8707,7 +8707,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
@@ -8759,7 +8759,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="C34" t="n">
         <v>0</v>
@@ -8785,7 +8785,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C36" t="n">
         <v>1</v>
@@ -8876,7 +8876,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
@@ -8918,7 +8918,7 @@
         <v>1</v>
       </c>
       <c r="C46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
@@ -9240,7 +9240,7 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="C71" t="n">
         <v>0</v>
@@ -9256,17 +9256,17 @@
         <v>0</v>
       </c>
       <c r="C72" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>nehal wadhera</t>
+          <t>navdeep saini</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
@@ -9275,11 +9275,11 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>nicholas pooran</t>
+          <t>nehal wadhera</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C74" t="n">
         <v>0</v>
@@ -9288,37 +9288,37 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>nitish kumar reddy</t>
+          <t>nicholas pooran</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>96</v>
+        <v>9</v>
       </c>
       <c r="C75" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>nitish rana</t>
+          <t>nitish kumar reddy</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>15</v>
+        <v>96</v>
       </c>
       <c r="C76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>noor ahmad</t>
+          <t>nitish rana</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C77" t="n">
         <v>0</v>
@@ -9327,11 +9327,11 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>pathum nissanka</t>
+          <t>noor ahmad</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="C78" t="n">
         <v>0</v>
@@ -9340,11 +9340,11 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>philip salt</t>
+          <t>pathum nissanka</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="C79" t="n">
         <v>0</v>
@@ -9353,11 +9353,11 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>prabhsimran singh</t>
+          <t>philip salt</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="C80" t="n">
         <v>0</v>
@@ -9366,11 +9366,11 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>prashant veer</t>
+          <t>prabhsimran singh</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="C81" t="n">
         <v>0</v>
@@ -9379,20 +9379,20 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>prasidh krishna</t>
+          <t>prashant veer</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="C82" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>prince yadav</t>
+          <t>prasidh krishna</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -9405,24 +9405,24 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>priyansh arya</t>
+          <t>prince yadav</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="C84" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>rahul chahar</t>
+          <t>priyansh arya</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
@@ -9431,11 +9431,11 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>rahul tewatia</t>
+          <t>rahul chahar</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
@@ -9444,11 +9444,11 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>rajat patidar</t>
+          <t>rahul tewatia</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>79</v>
+        <v>23</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
@@ -9457,11 +9457,11 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ramandeep singh</t>
+          <t>rajat patidar</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>14</v>
+        <v>79</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
@@ -9470,63 +9470,63 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>rashid khan</t>
+          <t>ramandeep singh</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="C89" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ravi bishnoi</t>
+          <t>rashid khan</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="C90" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ravindra jadeja</t>
+          <t>ravi bishnoi</t>
         </is>
       </c>
       <c r="B91" t="n">
+        <v>0</v>
+      </c>
+      <c r="C91" t="n">
         <v>7</v>
-      </c>
-      <c r="C91" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>rinku singh</t>
+          <t>ravindra jadeja</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>68</v>
+        <v>7</v>
       </c>
       <c r="C92" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>rishabh pant</t>
+          <t>rinku singh</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
@@ -9535,63 +9535,63 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>riyan parag</t>
+          <t>rishabh pant</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>22</v>
+        <v>75</v>
       </c>
       <c r="C94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>rohit sharma</t>
+          <t>riyan parag</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>113</v>
+        <v>42</v>
       </c>
       <c r="C95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>romario shepherd</t>
+          <t>rohit sharma</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="C96" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ruturaj gaikwad</t>
+          <t>romario shepherd</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="C97" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ryan rickelton</t>
+          <t>rovman powell</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="C98" t="n">
         <v>0</v>
@@ -9600,11 +9600,11 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>salil arora</t>
+          <t>ruturaj gaikwad</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="C99" t="n">
         <v>0</v>
@@ -9613,11 +9613,11 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>sameer rizvi</t>
+          <t>ryan rickelton</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>160</v>
+        <v>98</v>
       </c>
       <c r="C100" t="n">
         <v>0</v>
@@ -9626,24 +9626,24 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>sandeep sharma</t>
+          <t>salil arora</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>sanju samson</t>
+          <t>sameer rizvi</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>22</v>
+        <v>160</v>
       </c>
       <c r="C102" t="n">
         <v>0</v>
@@ -9652,24 +9652,24 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>sarfaraz khan</t>
+          <t>sandeep sharma</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="C103" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>shahbaz ahmed</t>
+          <t>sanju samson</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C104" t="n">
         <v>0</v>
@@ -9678,11 +9678,11 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>shahrukh khan</t>
+          <t>sarfaraz khan</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>15</v>
+        <v>99</v>
       </c>
       <c r="C105" t="n">
         <v>0</v>
@@ -9691,24 +9691,24 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>shardul thakur</t>
+          <t>shahbaz ahmed</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C106" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>shashank singh</t>
+          <t>shahrukh khan</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C107" t="n">
         <v>0</v>
@@ -9717,20 +9717,20 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>sherfane rutherford</t>
+          <t>shardul thakur</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C108" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>shimron hetmyer</t>
+          <t>shashank singh</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -9743,76 +9743,76 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>shivam dube</t>
+          <t>sherfane rutherford</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>69</v>
+        <v>30</v>
       </c>
       <c r="C110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>shivang kumar</t>
+          <t>shimron hetmyer</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="C111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>shreyas iyer</t>
+          <t>shivam dube</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>shubman gill</t>
+          <t>shivang kumar</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="C113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>sunil narine</t>
+          <t>shreyas iyer</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>12</v>
+        <v>68</v>
       </c>
       <c r="C114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>suryakumar yadav</t>
+          <t>shubman gill</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="C115" t="n">
         <v>0</v>
@@ -9821,63 +9821,63 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>suyash sharma</t>
+          <t>sunil narine</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C116" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>t natarajan</t>
+          <t>suryakumar yadav</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="C117" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>tilak varma</t>
+          <t>suyash sharma</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="C118" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>tim david</t>
+          <t>t natarajan</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="C119" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>travis head</t>
+          <t>tilak varma</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="C120" t="n">
         <v>0</v>
@@ -9886,11 +9886,11 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>trent boult</t>
+          <t>tim david</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="C121" t="n">
         <v>0</v>
@@ -9899,11 +9899,11 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>tristan stubbs</t>
+          <t>travis head</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="C122" t="n">
         <v>0</v>
@@ -9912,102 +9912,102 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>tushar deshpande</t>
+          <t>trent boult</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>vaibhav arora</t>
+          <t>tristan stubbs</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="C124" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>vaibhav suryavanshi</t>
+          <t>tushar deshpande</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="C125" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>varun chakravarthy</t>
+          <t>vaibhav arora</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C126" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>vijaykumar vyshak</t>
+          <t>vaibhav suryavanshi</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="C127" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>vipraj nigam</t>
+          <t>varun chakravarthy</t>
         </is>
       </c>
       <c r="B128" t="n">
         <v>0</v>
       </c>
       <c r="C128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>virat kohli</t>
+          <t>vijaykumar vyshak</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="C129" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>washington sundar</t>
+          <t>vipraj nigam</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="C130" t="n">
         <v>1</v>
@@ -10016,39 +10016,65 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>xavier bartlett</t>
+          <t>virat kohli</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>11</v>
+        <v>97</v>
       </c>
       <c r="C131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>yashasvi jaiswal</t>
+          <t>washington sundar</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>93</v>
+        <v>22</v>
       </c>
       <c r="C132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
+          <t>xavier bartlett</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>11</v>
+      </c>
+      <c r="C133" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>yashasvi jaiswal</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>170</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
           <t>yuzvendra chahal</t>
         </is>
       </c>
-      <c r="B133" t="n">
-        <v>0</v>
-      </c>
-      <c r="C133" t="n">
+      <c r="B135" t="n">
+        <v>0</v>
+      </c>
+      <c r="C135" t="n">
         <v>3</v>
       </c>
     </row>
@@ -10873,7 +10899,7 @@
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>romario shepherd</t>
+          <t>rovman powell</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -12914,7 +12940,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12974,49 +13000,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Mitchel Santner</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>BABA11</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>BOWL</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>mitchell santner</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>ai_structured</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>18</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>20</v>
-      </c>
-      <c r="K2" t="n">
-        <v>20</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/IPL_Fantasy_Points.xlsx
+++ b/IPL_Fantasy_Points.xlsx
@@ -994,16 +994,16 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="K13" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14">
@@ -1249,19 +1249,19 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>39</v>
+        <v>109</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>39</v>
+        <v>109</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>39</v>
+        <v>109</v>
       </c>
     </row>
     <row r="20">
@@ -1507,19 +1507,19 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H25" t="n">
         <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J25" t="n">
         <v>20</v>
       </c>
       <c r="K25" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="26">
@@ -1550,19 +1550,19 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27">
@@ -2195,19 +2195,19 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
     </row>
     <row r="42">
@@ -2413,16 +2413,16 @@
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="K46" t="n">
-        <v>80</v>
+        <v>120</v>
       </c>
     </row>
     <row r="47">
@@ -2840,19 +2840,19 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>21</v>
+        <v>62</v>
       </c>
     </row>
     <row r="57">
@@ -3187,16 +3187,16 @@
         <v>24</v>
       </c>
       <c r="H64" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I64" t="n">
         <v>24</v>
       </c>
       <c r="J64" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="K64" t="n">
-        <v>64</v>
+        <v>124</v>
       </c>
     </row>
     <row r="65">
@@ -3571,19 +3571,19 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>86</v>
+        <v>98</v>
       </c>
     </row>
     <row r="74">
@@ -3786,19 +3786,19 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
     </row>
     <row r="79">
@@ -4133,16 +4133,16 @@
         <v>0</v>
       </c>
       <c r="H86" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I86" t="n">
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="K86" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
     </row>
     <row r="87">
@@ -4431,19 +4431,19 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>64</v>
+        <v>116</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>64</v>
+        <v>116</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>64</v>
+        <v>116</v>
       </c>
     </row>
     <row r="94">
@@ -5291,19 +5291,19 @@
         </is>
       </c>
       <c r="G113" t="n">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="H113" t="n">
         <v>0</v>
       </c>
       <c r="I113" t="n">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
       </c>
       <c r="K113" t="n">
-        <v>45</v>
+        <v>86</v>
       </c>
     </row>
     <row r="114">
@@ -5552,16 +5552,16 @@
         <v>0</v>
       </c>
       <c r="H119" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I119" t="n">
         <v>0</v>
       </c>
       <c r="J119" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="K119" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="120">
@@ -6280,19 +6280,19 @@
         </is>
       </c>
       <c r="G136" t="n">
-        <v>22</v>
+        <v>77</v>
       </c>
       <c r="H136" t="n">
         <v>1</v>
       </c>
       <c r="I136" t="n">
-        <v>22</v>
+        <v>77</v>
       </c>
       <c r="J136" t="n">
         <v>20</v>
       </c>
       <c r="K136" t="n">
-        <v>42</v>
+        <v>97</v>
       </c>
     </row>
     <row r="137">
@@ -6323,19 +6323,19 @@
         </is>
       </c>
       <c r="G137" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H137" t="n">
         <v>2</v>
       </c>
       <c r="I137" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J137" t="n">
         <v>40</v>
       </c>
       <c r="K137" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="138">
@@ -6753,19 +6753,19 @@
         </is>
       </c>
       <c r="G147" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H147" t="n">
         <v>0</v>
       </c>
       <c r="I147" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
       </c>
       <c r="K147" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="148">
@@ -8086,19 +8086,19 @@
         </is>
       </c>
       <c r="G178" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H178" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I178" t="n">
         <v>0</v>
       </c>
       <c r="J178" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="K178" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="179">
@@ -8181,11 +8181,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DIPESH11</t>
+          <t>MEET11</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>797</v>
+        <v>879</v>
       </c>
     </row>
     <row r="3">
@@ -8194,11 +8194,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MEET11</t>
+          <t>DIPESH11</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>796</v>
+        <v>856</v>
       </c>
     </row>
     <row r="4">
@@ -8211,7 +8211,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>728</v>
+        <v>785</v>
       </c>
     </row>
     <row r="5">
@@ -8224,7 +8224,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>693</v>
+        <v>747</v>
       </c>
     </row>
     <row r="6">
@@ -8233,11 +8233,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>661</v>
+        <v>718</v>
       </c>
     </row>
     <row r="7">
@@ -8246,11 +8246,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>657</v>
+        <v>666</v>
       </c>
     </row>
     <row r="8">
@@ -8259,11 +8259,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>BABA11</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>524</v>
+        <v>600</v>
       </c>
     </row>
     <row r="9">
@@ -8272,11 +8272,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BABA11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>499</v>
+        <v>576</v>
       </c>
     </row>
     <row r="10">
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>385</v>
+        <v>405</v>
       </c>
     </row>
     <row r="11">
@@ -8302,7 +8302,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>381</v>
+        <v>401</v>
       </c>
     </row>
   </sheetData>
@@ -8525,7 +8525,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
         <v>2</v>
@@ -8564,7 +8564,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -8655,7 +8655,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
@@ -8772,7 +8772,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="C35" t="n">
         <v>0</v>
@@ -8928,7 +8928,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>64</v>
+        <v>116</v>
       </c>
       <c r="C47" t="n">
         <v>0</v>
@@ -9006,10 +9006,10 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54">
@@ -9045,7 +9045,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1</v>
+        <v>93</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
@@ -9061,7 +9061,7 @@
         <v>0</v>
       </c>
       <c r="C57" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58">
@@ -9191,7 +9191,7 @@
         <v>0</v>
       </c>
       <c r="C67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
@@ -9217,7 +9217,7 @@
         <v>0</v>
       </c>
       <c r="C69" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="70">
@@ -9318,7 +9318,7 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C77" t="n">
         <v>0</v>
@@ -9344,7 +9344,7 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="C79" t="n">
         <v>0</v>
@@ -9399,7 +9399,7 @@
         <v>0</v>
       </c>
       <c r="C83" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="84">
@@ -9448,7 +9448,7 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
@@ -9490,7 +9490,7 @@
         <v>24</v>
       </c>
       <c r="C90" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91">
@@ -9812,7 +9812,7 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>39</v>
+        <v>109</v>
       </c>
       <c r="C115" t="n">
         <v>0</v>
@@ -9929,7 +9929,7 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C124" t="n">
         <v>0</v>
@@ -10007,7 +10007,7 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C130" t="n">
         <v>1</v>
@@ -10033,7 +10033,7 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>22</v>
+        <v>77</v>
       </c>
       <c r="C132" t="n">
         <v>1</v>

--- a/IPL_Fantasy_Points.xlsx
+++ b/IPL_Fantasy_Points.xlsx
@@ -4320,7 +4320,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>KL Rahul</t>
+          <t>lokesh rahul</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4333,31 +4333,31 @@
           <t>BAT</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
-      <c r="E91" t="inlineStr">
+      <c r="D91" t="inlineStr">
         <is>
           <t>lokesh rahul</t>
         </is>
       </c>
+      <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="G91" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
       </c>
       <c r="I91" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
     </row>
     <row r="92">
@@ -5395,7 +5395,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Donovan Ferreira</t>
+          <t>Donavan Ferreira</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -5408,31 +5408,31 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
-      <c r="E116" t="inlineStr">
+      <c r="D116" t="inlineStr">
         <is>
           <t>donavon ferreira</t>
         </is>
       </c>
+      <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>ai_structured</t>
         </is>
       </c>
       <c r="G116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H116" t="n">
         <v>0</v>
       </c>
       <c r="I116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
       </c>
       <c r="K116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117">
@@ -8237,7 +8237,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>718</v>
+        <v>719</v>
       </c>
     </row>
     <row r="7">
@@ -8246,11 +8246,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>666</v>
+        <v>669</v>
       </c>
     </row>
     <row r="8">
@@ -8259,11 +8259,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BABA11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>600</v>
+        <v>666</v>
       </c>
     </row>
     <row r="9">
@@ -8272,11 +8272,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>BABA11</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>576</v>
+        <v>600</v>
       </c>
     </row>
     <row r="10">
@@ -10089,7 +10089,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K64"/>
+  <dimension ref="A1:K62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11270,7 +11270,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>KL Rahul</t>
+          <t>Urvil Patel</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -11286,7 +11286,7 @@
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>lokesh rahul</t>
+          <t>axar patel</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -11313,7 +11313,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Urvil Patel</t>
+          <t>Arshin Kulkarni</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -11329,7 +11329,7 @@
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>axar patel</t>
+          <t>shivang kumar</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -11356,7 +11356,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Arshin Kulkarni</t>
+          <t>Nishant Sindhu</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -11366,13 +11366,13 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>shivang kumar</t>
+          <t>shashank singh</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -11399,7 +11399,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Nishant Sindhu</t>
+          <t>Jayant Yadav</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -11415,7 +11415,7 @@
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>shashank singh</t>
+          <t>prince yadav</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -11442,7 +11442,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Jayant Yadav</t>
+          <t>Ajay Mandal</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -11458,7 +11458,7 @@
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>prince yadav</t>
+          <t>rajat patidar</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -11485,7 +11485,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Ajay Mandal</t>
+          <t>Will Jacks</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -11501,7 +11501,7 @@
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>rajat patidar</t>
+          <t>mitchell marsh</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -11528,7 +11528,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Will Jacks</t>
+          <t>Josh Hazelwood</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -11538,13 +11538,13 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>mitchell marsh</t>
+          <t>shahbaz ahmed</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -11571,7 +11571,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Josh Hazelwood</t>
+          <t>Kyle Jamieson</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -11587,7 +11587,7 @@
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>shahbaz ahmed</t>
+          <t>jamie overton</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -11614,7 +11614,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Kyle Jamieson</t>
+          <t>Matheesha Pathirana</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -11630,7 +11630,7 @@
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>jamie overton</t>
+          <t>eshan malinga</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -11657,7 +11657,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Matheesha Pathirana</t>
+          <t>M Siddharth</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -11673,7 +11673,7 @@
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>eshan malinga</t>
+          <t>manimaran siddharth</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -11700,7 +11700,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>M Siddharth</t>
+          <t>Ben Dwarshuis</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -11716,7 +11716,7 @@
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>manimaran siddharth</t>
+          <t>b sai sudharshan</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -11743,23 +11743,23 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Ben Dwarshuis</t>
+          <t>Manish Pandey</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>b sai sudharshan</t>
+          <t>hardik pandya</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -11786,7 +11786,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Manish Pandey</t>
+          <t>Mukesh Choudhary</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -11796,13 +11796,13 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>hardik pandya</t>
+          <t>mukul choudhary</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -11829,7 +11829,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Donovan Ferreira</t>
+          <t>Gurjapneet Singh</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -11839,13 +11839,13 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>donavon ferreira</t>
+          <t>ramandeep singh</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -11872,7 +11872,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Mukesh Choudhary</t>
+          <t>Arjun Tendulkar</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -11888,7 +11888,7 @@
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>mukul choudhary</t>
+          <t>krunal pandya</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -11915,7 +11915,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Gurjapneet Singh</t>
+          <t>Kwena Maphaka</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -11931,7 +11931,7 @@
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>ramandeep singh</t>
+          <t>aiden markram</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -11958,23 +11958,23 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Arjun Tendulkar</t>
+          <t>Ramkrishna Ghosh</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>krunal pandya</t>
+          <t>angkrish raghuvanshi</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -12001,23 +12001,23 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Kwena Maphaka</t>
+          <t>Venkatesh Iyer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>aiden markram</t>
+          <t>shreyas iyer</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -12044,7 +12044,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Ramkrishna Ghosh</t>
+          <t>ashutosh sharma</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -12060,7 +12060,7 @@
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>angkrish raghuvanshi</t>
+          <t>ashok sharma</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -12087,7 +12087,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Venkatesh Iyer</t>
+          <t>Azmatullah Omarzai</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -12097,13 +12097,13 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>shreyas iyer</t>
+          <t>mitchell marsh</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -12130,12 +12130,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ashutosh sharma</t>
+          <t>akshat raghuwanshi</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -12146,7 +12146,7 @@
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>ashok sharma</t>
+          <t>angkrish raghuvanshi</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -12173,23 +12173,23 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Azmatullah Omarzai</t>
+          <t>Himmat Singh</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>mitchell marsh</t>
+          <t>prabhsimran singh</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -12216,7 +12216,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>akshat raghuwanshi</t>
+          <t>Suryansh Shegde</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -12232,7 +12232,7 @@
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>angkrish raghuvanshi</t>
+          <t>suyash sharma</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -12259,7 +12259,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Himmat Singh</t>
+          <t>Tejasvi Singh</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -12302,7 +12302,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Suryansh Shegde</t>
+          <t>Sai Kishor</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -12312,13 +12312,13 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>suyash sharma</t>
+          <t>ishan kishan</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -12345,7 +12345,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Tejasvi Singh</t>
+          <t>Akash Deep</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -12355,13 +12355,13 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>prabhsimran singh</t>
+          <t>arshdeep singh</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -12388,23 +12388,23 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sai Kishor</t>
+          <t>Ben Duckett</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>ishan kishan</t>
+          <t>ryan rickelton</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -12431,23 +12431,23 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Akash Deep</t>
+          <t>Abhishek Porel</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>arshdeep singh</t>
+          <t>abhishek sharma</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -12474,7 +12474,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Ben Duckett</t>
+          <t>Rahul Tripathi</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -12490,7 +12490,7 @@
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>ryan rickelton</t>
+          <t>rahul tewatia</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -12517,7 +12517,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Abhishek Porel</t>
+          <t>Dre Pretorius</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -12533,7 +12533,7 @@
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>abhishek sharma</t>
+          <t>nandre burger</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -12560,7 +12560,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Rahul Tripathi</t>
+          <t>Matthew Breetzke</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -12576,7 +12576,7 @@
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>rahul tewatia</t>
+          <t>matt henry</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -12603,7 +12603,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Dre Pretorius</t>
+          <t>Anuj Rawat</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -12619,7 +12619,7 @@
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>nandre burger</t>
+          <t>rahul tewatia</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -12646,7 +12646,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Matthew Breetzke</t>
+          <t>Wanindu Hasaranga</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -12656,13 +12656,13 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>matt henry</t>
+          <t>sandeep sharma</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -12689,7 +12689,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Anuj Rawat</t>
+          <t>Harpreet Brar</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -12699,13 +12699,13 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>rahul tewatia</t>
+          <t>jasprit bumrah</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -12732,7 +12732,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Wanindu Hasaranga</t>
+          <t>Mayank Yadav</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -12742,13 +12742,13 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>sandeep sharma</t>
+          <t>mayank markande</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -12769,92 +12769,6 @@
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Harpreet Brar</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>BOWL</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>jasprit bumrah</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="G63" t="n">
-        <v>0</v>
-      </c>
-      <c r="H63" t="n">
-        <v>0</v>
-      </c>
-      <c r="I63" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" t="n">
-        <v>0</v>
-      </c>
-      <c r="K63" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Mayank Yadav</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>BOWL</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>mayank markande</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="G64" t="n">
-        <v>0</v>
-      </c>
-      <c r="H64" t="n">
-        <v>0</v>
-      </c>
-      <c r="I64" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" t="n">
-        <v>0</v>
-      </c>
-      <c r="K64" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12940,7 +12854,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13000,6 +12914,49 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Donavan Ferreira</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SKY11</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>donavon ferreira</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>ai_structured</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/IPL_Fantasy_Points.xlsx
+++ b/IPL_Fantasy_Points.xlsx
@@ -561,19 +561,19 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4">
@@ -862,19 +862,19 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K10" t="n">
-        <v>24</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11">
@@ -951,16 +951,16 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="K12" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13">
@@ -1292,19 +1292,19 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>83</v>
+        <v>124</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>83</v>
+        <v>124</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>83</v>
+        <v>124</v>
       </c>
     </row>
     <row r="21">
@@ -2926,19 +2926,19 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>12</v>
+        <v>66</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>12</v>
+        <v>66</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>12</v>
+        <v>66</v>
       </c>
     </row>
     <row r="59">
@@ -3055,19 +3055,19 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="62">
@@ -3915,19 +3915,19 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>56</v>
+        <v>78</v>
       </c>
     </row>
     <row r="82">
@@ -4087,19 +4087,19 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H85" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I85" t="n">
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="K85" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="86">
@@ -5119,19 +5119,19 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="H109" t="n">
         <v>0</v>
       </c>
       <c r="I109" t="n">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
       </c>
       <c r="K109" t="n">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="110">
@@ -5509,16 +5509,16 @@
         <v>5</v>
       </c>
       <c r="H118" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I118" t="n">
         <v>0</v>
       </c>
       <c r="J118" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="K118" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="119">
@@ -6194,19 +6194,19 @@
         </is>
       </c>
       <c r="G134" t="n">
-        <v>110</v>
+        <v>155</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
       </c>
       <c r="I134" t="n">
-        <v>110</v>
+        <v>155</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
       </c>
       <c r="K134" t="n">
-        <v>110</v>
+        <v>155</v>
       </c>
     </row>
     <row r="135">
@@ -6538,7 +6538,7 @@
         </is>
       </c>
       <c r="G142" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H142" t="n">
         <v>3</v>
@@ -6710,19 +6710,19 @@
         </is>
       </c>
       <c r="G146" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="H146" t="n">
         <v>0</v>
       </c>
       <c r="I146" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
       </c>
       <c r="K146" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
     </row>
     <row r="147">
@@ -7229,16 +7229,16 @@
         <v>1</v>
       </c>
       <c r="H158" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I158" t="n">
         <v>0</v>
       </c>
       <c r="J158" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="K158" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
     </row>
     <row r="159">
@@ -7570,19 +7570,19 @@
         </is>
       </c>
       <c r="G166" t="n">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="H166" t="n">
         <v>0</v>
       </c>
       <c r="I166" t="n">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
       </c>
       <c r="K166" t="n">
-        <v>71</v>
+        <v>80</v>
       </c>
     </row>
     <row r="167">
@@ -7831,16 +7831,16 @@
         <v>12</v>
       </c>
       <c r="H172" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I172" t="n">
         <v>12</v>
       </c>
       <c r="J172" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="K172" t="n">
-        <v>32</v>
+        <v>52</v>
       </c>
     </row>
     <row r="173">
@@ -8046,16 +8046,16 @@
         <v>0</v>
       </c>
       <c r="H177" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I177" t="n">
         <v>0</v>
       </c>
       <c r="J177" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="K177" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="178">
@@ -8185,7 +8185,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>879</v>
+        <v>920</v>
       </c>
     </row>
     <row r="3">
@@ -8198,7 +8198,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>856</v>
+        <v>898</v>
       </c>
     </row>
     <row r="4">
@@ -8211,7 +8211,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>785</v>
+        <v>830</v>
       </c>
     </row>
     <row r="5">
@@ -8220,11 +8220,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>VATSAL11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>747</v>
+        <v>754</v>
       </c>
     </row>
     <row r="6">
@@ -8233,11 +8233,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>VATSAL11</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>719</v>
+        <v>747</v>
       </c>
     </row>
     <row r="7">
@@ -8246,11 +8246,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>669</v>
+        <v>719</v>
       </c>
     </row>
     <row r="8">
@@ -8259,11 +8259,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>666</v>
+        <v>669</v>
       </c>
     </row>
     <row r="9">
@@ -8276,7 +8276,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>600</v>
+        <v>658</v>
       </c>
     </row>
     <row r="10">
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>405</v>
+        <v>507</v>
       </c>
     </row>
     <row r="11">
@@ -8302,7 +8302,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>401</v>
+        <v>450</v>
       </c>
     </row>
   </sheetData>
@@ -8343,7 +8343,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -8382,7 +8382,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -8395,7 +8395,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>83</v>
+        <v>124</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -8421,7 +8421,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>110</v>
+        <v>155</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -8476,7 +8476,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -8512,10 +8512,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -8538,7 +8538,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>66</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -8616,10 +8616,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -8723,7 +8723,7 @@
         <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -8759,7 +8759,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="C34" t="n">
         <v>0</v>
@@ -8970,7 +8970,7 @@
         <v>5</v>
       </c>
       <c r="C50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51">
@@ -9074,7 +9074,7 @@
         <v>0</v>
       </c>
       <c r="C58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -9149,7 +9149,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="C64" t="n">
         <v>0</v>
@@ -9175,7 +9175,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C66" t="n">
         <v>3</v>
@@ -9227,7 +9227,7 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="C70" t="n">
         <v>0</v>
@@ -9292,7 +9292,7 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="C75" t="n">
         <v>0</v>
@@ -9412,7 +9412,7 @@
         <v>0</v>
       </c>
       <c r="C84" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="85">
@@ -9526,7 +9526,7 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
@@ -9539,7 +9539,7 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
@@ -9591,7 +9591,7 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C98" t="n">
         <v>0</v>
@@ -9828,7 +9828,7 @@
         <v>12</v>
       </c>
       <c r="C116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="117">
@@ -9958,7 +9958,7 @@
         <v>1</v>
       </c>
       <c r="C126" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="127">

--- a/IPL_Fantasy_Points.xlsx
+++ b/IPL_Fantasy_Points.xlsx
@@ -647,19 +647,19 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -690,19 +690,19 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>79</v>
+        <v>142</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>79</v>
+        <v>142</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>79</v>
+        <v>142</v>
       </c>
     </row>
     <row r="7">
@@ -1335,19 +1335,19 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>122</v>
+        <v>200</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>122</v>
+        <v>200</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>122</v>
+        <v>200</v>
       </c>
     </row>
     <row r="22">
@@ -1725,16 +1725,16 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>140</v>
+        <v>180</v>
       </c>
       <c r="K30" t="n">
-        <v>140</v>
+        <v>180</v>
       </c>
     </row>
     <row r="31">
@@ -2238,19 +2238,19 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H42" t="n">
         <v>3</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="43">
@@ -2281,19 +2281,19 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="H43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I43" t="n">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="J43" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="K43" t="n">
-        <v>47</v>
+        <v>91</v>
       </c>
     </row>
     <row r="44">
@@ -2542,16 +2542,16 @@
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="K49" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
     </row>
     <row r="50">
@@ -2883,19 +2883,19 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>95</v>
+        <v>176</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>95</v>
+        <v>176</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>95</v>
+        <v>176</v>
       </c>
     </row>
     <row r="58">
@@ -3958,19 +3958,19 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>86</v>
+        <v>99</v>
       </c>
     </row>
     <row r="83">
@@ -4302,19 +4302,19 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>170</v>
+        <v>183</v>
       </c>
     </row>
     <row r="91">
@@ -4732,19 +4732,19 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="H100" t="n">
         <v>1</v>
       </c>
       <c r="I100" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="J100" t="n">
         <v>20</v>
       </c>
       <c r="K100" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="101">
@@ -4809,7 +4809,7 @@
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>shahbaz ahmed</t>
+          <t>josh hazlewood</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -4922,7 +4922,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>M Siddharth</t>
+          <t>Manimaran Siddharth</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4935,31 +4935,31 @@
           <t>BOWL</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
-      <c r="E105" t="inlineStr">
+      <c r="D105" t="inlineStr">
         <is>
           <t>manimaran siddharth</t>
         </is>
       </c>
+      <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="G105" t="n">
         <v>0</v>
       </c>
       <c r="H105" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I105" t="n">
         <v>0</v>
       </c>
       <c r="J105" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="K105" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="106">
@@ -5850,19 +5850,19 @@
         </is>
       </c>
       <c r="G126" t="n">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="H126" t="n">
         <v>0</v>
       </c>
       <c r="I126" t="n">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
       </c>
       <c r="K126" t="n">
-        <v>111</v>
+        <v>125</v>
       </c>
     </row>
     <row r="127">
@@ -5924,31 +5924,31 @@
           <t>BAT</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr"/>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>shreyas iyer</t>
-        </is>
-      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>venkatesh iyer</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="G128" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
       </c>
       <c r="I128" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
       </c>
       <c r="K128" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="129">
@@ -6624,19 +6624,19 @@
         </is>
       </c>
       <c r="G144" t="n">
-        <v>97</v>
+        <v>129</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
       </c>
       <c r="I144" t="n">
-        <v>97</v>
+        <v>129</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
       </c>
       <c r="K144" t="n">
-        <v>97</v>
+        <v>129</v>
       </c>
     </row>
     <row r="145">
@@ -7011,19 +7011,19 @@
         </is>
       </c>
       <c r="G153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H153" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J153" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="K153" t="n">
-        <v>40</v>
+        <v>81</v>
       </c>
     </row>
     <row r="154">
@@ -7057,16 +7057,16 @@
         <v>1</v>
       </c>
       <c r="H154" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I154" t="n">
         <v>1</v>
       </c>
       <c r="J154" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="K154" t="n">
-        <v>61</v>
+        <v>101</v>
       </c>
     </row>
     <row r="155">
@@ -7183,7 +7183,7 @@
         </is>
       </c>
       <c r="G157" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H157" t="n">
         <v>4</v>
@@ -8185,7 +8185,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>920</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="3">
@@ -8198,7 +8198,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>898</v>
+        <v>911</v>
       </c>
     </row>
     <row r="4">
@@ -8211,7 +8211,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>830</v>
+        <v>873</v>
       </c>
     </row>
     <row r="5">
@@ -8220,11 +8220,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>VATSAL11</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>754</v>
+        <v>833</v>
       </c>
     </row>
     <row r="6">
@@ -8233,11 +8233,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>VATSAL11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>747</v>
+        <v>832</v>
       </c>
     </row>
     <row r="7">
@@ -8246,11 +8246,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>719</v>
+        <v>754</v>
       </c>
     </row>
     <row r="8">
@@ -8259,11 +8259,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>BABA11</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>669</v>
+        <v>739</v>
       </c>
     </row>
     <row r="9">
@@ -8272,11 +8272,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BABA11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>658</v>
+        <v>725</v>
       </c>
     </row>
     <row r="10">
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>507</v>
+        <v>575</v>
       </c>
     </row>
     <row r="11">
@@ -8316,7 +8316,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C135"/>
+  <dimension ref="A1:C137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8577,7 +8577,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C20" t="n">
         <v>4</v>
@@ -8606,7 +8606,7 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -8694,7 +8694,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
@@ -8707,7 +8707,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>95</v>
+        <v>176</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
@@ -8902,7 +8902,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C45" t="n">
         <v>0</v>
@@ -8918,7 +8918,7 @@
         <v>1</v>
       </c>
       <c r="C46" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47">
@@ -8937,102 +8937,102 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>kagiso rabada</t>
+          <t>josh hazlewood</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>kartik sharma</t>
+          <t>kagiso rabada</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>kartik tyagi</t>
+          <t>kartik sharma</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="C50" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>khaleel ahmed</t>
+          <t>kartik tyagi</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>krunal pandya</t>
+          <t>khaleel ahmed</t>
         </is>
       </c>
       <c r="B52" t="n">
         <v>0</v>
       </c>
       <c r="C52" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>kuldeep yadav</t>
+          <t>krunal pandya</t>
         </is>
       </c>
       <c r="B53" t="n">
         <v>1</v>
       </c>
       <c r="C53" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>kumar kushagra</t>
+          <t>kuldeep yadav</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="C54" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>liam livingstone</t>
+          <t>kumar kushagra</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C55" t="n">
         <v>0</v>
@@ -9041,11 +9041,11 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>lokesh rahul</t>
+          <t>liam livingstone</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>93</v>
+        <v>14</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
@@ -9054,37 +9054,37 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>lungi ngidi</t>
+          <t>lokesh rahul</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="C57" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>manimaran siddharth</t>
+          <t>lungi ngidi</t>
         </is>
       </c>
       <c r="B58" t="n">
         <v>0</v>
       </c>
       <c r="C58" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>marco jansen</t>
+          <t>manimaran siddharth</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C59" t="n">
         <v>2</v>
@@ -9093,50 +9093,50 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>marcus stoinis</t>
+          <t>marco jansen</t>
         </is>
       </c>
       <c r="B60" t="n">
         <v>9</v>
       </c>
       <c r="C60" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>matt henry</t>
+          <t>marcus stoinis</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C61" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>matt short</t>
+          <t>matt henry</t>
         </is>
       </c>
       <c r="B62" t="n">
+        <v>7</v>
+      </c>
+      <c r="C62" t="n">
         <v>2</v>
-      </c>
-      <c r="C62" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>mayank markande</t>
+          <t>matt short</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C63" t="n">
         <v>0</v>
@@ -9145,11 +9145,11 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>mitchell marsh</t>
+          <t>mayank markande</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="C64" t="n">
         <v>0</v>
@@ -9158,89 +9158,89 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>mitchell santner</t>
+          <t>mitchell marsh</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>18</v>
+        <v>64</v>
       </c>
       <c r="C65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>mohammed shami</t>
+          <t>mitchell santner</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="C66" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>mohammed siraj</t>
+          <t>mohammed shami</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C67" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>mohsin khan</t>
+          <t>mohammed siraj</t>
         </is>
       </c>
       <c r="B68" t="n">
         <v>0</v>
       </c>
       <c r="C68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>mukesh kumar</t>
+          <t>mohsin khan</t>
         </is>
       </c>
       <c r="B69" t="n">
         <v>0</v>
       </c>
       <c r="C69" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>mukul choudhary</t>
+          <t>mukesh kumar</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="C70" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>naman dhir</t>
+          <t>mukul choudhary</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="C71" t="n">
         <v>0</v>
@@ -9249,37 +9249,37 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>nandre burger</t>
+          <t>naman dhir</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="C72" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>navdeep saini</t>
+          <t>nandre burger</t>
         </is>
       </c>
       <c r="B73" t="n">
         <v>0</v>
       </c>
       <c r="C73" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>nehal wadhera</t>
+          <t>navdeep saini</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C74" t="n">
         <v>0</v>
@@ -9288,11 +9288,11 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>nicholas pooran</t>
+          <t>nehal wadhera</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C75" t="n">
         <v>0</v>
@@ -9301,37 +9301,37 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>nitish kumar reddy</t>
+          <t>nicholas pooran</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>96</v>
+        <v>22</v>
       </c>
       <c r="C76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>nitish rana</t>
+          <t>nitish kumar reddy</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>20</v>
+        <v>96</v>
       </c>
       <c r="C77" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>noor ahmad</t>
+          <t>nitish rana</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C78" t="n">
         <v>0</v>
@@ -9340,11 +9340,11 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>pathum nissanka</t>
+          <t>noor ahmad</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>86</v>
+        <v>9</v>
       </c>
       <c r="C79" t="n">
         <v>0</v>
@@ -9353,11 +9353,11 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>philip salt</t>
+          <t>pathum nissanka</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="C80" t="n">
         <v>0</v>
@@ -9366,11 +9366,11 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>prabhsimran singh</t>
+          <t>philip salt</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="C81" t="n">
         <v>0</v>
@@ -9379,11 +9379,11 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>prashant veer</t>
+          <t>prabhsimran singh</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
@@ -9392,50 +9392,50 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>prasidh krishna</t>
+          <t>prashant veer</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="C83" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>prince yadav</t>
+          <t>prasidh krishna</t>
         </is>
       </c>
       <c r="B84" t="n">
         <v>0</v>
       </c>
       <c r="C84" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>priyansh arya</t>
+          <t>prince yadav</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="C85" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>rahul chahar</t>
+          <t>priyansh arya</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
@@ -9444,11 +9444,11 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>rahul tewatia</t>
+          <t>rahul chahar</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
@@ -9457,11 +9457,11 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>rajat patidar</t>
+          <t>rahul tewatia</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>79</v>
+        <v>24</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
@@ -9470,11 +9470,11 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ramandeep singh</t>
+          <t>rajat patidar</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>14</v>
+        <v>142</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
@@ -9483,63 +9483,63 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>rashid khan</t>
+          <t>ramandeep singh</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="C90" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ravi bishnoi</t>
+          <t>rashid khan</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="C91" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ravindra jadeja</t>
+          <t>ravi bishnoi</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C92" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>rinku singh</t>
+          <t>ravindra jadeja</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>72</v>
+        <v>31</v>
       </c>
       <c r="C93" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>rishabh pant</t>
+          <t>rinku singh</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
@@ -9548,63 +9548,63 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>riyan parag</t>
+          <t>rishabh pant</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>42</v>
+        <v>85</v>
       </c>
       <c r="C95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>rohit sharma</t>
+          <t>riyan parag</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>118</v>
+        <v>45</v>
       </c>
       <c r="C96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>romario shepherd</t>
+          <t>rohit sharma</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="C97" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>rovman powell</t>
+          <t>romario shepherd</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="C98" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ruturaj gaikwad</t>
+          <t>rovman powell</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C99" t="n">
         <v>0</v>
@@ -9613,11 +9613,11 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ryan rickelton</t>
+          <t>ruturaj gaikwad</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>98</v>
+        <v>41</v>
       </c>
       <c r="C100" t="n">
         <v>0</v>
@@ -9626,11 +9626,11 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>salil arora</t>
+          <t>ryan rickelton</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>9</v>
+        <v>98</v>
       </c>
       <c r="C101" t="n">
         <v>0</v>
@@ -9639,11 +9639,11 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>sameer rizvi</t>
+          <t>salil arora</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>160</v>
+        <v>9</v>
       </c>
       <c r="C102" t="n">
         <v>0</v>
@@ -9652,37 +9652,37 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>sandeep sharma</t>
+          <t>sameer rizvi</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="C103" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>sanju samson</t>
+          <t>sandeep sharma</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="C104" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>sarfaraz khan</t>
+          <t>sanju samson</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>99</v>
+        <v>22</v>
       </c>
       <c r="C105" t="n">
         <v>0</v>
@@ -9691,11 +9691,11 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>shahbaz ahmed</t>
+          <t>sarfaraz khan</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>15</v>
+        <v>99</v>
       </c>
       <c r="C106" t="n">
         <v>0</v>
@@ -9704,7 +9704,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>shahrukh khan</t>
+          <t>shahbaz ahmed</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -9717,37 +9717,37 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>shardul thakur</t>
+          <t>shahrukh khan</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C108" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>shashank singh</t>
+          <t>shardul thakur</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C109" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>sherfane rutherford</t>
+          <t>shashank singh</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C110" t="n">
         <v>0</v>
@@ -9756,11 +9756,11 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>shimron hetmyer</t>
+          <t>sherfane rutherford</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C111" t="n">
         <v>0</v>
@@ -9769,24 +9769,24 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>shivam dube</t>
+          <t>shimron hetmyer</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>69</v>
+        <v>24</v>
       </c>
       <c r="C112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>shivang kumar</t>
+          <t>shivam dube</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="C113" t="n">
         <v>1</v>
@@ -9795,24 +9795,24 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>shreyas iyer</t>
+          <t>shivang kumar</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>68</v>
+        <v>9</v>
       </c>
       <c r="C114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>shubman gill</t>
+          <t>shreyas iyer</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>109</v>
+        <v>68</v>
       </c>
       <c r="C115" t="n">
         <v>0</v>
@@ -9821,76 +9821,76 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>sunil narine</t>
+          <t>shubman gill</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>12</v>
+        <v>109</v>
       </c>
       <c r="C116" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>suryakumar yadav</t>
+          <t>sunil narine</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>73</v>
+        <v>12</v>
       </c>
       <c r="C117" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>suyash sharma</t>
+          <t>suryakumar yadav</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="C118" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>t natarajan</t>
+          <t>suyash sharma</t>
         </is>
       </c>
       <c r="B119" t="n">
         <v>0</v>
       </c>
       <c r="C119" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>tilak varma</t>
+          <t>t natarajan</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="C120" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>tim david</t>
+          <t>tilak varma</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>86</v>
+        <v>34</v>
       </c>
       <c r="C121" t="n">
         <v>0</v>
@@ -9899,11 +9899,11 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>travis head</t>
+          <t>tim david</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>64</v>
+        <v>99</v>
       </c>
       <c r="C122" t="n">
         <v>0</v>
@@ -9912,11 +9912,11 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>trent boult</t>
+          <t>travis head</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>1</v>
+        <v>64</v>
       </c>
       <c r="C123" t="n">
         <v>0</v>
@@ -9925,11 +9925,11 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>tristan stubbs</t>
+          <t>trent boult</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="C124" t="n">
         <v>0</v>
@@ -9938,50 +9938,50 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>tushar deshpande</t>
+          <t>tristan stubbs</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="C125" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>vaibhav arora</t>
+          <t>tushar deshpande</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C126" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>vaibhav suryavanshi</t>
+          <t>vaibhav arora</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>122</v>
+        <v>1</v>
       </c>
       <c r="C127" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>varun chakravarthy</t>
+          <t>vaibhav suryavanshi</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="C128" t="n">
         <v>0</v>
@@ -9990,50 +9990,50 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>vijaykumar vyshak</t>
+          <t>varun chakravarthy</t>
         </is>
       </c>
       <c r="B129" t="n">
         <v>0</v>
       </c>
       <c r="C129" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>vipraj nigam</t>
+          <t>venkatesh iyer</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="C130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>virat kohli</t>
+          <t>vijaykumar vyshak</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="C131" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>washington sundar</t>
+          <t>vipraj nigam</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>77</v>
+        <v>12</v>
       </c>
       <c r="C132" t="n">
         <v>1</v>
@@ -10042,39 +10042,65 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>xavier bartlett</t>
+          <t>virat kohli</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>11</v>
+        <v>129</v>
       </c>
       <c r="C133" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>yashasvi jaiswal</t>
+          <t>washington sundar</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>170</v>
+        <v>77</v>
       </c>
       <c r="C134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
+          <t>xavier bartlett</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>11</v>
+      </c>
+      <c r="C135" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>yashasvi jaiswal</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>183</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
           <t>yuzvendra chahal</t>
         </is>
       </c>
-      <c r="B135" t="n">
-        <v>0</v>
-      </c>
-      <c r="C135" t="n">
+      <c r="B137" t="n">
+        <v>0</v>
+      </c>
+      <c r="C137" t="n">
         <v>3</v>
       </c>
     </row>
@@ -10089,7 +10115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K62"/>
+  <dimension ref="A1:K60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11544,7 +11570,7 @@
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>shahbaz ahmed</t>
+          <t>josh hazlewood</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -11657,7 +11683,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>M Siddharth</t>
+          <t>Ben Dwarshuis</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -11673,7 +11699,7 @@
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>manimaran siddharth</t>
+          <t>b sai sudharshan</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -11700,23 +11726,23 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Ben Dwarshuis</t>
+          <t>Manish Pandey</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>b sai sudharshan</t>
+          <t>hardik pandya</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -11743,7 +11769,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Manish Pandey</t>
+          <t>Mukesh Choudhary</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -11753,13 +11779,13 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>hardik pandya</t>
+          <t>mukul choudhary</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -11786,7 +11812,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Mukesh Choudhary</t>
+          <t>Gurjapneet Singh</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -11802,7 +11828,7 @@
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>mukul choudhary</t>
+          <t>ramandeep singh</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -11829,7 +11855,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Gurjapneet Singh</t>
+          <t>Arjun Tendulkar</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -11845,7 +11871,7 @@
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>ramandeep singh</t>
+          <t>krunal pandya</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -11872,7 +11898,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Arjun Tendulkar</t>
+          <t>Kwena Maphaka</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -11888,7 +11914,7 @@
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>krunal pandya</t>
+          <t>aiden markram</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -11915,23 +11941,23 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Kwena Maphaka</t>
+          <t>Ramkrishna Ghosh</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>aiden markram</t>
+          <t>angkrish raghuvanshi</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -11958,7 +11984,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Ramkrishna Ghosh</t>
+          <t>ashutosh sharma</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -11974,7 +12000,7 @@
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>angkrish raghuvanshi</t>
+          <t>ashok sharma</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -12001,7 +12027,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Venkatesh Iyer</t>
+          <t>Azmatullah Omarzai</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -12011,13 +12037,13 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>shreyas iyer</t>
+          <t>mitchell marsh</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -12044,12 +12070,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ashutosh sharma</t>
+          <t>akshat raghuwanshi</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -12060,7 +12086,7 @@
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>ashok sharma</t>
+          <t>angkrish raghuvanshi</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -12087,23 +12113,23 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Azmatullah Omarzai</t>
+          <t>Himmat Singh</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>mitchell marsh</t>
+          <t>prabhsimran singh</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -12130,7 +12156,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>akshat raghuwanshi</t>
+          <t>Suryansh Shegde</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -12146,7 +12172,7 @@
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>angkrish raghuvanshi</t>
+          <t>suyash sharma</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -12173,7 +12199,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Himmat Singh</t>
+          <t>Tejasvi Singh</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -12216,7 +12242,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suryansh Shegde</t>
+          <t>Sai Kishor</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -12226,13 +12252,13 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>suyash sharma</t>
+          <t>ishan kishan</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -12259,7 +12285,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Tejasvi Singh</t>
+          <t>Akash Deep</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -12269,13 +12295,13 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>prabhsimran singh</t>
+          <t>arshdeep singh</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -12302,23 +12328,23 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sai Kishor</t>
+          <t>Ben Duckett</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>ishan kishan</t>
+          <t>ryan rickelton</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -12345,23 +12371,23 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Akash Deep</t>
+          <t>Abhishek Porel</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>arshdeep singh</t>
+          <t>abhishek sharma</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -12388,7 +12414,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Ben Duckett</t>
+          <t>Rahul Tripathi</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -12404,7 +12430,7 @@
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>ryan rickelton</t>
+          <t>rahul tewatia</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -12431,7 +12457,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Abhishek Porel</t>
+          <t>Dre Pretorius</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -12447,7 +12473,7 @@
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>abhishek sharma</t>
+          <t>nandre burger</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -12474,7 +12500,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Rahul Tripathi</t>
+          <t>Matthew Breetzke</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -12490,7 +12516,7 @@
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>rahul tewatia</t>
+          <t>matt henry</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -12517,7 +12543,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Dre Pretorius</t>
+          <t>Anuj Rawat</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -12533,7 +12559,7 @@
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>nandre burger</t>
+          <t>rahul tewatia</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -12560,7 +12586,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Matthew Breetzke</t>
+          <t>Wanindu Hasaranga</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -12570,13 +12596,13 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>matt henry</t>
+          <t>sandeep sharma</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -12603,7 +12629,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Anuj Rawat</t>
+          <t>Harpreet Brar</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -12613,13 +12639,13 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>rahul tewatia</t>
+          <t>jasprit bumrah</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -12646,7 +12672,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Wanindu Hasaranga</t>
+          <t>Mayank Yadav</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -12656,13 +12682,13 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>sandeep sharma</t>
+          <t>mayank markande</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -12683,92 +12709,6 @@
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Harpreet Brar</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>BOWL</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>jasprit bumrah</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="G61" t="n">
-        <v>0</v>
-      </c>
-      <c r="H61" t="n">
-        <v>0</v>
-      </c>
-      <c r="I61" t="n">
-        <v>0</v>
-      </c>
-      <c r="J61" t="n">
-        <v>0</v>
-      </c>
-      <c r="K61" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Mayank Yadav</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>BOWL</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>mayank markande</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="G62" t="n">
-        <v>0</v>
-      </c>
-      <c r="H62" t="n">
-        <v>0</v>
-      </c>
-      <c r="I62" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" t="n">
-        <v>0</v>
-      </c>
-      <c r="K62" t="n">
         <v>0</v>
       </c>
     </row>

--- a/IPL_Fantasy_Points.xlsx
+++ b/IPL_Fantasy_Points.xlsx
@@ -3116,7 +3116,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Rowman Powell</t>
+          <t>Rovman Powell</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3129,31 +3129,31 @@
           <t>BAT</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>rovman powell</t>
         </is>
       </c>
+      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
     </row>
     <row r="64">
@@ -8246,11 +8246,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>BABA11</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>754</v>
+        <v>778</v>
       </c>
     </row>
     <row r="8">
@@ -8259,11 +8259,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BABA11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>739</v>
+        <v>754</v>
       </c>
     </row>
     <row r="9">
@@ -10115,7 +10115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K60"/>
+  <dimension ref="A1:K59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10909,7 +10909,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Rowman Powell</t>
+          <t>liam livingston</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -10919,13 +10919,13 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>rovman powell</t>
+          <t>liam livingstone</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -10952,7 +10952,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>liam livingston</t>
+          <t>rachin ravindra</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -10968,7 +10968,7 @@
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>liam livingstone</t>
+          <t>rashid khan</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -10995,7 +10995,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>rachin ravindra</t>
+          <t>Zeeshan Ansari</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -11005,13 +11005,13 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>rashid khan</t>
+          <t>eshan malinga</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -11038,7 +11038,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Zeeshan Ansari</t>
+          <t>Mitchell Starc</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -11054,7 +11054,7 @@
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>eshan malinga</t>
+          <t>mitchell santner</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -11081,17 +11081,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Mitchell Starc</t>
+          <t>Mitchel Owen</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BABA11</t>
+          <t>DIPESH11</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -11124,7 +11124,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Mitchel Owen</t>
+          <t>Pat Cummins</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -11134,13 +11134,13 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>mitchell santner</t>
+          <t>pathum nissanka</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -11167,7 +11167,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Pat Cummins</t>
+          <t>Aqib Nabi Dar</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11177,13 +11177,13 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>pathum nissanka</t>
+          <t>b sai sudharshan</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -11210,7 +11210,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Aqib Nabi Dar</t>
+          <t>Rasik Dar Salam</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11226,7 +11226,7 @@
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>b sai sudharshan</t>
+          <t>rashid khan</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -11253,23 +11253,23 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rasik Dar Salam</t>
+          <t>Urvil Patel</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>DIPESH11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>rashid khan</t>
+          <t>axar patel</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -11296,7 +11296,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Urvil Patel</t>
+          <t>Arshin Kulkarni</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -11312,7 +11312,7 @@
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>axar patel</t>
+          <t>shivang kumar</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -11339,7 +11339,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Arshin Kulkarni</t>
+          <t>Nishant Sindhu</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -11349,13 +11349,13 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>shivang kumar</t>
+          <t>shashank singh</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -11382,7 +11382,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Nishant Sindhu</t>
+          <t>Jayant Yadav</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -11398,7 +11398,7 @@
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>shashank singh</t>
+          <t>prince yadav</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -11425,7 +11425,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Jayant Yadav</t>
+          <t>Ajay Mandal</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -11441,7 +11441,7 @@
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>prince yadav</t>
+          <t>rajat patidar</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -11468,7 +11468,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Ajay Mandal</t>
+          <t>Will Jacks</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -11484,7 +11484,7 @@
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>rajat patidar</t>
+          <t>mitchell marsh</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -11511,7 +11511,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Will Jacks</t>
+          <t>Josh Hazelwood</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -11521,13 +11521,13 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>mitchell marsh</t>
+          <t>josh hazlewood</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -11554,7 +11554,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Josh Hazelwood</t>
+          <t>Kyle Jamieson</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -11570,7 +11570,7 @@
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>josh hazlewood</t>
+          <t>jamie overton</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -11597,7 +11597,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Kyle Jamieson</t>
+          <t>Matheesha Pathirana</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -11613,7 +11613,7 @@
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>jamie overton</t>
+          <t>eshan malinga</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -11640,7 +11640,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Matheesha Pathirana</t>
+          <t>Ben Dwarshuis</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -11656,7 +11656,7 @@
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>eshan malinga</t>
+          <t>b sai sudharshan</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -11683,23 +11683,23 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Ben Dwarshuis</t>
+          <t>Manish Pandey</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>b sai sudharshan</t>
+          <t>hardik pandya</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -11726,7 +11726,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Manish Pandey</t>
+          <t>Mukesh Choudhary</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -11736,13 +11736,13 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>hardik pandya</t>
+          <t>mukul choudhary</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -11769,7 +11769,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Mukesh Choudhary</t>
+          <t>Gurjapneet Singh</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -11785,7 +11785,7 @@
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>mukul choudhary</t>
+          <t>ramandeep singh</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -11812,7 +11812,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Gurjapneet Singh</t>
+          <t>Arjun Tendulkar</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -11828,7 +11828,7 @@
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>ramandeep singh</t>
+          <t>krunal pandya</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -11855,7 +11855,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Arjun Tendulkar</t>
+          <t>Kwena Maphaka</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -11871,7 +11871,7 @@
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>krunal pandya</t>
+          <t>aiden markram</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -11898,23 +11898,23 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Kwena Maphaka</t>
+          <t>Ramkrishna Ghosh</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>aiden markram</t>
+          <t>angkrish raghuvanshi</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -11941,7 +11941,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Ramkrishna Ghosh</t>
+          <t>ashutosh sharma</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -11957,7 +11957,7 @@
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>angkrish raghuvanshi</t>
+          <t>ashok sharma</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -11984,7 +11984,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ashutosh sharma</t>
+          <t>Azmatullah Omarzai</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -11994,13 +11994,13 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>ashok sharma</t>
+          <t>mitchell marsh</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -12027,23 +12027,23 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Azmatullah Omarzai</t>
+          <t>akshat raghuwanshi</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>mitchell marsh</t>
+          <t>angkrish raghuvanshi</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -12070,7 +12070,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>akshat raghuwanshi</t>
+          <t>Himmat Singh</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -12086,7 +12086,7 @@
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>angkrish raghuvanshi</t>
+          <t>prabhsimran singh</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -12113,7 +12113,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Himmat Singh</t>
+          <t>Suryansh Shegde</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -12129,7 +12129,7 @@
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>prabhsimran singh</t>
+          <t>suyash sharma</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -12156,7 +12156,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Suryansh Shegde</t>
+          <t>Tejasvi Singh</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -12172,7 +12172,7 @@
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>suyash sharma</t>
+          <t>prabhsimran singh</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -12199,7 +12199,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Tejasvi Singh</t>
+          <t>Sai Kishor</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -12209,13 +12209,13 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>prabhsimran singh</t>
+          <t>ishan kishan</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -12242,7 +12242,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sai Kishor</t>
+          <t>Akash Deep</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -12258,7 +12258,7 @@
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>ishan kishan</t>
+          <t>arshdeep singh</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -12285,23 +12285,23 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Akash Deep</t>
+          <t>Ben Duckett</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>arshdeep singh</t>
+          <t>ryan rickelton</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -12328,7 +12328,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Ben Duckett</t>
+          <t>Abhishek Porel</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -12344,7 +12344,7 @@
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>ryan rickelton</t>
+          <t>abhishek sharma</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -12371,7 +12371,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Abhishek Porel</t>
+          <t>Rahul Tripathi</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -12387,7 +12387,7 @@
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>abhishek sharma</t>
+          <t>rahul tewatia</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -12414,7 +12414,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Rahul Tripathi</t>
+          <t>Dre Pretorius</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -12430,7 +12430,7 @@
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>rahul tewatia</t>
+          <t>nandre burger</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -12457,7 +12457,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Dre Pretorius</t>
+          <t>Matthew Breetzke</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -12473,7 +12473,7 @@
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>nandre burger</t>
+          <t>matt henry</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -12500,7 +12500,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Matthew Breetzke</t>
+          <t>Anuj Rawat</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -12516,7 +12516,7 @@
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>matt henry</t>
+          <t>rahul tewatia</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -12543,7 +12543,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Anuj Rawat</t>
+          <t>Wanindu Hasaranga</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -12553,13 +12553,13 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>rahul tewatia</t>
+          <t>sandeep sharma</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -12586,7 +12586,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Wanindu Hasaranga</t>
+          <t>Harpreet Brar</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -12596,13 +12596,13 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>sandeep sharma</t>
+          <t>jasprit bumrah</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -12629,7 +12629,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Harpreet Brar</t>
+          <t>Mayank Yadav</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -12645,7 +12645,7 @@
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>jasprit bumrah</t>
+          <t>mayank markande</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -12666,49 +12666,6 @@
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Mayank Yadav</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>BOWL</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>mayank markande</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="G60" t="n">
-        <v>0</v>
-      </c>
-      <c r="H60" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" t="n">
-        <v>0</v>
-      </c>
-      <c r="K60" t="n">
         <v>0</v>
       </c>
     </row>

--- a/IPL_Fantasy_Points.xlsx
+++ b/IPL_Fantasy_Points.xlsx
@@ -4793,7 +4793,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Josh Hazelwood</t>
+          <t>Josh Hazlewood</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4806,31 +4806,31 @@
           <t>BOWL</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
-      <c r="E102" t="inlineStr">
+      <c r="D102" t="inlineStr">
         <is>
           <t>josh hazlewood</t>
         </is>
       </c>
+      <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="G102" t="n">
         <v>0</v>
       </c>
       <c r="H102" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I102" t="n">
         <v>0</v>
       </c>
       <c r="J102" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="K102" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="103">
@@ -8259,11 +8259,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>754</v>
+        <v>765</v>
       </c>
     </row>
     <row r="9">
@@ -8272,11 +8272,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>725</v>
+        <v>754</v>
       </c>
     </row>
     <row r="10">
@@ -10115,7 +10115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K59"/>
+  <dimension ref="A1:K58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11511,7 +11511,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Josh Hazelwood</t>
+          <t>Kyle Jamieson</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -11527,7 +11527,7 @@
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>josh hazlewood</t>
+          <t>jamie overton</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -11554,7 +11554,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Kyle Jamieson</t>
+          <t>Matheesha Pathirana</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -11570,7 +11570,7 @@
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>jamie overton</t>
+          <t>eshan malinga</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -11597,7 +11597,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Matheesha Pathirana</t>
+          <t>Ben Dwarshuis</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -11613,7 +11613,7 @@
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>eshan malinga</t>
+          <t>b sai sudharshan</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -11640,23 +11640,23 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Ben Dwarshuis</t>
+          <t>Manish Pandey</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>b sai sudharshan</t>
+          <t>hardik pandya</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -11683,7 +11683,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Manish Pandey</t>
+          <t>Mukesh Choudhary</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -11693,13 +11693,13 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>hardik pandya</t>
+          <t>mukul choudhary</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -11726,7 +11726,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Mukesh Choudhary</t>
+          <t>Gurjapneet Singh</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -11742,7 +11742,7 @@
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>mukul choudhary</t>
+          <t>ramandeep singh</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -11769,7 +11769,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Gurjapneet Singh</t>
+          <t>Arjun Tendulkar</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -11785,7 +11785,7 @@
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>ramandeep singh</t>
+          <t>krunal pandya</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -11812,7 +11812,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Arjun Tendulkar</t>
+          <t>Kwena Maphaka</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -11828,7 +11828,7 @@
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>krunal pandya</t>
+          <t>aiden markram</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -11855,23 +11855,23 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Kwena Maphaka</t>
+          <t>Ramkrishna Ghosh</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>aiden markram</t>
+          <t>angkrish raghuvanshi</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -11898,7 +11898,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Ramkrishna Ghosh</t>
+          <t>ashutosh sharma</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -11914,7 +11914,7 @@
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>angkrish raghuvanshi</t>
+          <t>ashok sharma</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -11941,7 +11941,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ashutosh sharma</t>
+          <t>Azmatullah Omarzai</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -11951,13 +11951,13 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>ashok sharma</t>
+          <t>mitchell marsh</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -11984,23 +11984,23 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Azmatullah Omarzai</t>
+          <t>akshat raghuwanshi</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>mitchell marsh</t>
+          <t>angkrish raghuvanshi</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -12027,7 +12027,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>akshat raghuwanshi</t>
+          <t>Himmat Singh</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -12043,7 +12043,7 @@
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>angkrish raghuvanshi</t>
+          <t>prabhsimran singh</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -12070,7 +12070,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Himmat Singh</t>
+          <t>Suryansh Shegde</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -12086,7 +12086,7 @@
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>prabhsimran singh</t>
+          <t>suyash sharma</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -12113,7 +12113,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Suryansh Shegde</t>
+          <t>Tejasvi Singh</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -12129,7 +12129,7 @@
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>suyash sharma</t>
+          <t>prabhsimran singh</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -12156,7 +12156,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Tejasvi Singh</t>
+          <t>Sai Kishor</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -12166,13 +12166,13 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>prabhsimran singh</t>
+          <t>ishan kishan</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -12199,7 +12199,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sai Kishor</t>
+          <t>Akash Deep</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -12215,7 +12215,7 @@
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>ishan kishan</t>
+          <t>arshdeep singh</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -12242,23 +12242,23 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Akash Deep</t>
+          <t>Ben Duckett</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>arshdeep singh</t>
+          <t>ryan rickelton</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -12285,7 +12285,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Ben Duckett</t>
+          <t>Abhishek Porel</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -12301,7 +12301,7 @@
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>ryan rickelton</t>
+          <t>abhishek sharma</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -12328,7 +12328,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Abhishek Porel</t>
+          <t>Rahul Tripathi</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -12344,7 +12344,7 @@
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>abhishek sharma</t>
+          <t>rahul tewatia</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -12371,7 +12371,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Rahul Tripathi</t>
+          <t>Dre Pretorius</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -12387,7 +12387,7 @@
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>rahul tewatia</t>
+          <t>nandre burger</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -12414,7 +12414,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Dre Pretorius</t>
+          <t>Matthew Breetzke</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -12430,7 +12430,7 @@
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>nandre burger</t>
+          <t>matt henry</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -12457,7 +12457,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Matthew Breetzke</t>
+          <t>Anuj Rawat</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -12473,7 +12473,7 @@
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>matt henry</t>
+          <t>rahul tewatia</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -12500,7 +12500,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Anuj Rawat</t>
+          <t>Wanindu Hasaranga</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -12510,13 +12510,13 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>rahul tewatia</t>
+          <t>sandeep sharma</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -12543,7 +12543,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Wanindu Hasaranga</t>
+          <t>Harpreet Brar</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -12553,13 +12553,13 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>sandeep sharma</t>
+          <t>jasprit bumrah</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -12586,7 +12586,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Harpreet Brar</t>
+          <t>Mayank Yadav</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -12602,7 +12602,7 @@
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>jasprit bumrah</t>
+          <t>mayank markande</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -12623,49 +12623,6 @@
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Mayank Yadav</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>BOWL</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>mayank markande</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="G59" t="n">
-        <v>0</v>
-      </c>
-      <c r="H59" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" t="n">
-        <v>0</v>
-      </c>
-      <c r="K59" t="n">
         <v>0</v>
       </c>
     </row>

--- a/IPL_Fantasy_Points.xlsx
+++ b/IPL_Fantasy_Points.xlsx
@@ -604,19 +604,19 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>64</v>
+        <v>102</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>64</v>
+        <v>102</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>64</v>
+        <v>102</v>
       </c>
     </row>
     <row r="5">
@@ -1206,19 +1206,19 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>95</v>
+        <v>122</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>95</v>
+        <v>122</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>95</v>
+        <v>122</v>
       </c>
     </row>
     <row r="19">
@@ -1894,19 +1894,19 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="K34" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="35">
@@ -2023,19 +2023,19 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>145</v>
+        <v>184</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>145</v>
+        <v>184</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>145</v>
+        <v>184</v>
       </c>
     </row>
     <row r="38">
@@ -3614,19 +3614,19 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>80</v>
+        <v>131</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>80</v>
+        <v>131</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>80</v>
+        <v>131</v>
       </c>
     </row>
     <row r="75">
@@ -3657,19 +3657,19 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>46</v>
+        <v>103</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>46</v>
+        <v>103</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>46</v>
+        <v>103</v>
       </c>
     </row>
     <row r="76">
@@ -3743,19 +3743,19 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
     </row>
     <row r="78">
@@ -4001,19 +4001,19 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>108</v>
+        <v>119</v>
       </c>
     </row>
     <row r="84">
@@ -4047,16 +4047,16 @@
         <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I84" t="n">
         <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="K84" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="85">
@@ -4262,16 +4262,16 @@
         <v>11</v>
       </c>
       <c r="H89" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I89" t="n">
         <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="K89" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
     </row>
     <row r="90">
@@ -4388,19 +4388,19 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>68</v>
+        <v>137</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>68</v>
+        <v>137</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>68</v>
+        <v>137</v>
       </c>
     </row>
     <row r="93">
@@ -6108,19 +6108,19 @@
         </is>
       </c>
       <c r="G132" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="H132" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I132" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
       </c>
       <c r="K132" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
     </row>
     <row r="133">
@@ -6409,19 +6409,19 @@
         </is>
       </c>
       <c r="G139" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="H139" t="n">
         <v>0</v>
       </c>
       <c r="I139" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
       </c>
       <c r="K139" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="140">
@@ -6796,19 +6796,19 @@
         </is>
       </c>
       <c r="G148" t="n">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="H148" t="n">
         <v>0</v>
       </c>
       <c r="I148" t="n">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
       </c>
       <c r="K148" t="n">
-        <v>46</v>
+        <v>64</v>
       </c>
     </row>
     <row r="149">
@@ -7398,19 +7398,19 @@
         </is>
       </c>
       <c r="G162" t="n">
-        <v>55</v>
+        <v>129</v>
       </c>
       <c r="H162" t="n">
         <v>0</v>
       </c>
       <c r="I162" t="n">
-        <v>55</v>
+        <v>129</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
       </c>
       <c r="K162" t="n">
-        <v>55</v>
+        <v>129</v>
       </c>
     </row>
     <row r="163">
@@ -8181,11 +8181,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MEET11</t>
+          <t>DIPESH11</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1038</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="3">
@@ -8194,11 +8194,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DIPESH11</t>
+          <t>MEET11</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>911</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="4">
@@ -8211,7 +8211,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>873</v>
+        <v>898</v>
       </c>
     </row>
     <row r="5">
@@ -8224,7 +8224,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>833</v>
+        <v>872</v>
       </c>
     </row>
     <row r="6">
@@ -8237,7 +8237,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>832</v>
+        <v>850</v>
       </c>
     </row>
     <row r="7">
@@ -8246,11 +8246,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BABA11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>778</v>
+        <v>834</v>
       </c>
     </row>
     <row r="8">
@@ -8259,11 +8259,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>BABA11</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>765</v>
+        <v>778</v>
       </c>
     </row>
     <row r="9">
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>575</v>
+        <v>613</v>
       </c>
     </row>
     <row r="11">
@@ -8302,7 +8302,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>450</v>
+        <v>524</v>
       </c>
     </row>
   </sheetData>
@@ -8369,7 +8369,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>55</v>
+        <v>129</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -8434,7 +8434,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -8489,7 +8489,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
@@ -8798,10 +8798,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C37" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38">
@@ -8824,7 +8824,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>145</v>
+        <v>184</v>
       </c>
       <c r="C39" t="n">
         <v>0</v>
@@ -8837,7 +8837,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>95</v>
+        <v>122</v>
       </c>
       <c r="C40" t="n">
         <v>0</v>
@@ -9292,7 +9292,7 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="C75" t="n">
         <v>0</v>
@@ -9383,7 +9383,7 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>80</v>
+        <v>131</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
@@ -9435,7 +9435,7 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>46</v>
+        <v>103</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
@@ -9643,7 +9643,7 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C102" t="n">
         <v>0</v>
@@ -9747,10 +9747,10 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="C110" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="111">
@@ -9802,7 +9802,7 @@
         <v>9</v>
       </c>
       <c r="C114" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="115">
@@ -9812,7 +9812,7 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>68</v>
+        <v>137</v>
       </c>
       <c r="C115" t="n">
         <v>0</v>
@@ -9916,7 +9916,7 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>64</v>
+        <v>102</v>
       </c>
       <c r="C123" t="n">
         <v>0</v>
@@ -10075,7 +10075,7 @@
         <v>11</v>
       </c>
       <c r="C135" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="136">

--- a/IPL_Fantasy_Points.xlsx
+++ b/IPL_Fantasy_Points.xlsx
@@ -721,15 +721,15 @@
           <t>BAT</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>nandre burger</t>
-        </is>
-      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>dewald brevis</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -893,15 +893,15 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>jamie overton</t>
-        </is>
-      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>akeal hosein</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1768,16 +1768,16 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32">
@@ -1854,16 +1854,16 @@
         <v>26</v>
       </c>
       <c r="H33" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="K33" t="n">
-        <v>100</v>
+        <v>160</v>
       </c>
     </row>
     <row r="34">
@@ -2754,19 +2754,19 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>22</v>
+        <v>137</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>22</v>
+        <v>137</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>22</v>
+        <v>137</v>
       </c>
     </row>
     <row r="55">
@@ -2840,19 +2840,19 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>62</v>
+        <v>79</v>
       </c>
     </row>
     <row r="57">
@@ -3098,19 +3098,19 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="H62" t="n">
         <v>1</v>
       </c>
       <c r="I62" t="n">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>69</v>
+        <v>89</v>
       </c>
     </row>
     <row r="63">
@@ -3528,19 +3528,19 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>41</v>
+        <v>56</v>
       </c>
     </row>
     <row r="73">
@@ -3786,19 +3786,19 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>49</v>
+        <v>109</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>49</v>
+        <v>109</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>49</v>
+        <v>109</v>
       </c>
     </row>
     <row r="79">
@@ -4164,7 +4164,7 @@
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>b sai sudharshan</t>
+          <t>auqib nabi</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -4345,19 +4345,19 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
       </c>
       <c r="I91" t="n">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>93</v>
+        <v>111</v>
       </c>
     </row>
     <row r="92">
@@ -5291,19 +5291,19 @@
         </is>
       </c>
       <c r="G113" t="n">
-        <v>86</v>
+        <v>127</v>
       </c>
       <c r="H113" t="n">
         <v>0</v>
       </c>
       <c r="I113" t="n">
-        <v>86</v>
+        <v>127</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
       </c>
       <c r="K113" t="n">
-        <v>86</v>
+        <v>127</v>
       </c>
     </row>
     <row r="114">
@@ -5380,16 +5380,16 @@
         <v>80</v>
       </c>
       <c r="H115" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I115" t="n">
         <v>80</v>
       </c>
       <c r="J115" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="K115" t="n">
-        <v>100</v>
+        <v>180</v>
       </c>
     </row>
     <row r="116">
@@ -5549,7 +5549,7 @@
         </is>
       </c>
       <c r="G119" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H119" t="n">
         <v>5</v>
@@ -5666,31 +5666,31 @@
           <t>BOWL</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr"/>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>ramandeep singh</t>
-        </is>
-      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>gurjapneet singh</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="G122" t="n">
         <v>0</v>
       </c>
       <c r="H122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I122" t="n">
         <v>0</v>
       </c>
       <c r="J122" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K122" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="123">
@@ -6010,31 +6010,31 @@
           <t>BAT</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr"/>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>ashok sharma</t>
-        </is>
-      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>ashutosh sharma</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="G130" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
       </c>
       <c r="I130" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
       </c>
       <c r="K130" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="131">
@@ -6151,19 +6151,19 @@
         </is>
       </c>
       <c r="G133" t="n">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="H133" t="n">
         <v>0</v>
       </c>
       <c r="I133" t="n">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
       </c>
       <c r="K133" t="n">
-        <v>160</v>
+        <v>166</v>
       </c>
     </row>
     <row r="134">
@@ -6323,19 +6323,19 @@
         </is>
       </c>
       <c r="G137" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H137" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I137" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J137" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="K137" t="n">
-        <v>42</v>
+        <v>63</v>
       </c>
     </row>
     <row r="138">
@@ -7097,19 +7097,19 @@
         </is>
       </c>
       <c r="G155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H155" t="n">
         <v>4</v>
       </c>
       <c r="I155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J155" t="n">
         <v>80</v>
       </c>
       <c r="K155" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="156">
@@ -7527,19 +7527,19 @@
         </is>
       </c>
       <c r="G165" t="n">
-        <v>74</v>
+        <v>133</v>
       </c>
       <c r="H165" t="n">
         <v>0</v>
       </c>
       <c r="I165" t="n">
-        <v>74</v>
+        <v>133</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
       </c>
       <c r="K165" t="n">
-        <v>74</v>
+        <v>133</v>
       </c>
     </row>
     <row r="166">
@@ -7647,7 +7647,7 @@
       <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr">
         <is>
-          <t>nandre burger</t>
+          <t>dewald brevis</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -8086,7 +8086,7 @@
         </is>
       </c>
       <c r="G178" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H178" t="n">
         <v>3</v>
@@ -8132,16 +8132,16 @@
         <v>9</v>
       </c>
       <c r="H179" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I179" t="n">
         <v>0</v>
       </c>
       <c r="J179" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K179" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -8185,7 +8185,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1104</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="3">
@@ -8198,7 +8198,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1085</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="4">
@@ -8211,7 +8211,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>898</v>
+        <v>944</v>
       </c>
     </row>
     <row r="5">
@@ -8220,11 +8220,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>VATSAL11</t>
+          <t>BABA11</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>872</v>
+        <v>930</v>
       </c>
     </row>
     <row r="6">
@@ -8233,11 +8233,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>850</v>
+        <v>895</v>
       </c>
     </row>
     <row r="7">
@@ -8246,11 +8246,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>VATSAL11</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>834</v>
+        <v>872</v>
       </c>
     </row>
     <row r="8">
@@ -8259,11 +8259,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BABA11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>778</v>
+        <v>852</v>
       </c>
     </row>
     <row r="9">
@@ -8272,11 +8272,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>754</v>
+        <v>851</v>
       </c>
     </row>
     <row r="10">
@@ -8302,7 +8302,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>524</v>
+        <v>603</v>
       </c>
     </row>
   </sheetData>
@@ -8316,7 +8316,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C137"/>
+  <dimension ref="A1:C142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8404,37 +8404,37 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>am ghazanfar</t>
+          <t>akeal hosein</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>angkrish raghuvanshi</t>
+          <t>am ghazanfar</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>155</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>aniket verma</t>
+          <t>angkrish raghuvanshi</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>64</v>
+        <v>155</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -8443,11 +8443,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>anrich nortje</t>
+          <t>aniket verma</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -8456,46 +8456,46 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>anshul kamboj</t>
+          <t>anrich nortje</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>anukul roy</t>
+          <t>anshul kamboj</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>arshdeep singh</t>
+          <t>anukul roy</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ashok sharma</t>
+          <t>arshdeep singh</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -8508,37 +8508,37 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>avesh khan</t>
+          <t>ashok sharma</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>axar patel</t>
+          <t>ashutosh sharma</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ayush badoni</t>
+          <t>auqib nabi</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>66</v>
+        <v>4</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -8547,141 +8547,141 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ayush mhatre</t>
+          <t>avesh khan</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>74</v>
+        <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>b sai sudharshan</t>
+          <t>axar patel</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>98</v>
+        <v>3</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>bhuvneshwar kumar</t>
+          <t>ayush badoni</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>9</v>
+        <v>66</v>
       </c>
       <c r="C20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>blessing muzarabani</t>
+          <t>ayush mhatre</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="C21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>brijesh sharma</t>
+          <t>b sai sudharshan</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>cameron green</t>
+          <t>bhuvneshwar kumar</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>56</v>
+        <v>9</v>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>cooper connolly</t>
+          <t>blessing muzarabani</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>119</v>
+        <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>corbin bosch</t>
+          <t>brijesh sharma</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>david miller</t>
+          <t>cameron green</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>david payne</t>
+          <t>cooper connolly</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>6</v>
+        <v>119</v>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>deepak chahar</t>
+          <t>corbin bosch</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C28" t="n">
         <v>1</v>
@@ -8690,11 +8690,11 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>devdutt padikkal</t>
+          <t>david miller</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>125</v>
+        <v>79</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
@@ -8703,37 +8703,37 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>dhruv chand jurel</t>
+          <t>david payne</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>176</v>
+        <v>6</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>digvesh rathi</t>
+          <t>deepak chahar</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>donavon ferreira</t>
+          <t>devdutt padikkal</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1</v>
+        <v>125</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
@@ -8742,24 +8742,24 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>eshan malinga</t>
+          <t>dewald brevis</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>finn allen</t>
+          <t>dhruv chand jurel</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>80</v>
+        <v>176</v>
       </c>
       <c r="C34" t="n">
         <v>0</v>
@@ -8768,50 +8768,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>glenn phillips</t>
+          <t>digvesh rathi</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>hardik pandya</t>
+          <t>donavon ferreira</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>harsh dubey</t>
+          <t>eshan malinga</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C37" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>harshal patel</t>
+          <t>finn allen</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -8820,11 +8820,11 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>heinrich klaasen</t>
+          <t>glenn phillips</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>184</v>
+        <v>42</v>
       </c>
       <c r="C39" t="n">
         <v>0</v>
@@ -8833,50 +8833,50 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ishan kishan</t>
+          <t>gurjapneet singh</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>122</v>
+        <v>0</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>jacob duffy</t>
+          <t>hardik pandya</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="C41" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>jamie overton</t>
+          <t>harsh dubey</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>80</v>
+        <v>13</v>
       </c>
       <c r="C42" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>jasprit bumrah</t>
+          <t>harshal patel</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
@@ -8885,24 +8885,24 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>jaydev unadkat</t>
+          <t>heinrich klaasen</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4</v>
+        <v>184</v>
       </c>
       <c r="C44" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>jitesh sharma</t>
+          <t>ishan kishan</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>5</v>
+        <v>122</v>
       </c>
       <c r="C45" t="n">
         <v>0</v>
@@ -8911,11 +8911,11 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>jofra archer</t>
+          <t>jacob duffy</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C46" t="n">
         <v>5</v>
@@ -8924,50 +8924,50 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>jos buttler</t>
+          <t>jamie overton</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>josh hazlewood</t>
+          <t>jasprit bumrah</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>kagiso rabada</t>
+          <t>jaydev unadkat</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="C49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>kartik sharma</t>
+          <t>jitesh sharma</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="C50" t="n">
         <v>0</v>
@@ -8976,24 +8976,24 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>kartik tyagi</t>
+          <t>jofra archer</t>
         </is>
       </c>
       <c r="B51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C51" t="n">
         <v>5</v>
-      </c>
-      <c r="C51" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>khaleel ahmed</t>
+          <t>jos buttler</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="C52" t="n">
         <v>0</v>
@@ -9002,24 +9002,24 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>krunal pandya</t>
+          <t>josh hazlewood</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C53" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>kuldeep yadav</t>
+          <t>kagiso rabada</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="C54" t="n">
         <v>3</v>
@@ -9028,11 +9028,11 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>kumar kushagra</t>
+          <t>kartik sharma</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C55" t="n">
         <v>0</v>
@@ -9041,76 +9041,76 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>liam livingstone</t>
+          <t>kartik tyagi</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="C56" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>lokesh rahul</t>
+          <t>khaleel ahmed</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="C57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>lungi ngidi</t>
+          <t>krunal pandya</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C58" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>manimaran siddharth</t>
+          <t>kuldeep yadav</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>marco jansen</t>
+          <t>kumar kushagra</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C60" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>marcus stoinis</t>
+          <t>liam livingstone</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C61" t="n">
         <v>0</v>
@@ -9119,193 +9119,193 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>matt henry</t>
+          <t>lokesh rahul</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>7</v>
+        <v>111</v>
       </c>
       <c r="C62" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>matt short</t>
+          <t>lungi ngidi</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C63" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>mayank markande</t>
+          <t>manimaran siddharth</t>
         </is>
       </c>
       <c r="B64" t="n">
         <v>0</v>
       </c>
       <c r="C64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>mitchell marsh</t>
+          <t>marco jansen</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>64</v>
+        <v>9</v>
       </c>
       <c r="C65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>mitchell santner</t>
+          <t>marcus stoinis</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>mohammed shami</t>
+          <t>matt henry</t>
         </is>
       </c>
       <c r="B67" t="n">
+        <v>7</v>
+      </c>
+      <c r="C67" t="n">
         <v>2</v>
-      </c>
-      <c r="C67" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>mohammed siraj</t>
+          <t>matt short</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>mohsin khan</t>
+          <t>mayank markande</t>
         </is>
       </c>
       <c r="B69" t="n">
         <v>0</v>
       </c>
       <c r="C69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>mukesh kumar</t>
+          <t>mitchell marsh</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="C70" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>mukul choudhary</t>
+          <t>mitchell santner</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="C71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>naman dhir</t>
+          <t>mohammed shami</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>58</v>
+        <v>2</v>
       </c>
       <c r="C72" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>nandre burger</t>
+          <t>mohammed siraj</t>
         </is>
       </c>
       <c r="B73" t="n">
         <v>0</v>
       </c>
       <c r="C73" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>navdeep saini</t>
+          <t>mohsin khan</t>
         </is>
       </c>
       <c r="B74" t="n">
         <v>0</v>
       </c>
       <c r="C74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>nehal wadhera</t>
+          <t>mukesh kumar</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="C75" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>nicholas pooran</t>
+          <t>mukul choudhary</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="C76" t="n">
         <v>0</v>
@@ -9314,37 +9314,37 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>nitish kumar reddy</t>
+          <t>naman dhir</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>96</v>
+        <v>58</v>
       </c>
       <c r="C77" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>nitish rana</t>
+          <t>nandre burger</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="C78" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>noor ahmad</t>
+          <t>navdeep saini</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C79" t="n">
         <v>0</v>
@@ -9353,11 +9353,11 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>pathum nissanka</t>
+          <t>nehal wadhera</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>86</v>
+        <v>27</v>
       </c>
       <c r="C80" t="n">
         <v>0</v>
@@ -9366,11 +9366,11 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>philip salt</t>
+          <t>nicholas pooran</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="C81" t="n">
         <v>0</v>
@@ -9379,24 +9379,24 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>prabhsimran singh</t>
+          <t>nitish kumar reddy</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>131</v>
+        <v>96</v>
       </c>
       <c r="C82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>prashant veer</t>
+          <t>nitish rana</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
@@ -9405,37 +9405,37 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>prasidh krishna</t>
+          <t>noor ahmad</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C84" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>prince yadav</t>
+          <t>pathum nissanka</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="C85" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>priyansh arya</t>
+          <t>philip salt</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>103</v>
+        <v>54</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
@@ -9444,11 +9444,11 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>rahul chahar</t>
+          <t>prabhsimran singh</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
@@ -9457,11 +9457,11 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>rahul tewatia</t>
+          <t>prashant veer</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
@@ -9470,76 +9470,76 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>rajat patidar</t>
+          <t>prasidh krishna</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>142</v>
+        <v>0</v>
       </c>
       <c r="C89" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ramandeep singh</t>
+          <t>prince yadav</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C90" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>rashid khan</t>
+          <t>priyansh arya</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>24</v>
+        <v>103</v>
       </c>
       <c r="C91" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ravi bishnoi</t>
+          <t>rahul chahar</t>
         </is>
       </c>
       <c r="B92" t="n">
         <v>0</v>
       </c>
       <c r="C92" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ravindra jadeja</t>
+          <t>rahul tewatia</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C93" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>rinku singh</t>
+          <t>rajat patidar</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>72</v>
+        <v>142</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
@@ -9548,11 +9548,11 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>rishabh pant</t>
+          <t>ramandeep singh</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>85</v>
+        <v>14</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
@@ -9561,37 +9561,37 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>riyan parag</t>
+          <t>rashid khan</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="C96" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>rohit sharma</t>
+          <t>ravi bishnoi</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>118</v>
+        <v>0</v>
       </c>
       <c r="C97" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>romario shepherd</t>
+          <t>ravindra jadeja</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="C98" t="n">
         <v>3</v>
@@ -9600,11 +9600,11 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>rovman powell</t>
+          <t>rinku singh</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="C99" t="n">
         <v>0</v>
@@ -9613,11 +9613,11 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ruturaj gaikwad</t>
+          <t>rishabh pant</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>41</v>
+        <v>85</v>
       </c>
       <c r="C100" t="n">
         <v>0</v>
@@ -9626,24 +9626,24 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ryan rickelton</t>
+          <t>riyan parag</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>98</v>
+        <v>45</v>
       </c>
       <c r="C101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>salil arora</t>
+          <t>rohit sharma</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>18</v>
+        <v>118</v>
       </c>
       <c r="C102" t="n">
         <v>0</v>
@@ -9652,37 +9652,37 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>sameer rizvi</t>
+          <t>romario shepherd</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>160</v>
+        <v>22</v>
       </c>
       <c r="C103" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>sandeep sharma</t>
+          <t>rovman powell</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C104" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>sanju samson</t>
+          <t>ruturaj gaikwad</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="C105" t="n">
         <v>0</v>
@@ -9691,11 +9691,11 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>sarfaraz khan</t>
+          <t>ryan rickelton</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C106" t="n">
         <v>0</v>
@@ -9704,11 +9704,11 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>shahbaz ahmed</t>
+          <t>salil arora</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C107" t="n">
         <v>0</v>
@@ -9717,11 +9717,11 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>shahrukh khan</t>
+          <t>sameer rizvi</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>15</v>
+        <v>166</v>
       </c>
       <c r="C108" t="n">
         <v>0</v>
@@ -9730,11 +9730,11 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>shardul thakur</t>
+          <t>sandeep sharma</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C109" t="n">
         <v>4</v>
@@ -9743,24 +9743,24 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>shashank singh</t>
+          <t>sanju samson</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>34</v>
+        <v>137</v>
       </c>
       <c r="C110" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>sherfane rutherford</t>
+          <t>sarfaraz khan</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>30</v>
+        <v>99</v>
       </c>
       <c r="C111" t="n">
         <v>0</v>
@@ -9769,11 +9769,11 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>shimron hetmyer</t>
+          <t>shahbaz ahmed</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C112" t="n">
         <v>0</v>
@@ -9782,24 +9782,24 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>shivam dube</t>
+          <t>shahrukh khan</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>69</v>
+        <v>15</v>
       </c>
       <c r="C113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>shivang kumar</t>
+          <t>shardul thakur</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C114" t="n">
         <v>4</v>
@@ -9808,24 +9808,24 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>shreyas iyer</t>
+          <t>shashank singh</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>137</v>
+        <v>34</v>
       </c>
       <c r="C115" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>shubman gill</t>
+          <t>sherfane rutherford</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>109</v>
+        <v>30</v>
       </c>
       <c r="C116" t="n">
         <v>0</v>
@@ -9834,63 +9834,63 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>sunil narine</t>
+          <t>shimron hetmyer</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="C117" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>suryakumar yadav</t>
+          <t>shivam dube</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="C118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>suyash sharma</t>
+          <t>shivang kumar</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C119" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>t natarajan</t>
+          <t>shreyas iyer</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0</v>
+        <v>137</v>
       </c>
       <c r="C120" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>tilak varma</t>
+          <t>shubman gill</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>34</v>
+        <v>109</v>
       </c>
       <c r="C121" t="n">
         <v>0</v>
@@ -9899,24 +9899,24 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>tim david</t>
+          <t>sunil narine</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>99</v>
+        <v>12</v>
       </c>
       <c r="C122" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>travis head</t>
+          <t>suryakumar yadav</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>102</v>
+        <v>73</v>
       </c>
       <c r="C123" t="n">
         <v>0</v>
@@ -9925,63 +9925,63 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>trent boult</t>
+          <t>suyash sharma</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C124" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>tristan stubbs</t>
+          <t>t natarajan</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="C125" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>tushar deshpande</t>
+          <t>tilak varma</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="C126" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>vaibhav arora</t>
+          <t>tim david</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>1</v>
+        <v>99</v>
       </c>
       <c r="C127" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>vaibhav suryavanshi</t>
+          <t>travis head</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>200</v>
+        <v>102</v>
       </c>
       <c r="C128" t="n">
         <v>0</v>
@@ -9990,11 +9990,11 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>varun chakravarthy</t>
+          <t>trent boult</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C129" t="n">
         <v>0</v>
@@ -10003,11 +10003,11 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>venkatesh iyer</t>
+          <t>tristan stubbs</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>29</v>
+        <v>109</v>
       </c>
       <c r="C130" t="n">
         <v>0</v>
@@ -10016,37 +10016,37 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>vijaykumar vyshak</t>
+          <t>tushar deshpande</t>
         </is>
       </c>
       <c r="B131" t="n">
         <v>0</v>
       </c>
       <c r="C131" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>vipraj nigam</t>
+          <t>vaibhav arora</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C132" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>virat kohli</t>
+          <t>vaibhav suryavanshi</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>129</v>
+        <v>200</v>
       </c>
       <c r="C133" t="n">
         <v>0</v>
@@ -10055,52 +10055,117 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>washington sundar</t>
+          <t>varun chakravarthy</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="C134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>xavier bartlett</t>
+          <t>venkatesh iyer</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="C135" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>yashasvi jaiswal</t>
+          <t>vijaykumar vyshak</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>183</v>
+        <v>0</v>
       </c>
       <c r="C136" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
+          <t>vipraj nigam</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>12</v>
+      </c>
+      <c r="C137" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>virat kohli</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>129</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>washington sundar</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>77</v>
+      </c>
+      <c r="C139" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>xavier bartlett</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>11</v>
+      </c>
+      <c r="C140" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>yashasvi jaiswal</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>183</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
           <t>yuzvendra chahal</t>
         </is>
       </c>
-      <c r="B137" t="n">
-        <v>0</v>
-      </c>
-      <c r="C137" t="n">
+      <c r="B142" t="n">
+        <v>0</v>
+      </c>
+      <c r="C142" t="n">
         <v>3</v>
       </c>
     </row>
@@ -10115,7 +10180,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K58"/>
+  <dimension ref="A1:K54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10221,7 +10286,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Dewald Brevis</t>
+          <t>Brydon Carse</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -10231,13 +10296,13 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>nandre burger</t>
+          <t>riyan parag</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -10264,7 +10329,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Akeal Hosein</t>
+          <t>Umran Malik</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -10274,13 +10339,13 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>jamie overton</t>
+          <t>eshan malinga</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -10307,23 +10372,23 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Brydon Carse</t>
+          <t>karun nair</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NIRAV11</t>
+          <t>MEET11</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>riyan parag</t>
+          <t>krunal pandya</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -10350,23 +10415,23 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Umran Malik</t>
+          <t>jacob bethel</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NIRAV11</t>
+          <t>MEET11</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>eshan malinga</t>
+          <t>jacob duffy</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -10393,7 +10458,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>karun nair</t>
+          <t>Jason Holder</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -10403,13 +10468,13 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>krunal pandya</t>
+          <t>jos buttler</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -10436,7 +10501,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>jacob bethel</t>
+          <t>kamindu mendis</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -10446,13 +10511,13 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>jacob duffy</t>
+          <t>naman dhir</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -10479,7 +10544,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Jason Holder</t>
+          <t>Kuldeep sen</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -10489,13 +10554,13 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>jos buttler</t>
+          <t>kuldeep yadav</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -10522,23 +10587,23 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>kamindu mendis</t>
+          <t>Quinton de Kock</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MEET11</t>
+          <t>VATSAL11</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>naman dhir</t>
+          <t>washington sundar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -10565,23 +10630,23 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Kuldeep sen</t>
+          <t>Tom Banton</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MEET11</t>
+          <t>VATSAL11</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>kuldeep yadav</t>
+          <t>t natarajan</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -10608,7 +10673,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Quinton de Kock</t>
+          <t>Tim Siefert</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -10624,7 +10689,7 @@
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>washington sundar</t>
+          <t>jamie overton</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -10651,7 +10716,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Tom Banton</t>
+          <t>Lockie Ferguson</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -10661,13 +10726,13 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>t natarajan</t>
+          <t>lokesh rahul</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -10694,7 +10759,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Tim Siefert</t>
+          <t>Adam Milne</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -10704,13 +10769,13 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>jamie overton</t>
+          <t>david miller</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -10737,23 +10802,23 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Lockie Ferguson</t>
+          <t>Jos Inglis</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>VATSAL11</t>
+          <t>BABA11</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>lokesh rahul</t>
+          <t>marcus stoinis</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -10780,23 +10845,23 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Adam Milne</t>
+          <t>Prithvi Shaw</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>VATSAL11</t>
+          <t>BABA11</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>david miller</t>
+          <t>prasidh krishna</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -10823,7 +10888,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Jos Inglis</t>
+          <t>liam livingston</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -10833,13 +10898,13 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>marcus stoinis</t>
+          <t>liam livingstone</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -10866,7 +10931,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Prithvi Shaw</t>
+          <t>rachin ravindra</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -10876,13 +10941,13 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>prasidh krishna</t>
+          <t>rashid khan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -10909,7 +10974,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>liam livingston</t>
+          <t>Zeeshan Ansari</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -10919,13 +10984,13 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>liam livingstone</t>
+          <t>eshan malinga</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -10952,7 +11017,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>rachin ravindra</t>
+          <t>Mitchell Starc</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -10962,13 +11027,13 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>rashid khan</t>
+          <t>mitchell santner</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -10995,23 +11060,23 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Zeeshan Ansari</t>
+          <t>Mitchel Owen</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BABA11</t>
+          <t>DIPESH11</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>eshan malinga</t>
+          <t>mitchell santner</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -11038,23 +11103,23 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Mitchell Starc</t>
+          <t>Pat Cummins</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BABA11</t>
+          <t>DIPESH11</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>mitchell santner</t>
+          <t>pathum nissanka</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -11081,7 +11146,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Mitchel Owen</t>
+          <t>Aqib Nabi Dar</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -11091,13 +11156,13 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>mitchell santner</t>
+          <t>auqib nabi</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -11124,7 +11189,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Pat Cummins</t>
+          <t>Rasik Dar Salam</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -11134,13 +11199,13 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>pathum nissanka</t>
+          <t>rashid khan</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -11167,23 +11232,23 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Aqib Nabi Dar</t>
+          <t>Urvil Patel</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DIPESH11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>b sai sudharshan</t>
+          <t>axar patel</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -11210,23 +11275,23 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rasik Dar Salam</t>
+          <t>Arshin Kulkarni</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>DIPESH11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>rashid khan</t>
+          <t>shivang kumar</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -11253,7 +11318,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Urvil Patel</t>
+          <t>Nishant Sindhu</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11263,13 +11328,13 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>axar patel</t>
+          <t>shashank singh</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -11296,7 +11361,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Arshin Kulkarni</t>
+          <t>Jayant Yadav</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -11306,13 +11371,13 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>shivang kumar</t>
+          <t>prince yadav</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -11339,7 +11404,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Nishant Sindhu</t>
+          <t>Ajay Mandal</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -11355,7 +11420,7 @@
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>shashank singh</t>
+          <t>rajat patidar</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -11382,7 +11447,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Jayant Yadav</t>
+          <t>Will Jacks</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -11398,7 +11463,7 @@
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>prince yadav</t>
+          <t>mitchell marsh</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -11425,7 +11490,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Ajay Mandal</t>
+          <t>Kyle Jamieson</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -11435,13 +11500,13 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>rajat patidar</t>
+          <t>jamie overton</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -11468,7 +11533,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Will Jacks</t>
+          <t>Matheesha Pathirana</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -11478,13 +11543,13 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>mitchell marsh</t>
+          <t>eshan malinga</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -11511,7 +11576,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Kyle Jamieson</t>
+          <t>Ben Dwarshuis</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -11527,7 +11592,7 @@
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>jamie overton</t>
+          <t>b sai sudharshan</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -11554,23 +11619,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Matheesha Pathirana</t>
+          <t>Manish Pandey</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>eshan malinga</t>
+          <t>hardik pandya</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -11597,12 +11662,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Ben Dwarshuis</t>
+          <t>Mukesh Choudhary</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -11613,7 +11678,7 @@
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>b sai sudharshan</t>
+          <t>mukul choudhary</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -11640,7 +11705,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Manish Pandey</t>
+          <t>Arjun Tendulkar</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -11650,13 +11715,13 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>hardik pandya</t>
+          <t>krunal pandya</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -11683,7 +11748,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Mukesh Choudhary</t>
+          <t>Kwena Maphaka</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -11699,7 +11764,7 @@
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>mukul choudhary</t>
+          <t>aiden markram</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -11726,23 +11791,23 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Gurjapneet Singh</t>
+          <t>Ramkrishna Ghosh</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>ramandeep singh</t>
+          <t>angkrish raghuvanshi</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -11769,23 +11834,23 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Arjun Tendulkar</t>
+          <t>Azmatullah Omarzai</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>krunal pandya</t>
+          <t>mitchell marsh</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -11812,23 +11877,23 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Kwena Maphaka</t>
+          <t>akshat raghuwanshi</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>aiden markram</t>
+          <t>angkrish raghuvanshi</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -11855,12 +11920,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Ramkrishna Ghosh</t>
+          <t>Himmat Singh</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -11871,7 +11936,7 @@
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>angkrish raghuvanshi</t>
+          <t>prabhsimran singh</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -11898,12 +11963,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ashutosh sharma</t>
+          <t>Suryansh Shegde</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -11914,7 +11979,7 @@
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>ashok sharma</t>
+          <t>suyash sharma</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -11941,23 +12006,23 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Azmatullah Omarzai</t>
+          <t>Tejasvi Singh</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>mitchell marsh</t>
+          <t>prabhsimran singh</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -11984,7 +12049,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>akshat raghuwanshi</t>
+          <t>Sai Kishor</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -11994,13 +12059,13 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>angkrish raghuvanshi</t>
+          <t>ishan kishan</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -12027,7 +12092,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Himmat Singh</t>
+          <t>Akash Deep</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -12037,13 +12102,13 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>prabhsimran singh</t>
+          <t>arshdeep singh</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -12070,12 +12135,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Suryansh Shegde</t>
+          <t>Ben Duckett</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -12086,7 +12151,7 @@
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>suyash sharma</t>
+          <t>ryan rickelton</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -12113,12 +12178,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Tejasvi Singh</t>
+          <t>Abhishek Porel</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -12129,7 +12194,7 @@
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>prabhsimran singh</t>
+          <t>abhishek sharma</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -12156,23 +12221,23 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sai Kishor</t>
+          <t>Rahul Tripathi</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>ishan kishan</t>
+          <t>rahul tewatia</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -12199,23 +12264,23 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Akash Deep</t>
+          <t>Dre Pretorius</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>arshdeep singh</t>
+          <t>dewald brevis</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -12242,7 +12307,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Ben Duckett</t>
+          <t>Matthew Breetzke</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -12258,7 +12323,7 @@
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>ryan rickelton</t>
+          <t>matt henry</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -12285,7 +12350,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Abhishek Porel</t>
+          <t>Anuj Rawat</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -12301,7 +12366,7 @@
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>abhishek sharma</t>
+          <t>rahul tewatia</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -12328,7 +12393,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Rahul Tripathi</t>
+          <t>Wanindu Hasaranga</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -12338,13 +12403,13 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>rahul tewatia</t>
+          <t>sandeep sharma</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -12371,7 +12436,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Dre Pretorius</t>
+          <t>Harpreet Brar</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -12381,13 +12446,13 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>nandre burger</t>
+          <t>jasprit bumrah</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -12414,7 +12479,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Matthew Breetzke</t>
+          <t>Mayank Yadav</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -12424,13 +12489,13 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>matt henry</t>
+          <t>mayank markande</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -12451,178 +12516,6 @@
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Anuj Rawat</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>BAT</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>rahul tewatia</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="G55" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0</v>
-      </c>
-      <c r="I55" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Wanindu Hasaranga</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>AR</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>sandeep sharma</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="G56" t="n">
-        <v>0</v>
-      </c>
-      <c r="H56" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Harpreet Brar</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>BOWL</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>jasprit bumrah</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="G57" t="n">
-        <v>0</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" t="n">
-        <v>0</v>
-      </c>
-      <c r="J57" t="n">
-        <v>0</v>
-      </c>
-      <c r="K57" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Mayank Yadav</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>BOWL</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>mayank markande</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="G58" t="n">
-        <v>0</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" t="n">
-        <v>0</v>
-      </c>
-      <c r="K58" t="n">
         <v>0</v>
       </c>
     </row>

--- a/IPL_Fantasy_Points.xlsx
+++ b/IPL_Fantasy_Points.xlsx
@@ -561,19 +561,19 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>85</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4">
@@ -994,16 +994,16 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="K13" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -1249,19 +1249,19 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>109</v>
+        <v>165</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>109</v>
+        <v>165</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>109</v>
+        <v>165</v>
       </c>
     </row>
     <row r="20">
@@ -1550,19 +1550,19 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27">
@@ -2413,16 +2413,16 @@
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="K46" t="n">
-        <v>120</v>
+        <v>200</v>
       </c>
     </row>
     <row r="47">
@@ -2926,19 +2926,19 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>66</v>
+        <v>75</v>
       </c>
     </row>
     <row r="59">
@@ -3571,19 +3571,19 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>98</v>
+        <v>113</v>
       </c>
     </row>
     <row r="74">
@@ -3915,19 +3915,19 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>78</v>
+        <v>108</v>
       </c>
     </row>
     <row r="82">
@@ -4087,7 +4087,7 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H85" t="n">
         <v>3</v>
@@ -4431,19 +4431,19 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>116</v>
+        <v>176</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>116</v>
+        <v>176</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>116</v>
+        <v>176</v>
       </c>
     </row>
     <row r="94">
@@ -4778,16 +4778,16 @@
         <v>23</v>
       </c>
       <c r="H101" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I101" t="n">
         <v>0</v>
       </c>
       <c r="J101" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="K101" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
     </row>
     <row r="102">
@@ -5119,19 +5119,19 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="H109" t="n">
         <v>0</v>
       </c>
       <c r="I109" t="n">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
       </c>
       <c r="K109" t="n">
-        <v>64</v>
+        <v>75</v>
       </c>
     </row>
     <row r="110">
@@ -6280,19 +6280,19 @@
         </is>
       </c>
       <c r="G136" t="n">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="H136" t="n">
         <v>1</v>
       </c>
       <c r="I136" t="n">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="J136" t="n">
         <v>20</v>
       </c>
       <c r="K136" t="n">
-        <v>97</v>
+        <v>118</v>
       </c>
     </row>
     <row r="137">
@@ -6538,19 +6538,19 @@
         </is>
       </c>
       <c r="G142" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="H142" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I142" t="n">
         <v>0</v>
       </c>
       <c r="J142" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="K142" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
     </row>
     <row r="143">
@@ -6710,19 +6710,19 @@
         </is>
       </c>
       <c r="G146" t="n">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="H146" t="n">
         <v>0</v>
       </c>
       <c r="I146" t="n">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
       </c>
       <c r="K146" t="n">
-        <v>22</v>
+        <v>41</v>
       </c>
     </row>
     <row r="147">
@@ -8046,16 +8046,16 @@
         <v>0</v>
       </c>
       <c r="H177" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I177" t="n">
         <v>0</v>
       </c>
       <c r="J177" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="K177" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="178">
@@ -8181,11 +8181,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DIPESH11</t>
+          <t>MEET11</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1179</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="3">
@@ -8194,11 +8194,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MEET11</t>
+          <t>DIPESH11</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1165</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="4">
@@ -8211,7 +8211,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>944</v>
+        <v>985</v>
       </c>
     </row>
     <row r="5">
@@ -8220,11 +8220,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BABA11</t>
+          <t>VATSAL11</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>930</v>
+        <v>952</v>
       </c>
     </row>
     <row r="6">
@@ -8233,11 +8233,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>BABA11</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>895</v>
+        <v>939</v>
       </c>
     </row>
     <row r="7">
@@ -8246,11 +8246,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>VATSAL11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>872</v>
+        <v>932</v>
       </c>
     </row>
     <row r="8">
@@ -8259,11 +8259,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>852</v>
+        <v>906</v>
       </c>
     </row>
     <row r="9">
@@ -8276,7 +8276,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>851</v>
+        <v>870</v>
       </c>
     </row>
     <row r="10">
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>613</v>
+        <v>651</v>
       </c>
     </row>
     <row r="11">
@@ -8302,7 +8302,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>603</v>
+        <v>623</v>
       </c>
     </row>
   </sheetData>
@@ -8316,7 +8316,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C142"/>
+  <dimension ref="A1:C143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8343,7 +8343,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -8382,7 +8382,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -8515,7 +8515,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -8551,7 +8551,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C18" t="n">
         <v>3</v>
@@ -8577,7 +8577,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
@@ -8603,7 +8603,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
@@ -8775,7 +8775,7 @@
         <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
@@ -8820,11 +8820,11 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>glenn phillips</t>
+          <t>george linde</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="C39" t="n">
         <v>0</v>
@@ -8833,24 +8833,24 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>gurjapneet singh</t>
+          <t>glenn phillips</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="C40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>hardik pandya</t>
+          <t>gurjapneet singh</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="C41" t="n">
         <v>1</v>
@@ -8859,37 +8859,37 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>harsh dubey</t>
+          <t>hardik pandya</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="C42" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>harshal patel</t>
+          <t>harsh dubey</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>heinrich klaasen</t>
+          <t>harshal patel</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>184</v>
+        <v>4</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
@@ -8898,11 +8898,11 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ishan kishan</t>
+          <t>heinrich klaasen</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>122</v>
+        <v>184</v>
       </c>
       <c r="C45" t="n">
         <v>0</v>
@@ -8911,24 +8911,24 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>jacob duffy</t>
+          <t>ishan kishan</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="C46" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>jamie overton</t>
+          <t>jacob duffy</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="C47" t="n">
         <v>5</v>
@@ -8937,180 +8937,180 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>jasprit bumrah</t>
+          <t>jamie overton</t>
         </is>
       </c>
       <c r="B48" t="n">
+        <v>80</v>
+      </c>
+      <c r="C48" t="n">
         <v>5</v>
-      </c>
-      <c r="C48" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>jaydev unadkat</t>
+          <t>jasprit bumrah</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C49" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>jitesh sharma</t>
+          <t>jaydev unadkat</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>jofra archer</t>
+          <t>jitesh sharma</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C51" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>jos buttler</t>
+          <t>jofra archer</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>116</v>
+        <v>1</v>
       </c>
       <c r="C52" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>josh hazlewood</t>
+          <t>jos buttler</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0</v>
+        <v>176</v>
       </c>
       <c r="C53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>kagiso rabada</t>
+          <t>josh hazlewood</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="C54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>kartik sharma</t>
+          <t>kagiso rabada</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C55" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>kartik tyagi</t>
+          <t>kartik sharma</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="C56" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>khaleel ahmed</t>
+          <t>kartik tyagi</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>krunal pandya</t>
+          <t>khaleel ahmed</t>
         </is>
       </c>
       <c r="B58" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" t="n">
         <v>1</v>
-      </c>
-      <c r="C58" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>kuldeep yadav</t>
+          <t>krunal pandya</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C59" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>kumar kushagra</t>
+          <t>kuldeep yadav</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="C60" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>liam livingstone</t>
+          <t>kumar kushagra</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C61" t="n">
         <v>0</v>
@@ -9119,11 +9119,11 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>lokesh rahul</t>
+          <t>liam livingstone</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>111</v>
+        <v>14</v>
       </c>
       <c r="C62" t="n">
         <v>0</v>
@@ -9132,37 +9132,37 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>lungi ngidi</t>
+          <t>lokesh rahul</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>3</v>
+        <v>111</v>
       </c>
       <c r="C63" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>manimaran siddharth</t>
+          <t>lungi ngidi</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C64" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>marco jansen</t>
+          <t>manimaran siddharth</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C65" t="n">
         <v>2</v>
@@ -9171,50 +9171,50 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>marcus stoinis</t>
+          <t>marco jansen</t>
         </is>
       </c>
       <c r="B66" t="n">
         <v>9</v>
       </c>
       <c r="C66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>matt henry</t>
+          <t>marcus stoinis</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>matt short</t>
+          <t>matt henry</t>
         </is>
       </c>
       <c r="B68" t="n">
+        <v>7</v>
+      </c>
+      <c r="C68" t="n">
         <v>2</v>
-      </c>
-      <c r="C68" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>mayank markande</t>
+          <t>matt short</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C69" t="n">
         <v>0</v>
@@ -9223,11 +9223,11 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>mitchell marsh</t>
+          <t>mayank markande</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="C70" t="n">
         <v>0</v>
@@ -9236,89 +9236,89 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>mitchell santner</t>
+          <t>mitchell marsh</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>18</v>
+        <v>75</v>
       </c>
       <c r="C71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>mohammed shami</t>
+          <t>mitchell santner</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="C72" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>mohammed siraj</t>
+          <t>mohammed shami</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="C73" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>mohsin khan</t>
+          <t>mohammed siraj</t>
         </is>
       </c>
       <c r="B74" t="n">
         <v>0</v>
       </c>
       <c r="C74" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>mukesh kumar</t>
+          <t>mohsin khan</t>
         </is>
       </c>
       <c r="B75" t="n">
         <v>0</v>
       </c>
       <c r="C75" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>mukul choudhary</t>
+          <t>mukesh kumar</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="C76" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>naman dhir</t>
+          <t>mukul choudhary</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="C77" t="n">
         <v>0</v>
@@ -9327,37 +9327,37 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>nandre burger</t>
+          <t>naman dhir</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="C78" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>navdeep saini</t>
+          <t>nandre burger</t>
         </is>
       </c>
       <c r="B79" t="n">
         <v>0</v>
       </c>
       <c r="C79" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>nehal wadhera</t>
+          <t>navdeep saini</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="C80" t="n">
         <v>0</v>
@@ -9366,11 +9366,11 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>nicholas pooran</t>
+          <t>nehal wadhera</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C81" t="n">
         <v>0</v>
@@ -9379,63 +9379,63 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>nitish kumar reddy</t>
+          <t>nicholas pooran</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>96</v>
+        <v>41</v>
       </c>
       <c r="C82" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>nitish rana</t>
+          <t>nitish kumar reddy</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>20</v>
+        <v>96</v>
       </c>
       <c r="C83" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>noor ahmad</t>
+          <t>nitish rana</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>pathum nissanka</t>
+          <t>noor ahmad</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>127</v>
+        <v>9</v>
       </c>
       <c r="C85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>philip salt</t>
+          <t>pathum nissanka</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>54</v>
+        <v>127</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
@@ -9444,11 +9444,11 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>prabhsimran singh</t>
+          <t>philip salt</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>131</v>
+        <v>54</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
@@ -9457,11 +9457,11 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>prashant veer</t>
+          <t>prabhsimran singh</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>49</v>
+        <v>131</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
@@ -9470,50 +9470,50 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>prasidh krishna</t>
+          <t>prashant veer</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="C89" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>prince yadav</t>
+          <t>prasidh krishna</t>
         </is>
       </c>
       <c r="B90" t="n">
         <v>0</v>
       </c>
       <c r="C90" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>priyansh arya</t>
+          <t>prince yadav</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="C91" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>rahul chahar</t>
+          <t>priyansh arya</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
@@ -9522,11 +9522,11 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>rahul tewatia</t>
+          <t>rahul chahar</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
@@ -9535,11 +9535,11 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>rajat patidar</t>
+          <t>rahul tewatia</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>142</v>
+        <v>34</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
@@ -9548,11 +9548,11 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ramandeep singh</t>
+          <t>rajat patidar</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>14</v>
+        <v>142</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
@@ -9561,63 +9561,63 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>rashid khan</t>
+          <t>ramandeep singh</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="C96" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ravi bishnoi</t>
+          <t>rashid khan</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="C97" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ravindra jadeja</t>
+          <t>ravi bishnoi</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="C98" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>rinku singh</t>
+          <t>ravindra jadeja</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>72</v>
+        <v>31</v>
       </c>
       <c r="C99" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>rishabh pant</t>
+          <t>rinku singh</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="C100" t="n">
         <v>0</v>
@@ -9626,63 +9626,63 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>riyan parag</t>
+          <t>rishabh pant</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>45</v>
+        <v>103</v>
       </c>
       <c r="C101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>rohit sharma</t>
+          <t>riyan parag</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>118</v>
+        <v>45</v>
       </c>
       <c r="C102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>romario shepherd</t>
+          <t>rohit sharma</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>22</v>
+        <v>118</v>
       </c>
       <c r="C103" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>rovman powell</t>
+          <t>romario shepherd</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="C104" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>ruturaj gaikwad</t>
+          <t>rovman powell</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="C105" t="n">
         <v>0</v>
@@ -9691,11 +9691,11 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ryan rickelton</t>
+          <t>ruturaj gaikwad</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>98</v>
+        <v>56</v>
       </c>
       <c r="C106" t="n">
         <v>0</v>
@@ -9704,11 +9704,11 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>salil arora</t>
+          <t>ryan rickelton</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>18</v>
+        <v>98</v>
       </c>
       <c r="C107" t="n">
         <v>0</v>
@@ -9717,11 +9717,11 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>sameer rizvi</t>
+          <t>salil arora</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>166</v>
+        <v>18</v>
       </c>
       <c r="C108" t="n">
         <v>0</v>
@@ -9730,37 +9730,37 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>sandeep sharma</t>
+          <t>sameer rizvi</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0</v>
+        <v>166</v>
       </c>
       <c r="C109" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>sanju samson</t>
+          <t>sandeep sharma</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="C110" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>sarfaraz khan</t>
+          <t>sanju samson</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>99</v>
+        <v>137</v>
       </c>
       <c r="C111" t="n">
         <v>0</v>
@@ -9769,11 +9769,11 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>shahbaz ahmed</t>
+          <t>sarfaraz khan</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>15</v>
+        <v>99</v>
       </c>
       <c r="C112" t="n">
         <v>0</v>
@@ -9782,7 +9782,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>shahrukh khan</t>
+          <t>shahbaz ahmed</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -9795,50 +9795,50 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>shardul thakur</t>
+          <t>shahrukh khan</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C114" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>shashank singh</t>
+          <t>shardul thakur</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="C115" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>sherfane rutherford</t>
+          <t>shashank singh</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C116" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>shimron hetmyer</t>
+          <t>sherfane rutherford</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C117" t="n">
         <v>0</v>
@@ -9847,50 +9847,50 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>shivam dube</t>
+          <t>shimron hetmyer</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>89</v>
+        <v>24</v>
       </c>
       <c r="C118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>shivang kumar</t>
+          <t>shivam dube</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>9</v>
+        <v>89</v>
       </c>
       <c r="C119" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>shreyas iyer</t>
+          <t>shivang kumar</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>137</v>
+        <v>9</v>
       </c>
       <c r="C120" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>shubman gill</t>
+          <t>shreyas iyer</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>109</v>
+        <v>137</v>
       </c>
       <c r="C121" t="n">
         <v>0</v>
@@ -9899,76 +9899,76 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>sunil narine</t>
+          <t>shubman gill</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>12</v>
+        <v>165</v>
       </c>
       <c r="C122" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>suryakumar yadav</t>
+          <t>sunil narine</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>73</v>
+        <v>12</v>
       </c>
       <c r="C123" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>suyash sharma</t>
+          <t>suryakumar yadav</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="C124" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>t natarajan</t>
+          <t>suyash sharma</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C125" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>tilak varma</t>
+          <t>t natarajan</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="C126" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>tim david</t>
+          <t>tilak varma</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>99</v>
+        <v>34</v>
       </c>
       <c r="C127" t="n">
         <v>0</v>
@@ -9977,11 +9977,11 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>travis head</t>
+          <t>tim david</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C128" t="n">
         <v>0</v>
@@ -9990,11 +9990,11 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>trent boult</t>
+          <t>travis head</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>1</v>
+        <v>102</v>
       </c>
       <c r="C129" t="n">
         <v>0</v>
@@ -10003,11 +10003,11 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>tristan stubbs</t>
+          <t>trent boult</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>109</v>
+        <v>1</v>
       </c>
       <c r="C130" t="n">
         <v>0</v>
@@ -10016,50 +10016,50 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>tushar deshpande</t>
+          <t>tristan stubbs</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="C131" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>vaibhav arora</t>
+          <t>tushar deshpande</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C132" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>vaibhav suryavanshi</t>
+          <t>vaibhav arora</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>200</v>
+        <v>1</v>
       </c>
       <c r="C133" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>varun chakravarthy</t>
+          <t>vaibhav suryavanshi</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="C134" t="n">
         <v>0</v>
@@ -10068,11 +10068,11 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>venkatesh iyer</t>
+          <t>varun chakravarthy</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="C135" t="n">
         <v>0</v>
@@ -10081,91 +10081,104 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>vijaykumar vyshak</t>
+          <t>venkatesh iyer</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="C136" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>vipraj nigam</t>
+          <t>vijaykumar vyshak</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C137" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>virat kohli</t>
+          <t>vipraj nigam</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>129</v>
+        <v>12</v>
       </c>
       <c r="C138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>washington sundar</t>
+          <t>virat kohli</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>77</v>
+        <v>129</v>
       </c>
       <c r="C139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>xavier bartlett</t>
+          <t>washington sundar</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>11</v>
+        <v>98</v>
       </c>
       <c r="C140" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>yashasvi jaiswal</t>
+          <t>xavier bartlett</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>183</v>
+        <v>11</v>
       </c>
       <c r="C141" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
+          <t>yashasvi jaiswal</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>183</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
           <t>yuzvendra chahal</t>
         </is>
       </c>
-      <c r="B142" t="n">
-        <v>0</v>
-      </c>
-      <c r="C142" t="n">
+      <c r="B143" t="n">
+        <v>0</v>
+      </c>
+      <c r="C143" t="n">
         <v>3</v>
       </c>
     </row>

--- a/IPL_Fantasy_Points.xlsx
+++ b/IPL_Fantasy_Points.xlsx
@@ -647,19 +647,19 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
@@ -690,19 +690,19 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>142</v>
+        <v>195</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>142</v>
+        <v>195</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>142</v>
+        <v>195</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +819,19 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10">
@@ -2238,19 +2238,19 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H42" t="n">
         <v>3</v>
       </c>
       <c r="I42" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="43">
@@ -2327,16 +2327,16 @@
         <v>8</v>
       </c>
       <c r="H44" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I44" t="n">
         <v>8</v>
       </c>
       <c r="J44" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="K44" t="n">
-        <v>88</v>
+        <v>108</v>
       </c>
     </row>
     <row r="45">
@@ -2499,16 +2499,16 @@
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I48" t="n">
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="K48" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
     </row>
     <row r="49">
@@ -3012,19 +3012,19 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>98</v>
+        <v>135</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>98</v>
+        <v>135</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>98</v>
+        <v>135</v>
       </c>
     </row>
     <row r="61">
@@ -3313,19 +3313,19 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>30</v>
+        <v>101</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>30</v>
+        <v>101</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>30</v>
+        <v>101</v>
       </c>
     </row>
     <row r="68">
@@ -3485,19 +3485,19 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="H71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I71" t="n">
         <v>0</v>
       </c>
       <c r="J71" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="K71" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="72">
@@ -3958,19 +3958,19 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>99</v>
+        <v>133</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>99</v>
+        <v>133</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>99</v>
+        <v>133</v>
       </c>
     </row>
     <row r="83">
@@ -4207,12 +4207,12 @@
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>rashid khan</t>
+          <t>rasikh salam</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>possible_mismatch:81.4814814814815</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -5076,19 +5076,19 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>54</v>
+        <v>132</v>
       </c>
       <c r="H108" t="n">
         <v>0</v>
       </c>
       <c r="I108" t="n">
-        <v>54</v>
+        <v>132</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
       </c>
       <c r="K108" t="n">
-        <v>54</v>
+        <v>132</v>
       </c>
     </row>
     <row r="109">
@@ -5162,19 +5162,19 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
       </c>
       <c r="I110" t="n">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
       </c>
       <c r="K110" t="n">
-        <v>118</v>
+        <v>137</v>
       </c>
     </row>
     <row r="111">
@@ -5334,19 +5334,19 @@
         </is>
       </c>
       <c r="G114" t="n">
-        <v>27</v>
+        <v>67</v>
       </c>
       <c r="H114" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I114" t="n">
-        <v>27</v>
+        <v>67</v>
       </c>
       <c r="J114" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="K114" t="n">
-        <v>47</v>
+        <v>107</v>
       </c>
     </row>
     <row r="115">
@@ -6065,19 +6065,19 @@
         </is>
       </c>
       <c r="G131" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H131" t="n">
         <v>0</v>
       </c>
       <c r="I131" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
       </c>
       <c r="K131" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="132">
@@ -6584,16 +6584,16 @@
         <v>1</v>
       </c>
       <c r="H143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I143" t="n">
         <v>0</v>
       </c>
       <c r="J143" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K143" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="144">
@@ -6624,19 +6624,19 @@
         </is>
       </c>
       <c r="G144" t="n">
-        <v>129</v>
+        <v>179</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
       </c>
       <c r="I144" t="n">
-        <v>129</v>
+        <v>179</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
       </c>
       <c r="K144" t="n">
-        <v>129</v>
+        <v>179</v>
       </c>
     </row>
     <row r="145">
@@ -6667,19 +6667,19 @@
         </is>
       </c>
       <c r="G145" t="n">
-        <v>73</v>
+        <v>106</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
       </c>
       <c r="I145" t="n">
-        <v>73</v>
+        <v>106</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
       </c>
       <c r="K145" t="n">
-        <v>73</v>
+        <v>106</v>
       </c>
     </row>
     <row r="146">
@@ -7014,16 +7014,16 @@
         <v>1</v>
       </c>
       <c r="H153" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I153" t="n">
         <v>1</v>
       </c>
       <c r="J153" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="K153" t="n">
-        <v>81</v>
+        <v>101</v>
       </c>
     </row>
     <row r="154">
@@ -8003,16 +8003,16 @@
         <v>0</v>
       </c>
       <c r="H176" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I176" t="n">
         <v>0</v>
       </c>
       <c r="J176" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="K176" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
     </row>
     <row r="177">
@@ -8181,11 +8181,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MEET11</t>
+          <t>DIPESH11</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1231</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="3">
@@ -8194,11 +8194,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DIPESH11</t>
+          <t>MEET11</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1224</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="4">
@@ -8207,11 +8207,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>BABA11</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>985</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="5">
@@ -8220,11 +8220,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>VATSAL11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>952</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="6">
@@ -8233,11 +8233,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BABA11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>939</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="7">
@@ -8246,11 +8246,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>VATSAL11</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>932</v>
+        <v>994</v>
       </c>
     </row>
     <row r="8">
@@ -8259,11 +8259,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>906</v>
+        <v>973</v>
       </c>
     </row>
     <row r="9">
@@ -8272,11 +8272,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>870</v>
+        <v>932</v>
       </c>
     </row>
     <row r="10">
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>651</v>
+        <v>715</v>
       </c>
     </row>
     <row r="11">
@@ -8302,7 +8302,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>623</v>
+        <v>663</v>
       </c>
     </row>
   </sheetData>
@@ -8316,7 +8316,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C143"/>
+  <dimension ref="A1:C144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8863,10 +8863,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>27</v>
+        <v>67</v>
       </c>
       <c r="C42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -8931,7 +8931,7 @@
         <v>0</v>
       </c>
       <c r="C47" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48">
@@ -8980,7 +8980,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="C51" t="n">
         <v>0</v>
@@ -9087,7 +9087,7 @@
         <v>1</v>
       </c>
       <c r="C59" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="60">
@@ -9253,10 +9253,10 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="C72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
@@ -9331,7 +9331,7 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C78" t="n">
         <v>0</v>
@@ -9448,7 +9448,7 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>54</v>
+        <v>132</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
@@ -9552,7 +9552,7 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>142</v>
+        <v>195</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
@@ -9587,50 +9587,50 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ravi bishnoi</t>
+          <t>rasikh salam</t>
         </is>
       </c>
       <c r="B98" t="n">
         <v>0</v>
       </c>
       <c r="C98" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ravindra jadeja</t>
+          <t>ravi bishnoi</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="C99" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>rinku singh</t>
+          <t>ravindra jadeja</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>72</v>
+        <v>31</v>
       </c>
       <c r="C100" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>rishabh pant</t>
+          <t>rinku singh</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>103</v>
+        <v>72</v>
       </c>
       <c r="C101" t="n">
         <v>0</v>
@@ -9639,63 +9639,63 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>riyan parag</t>
+          <t>rishabh pant</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>45</v>
+        <v>103</v>
       </c>
       <c r="C102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>rohit sharma</t>
+          <t>riyan parag</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>118</v>
+        <v>45</v>
       </c>
       <c r="C103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>romario shepherd</t>
+          <t>rohit sharma</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>22</v>
+        <v>137</v>
       </c>
       <c r="C104" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>rovman powell</t>
+          <t>romario shepherd</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="C105" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ruturaj gaikwad</t>
+          <t>rovman powell</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="C106" t="n">
         <v>0</v>
@@ -9704,11 +9704,11 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ryan rickelton</t>
+          <t>ruturaj gaikwad</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>98</v>
+        <v>56</v>
       </c>
       <c r="C107" t="n">
         <v>0</v>
@@ -9717,11 +9717,11 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>salil arora</t>
+          <t>ryan rickelton</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>18</v>
+        <v>135</v>
       </c>
       <c r="C108" t="n">
         <v>0</v>
@@ -9730,11 +9730,11 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>sameer rizvi</t>
+          <t>salil arora</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>166</v>
+        <v>18</v>
       </c>
       <c r="C109" t="n">
         <v>0</v>
@@ -9743,37 +9743,37 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>sandeep sharma</t>
+          <t>sameer rizvi</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0</v>
+        <v>166</v>
       </c>
       <c r="C110" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>sanju samson</t>
+          <t>sandeep sharma</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="C111" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>sarfaraz khan</t>
+          <t>sanju samson</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>99</v>
+        <v>137</v>
       </c>
       <c r="C112" t="n">
         <v>0</v>
@@ -9782,11 +9782,11 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>shahbaz ahmed</t>
+          <t>sarfaraz khan</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>15</v>
+        <v>99</v>
       </c>
       <c r="C113" t="n">
         <v>0</v>
@@ -9795,7 +9795,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>shahrukh khan</t>
+          <t>shahbaz ahmed</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -9808,50 +9808,50 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>shardul thakur</t>
+          <t>shahrukh khan</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C115" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>shashank singh</t>
+          <t>shardul thakur</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="C116" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>sherfane rutherford</t>
+          <t>shashank singh</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C117" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>shimron hetmyer</t>
+          <t>sherfane rutherford</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="C118" t="n">
         <v>0</v>
@@ -9860,50 +9860,50 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>shivam dube</t>
+          <t>shimron hetmyer</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>89</v>
+        <v>24</v>
       </c>
       <c r="C119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>shivang kumar</t>
+          <t>shivam dube</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>9</v>
+        <v>89</v>
       </c>
       <c r="C120" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>shreyas iyer</t>
+          <t>shivang kumar</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>137</v>
+        <v>9</v>
       </c>
       <c r="C121" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>shubman gill</t>
+          <t>shreyas iyer</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>165</v>
+        <v>137</v>
       </c>
       <c r="C122" t="n">
         <v>0</v>
@@ -9912,50 +9912,50 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>sunil narine</t>
+          <t>shubman gill</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>12</v>
+        <v>165</v>
       </c>
       <c r="C123" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>suryakumar yadav</t>
+          <t>sunil narine</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>73</v>
+        <v>12</v>
       </c>
       <c r="C124" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>suyash sharma</t>
+          <t>suryakumar yadav</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="C125" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>t natarajan</t>
+          <t>suyash sharma</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C126" t="n">
         <v>4</v>
@@ -9964,24 +9964,24 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>tilak varma</t>
+          <t>t natarajan</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="C127" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>tim david</t>
+          <t>tilak varma</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>99</v>
+        <v>35</v>
       </c>
       <c r="C128" t="n">
         <v>0</v>
@@ -9990,11 +9990,11 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>travis head</t>
+          <t>tim david</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>102</v>
+        <v>133</v>
       </c>
       <c r="C129" t="n">
         <v>0</v>
@@ -10003,11 +10003,11 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>trent boult</t>
+          <t>travis head</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>1</v>
+        <v>102</v>
       </c>
       <c r="C130" t="n">
         <v>0</v>
@@ -10016,63 +10016,63 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>tristan stubbs</t>
+          <t>trent boult</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>109</v>
+        <v>1</v>
       </c>
       <c r="C131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>tushar deshpande</t>
+          <t>tristan stubbs</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="C132" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>vaibhav arora</t>
+          <t>tushar deshpande</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C133" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>vaibhav suryavanshi</t>
+          <t>vaibhav arora</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>200</v>
+        <v>1</v>
       </c>
       <c r="C134" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>varun chakravarthy</t>
+          <t>vaibhav suryavanshi</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="C135" t="n">
         <v>0</v>
@@ -10081,11 +10081,11 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>venkatesh iyer</t>
+          <t>varun chakravarthy</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="C136" t="n">
         <v>0</v>
@@ -10094,91 +10094,104 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>vijaykumar vyshak</t>
+          <t>venkatesh iyer</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="C137" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>vipraj nigam</t>
+          <t>vijaykumar vyshak</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C138" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>virat kohli</t>
+          <t>vipraj nigam</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>129</v>
+        <v>12</v>
       </c>
       <c r="C139" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>washington sundar</t>
+          <t>virat kohli</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>98</v>
+        <v>179</v>
       </c>
       <c r="C140" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>xavier bartlett</t>
+          <t>washington sundar</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>11</v>
+        <v>98</v>
       </c>
       <c r="C141" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>yashasvi jaiswal</t>
+          <t>xavier bartlett</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>183</v>
+        <v>11</v>
       </c>
       <c r="C142" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
+          <t>yashasvi jaiswal</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>183</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
           <t>yuzvendra chahal</t>
         </is>
       </c>
-      <c r="B143" t="n">
-        <v>0</v>
-      </c>
-      <c r="C143" t="n">
+      <c r="B144" t="n">
+        <v>0</v>
+      </c>
+      <c r="C144" t="n">
         <v>3</v>
       </c>
     </row>
@@ -10193,7 +10206,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K54"/>
+  <dimension ref="A1:K53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11202,23 +11215,23 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rasik Dar Salam</t>
+          <t>Urvil Patel</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DIPESH11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>rashid khan</t>
+          <t>axar patel</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -11245,7 +11258,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Urvil Patel</t>
+          <t>Arshin Kulkarni</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11261,7 +11274,7 @@
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>axar patel</t>
+          <t>shivang kumar</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -11288,7 +11301,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Arshin Kulkarni</t>
+          <t>Nishant Sindhu</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11298,13 +11311,13 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>shivang kumar</t>
+          <t>shashank singh</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -11331,7 +11344,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Nishant Sindhu</t>
+          <t>Jayant Yadav</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11347,7 +11360,7 @@
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>shashank singh</t>
+          <t>prince yadav</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -11374,7 +11387,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Jayant Yadav</t>
+          <t>Ajay Mandal</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -11390,7 +11403,7 @@
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>prince yadav</t>
+          <t>rajat patidar</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -11417,7 +11430,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Ajay Mandal</t>
+          <t>Will Jacks</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -11433,7 +11446,7 @@
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>rajat patidar</t>
+          <t>mitchell marsh</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -11460,7 +11473,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Will Jacks</t>
+          <t>Kyle Jamieson</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -11470,13 +11483,13 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>mitchell marsh</t>
+          <t>jamie overton</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -11503,7 +11516,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Kyle Jamieson</t>
+          <t>Matheesha Pathirana</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -11519,7 +11532,7 @@
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>jamie overton</t>
+          <t>eshan malinga</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -11546,7 +11559,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Matheesha Pathirana</t>
+          <t>Ben Dwarshuis</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -11562,7 +11575,7 @@
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>eshan malinga</t>
+          <t>b sai sudharshan</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -11589,23 +11602,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Ben Dwarshuis</t>
+          <t>Manish Pandey</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>b sai sudharshan</t>
+          <t>hardik pandya</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -11632,7 +11645,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Manish Pandey</t>
+          <t>Mukesh Choudhary</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -11642,13 +11655,13 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>hardik pandya</t>
+          <t>mukul choudhary</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -11675,7 +11688,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Mukesh Choudhary</t>
+          <t>Arjun Tendulkar</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -11691,7 +11704,7 @@
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>mukul choudhary</t>
+          <t>krunal pandya</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -11718,7 +11731,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Arjun Tendulkar</t>
+          <t>Kwena Maphaka</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -11734,7 +11747,7 @@
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>krunal pandya</t>
+          <t>aiden markram</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -11761,23 +11774,23 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Kwena Maphaka</t>
+          <t>Ramkrishna Ghosh</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>aiden markram</t>
+          <t>angkrish raghuvanshi</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -11804,7 +11817,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Ramkrishna Ghosh</t>
+          <t>Azmatullah Omarzai</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -11814,13 +11827,13 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>angkrish raghuvanshi</t>
+          <t>mitchell marsh</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -11847,23 +11860,23 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Azmatullah Omarzai</t>
+          <t>akshat raghuwanshi</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>mitchell marsh</t>
+          <t>angkrish raghuvanshi</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -11890,7 +11903,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>akshat raghuwanshi</t>
+          <t>Himmat Singh</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -11906,7 +11919,7 @@
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>angkrish raghuvanshi</t>
+          <t>prabhsimran singh</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -11933,7 +11946,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Himmat Singh</t>
+          <t>Suryansh Shegde</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -11949,7 +11962,7 @@
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>prabhsimran singh</t>
+          <t>suyash sharma</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -11976,7 +11989,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Suryansh Shegde</t>
+          <t>Tejasvi Singh</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -11992,7 +12005,7 @@
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>suyash sharma</t>
+          <t>prabhsimran singh</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -12019,7 +12032,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Tejasvi Singh</t>
+          <t>Sai Kishor</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -12029,13 +12042,13 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>prabhsimran singh</t>
+          <t>ishan kishan</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -12062,7 +12075,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sai Kishor</t>
+          <t>Akash Deep</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -12078,7 +12091,7 @@
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>ishan kishan</t>
+          <t>arshdeep singh</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -12105,23 +12118,23 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Akash Deep</t>
+          <t>Ben Duckett</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>arshdeep singh</t>
+          <t>ryan rickelton</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -12148,7 +12161,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Ben Duckett</t>
+          <t>Abhishek Porel</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -12164,7 +12177,7 @@
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>ryan rickelton</t>
+          <t>abhishek sharma</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -12191,7 +12204,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Abhishek Porel</t>
+          <t>Rahul Tripathi</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -12207,7 +12220,7 @@
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>abhishek sharma</t>
+          <t>rahul tewatia</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -12234,7 +12247,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Rahul Tripathi</t>
+          <t>Dre Pretorius</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -12250,7 +12263,7 @@
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>rahul tewatia</t>
+          <t>dewald brevis</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -12277,7 +12290,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Dre Pretorius</t>
+          <t>Matthew Breetzke</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -12293,7 +12306,7 @@
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>dewald brevis</t>
+          <t>matt henry</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -12320,7 +12333,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Matthew Breetzke</t>
+          <t>Anuj Rawat</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -12336,7 +12349,7 @@
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>matt henry</t>
+          <t>rahul tewatia</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -12363,7 +12376,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Anuj Rawat</t>
+          <t>Wanindu Hasaranga</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -12373,13 +12386,13 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>rahul tewatia</t>
+          <t>sandeep sharma</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -12406,7 +12419,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Wanindu Hasaranga</t>
+          <t>Harpreet Brar</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -12416,13 +12429,13 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>sandeep sharma</t>
+          <t>jasprit bumrah</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -12449,7 +12462,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Harpreet Brar</t>
+          <t>Mayank Yadav</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -12465,7 +12478,7 @@
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>jasprit bumrah</t>
+          <t>mayank markande</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -12486,49 +12499,6 @@
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Mayank Yadav</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>BOWL</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>mayank markande</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="G54" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12543,7 +12513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12601,6 +12571,49 @@
         <is>
           <t>Points</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Rasik Dar Salam</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>DIPESH11</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>BOWL</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>rasikh salam</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>possible_mismatch:81.4814814814815</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/IPL_Fantasy_Points.xlsx
+++ b/IPL_Fantasy_Points.xlsx
@@ -604,19 +604,19 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>102</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5">
@@ -1206,19 +1206,19 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>122</v>
+        <v>213</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>122</v>
+        <v>213</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>122</v>
+        <v>213</v>
       </c>
     </row>
     <row r="19">
@@ -1679,19 +1679,19 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="K29" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="30">
@@ -2023,19 +2023,19 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>184</v>
+        <v>224</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>184</v>
+        <v>224</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>184</v>
+        <v>224</v>
       </c>
     </row>
     <row r="38">
@@ -2109,19 +2109,19 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>96</v>
+        <v>124</v>
       </c>
       <c r="H39" t="n">
         <v>2</v>
       </c>
       <c r="I39" t="n">
-        <v>96</v>
+        <v>124</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>96</v>
+        <v>124</v>
       </c>
     </row>
     <row r="40">
@@ -2281,19 +2281,19 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>31</v>
+        <v>76</v>
       </c>
       <c r="H43" t="n">
         <v>3</v>
       </c>
       <c r="I43" t="n">
-        <v>31</v>
+        <v>76</v>
       </c>
       <c r="J43" t="n">
         <v>60</v>
       </c>
       <c r="K43" t="n">
-        <v>91</v>
+        <v>136</v>
       </c>
     </row>
     <row r="44">
@@ -2542,16 +2542,16 @@
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="K49" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="50">
@@ -4302,19 +4302,19 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="91">
@@ -4732,19 +4732,19 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="H100" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I100" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="J100" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="K100" t="n">
-        <v>65</v>
+        <v>89</v>
       </c>
     </row>
     <row r="101">
@@ -5033,7 +5033,7 @@
         </is>
       </c>
       <c r="G107" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H107" t="n">
         <v>5</v>
@@ -5420,19 +5420,19 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="H116" t="n">
         <v>0</v>
       </c>
       <c r="I116" t="n">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
       </c>
       <c r="K116" t="n">
-        <v>1</v>
+        <v>70</v>
       </c>
     </row>
     <row r="117">
@@ -6409,19 +6409,19 @@
         </is>
       </c>
       <c r="G139" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="H139" t="n">
         <v>0</v>
       </c>
       <c r="I139" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
       </c>
       <c r="K139" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
     </row>
     <row r="140">
@@ -6796,19 +6796,19 @@
         </is>
       </c>
       <c r="G148" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="H148" t="n">
         <v>0</v>
       </c>
       <c r="I148" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
       </c>
       <c r="K148" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
     </row>
     <row r="149">
@@ -7054,19 +7054,19 @@
         </is>
       </c>
       <c r="G154" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H154" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I154" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J154" t="n">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="K154" t="n">
-        <v>101</v>
+        <v>143</v>
       </c>
     </row>
     <row r="155">
@@ -7647,7 +7647,7 @@
       <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr">
         <is>
-          <t>dewald brevis</t>
+          <t>lhuan dre pretorius</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -8181,11 +8181,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DIPESH11</t>
+          <t>MEET11</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1258</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="3">
@@ -8194,11 +8194,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MEET11</t>
+          <t>DIPESH11</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1231</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="4">
@@ -8207,11 +8207,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BABA11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1067</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="5">
@@ -8220,11 +8220,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>VATSAL11</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1063</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="6">
@@ -8233,11 +8233,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>BABA11</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1006</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="7">
@@ -8246,11 +8246,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>VATSAL11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>994</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="8">
@@ -8263,7 +8263,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>973</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="9">
@@ -8276,7 +8276,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>932</v>
+        <v>957</v>
       </c>
     </row>
     <row r="10">
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>715</v>
+        <v>733</v>
       </c>
     </row>
     <row r="11">
@@ -8316,7 +8316,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C144"/>
+  <dimension ref="A1:C147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -8785,7 +8785,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
@@ -8801,7 +8801,7 @@
         <v>0</v>
       </c>
       <c r="C37" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38">
@@ -8902,7 +8902,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>184</v>
+        <v>224</v>
       </c>
       <c r="C45" t="n">
         <v>0</v>
@@ -8915,7 +8915,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>122</v>
+        <v>213</v>
       </c>
       <c r="C46" t="n">
         <v>0</v>
@@ -8993,10 +8993,10 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C52" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="53">
@@ -9119,11 +9119,11 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>liam livingstone</t>
+          <t>lhuan dre pretorius</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C62" t="n">
         <v>0</v>
@@ -9132,11 +9132,11 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>lokesh rahul</t>
+          <t>liam livingstone</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>111</v>
+        <v>14</v>
       </c>
       <c r="C63" t="n">
         <v>0</v>
@@ -9145,37 +9145,37 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>lungi ngidi</t>
+          <t>lokesh rahul</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>3</v>
+        <v>111</v>
       </c>
       <c r="C64" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>manimaran siddharth</t>
+          <t>lungi ngidi</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C65" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>marco jansen</t>
+          <t>manimaran siddharth</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C66" t="n">
         <v>2</v>
@@ -9184,50 +9184,50 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>marcus stoinis</t>
+          <t>marco jansen</t>
         </is>
       </c>
       <c r="B67" t="n">
         <v>9</v>
       </c>
       <c r="C67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>matt henry</t>
+          <t>marcus stoinis</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>matt short</t>
+          <t>matt henry</t>
         </is>
       </c>
       <c r="B69" t="n">
+        <v>7</v>
+      </c>
+      <c r="C69" t="n">
         <v>2</v>
-      </c>
-      <c r="C69" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>mayank markande</t>
+          <t>matt short</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C70" t="n">
         <v>0</v>
@@ -9236,11 +9236,11 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>mitchell marsh</t>
+          <t>mayank markande</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="C71" t="n">
         <v>0</v>
@@ -9249,89 +9249,89 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>mitchell santner</t>
+          <t>mitchell marsh</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>26</v>
+        <v>75</v>
       </c>
       <c r="C72" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>mohammed shami</t>
+          <t>mitchell santner</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="C73" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>mohammed siraj</t>
+          <t>mohammed shami</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="C74" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>mohsin khan</t>
+          <t>mohammed siraj</t>
         </is>
       </c>
       <c r="B75" t="n">
         <v>0</v>
       </c>
       <c r="C75" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>mukesh kumar</t>
+          <t>mohsin khan</t>
         </is>
       </c>
       <c r="B76" t="n">
         <v>0</v>
       </c>
       <c r="C76" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>mukul choudhary</t>
+          <t>mukesh kumar</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="C77" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>naman dhir</t>
+          <t>mukul choudhary</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>59</v>
+        <v>88</v>
       </c>
       <c r="C78" t="n">
         <v>0</v>
@@ -9340,37 +9340,37 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>nandre burger</t>
+          <t>naman dhir</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="C79" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>navdeep saini</t>
+          <t>nandre burger</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C80" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>nehal wadhera</t>
+          <t>navdeep saini</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="C81" t="n">
         <v>0</v>
@@ -9379,11 +9379,11 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>nicholas pooran</t>
+          <t>nehal wadhera</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
@@ -9392,63 +9392,63 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>nitish kumar reddy</t>
+          <t>nicholas pooran</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>96</v>
+        <v>41</v>
       </c>
       <c r="C83" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>nitish rana</t>
+          <t>nitish kumar reddy</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>20</v>
+        <v>124</v>
       </c>
       <c r="C84" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>noor ahmad</t>
+          <t>nitish rana</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>pathum nissanka</t>
+          <t>noor ahmad</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>127</v>
+        <v>9</v>
       </c>
       <c r="C86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>philip salt</t>
+          <t>pathum nissanka</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
@@ -9457,11 +9457,11 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>prabhsimran singh</t>
+          <t>philip salt</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
@@ -9470,11 +9470,11 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>prashant veer</t>
+          <t>prabhsimran singh</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>49</v>
+        <v>131</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
@@ -9483,63 +9483,63 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>prasidh krishna</t>
+          <t>praful hinge</t>
         </is>
       </c>
       <c r="B90" t="n">
         <v>0</v>
       </c>
       <c r="C90" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>prince yadav</t>
+          <t>prashant veer</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="C91" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>priyansh arya</t>
+          <t>prasidh krishna</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="C92" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>rahul chahar</t>
+          <t>prince yadav</t>
         </is>
       </c>
       <c r="B93" t="n">
         <v>0</v>
       </c>
       <c r="C93" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>rahul tewatia</t>
+          <t>priyansh arya</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>34</v>
+        <v>103</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
@@ -9548,11 +9548,11 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>rajat patidar</t>
+          <t>rahul chahar</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>195</v>
+        <v>0</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
@@ -9561,11 +9561,11 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ramandeep singh</t>
+          <t>rahul tewatia</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="C96" t="n">
         <v>0</v>
@@ -9574,102 +9574,102 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>rashid khan</t>
+          <t>rajat patidar</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>24</v>
+        <v>195</v>
       </c>
       <c r="C97" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>rasikh salam</t>
+          <t>ramandeep singh</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="C98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ravi bishnoi</t>
+          <t>rashid khan</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="C99" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ravindra jadeja</t>
+          <t>rasikh salam</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="C100" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>rinku singh</t>
+          <t>ravi bishnoi</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="C101" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>rishabh pant</t>
+          <t>ravindra jadeja</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>103</v>
+        <v>76</v>
       </c>
       <c r="C102" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>riyan parag</t>
+          <t>rinku singh</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="C103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>rohit sharma</t>
+          <t>rishabh pant</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>137</v>
+        <v>103</v>
       </c>
       <c r="C104" t="n">
         <v>0</v>
@@ -9678,24 +9678,24 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>romario shepherd</t>
+          <t>riyan parag</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C105" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>rovman powell</t>
+          <t>rohit sharma</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>39</v>
+        <v>137</v>
       </c>
       <c r="C106" t="n">
         <v>0</v>
@@ -9704,24 +9704,24 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ruturaj gaikwad</t>
+          <t>romario shepherd</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="C107" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ryan rickelton</t>
+          <t>rovman powell</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>135</v>
+        <v>39</v>
       </c>
       <c r="C108" t="n">
         <v>0</v>
@@ -9730,11 +9730,11 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>salil arora</t>
+          <t>ruturaj gaikwad</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="C109" t="n">
         <v>0</v>
@@ -9743,11 +9743,11 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>sameer rizvi</t>
+          <t>ryan rickelton</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>166</v>
+        <v>135</v>
       </c>
       <c r="C110" t="n">
         <v>0</v>
@@ -9756,7 +9756,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>sandeep sharma</t>
+          <t>sakib hussain</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -9769,11 +9769,11 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>sanju samson</t>
+          <t>salil arora</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>137</v>
+        <v>42</v>
       </c>
       <c r="C112" t="n">
         <v>0</v>
@@ -9782,11 +9782,11 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>sarfaraz khan</t>
+          <t>sameer rizvi</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>99</v>
+        <v>166</v>
       </c>
       <c r="C113" t="n">
         <v>0</v>
@@ -9795,24 +9795,24 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>shahbaz ahmed</t>
+          <t>sandeep sharma</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="C114" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>shahrukh khan</t>
+          <t>sanju samson</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="C115" t="n">
         <v>0</v>
@@ -9821,37 +9821,37 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>shardul thakur</t>
+          <t>sarfaraz khan</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>8</v>
+        <v>99</v>
       </c>
       <c r="C116" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>shashank singh</t>
+          <t>shahbaz ahmed</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="C117" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>sherfane rutherford</t>
+          <t>shahrukh khan</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>101</v>
+        <v>15</v>
       </c>
       <c r="C118" t="n">
         <v>0</v>
@@ -9860,50 +9860,50 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>shimron hetmyer</t>
+          <t>shardul thakur</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="C119" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>shivam dube</t>
+          <t>shashank singh</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>89</v>
+        <v>34</v>
       </c>
       <c r="C120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>shivang kumar</t>
+          <t>sherfane rutherford</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>9</v>
+        <v>101</v>
       </c>
       <c r="C121" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>shreyas iyer</t>
+          <t>shimron hetmyer</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>137</v>
+        <v>24</v>
       </c>
       <c r="C122" t="n">
         <v>0</v>
@@ -9912,37 +9912,37 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>shubman gill</t>
+          <t>shivam dube</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>165</v>
+        <v>89</v>
       </c>
       <c r="C123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>sunil narine</t>
+          <t>shivang kumar</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C124" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>suryakumar yadav</t>
+          <t>shreyas iyer</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>106</v>
+        <v>137</v>
       </c>
       <c r="C125" t="n">
         <v>0</v>
@@ -9951,37 +9951,37 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>suyash sharma</t>
+          <t>shubman gill</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0</v>
+        <v>165</v>
       </c>
       <c r="C126" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>t natarajan</t>
+          <t>sunil narine</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C127" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>tilak varma</t>
+          <t>suryakumar yadav</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>35</v>
+        <v>106</v>
       </c>
       <c r="C128" t="n">
         <v>0</v>
@@ -9990,50 +9990,50 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>tim david</t>
+          <t>suyash sharma</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>133</v>
+        <v>0</v>
       </c>
       <c r="C129" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>travis head</t>
+          <t>t natarajan</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>102</v>
+        <v>1</v>
       </c>
       <c r="C130" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>trent boult</t>
+          <t>tilak varma</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="C131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>tristan stubbs</t>
+          <t>tim david</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>109</v>
+        <v>133</v>
       </c>
       <c r="C132" t="n">
         <v>0</v>
@@ -10042,37 +10042,37 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>tushar deshpande</t>
+          <t>travis head</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="C133" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>vaibhav arora</t>
+          <t>trent boult</t>
         </is>
       </c>
       <c r="B134" t="n">
         <v>1</v>
       </c>
       <c r="C134" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>vaibhav suryavanshi</t>
+          <t>tristan stubbs</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>200</v>
+        <v>109</v>
       </c>
       <c r="C135" t="n">
         <v>0</v>
@@ -10081,63 +10081,63 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>varun chakravarthy</t>
+          <t>tushar deshpande</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="C136" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>venkatesh iyer</t>
+          <t>vaibhav arora</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C137" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>vijaykumar vyshak</t>
+          <t>vaibhav suryavanshi</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="C138" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>vipraj nigam</t>
+          <t>varun chakravarthy</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>virat kohli</t>
+          <t>venkatesh iyer</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>179</v>
+        <v>29</v>
       </c>
       <c r="C140" t="n">
         <v>0</v>
@@ -10146,37 +10146,37 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>washington sundar</t>
+          <t>vijaykumar vyshak</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="C141" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>xavier bartlett</t>
+          <t>vipraj nigam</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C142" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>yashasvi jaiswal</t>
+          <t>virat kohli</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C143" t="n">
         <v>0</v>
@@ -10185,13 +10185,52 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
+          <t>washington sundar</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>98</v>
+      </c>
+      <c r="C144" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>xavier bartlett</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>11</v>
+      </c>
+      <c r="C145" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>yashasvi jaiswal</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>184</v>
+      </c>
+      <c r="C146" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
           <t>yuzvendra chahal</t>
         </is>
       </c>
-      <c r="B144" t="n">
-        <v>0</v>
-      </c>
-      <c r="C144" t="n">
+      <c r="B147" t="n">
+        <v>0</v>
+      </c>
+      <c r="C147" t="n">
         <v>3</v>
       </c>
     </row>
@@ -12263,7 +12302,7 @@
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>dewald brevis</t>
+          <t>lhuan dre pretorius</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -12715,19 +12754,19 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/IPL_Fantasy_Points.xlsx
+++ b/IPL_Fantasy_Points.xlsx
@@ -733,19 +733,19 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8">
@@ -908,16 +908,16 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12">
@@ -948,19 +948,19 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="K12" t="n">
-        <v>60</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13">
@@ -1292,19 +1292,19 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>124</v>
+        <v>152</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>124</v>
+        <v>152</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>124</v>
+        <v>152</v>
       </c>
     </row>
     <row r="21">
@@ -1378,19 +1378,19 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>14</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23">
@@ -1768,16 +1768,16 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="K31" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="32">
@@ -1854,16 +1854,16 @@
         <v>26</v>
       </c>
       <c r="H33" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="K33" t="n">
-        <v>160</v>
+        <v>200</v>
       </c>
     </row>
     <row r="34">
@@ -2754,19 +2754,19 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>137</v>
+        <v>185</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>137</v>
+        <v>185</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>137</v>
+        <v>185</v>
       </c>
     </row>
     <row r="55">
@@ -3055,19 +3055,19 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
     </row>
     <row r="62">
@@ -3098,19 +3098,19 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="H62" t="n">
         <v>1</v>
       </c>
       <c r="I62" t="n">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>89</v>
+        <v>102</v>
       </c>
     </row>
     <row r="63">
@@ -3141,19 +3141,19 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>39</v>
+        <v>70</v>
       </c>
     </row>
     <row r="64">
@@ -3528,19 +3528,19 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
     </row>
     <row r="73">
@@ -3829,19 +3829,19 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>99</v>
+        <v>122</v>
       </c>
       <c r="H79" t="n">
         <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>99</v>
+        <v>122</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>99</v>
+        <v>122</v>
       </c>
     </row>
     <row r="80">
@@ -4148,7 +4148,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Aqib Nabi Dar</t>
+          <t>Auqib Dar</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4191,7 +4191,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Rasik Dar Salam</t>
+          <t>Rasikh Salam</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4204,31 +4204,31 @@
           <t>BOWL</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr">
+      <c r="D88" t="inlineStr">
         <is>
           <t>rasikh salam</t>
         </is>
       </c>
+      <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
-          <t>possible_mismatch:81.4814814814815</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="G88" t="n">
         <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I88" t="n">
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K88" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="89">
@@ -5377,19 +5377,19 @@
         </is>
       </c>
       <c r="G115" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H115" t="n">
         <v>5</v>
       </c>
       <c r="I115" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="J115" t="n">
         <v>100</v>
       </c>
       <c r="K115" t="n">
-        <v>180</v>
+        <v>187</v>
       </c>
     </row>
     <row r="116">
@@ -5509,16 +5509,16 @@
         <v>5</v>
       </c>
       <c r="H118" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I118" t="n">
         <v>0</v>
       </c>
       <c r="J118" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="K118" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
     </row>
     <row r="119">
@@ -6194,19 +6194,19 @@
         </is>
       </c>
       <c r="G134" t="n">
-        <v>155</v>
+        <v>182</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
       </c>
       <c r="I134" t="n">
-        <v>155</v>
+        <v>182</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
       </c>
       <c r="K134" t="n">
-        <v>155</v>
+        <v>182</v>
       </c>
     </row>
     <row r="135">
@@ -7229,16 +7229,16 @@
         <v>1</v>
       </c>
       <c r="H158" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I158" t="n">
         <v>0</v>
       </c>
       <c r="J158" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="K158" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
     </row>
     <row r="159">
@@ -7527,19 +7527,19 @@
         </is>
       </c>
       <c r="G165" t="n">
-        <v>133</v>
+        <v>171</v>
       </c>
       <c r="H165" t="n">
         <v>0</v>
       </c>
       <c r="I165" t="n">
-        <v>133</v>
+        <v>171</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
       </c>
       <c r="K165" t="n">
-        <v>133</v>
+        <v>171</v>
       </c>
     </row>
     <row r="166">
@@ -7570,19 +7570,19 @@
         </is>
       </c>
       <c r="G166" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H166" t="n">
         <v>0</v>
       </c>
       <c r="I166" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
       </c>
       <c r="K166" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="167">
@@ -7828,19 +7828,19 @@
         </is>
       </c>
       <c r="G172" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="H172" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I172" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="J172" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="K172" t="n">
-        <v>52</v>
+        <v>96</v>
       </c>
     </row>
     <row r="173">
@@ -8132,16 +8132,16 @@
         <v>9</v>
       </c>
       <c r="H179" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I179" t="n">
         <v>0</v>
       </c>
       <c r="J179" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="K179" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -8185,7 +8185,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1342</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="3">
@@ -8198,7 +8198,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1258</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="4">
@@ -8211,7 +8211,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1132</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="5">
@@ -8220,11 +8220,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>VATSAL11</t>
+          <t>BABA11</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1127</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="6">
@@ -8233,11 +8233,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BABA11</t>
+          <t>VATSAL11</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1067</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="7">
@@ -8250,7 +8250,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1030</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="8">
@@ -8263,7 +8263,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1021</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="9">
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>733</v>
+        <v>815</v>
       </c>
     </row>
     <row r="11">
@@ -8302,7 +8302,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>663</v>
+        <v>806</v>
       </c>
     </row>
   </sheetData>
@@ -8395,7 +8395,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>124</v>
+        <v>152</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -8411,7 +8411,7 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -8434,7 +8434,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>155</v>
+        <v>182</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -8476,7 +8476,7 @@
         <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
@@ -8486,10 +8486,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -8590,7 +8590,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>133</v>
+        <v>171</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
@@ -8746,7 +8746,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="C33" t="n">
         <v>0</v>
@@ -8811,7 +8811,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -8941,7 +8941,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="C48" t="n">
         <v>5</v>
@@ -9061,7 +9061,7 @@
         <v>5</v>
       </c>
       <c r="C57" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58">
@@ -9074,7 +9074,7 @@
         <v>0</v>
       </c>
       <c r="C58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -9438,7 +9438,7 @@
         <v>9</v>
       </c>
       <c r="C86" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="87">
@@ -9591,7 +9591,7 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="C98" t="n">
         <v>0</v>
@@ -9656,7 +9656,7 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C103" t="n">
         <v>0</v>
@@ -9721,7 +9721,7 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="C108" t="n">
         <v>0</v>
@@ -9734,7 +9734,7 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="C109" t="n">
         <v>0</v>
@@ -9812,7 +9812,7 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>137</v>
+        <v>185</v>
       </c>
       <c r="C115" t="n">
         <v>0</v>
@@ -9825,7 +9825,7 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>99</v>
+        <v>122</v>
       </c>
       <c r="C116" t="n">
         <v>0</v>
@@ -9916,7 +9916,7 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="C123" t="n">
         <v>1</v>
@@ -9968,10 +9968,10 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="C127" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="128">
@@ -10101,7 +10101,7 @@
         <v>1</v>
       </c>
       <c r="C137" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="138">
@@ -11211,7 +11211,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Aqib Nabi Dar</t>
+          <t>Auqib Dar</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -12552,7 +12552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12610,49 +12610,6 @@
         <is>
           <t>Points</t>
         </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Rasik Dar Salam</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>DIPESH11</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>BOWL</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>rasikh salam</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>possible_mismatch:81.4814814814815</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/IPL_Fantasy_Points.xlsx
+++ b/IPL_Fantasy_Points.xlsx
@@ -561,19 +561,19 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4">
@@ -647,19 +647,19 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>15</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6">
@@ -690,19 +690,19 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>195</v>
+        <v>222</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>195</v>
+        <v>222</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>195</v>
+        <v>222</v>
       </c>
     </row>
     <row r="7">
@@ -2238,19 +2238,19 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="H42" t="n">
         <v>3</v>
       </c>
       <c r="I42" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
     </row>
     <row r="43">
@@ -2926,19 +2926,19 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>75</v>
+        <v>113</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>75</v>
+        <v>113</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>75</v>
+        <v>113</v>
       </c>
     </row>
     <row r="59">
@@ -3915,19 +3915,19 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>108</v>
+        <v>120</v>
       </c>
     </row>
     <row r="82">
@@ -3958,19 +3958,19 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>133</v>
+        <v>147</v>
       </c>
     </row>
     <row r="83">
@@ -4087,19 +4087,19 @@
         </is>
       </c>
       <c r="G85" t="n">
+        <v>6</v>
+      </c>
+      <c r="H85" t="n">
         <v>5</v>
       </c>
-      <c r="H85" t="n">
-        <v>3</v>
-      </c>
       <c r="I85" t="n">
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="K85" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
     </row>
     <row r="86">
@@ -4219,16 +4219,16 @@
         <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I88" t="n">
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="K88" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
     </row>
     <row r="89">
@@ -4821,16 +4821,16 @@
         <v>0</v>
       </c>
       <c r="H102" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I102" t="n">
         <v>0</v>
       </c>
       <c r="J102" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="K102" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="103">
@@ -5076,19 +5076,19 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="H108" t="n">
         <v>0</v>
       </c>
       <c r="I108" t="n">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
       </c>
       <c r="K108" t="n">
-        <v>132</v>
+        <v>139</v>
       </c>
     </row>
     <row r="109">
@@ -5119,19 +5119,19 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>75</v>
+        <v>115</v>
       </c>
       <c r="H109" t="n">
         <v>0</v>
       </c>
       <c r="I109" t="n">
-        <v>75</v>
+        <v>115</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
       </c>
       <c r="K109" t="n">
-        <v>75</v>
+        <v>115</v>
       </c>
     </row>
     <row r="110">
@@ -5850,19 +5850,19 @@
         </is>
       </c>
       <c r="G126" t="n">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="H126" t="n">
         <v>0</v>
       </c>
       <c r="I126" t="n">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
       </c>
       <c r="K126" t="n">
-        <v>125</v>
+        <v>135</v>
       </c>
     </row>
     <row r="127">
@@ -6624,19 +6624,19 @@
         </is>
       </c>
       <c r="G144" t="n">
-        <v>179</v>
+        <v>228</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
       </c>
       <c r="I144" t="n">
-        <v>179</v>
+        <v>228</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
       </c>
       <c r="K144" t="n">
-        <v>179</v>
+        <v>228</v>
       </c>
     </row>
     <row r="145">
@@ -6710,19 +6710,19 @@
         </is>
       </c>
       <c r="G146" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H146" t="n">
         <v>0</v>
       </c>
       <c r="I146" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
       </c>
       <c r="K146" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="147">
@@ -7014,16 +7014,16 @@
         <v>1</v>
       </c>
       <c r="H153" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I153" t="n">
         <v>1</v>
       </c>
       <c r="J153" t="n">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="K153" t="n">
-        <v>101</v>
+        <v>141</v>
       </c>
     </row>
     <row r="154">
@@ -7186,16 +7186,16 @@
         <v>9</v>
       </c>
       <c r="H157" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I157" t="n">
         <v>0</v>
       </c>
       <c r="J157" t="n">
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="K157" t="n">
-        <v>80</v>
+        <v>140</v>
       </c>
     </row>
     <row r="158">
@@ -8198,7 +8198,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1308</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="4">
@@ -8211,7 +8211,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1179</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="5">
@@ -8224,7 +8224,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1165</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="6">
@@ -8233,11 +8233,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>VATSAL11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1127</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="7">
@@ -8246,11 +8246,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>VATSAL11</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1057</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="8">
@@ -8259,11 +8259,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1041</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="9">
@@ -8276,7 +8276,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>957</v>
+        <v>977</v>
       </c>
     </row>
     <row r="10">
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>815</v>
+        <v>866</v>
       </c>
     </row>
     <row r="11">
@@ -8382,7 +8382,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -8551,10 +8551,10 @@
         </is>
       </c>
       <c r="B18" t="n">
+        <v>6</v>
+      </c>
+      <c r="C18" t="n">
         <v>5</v>
-      </c>
-      <c r="C18" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -8577,7 +8577,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>75</v>
+        <v>113</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
@@ -8619,7 +8619,7 @@
         <v>9</v>
       </c>
       <c r="C23" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
@@ -8733,7 +8733,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
@@ -8824,7 +8824,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C39" t="n">
         <v>0</v>
@@ -8980,7 +8980,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="C51" t="n">
         <v>0</v>
@@ -9022,7 +9022,7 @@
         <v>0</v>
       </c>
       <c r="C54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
@@ -9087,7 +9087,7 @@
         <v>1</v>
       </c>
       <c r="C59" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60">
@@ -9253,7 +9253,7 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>75</v>
+        <v>115</v>
       </c>
       <c r="C72" t="n">
         <v>0</v>
@@ -9331,7 +9331,7 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>88</v>
+        <v>127</v>
       </c>
       <c r="C78" t="n">
         <v>0</v>
@@ -9396,7 +9396,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
@@ -9461,7 +9461,7 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
@@ -9529,7 +9529,7 @@
         <v>0</v>
       </c>
       <c r="C93" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="94">
@@ -9578,7 +9578,7 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>195</v>
+        <v>222</v>
       </c>
       <c r="C97" t="n">
         <v>0</v>
@@ -9620,7 +9620,7 @@
         <v>0</v>
       </c>
       <c r="C100" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="101">
@@ -9669,7 +9669,7 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C104" t="n">
         <v>0</v>
@@ -9708,7 +9708,7 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="C107" t="n">
         <v>3</v>
@@ -10033,7 +10033,7 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="C132" t="n">
         <v>0</v>
@@ -10176,7 +10176,7 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>179</v>
+        <v>228</v>
       </c>
       <c r="C143" t="n">
         <v>0</v>

--- a/IPL_Fantasy_Points.xlsx
+++ b/IPL_Fantasy_Points.xlsx
@@ -819,19 +819,19 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>59</v>
+        <v>109</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>59</v>
+        <v>109</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>59</v>
+        <v>109</v>
       </c>
     </row>
     <row r="10">
@@ -1811,16 +1811,16 @@
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="K32" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
     </row>
     <row r="33">
@@ -1968,31 +1968,31 @@
           <t>BAT</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>washington sundar</t>
-        </is>
-      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>quinton de kock</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>112</v>
       </c>
     </row>
     <row r="37">
@@ -2327,16 +2327,16 @@
         <v>8</v>
       </c>
       <c r="H44" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I44" t="n">
         <v>8</v>
       </c>
       <c r="J44" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="K44" t="n">
-        <v>108</v>
+        <v>128</v>
       </c>
     </row>
     <row r="45">
@@ -2367,19 +2367,19 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="46">
@@ -3012,19 +3012,19 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="61">
@@ -3313,19 +3313,19 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="68">
@@ -3614,19 +3614,19 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>131</v>
+        <v>211</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>131</v>
+        <v>211</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>131</v>
+        <v>211</v>
       </c>
     </row>
     <row r="75">
@@ -3657,19 +3657,19 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>103</v>
+        <v>118</v>
       </c>
     </row>
     <row r="76">
@@ -4001,19 +4001,19 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>119</v>
+        <v>136</v>
       </c>
     </row>
     <row r="84">
@@ -4047,16 +4047,16 @@
         <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I84" t="n">
         <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="K84" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
     </row>
     <row r="85">
@@ -4388,19 +4388,19 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>137</v>
+        <v>203</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>137</v>
+        <v>203</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>137</v>
+        <v>203</v>
       </c>
     </row>
     <row r="93">
@@ -4594,7 +4594,7 @@
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>prince yadav</t>
+          <t>mayank rawat</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -5334,19 +5334,19 @@
         </is>
       </c>
       <c r="G114" t="n">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="H114" t="n">
         <v>2</v>
       </c>
       <c r="I114" t="n">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="J114" t="n">
         <v>40</v>
       </c>
       <c r="K114" t="n">
-        <v>107</v>
+        <v>121</v>
       </c>
     </row>
     <row r="115">
@@ -6065,19 +6065,19 @@
         </is>
       </c>
       <c r="G131" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="H131" t="n">
         <v>0</v>
       </c>
       <c r="I131" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
       </c>
       <c r="K131" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="132">
@@ -6111,7 +6111,7 @@
         <v>34</v>
       </c>
       <c r="H132" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I132" t="n">
         <v>34</v>
@@ -7733,7 +7733,7 @@
       <c r="D170" t="inlineStr"/>
       <c r="E170" t="inlineStr">
         <is>
-          <t>rahul tewatia</t>
+          <t>mayank rawat</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -7788,16 +7788,16 @@
         <v>9</v>
       </c>
       <c r="H171" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I171" t="n">
         <v>9</v>
       </c>
       <c r="J171" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="K171" t="n">
-        <v>49</v>
+        <v>69</v>
       </c>
     </row>
     <row r="172">
@@ -7948,7 +7948,7 @@
       <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr">
         <is>
-          <t>mayank markande</t>
+          <t>mayank rawat</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -8181,11 +8181,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MEET11</t>
+          <t>DIPESH11</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1465</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="3">
@@ -8194,11 +8194,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DIPESH11</t>
+          <t>MEET11</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1454</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="4">
@@ -8207,11 +8207,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>VATSAL11</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1226</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="5">
@@ -8220,11 +8220,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BABA11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1203</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="6">
@@ -8233,11 +8233,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>BABA11</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1191</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="7">
@@ -8246,11 +8246,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>VATSAL11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1141</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="8">
@@ -8263,7 +8263,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1067</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="9">
@@ -8276,7 +8276,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>977</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="10">
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>866</v>
+        <v>916</v>
       </c>
     </row>
     <row r="11">
@@ -8302,7 +8302,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>806</v>
+        <v>826</v>
       </c>
     </row>
   </sheetData>
@@ -8316,7 +8316,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C147"/>
+  <dimension ref="A1:C149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8424,7 +8424,7 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -8502,7 +8502,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -8668,7 +8668,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="C42" t="n">
         <v>2</v>
@@ -9191,7 +9191,7 @@
         <v>9</v>
       </c>
       <c r="C67" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68">
@@ -9201,7 +9201,7 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C68" t="n">
         <v>0</v>
@@ -9249,11 +9249,11 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>mitchell marsh</t>
+          <t>mayank rawat</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="C72" t="n">
         <v>0</v>
@@ -9262,89 +9262,89 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>mitchell santner</t>
+          <t>mitchell marsh</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>26</v>
+        <v>115</v>
       </c>
       <c r="C73" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>mohammed shami</t>
+          <t>mitchell santner</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="C74" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>mohammed siraj</t>
+          <t>mohammed shami</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="C75" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>mohsin khan</t>
+          <t>mohammed siraj</t>
         </is>
       </c>
       <c r="B76" t="n">
         <v>0</v>
       </c>
       <c r="C76" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>mukesh kumar</t>
+          <t>mohsin khan</t>
         </is>
       </c>
       <c r="B77" t="n">
         <v>0</v>
       </c>
       <c r="C77" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>mukul choudhary</t>
+          <t>mukesh kumar</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>127</v>
+        <v>0</v>
       </c>
       <c r="C78" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>naman dhir</t>
+          <t>mukul choudhary</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>59</v>
+        <v>127</v>
       </c>
       <c r="C79" t="n">
         <v>0</v>
@@ -9353,37 +9353,37 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>nandre burger</t>
+          <t>naman dhir</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="C80" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>navdeep saini</t>
+          <t>nandre burger</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C81" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>nehal wadhera</t>
+          <t>navdeep saini</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
@@ -9392,11 +9392,11 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>nicholas pooran</t>
+          <t>nehal wadhera</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
@@ -9405,63 +9405,63 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>nitish kumar reddy</t>
+          <t>nicholas pooran</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>124</v>
+        <v>42</v>
       </c>
       <c r="C84" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>nitish rana</t>
+          <t>nitish kumar reddy</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>20</v>
+        <v>124</v>
       </c>
       <c r="C85" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>noor ahmad</t>
+          <t>nitish rana</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C86" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>pathum nissanka</t>
+          <t>noor ahmad</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>127</v>
+        <v>9</v>
       </c>
       <c r="C87" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>philip salt</t>
+          <t>pathum nissanka</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
@@ -9470,11 +9470,11 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>prabhsimran singh</t>
+          <t>philip salt</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
@@ -9483,76 +9483,76 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>praful hinge</t>
+          <t>prabhsimran singh</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0</v>
+        <v>211</v>
       </c>
       <c r="C90" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>prashant veer</t>
+          <t>praful hinge</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="C91" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>prasidh krishna</t>
+          <t>prashant veer</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="C92" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>prince yadav</t>
+          <t>prasidh krishna</t>
         </is>
       </c>
       <c r="B93" t="n">
         <v>0</v>
       </c>
       <c r="C93" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>priyansh arya</t>
+          <t>prince yadav</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="C94" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>rahul chahar</t>
+          <t>priyansh arya</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
@@ -9561,11 +9561,11 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>rahul tewatia</t>
+          <t>quinton de kock</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>34</v>
+        <v>112</v>
       </c>
       <c r="C96" t="n">
         <v>0</v>
@@ -9574,11 +9574,11 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>rajat patidar</t>
+          <t>rahul chahar</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>222</v>
+        <v>0</v>
       </c>
       <c r="C97" t="n">
         <v>0</v>
@@ -9587,11 +9587,11 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ramandeep singh</t>
+          <t>rahul tewatia</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="C98" t="n">
         <v>0</v>
@@ -9600,102 +9600,102 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>rashid khan</t>
+          <t>rajat patidar</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>24</v>
+        <v>222</v>
       </c>
       <c r="C99" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>rasikh salam</t>
+          <t>ramandeep singh</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="C100" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ravi bishnoi</t>
+          <t>rashid khan</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="C101" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ravindra jadeja</t>
+          <t>rasikh salam</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="C102" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>rinku singh</t>
+          <t>ravi bishnoi</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="C103" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>rishabh pant</t>
+          <t>ravindra jadeja</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>104</v>
+        <v>76</v>
       </c>
       <c r="C104" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>riyan parag</t>
+          <t>rinku singh</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="C105" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>rohit sharma</t>
+          <t>rishabh pant</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>137</v>
+        <v>104</v>
       </c>
       <c r="C106" t="n">
         <v>0</v>
@@ -9704,24 +9704,24 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>romario shepherd</t>
+          <t>riyan parag</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="C107" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>rovman powell</t>
+          <t>rohit sharma</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>70</v>
+        <v>137</v>
       </c>
       <c r="C108" t="n">
         <v>0</v>
@@ -9730,24 +9730,24 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>ruturaj gaikwad</t>
+          <t>romario shepherd</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="C109" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ryan rickelton</t>
+          <t>rovman powell</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
       <c r="C110" t="n">
         <v>0</v>
@@ -9756,24 +9756,24 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>sakib hussain</t>
+          <t>ruturaj gaikwad</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="C111" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>salil arora</t>
+          <t>ryan rickelton</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>42</v>
+        <v>137</v>
       </c>
       <c r="C112" t="n">
         <v>0</v>
@@ -9782,37 +9782,37 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>sameer rizvi</t>
+          <t>sakib hussain</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>166</v>
+        <v>0</v>
       </c>
       <c r="C113" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>sandeep sharma</t>
+          <t>salil arora</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="C114" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>sanju samson</t>
+          <t>sameer rizvi</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>185</v>
+        <v>166</v>
       </c>
       <c r="C115" t="n">
         <v>0</v>
@@ -9821,24 +9821,24 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>sarfaraz khan</t>
+          <t>sandeep sharma</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>122</v>
+        <v>0</v>
       </c>
       <c r="C116" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>shahbaz ahmed</t>
+          <t>sanju samson</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>15</v>
+        <v>185</v>
       </c>
       <c r="C117" t="n">
         <v>0</v>
@@ -9847,11 +9847,11 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>shahrukh khan</t>
+          <t>sarfaraz khan</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>15</v>
+        <v>122</v>
       </c>
       <c r="C118" t="n">
         <v>0</v>
@@ -9860,128 +9860,128 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>shardul thakur</t>
+          <t>shahbaz ahmed</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C119" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>shashank singh</t>
+          <t>shahrukh khan</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="C120" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>sherfane rutherford</t>
+          <t>shardul thakur</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>101</v>
+        <v>8</v>
       </c>
       <c r="C121" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>shimron hetmyer</t>
+          <t>shashank singh</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="C122" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>shivam dube</t>
+          <t>sherfane rutherford</t>
         </is>
       </c>
       <c r="B123" t="n">
         <v>102</v>
       </c>
       <c r="C123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>shivang kumar</t>
+          <t>shimron hetmyer</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="C124" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>shreyas iyer</t>
+          <t>shivam dube</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>137</v>
+        <v>102</v>
       </c>
       <c r="C125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>shubman gill</t>
+          <t>shivang kumar</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>165</v>
+        <v>9</v>
       </c>
       <c r="C126" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>sunil narine</t>
+          <t>shreyas iyer</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>36</v>
+        <v>203</v>
       </c>
       <c r="C127" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>suryakumar yadav</t>
+          <t>shubman gill</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>106</v>
+        <v>165</v>
       </c>
       <c r="C128" t="n">
         <v>0</v>
@@ -9990,63 +9990,63 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>suyash sharma</t>
+          <t>sunil narine</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="C129" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>t natarajan</t>
+          <t>suryakumar yadav</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>1</v>
+        <v>106</v>
       </c>
       <c r="C130" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>tilak varma</t>
+          <t>suyash sharma</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="C131" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>tim david</t>
+          <t>t natarajan</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>147</v>
+        <v>1</v>
       </c>
       <c r="C132" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>travis head</t>
+          <t>tilak varma</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>120</v>
+        <v>43</v>
       </c>
       <c r="C133" t="n">
         <v>0</v>
@@ -10055,24 +10055,24 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>trent boult</t>
+          <t>tim david</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>1</v>
+        <v>147</v>
       </c>
       <c r="C134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>tristan stubbs</t>
+          <t>travis head</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="C135" t="n">
         <v>0</v>
@@ -10081,63 +10081,63 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>tushar deshpande</t>
+          <t>trent boult</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C136" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>vaibhav arora</t>
+          <t>tristan stubbs</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>1</v>
+        <v>109</v>
       </c>
       <c r="C137" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>vaibhav suryavanshi</t>
+          <t>tushar deshpande</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>200</v>
+        <v>25</v>
       </c>
       <c r="C138" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>varun chakravarthy</t>
+          <t>vaibhav arora</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C139" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>venkatesh iyer</t>
+          <t>vaibhav suryavanshi</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>29</v>
+        <v>200</v>
       </c>
       <c r="C140" t="n">
         <v>0</v>
@@ -10146,50 +10146,50 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>vijaykumar vyshak</t>
+          <t>varun chakravarthy</t>
         </is>
       </c>
       <c r="B141" t="n">
         <v>0</v>
       </c>
       <c r="C141" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>vipraj nigam</t>
+          <t>venkatesh iyer</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="C142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>virat kohli</t>
+          <t>vijaykumar vyshak</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>228</v>
+        <v>0</v>
       </c>
       <c r="C143" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>washington sundar</t>
+          <t>vipraj nigam</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>98</v>
+        <v>12</v>
       </c>
       <c r="C144" t="n">
         <v>1</v>
@@ -10198,39 +10198,65 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>xavier bartlett</t>
+          <t>virat kohli</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>11</v>
+        <v>228</v>
       </c>
       <c r="C145" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>yashasvi jaiswal</t>
+          <t>washington sundar</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>184</v>
+        <v>98</v>
       </c>
       <c r="C146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
+          <t>xavier bartlett</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>11</v>
+      </c>
+      <c r="C147" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>yashasvi jaiswal</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>184</v>
+      </c>
+      <c r="C148" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
           <t>yuzvendra chahal</t>
         </is>
       </c>
-      <c r="B147" t="n">
-        <v>0</v>
-      </c>
-      <c r="C147" t="n">
+      <c r="B149" t="n">
+        <v>0</v>
+      </c>
+      <c r="C149" t="n">
         <v>3</v>
       </c>
     </row>
@@ -10245,7 +10271,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K53"/>
+  <dimension ref="A1:K52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10652,7 +10678,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Quinton de Kock</t>
+          <t>Tom Banton</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -10668,7 +10694,7 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>washington sundar</t>
+          <t>t natarajan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -10695,7 +10721,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Tom Banton</t>
+          <t>Tim Siefert</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -10711,7 +10737,7 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>t natarajan</t>
+          <t>jamie overton</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -10738,7 +10764,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Tim Siefert</t>
+          <t>Lockie Ferguson</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -10748,13 +10774,13 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>jamie overton</t>
+          <t>lokesh rahul</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -10781,7 +10807,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Lockie Ferguson</t>
+          <t>Adam Milne</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -10797,7 +10823,7 @@
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>lokesh rahul</t>
+          <t>david miller</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -10824,23 +10850,23 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Adam Milne</t>
+          <t>Jos Inglis</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>VATSAL11</t>
+          <t>BABA11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>david miller</t>
+          <t>marcus stoinis</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -10867,7 +10893,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Jos Inglis</t>
+          <t>Prithvi Shaw</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -10883,7 +10909,7 @@
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>marcus stoinis</t>
+          <t>prasidh krishna</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -10910,7 +10936,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Prithvi Shaw</t>
+          <t>liam livingston</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -10920,13 +10946,13 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>prasidh krishna</t>
+          <t>liam livingstone</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -10953,7 +10979,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>liam livingston</t>
+          <t>rachin ravindra</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -10969,7 +10995,7 @@
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>liam livingstone</t>
+          <t>rashid khan</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -10996,7 +11022,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>rachin ravindra</t>
+          <t>Zeeshan Ansari</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -11006,13 +11032,13 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>rashid khan</t>
+          <t>eshan malinga</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -11039,7 +11065,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Zeeshan Ansari</t>
+          <t>Mitchell Starc</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -11055,7 +11081,7 @@
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>eshan malinga</t>
+          <t>mitchell santner</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -11082,17 +11108,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Mitchell Starc</t>
+          <t>Mitchel Owen</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BABA11</t>
+          <t>DIPESH11</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -11125,7 +11151,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Mitchel Owen</t>
+          <t>Pat Cummins</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -11135,13 +11161,13 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>mitchell santner</t>
+          <t>pathum nissanka</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -11168,7 +11194,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Pat Cummins</t>
+          <t>Auqib Dar</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -11178,13 +11204,13 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>pathum nissanka</t>
+          <t>auqib nabi</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -11211,23 +11237,23 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Auqib Dar</t>
+          <t>Urvil Patel</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>DIPESH11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>auqib nabi</t>
+          <t>axar patel</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -11254,7 +11280,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Urvil Patel</t>
+          <t>Arshin Kulkarni</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -11270,7 +11296,7 @@
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>axar patel</t>
+          <t>shivang kumar</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -11297,7 +11323,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Arshin Kulkarni</t>
+          <t>Nishant Sindhu</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11307,13 +11333,13 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>shivang kumar</t>
+          <t>shashank singh</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -11340,7 +11366,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Nishant Sindhu</t>
+          <t>Jayant Yadav</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11356,7 +11382,7 @@
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>shashank singh</t>
+          <t>mayank rawat</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -11383,7 +11409,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Jayant Yadav</t>
+          <t>Ajay Mandal</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11399,7 +11425,7 @@
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>prince yadav</t>
+          <t>rajat patidar</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -11426,7 +11452,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Ajay Mandal</t>
+          <t>Will Jacks</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -11442,7 +11468,7 @@
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>rajat patidar</t>
+          <t>mitchell marsh</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -11469,7 +11495,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Will Jacks</t>
+          <t>Kyle Jamieson</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -11479,13 +11505,13 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>mitchell marsh</t>
+          <t>jamie overton</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -11512,7 +11538,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Kyle Jamieson</t>
+          <t>Matheesha Pathirana</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -11528,7 +11554,7 @@
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>jamie overton</t>
+          <t>eshan malinga</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -11555,7 +11581,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Matheesha Pathirana</t>
+          <t>Ben Dwarshuis</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -11571,7 +11597,7 @@
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>eshan malinga</t>
+          <t>b sai sudharshan</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -11598,23 +11624,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Ben Dwarshuis</t>
+          <t>Manish Pandey</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>b sai sudharshan</t>
+          <t>hardik pandya</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -11641,7 +11667,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Manish Pandey</t>
+          <t>Mukesh Choudhary</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -11651,13 +11677,13 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>hardik pandya</t>
+          <t>mukul choudhary</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -11684,7 +11710,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Mukesh Choudhary</t>
+          <t>Arjun Tendulkar</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -11700,7 +11726,7 @@
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>mukul choudhary</t>
+          <t>krunal pandya</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -11727,7 +11753,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Arjun Tendulkar</t>
+          <t>Kwena Maphaka</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -11743,7 +11769,7 @@
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>krunal pandya</t>
+          <t>aiden markram</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -11770,23 +11796,23 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Kwena Maphaka</t>
+          <t>Ramkrishna Ghosh</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>aiden markram</t>
+          <t>angkrish raghuvanshi</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -11813,7 +11839,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Ramkrishna Ghosh</t>
+          <t>Azmatullah Omarzai</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -11823,13 +11849,13 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>angkrish raghuvanshi</t>
+          <t>mitchell marsh</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -11856,23 +11882,23 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Azmatullah Omarzai</t>
+          <t>akshat raghuwanshi</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>mitchell marsh</t>
+          <t>angkrish raghuvanshi</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -11899,7 +11925,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>akshat raghuwanshi</t>
+          <t>Himmat Singh</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -11915,7 +11941,7 @@
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>angkrish raghuvanshi</t>
+          <t>prabhsimran singh</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -11942,7 +11968,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Himmat Singh</t>
+          <t>Suryansh Shegde</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -11958,7 +11984,7 @@
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>prabhsimran singh</t>
+          <t>suyash sharma</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -11985,7 +12011,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Suryansh Shegde</t>
+          <t>Tejasvi Singh</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -12001,7 +12027,7 @@
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>suyash sharma</t>
+          <t>prabhsimran singh</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -12028,7 +12054,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Tejasvi Singh</t>
+          <t>Sai Kishor</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -12038,13 +12064,13 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>prabhsimran singh</t>
+          <t>ishan kishan</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -12071,7 +12097,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sai Kishor</t>
+          <t>Akash Deep</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -12087,7 +12113,7 @@
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>ishan kishan</t>
+          <t>arshdeep singh</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -12114,23 +12140,23 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Akash Deep</t>
+          <t>Ben Duckett</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>arshdeep singh</t>
+          <t>ryan rickelton</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -12157,7 +12183,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Ben Duckett</t>
+          <t>Abhishek Porel</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -12173,7 +12199,7 @@
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>ryan rickelton</t>
+          <t>abhishek sharma</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -12200,7 +12226,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Abhishek Porel</t>
+          <t>Rahul Tripathi</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -12216,7 +12242,7 @@
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>abhishek sharma</t>
+          <t>rahul tewatia</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -12243,7 +12269,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Rahul Tripathi</t>
+          <t>Dre Pretorius</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -12259,7 +12285,7 @@
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>rahul tewatia</t>
+          <t>lhuan dre pretorius</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -12286,7 +12312,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Dre Pretorius</t>
+          <t>Matthew Breetzke</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -12302,7 +12328,7 @@
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>lhuan dre pretorius</t>
+          <t>matt henry</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -12329,7 +12355,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Matthew Breetzke</t>
+          <t>Anuj Rawat</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -12345,7 +12371,7 @@
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>matt henry</t>
+          <t>mayank rawat</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -12372,7 +12398,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Anuj Rawat</t>
+          <t>Wanindu Hasaranga</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -12382,13 +12408,13 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>rahul tewatia</t>
+          <t>sandeep sharma</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -12415,7 +12441,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Wanindu Hasaranga</t>
+          <t>Harpreet Brar</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -12425,13 +12451,13 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>sandeep sharma</t>
+          <t>jasprit bumrah</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -12458,7 +12484,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Harpreet Brar</t>
+          <t>Mayank Yadav</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -12474,7 +12500,7 @@
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>jasprit bumrah</t>
+          <t>mayank rawat</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -12495,49 +12521,6 @@
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Mayank Yadav</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>BOWL</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>mayank markande</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="G53" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" t="n">
         <v>0</v>
       </c>
     </row>

--- a/IPL_Fantasy_Points.xlsx
+++ b/IPL_Fantasy_Points.xlsx
@@ -862,19 +862,19 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>56</v>
+        <v>135</v>
       </c>
       <c r="H10" t="n">
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>56</v>
+        <v>135</v>
       </c>
       <c r="J10" t="n">
         <v>20</v>
       </c>
       <c r="K10" t="n">
-        <v>76</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11">
@@ -948,19 +948,19 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H12" t="n">
         <v>4</v>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J12" t="n">
         <v>80</v>
       </c>
       <c r="K12" t="n">
-        <v>81</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13">
@@ -994,16 +994,16 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="K13" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -1249,19 +1249,19 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>165</v>
+        <v>251</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>165</v>
+        <v>251</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>165</v>
+        <v>251</v>
       </c>
     </row>
     <row r="20">
@@ -1378,19 +1378,19 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>49</v>
+        <v>66</v>
       </c>
     </row>
     <row r="23">
@@ -1550,19 +1550,19 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="27">
@@ -2143,7 +2143,7 @@
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>jamie overton</t>
+          <t>tim seifert</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2195,19 +2195,19 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>42</v>
+        <v>61</v>
       </c>
     </row>
     <row r="42">
@@ -2413,16 +2413,16 @@
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="K46" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
     </row>
     <row r="47">
@@ -3055,19 +3055,19 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="62">
@@ -3141,19 +3141,19 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>70</v>
+        <v>97</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>70</v>
+        <v>97</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>70</v>
+        <v>97</v>
       </c>
     </row>
     <row r="64">
@@ -3187,16 +3187,16 @@
         <v>24</v>
       </c>
       <c r="H64" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I64" t="n">
         <v>24</v>
       </c>
       <c r="J64" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="K64" t="n">
-        <v>124</v>
+        <v>144</v>
       </c>
     </row>
     <row r="65">
@@ -3359,16 +3359,16 @@
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I68" t="n">
         <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="K68" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="69">
@@ -3571,19 +3571,19 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>113</v>
+        <v>135</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>113</v>
+        <v>135</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>113</v>
+        <v>135</v>
       </c>
     </row>
     <row r="74">
@@ -4431,19 +4431,19 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>176</v>
+        <v>201</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>176</v>
+        <v>201</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>176</v>
+        <v>201</v>
       </c>
     </row>
     <row r="94">
@@ -4778,16 +4778,16 @@
         <v>23</v>
       </c>
       <c r="H101" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I101" t="n">
         <v>0</v>
       </c>
       <c r="J101" t="n">
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="K101" t="n">
-        <v>80</v>
+        <v>140</v>
       </c>
     </row>
     <row r="102">
@@ -5506,7 +5506,7 @@
         </is>
       </c>
       <c r="G118" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H118" t="n">
         <v>5</v>
@@ -5979,19 +5979,19 @@
         </is>
       </c>
       <c r="G129" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
       </c>
       <c r="I129" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
       </c>
       <c r="K129" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="130">
@@ -6194,19 +6194,19 @@
         </is>
       </c>
       <c r="G134" t="n">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
       </c>
       <c r="I134" t="n">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
       </c>
       <c r="K134" t="n">
-        <v>182</v>
+        <v>190</v>
       </c>
     </row>
     <row r="135">
@@ -6280,19 +6280,19 @@
         </is>
       </c>
       <c r="G136" t="n">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="H136" t="n">
         <v>1</v>
       </c>
       <c r="I136" t="n">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="J136" t="n">
         <v>20</v>
       </c>
       <c r="K136" t="n">
-        <v>118</v>
+        <v>131</v>
       </c>
     </row>
     <row r="137">
@@ -7229,16 +7229,16 @@
         <v>1</v>
       </c>
       <c r="H158" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I158" t="n">
         <v>0</v>
       </c>
       <c r="J158" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="K158" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
     </row>
     <row r="159">
@@ -7831,16 +7831,16 @@
         <v>36</v>
       </c>
       <c r="H172" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I172" t="n">
         <v>36</v>
       </c>
       <c r="J172" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="K172" t="n">
-        <v>96</v>
+        <v>116</v>
       </c>
     </row>
     <row r="173">
@@ -8185,7 +8185,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1626</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="3">
@@ -8198,7 +8198,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1505</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="4">
@@ -8211,7 +8211,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1283</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="5">
@@ -8220,11 +8220,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>BABA11</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1240</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="6">
@@ -8233,11 +8233,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BABA11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1206</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="7">
@@ -8250,7 +8250,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1191</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="8">
@@ -8259,11 +8259,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1075</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="9">
@@ -8272,11 +8272,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1043</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="10">
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>916</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="11">
@@ -8302,7 +8302,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>826</v>
+        <v>846</v>
       </c>
     </row>
   </sheetData>
@@ -8316,7 +8316,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C149"/>
+  <dimension ref="A1:C150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8434,7 +8434,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -8486,7 +8486,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
         <v>4</v>
@@ -8515,7 +8515,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -8603,7 +8603,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>113</v>
+        <v>135</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
@@ -8655,7 +8655,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>56</v>
+        <v>135</v>
       </c>
       <c r="C26" t="n">
         <v>1</v>
@@ -8837,7 +8837,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="C40" t="n">
         <v>0</v>
@@ -9006,7 +9006,7 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>176</v>
+        <v>201</v>
       </c>
       <c r="C53" t="n">
         <v>0</v>
@@ -9035,7 +9035,7 @@
         <v>23</v>
       </c>
       <c r="C55" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="56">
@@ -9058,7 +9058,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C57" t="n">
         <v>5</v>
@@ -9308,7 +9308,7 @@
         <v>0</v>
       </c>
       <c r="C76" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="77">
@@ -9529,7 +9529,7 @@
         <v>0</v>
       </c>
       <c r="C93" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="94">
@@ -9591,7 +9591,7 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C98" t="n">
         <v>0</v>
@@ -9617,10 +9617,10 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="C100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101">
@@ -9633,7 +9633,7 @@
         <v>24</v>
       </c>
       <c r="C101" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="102">
@@ -9682,7 +9682,7 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C105" t="n">
         <v>0</v>
@@ -9747,7 +9747,7 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>70</v>
+        <v>97</v>
       </c>
       <c r="C110" t="n">
         <v>0</v>
@@ -9877,7 +9877,7 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C120" t="n">
         <v>0</v>
@@ -9981,7 +9981,7 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>165</v>
+        <v>251</v>
       </c>
       <c r="C128" t="n">
         <v>0</v>
@@ -9997,7 +9997,7 @@
         <v>36</v>
       </c>
       <c r="C129" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="130">
@@ -10068,11 +10068,11 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>travis head</t>
+          <t>tim seifert</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>120</v>
+        <v>19</v>
       </c>
       <c r="C135" t="n">
         <v>0</v>
@@ -10081,76 +10081,76 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>trent boult</t>
+          <t>travis head</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="C136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>tristan stubbs</t>
+          <t>trent boult</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>109</v>
+        <v>1</v>
       </c>
       <c r="C137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>tushar deshpande</t>
+          <t>tristan stubbs</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>25</v>
+        <v>109</v>
       </c>
       <c r="C138" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>vaibhav arora</t>
+          <t>tushar deshpande</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C139" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>vaibhav suryavanshi</t>
+          <t>vaibhav arora</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>200</v>
+        <v>1</v>
       </c>
       <c r="C140" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>varun chakravarthy</t>
+          <t>vaibhav suryavanshi</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="C141" t="n">
         <v>0</v>
@@ -10159,104 +10159,117 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>venkatesh iyer</t>
+          <t>varun chakravarthy</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="C142" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>vijaykumar vyshak</t>
+          <t>venkatesh iyer</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="C143" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>vipraj nigam</t>
+          <t>vijaykumar vyshak</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C144" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>virat kohli</t>
+          <t>vipraj nigam</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>228</v>
+        <v>12</v>
       </c>
       <c r="C145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>washington sundar</t>
+          <t>virat kohli</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>98</v>
+        <v>228</v>
       </c>
       <c r="C146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>xavier bartlett</t>
+          <t>washington sundar</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>11</v>
+        <v>111</v>
       </c>
       <c r="C147" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>yashasvi jaiswal</t>
+          <t>xavier bartlett</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>184</v>
+        <v>11</v>
       </c>
       <c r="C148" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
+          <t>yashasvi jaiswal</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>184</v>
+      </c>
+      <c r="C149" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
           <t>yuzvendra chahal</t>
         </is>
       </c>
-      <c r="B149" t="n">
-        <v>0</v>
-      </c>
-      <c r="C149" t="n">
+      <c r="B150" t="n">
+        <v>0</v>
+      </c>
+      <c r="C150" t="n">
         <v>3</v>
       </c>
     </row>
@@ -10737,7 +10750,7 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>jamie overton</t>
+          <t>tim seifert</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">

--- a/IPL_Fantasy_Points.xlsx
+++ b/IPL_Fantasy_Points.xlsx
@@ -604,19 +604,19 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>120</v>
+        <v>143</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>120</v>
+        <v>143</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>120</v>
+        <v>143</v>
       </c>
     </row>
     <row r="5">
@@ -647,19 +647,19 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6">
@@ -690,19 +690,19 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>222</v>
+        <v>230</v>
       </c>
     </row>
     <row r="7">
@@ -1409,31 +1409,31 @@
           <t>BAT</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>krunal pandya</t>
-        </is>
-      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>karun nair</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
@@ -1627,7 +1627,7 @@
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>naman dhir</t>
+          <t>karun nair</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1851,19 +1851,19 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="H33" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>200</v>
+        <v>260</v>
       </c>
       <c r="K33" t="n">
-        <v>200</v>
+        <v>260</v>
       </c>
     </row>
     <row r="34">
@@ -2023,19 +2023,19 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>224</v>
+        <v>283</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>224</v>
+        <v>283</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>224</v>
+        <v>283</v>
       </c>
     </row>
     <row r="38">
@@ -2109,19 +2109,19 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="H39" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I39" t="n">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>124</v>
+        <v>136</v>
       </c>
     </row>
     <row r="40">
@@ -2238,19 +2238,19 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H42" t="n">
         <v>3</v>
       </c>
       <c r="I42" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="43">
@@ -2754,19 +2754,19 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>185</v>
+        <v>192</v>
       </c>
     </row>
     <row r="55">
@@ -2840,19 +2840,19 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>79</v>
+        <v>101</v>
       </c>
     </row>
     <row r="57">
@@ -3098,19 +3098,19 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>102</v>
+        <v>123</v>
       </c>
       <c r="H62" t="n">
         <v>1</v>
       </c>
       <c r="I62" t="n">
-        <v>102</v>
+        <v>123</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>102</v>
+        <v>123</v>
       </c>
     </row>
     <row r="63">
@@ -3528,19 +3528,19 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>63</v>
+        <v>82</v>
       </c>
     </row>
     <row r="73">
@@ -3786,19 +3786,19 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>109</v>
+        <v>169</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>109</v>
+        <v>169</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>109</v>
+        <v>169</v>
       </c>
     </row>
     <row r="79">
@@ -3829,19 +3829,19 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>122</v>
+        <v>147</v>
       </c>
       <c r="H79" t="n">
         <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>122</v>
+        <v>147</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>122</v>
+        <v>147</v>
       </c>
     </row>
     <row r="80">
@@ -3958,19 +3958,19 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>147</v>
+        <v>173</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>147</v>
+        <v>173</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>147</v>
+        <v>173</v>
       </c>
     </row>
     <row r="83">
@@ -4133,16 +4133,16 @@
         <v>0</v>
       </c>
       <c r="H86" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I86" t="n">
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="K86" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="87">
@@ -4345,19 +4345,19 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>111</v>
+        <v>168</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
       </c>
       <c r="I91" t="n">
-        <v>111</v>
+        <v>168</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>111</v>
+        <v>168</v>
       </c>
     </row>
     <row r="92">
@@ -5076,19 +5076,19 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>139</v>
+        <v>202</v>
       </c>
       <c r="H108" t="n">
         <v>0</v>
       </c>
       <c r="I108" t="n">
-        <v>139</v>
+        <v>202</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
       </c>
       <c r="K108" t="n">
-        <v>139</v>
+        <v>202</v>
       </c>
     </row>
     <row r="109">
@@ -5291,19 +5291,19 @@
         </is>
       </c>
       <c r="G113" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H113" t="n">
         <v>0</v>
       </c>
       <c r="I113" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
       </c>
       <c r="K113" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="114">
@@ -5377,19 +5377,19 @@
         </is>
       </c>
       <c r="G115" t="n">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="H115" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I115" t="n">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="J115" t="n">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="K115" t="n">
-        <v>187</v>
+        <v>263</v>
       </c>
     </row>
     <row r="116">
@@ -5552,16 +5552,16 @@
         <v>3</v>
       </c>
       <c r="H119" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I119" t="n">
         <v>0</v>
       </c>
       <c r="J119" t="n">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="K119" t="n">
-        <v>100</v>
+        <v>140</v>
       </c>
     </row>
     <row r="120">
@@ -5623,31 +5623,31 @@
           <t>BOWL</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr"/>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>mukul choudhary</t>
-        </is>
-      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>mukesh choudhary</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="G121" t="n">
         <v>0</v>
       </c>
       <c r="H121" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I121" t="n">
         <v>0</v>
       </c>
       <c r="J121" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="K121" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="122">
@@ -5681,16 +5681,16 @@
         <v>0</v>
       </c>
       <c r="H122" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I122" t="n">
         <v>0</v>
       </c>
       <c r="J122" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="K122" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="123">
@@ -5712,7 +5712,7 @@
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr">
         <is>
-          <t>krunal pandya</t>
+          <t>karun nair</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -5850,19 +5850,19 @@
         </is>
       </c>
       <c r="G126" t="n">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="H126" t="n">
         <v>0</v>
       </c>
       <c r="I126" t="n">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
       </c>
       <c r="K126" t="n">
-        <v>135</v>
+        <v>153</v>
       </c>
     </row>
     <row r="127">
@@ -6151,19 +6151,19 @@
         </is>
       </c>
       <c r="G133" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="H133" t="n">
         <v>0</v>
       </c>
       <c r="I133" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
       </c>
       <c r="K133" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="134">
@@ -6323,19 +6323,19 @@
         </is>
       </c>
       <c r="G137" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="H137" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I137" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="J137" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="K137" t="n">
-        <v>63</v>
+        <v>129</v>
       </c>
     </row>
     <row r="138">
@@ -6409,19 +6409,19 @@
         </is>
       </c>
       <c r="G139" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="H139" t="n">
         <v>0</v>
       </c>
       <c r="I139" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
       </c>
       <c r="K139" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
     </row>
     <row r="140">
@@ -6624,19 +6624,19 @@
         </is>
       </c>
       <c r="G144" t="n">
-        <v>228</v>
+        <v>247</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
       </c>
       <c r="I144" t="n">
-        <v>228</v>
+        <v>247</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
       </c>
       <c r="K144" t="n">
-        <v>228</v>
+        <v>247</v>
       </c>
     </row>
     <row r="145">
@@ -6796,19 +6796,19 @@
         </is>
       </c>
       <c r="G148" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H148" t="n">
         <v>0</v>
       </c>
       <c r="I148" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
       </c>
       <c r="K148" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="149">
@@ -7011,19 +7011,19 @@
         </is>
       </c>
       <c r="G153" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="H153" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I153" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="J153" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="K153" t="n">
-        <v>141</v>
+        <v>173</v>
       </c>
     </row>
     <row r="154">
@@ -7183,19 +7183,19 @@
         </is>
       </c>
       <c r="G157" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H157" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I157" t="n">
         <v>0</v>
       </c>
       <c r="J157" t="n">
-        <v>140</v>
+        <v>200</v>
       </c>
       <c r="K157" t="n">
-        <v>140</v>
+        <v>200</v>
       </c>
     </row>
     <row r="158">
@@ -7398,19 +7398,19 @@
         </is>
       </c>
       <c r="G162" t="n">
-        <v>129</v>
+        <v>188</v>
       </c>
       <c r="H162" t="n">
         <v>0</v>
       </c>
       <c r="I162" t="n">
-        <v>129</v>
+        <v>188</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
       </c>
       <c r="K162" t="n">
-        <v>129</v>
+        <v>188</v>
       </c>
     </row>
     <row r="163">
@@ -7527,19 +7527,19 @@
         </is>
       </c>
       <c r="G165" t="n">
-        <v>171</v>
+        <v>201</v>
       </c>
       <c r="H165" t="n">
         <v>0</v>
       </c>
       <c r="I165" t="n">
-        <v>171</v>
+        <v>201</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
       </c>
       <c r="K165" t="n">
-        <v>171</v>
+        <v>201</v>
       </c>
     </row>
     <row r="166">
@@ -8089,16 +8089,16 @@
         <v>5</v>
       </c>
       <c r="H178" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I178" t="n">
         <v>0</v>
       </c>
       <c r="J178" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="K178" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
     </row>
     <row r="179">
@@ -8129,7 +8129,7 @@
         </is>
       </c>
       <c r="G179" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H179" t="n">
         <v>4</v>
@@ -8185,7 +8185,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1648</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="3">
@@ -8198,7 +8198,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1615</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="4">
@@ -8207,11 +8207,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>VATSAL11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1322</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="5">
@@ -8220,11 +8220,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BABA11</t>
+          <t>VATSAL11</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1294</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="6">
@@ -8233,11 +8233,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>BABA11</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1240</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="7">
@@ -8250,7 +8250,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1211</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="8">
@@ -8259,11 +8259,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1128</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="9">
@@ -8272,11 +8272,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1099</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="10">
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1044</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="11">
@@ -8302,7 +8302,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>846</v>
+        <v>975</v>
       </c>
     </row>
   </sheetData>
@@ -8316,7 +8316,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C150"/>
+  <dimension ref="A1:C152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8369,7 +8369,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>129</v>
+        <v>188</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -8473,10 +8473,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="C12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13">
@@ -8564,10 +8564,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -8590,7 +8590,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>171</v>
+        <v>201</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
@@ -8616,10 +8616,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C23" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24">
@@ -8694,7 +8694,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
@@ -8733,7 +8733,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
@@ -8801,7 +8801,7 @@
         <v>0</v>
       </c>
       <c r="C37" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38">
@@ -8853,7 +8853,7 @@
         <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -8902,7 +8902,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>224</v>
+        <v>283</v>
       </c>
       <c r="C45" t="n">
         <v>0</v>
@@ -8941,10 +8941,10 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="C48" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="49">
@@ -8980,7 +8980,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="C51" t="n">
         <v>0</v>
@@ -9067,63 +9067,63 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>khaleel ahmed</t>
+          <t>karun nair</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>krunal pandya</t>
+          <t>khaleel ahmed</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C59" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>kuldeep yadav</t>
+          <t>krunal pandya</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C60" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>kumar kushagra</t>
+          <t>kuldeep yadav</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="C61" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>lhuan dre pretorius</t>
+          <t>kumar kushagra</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C62" t="n">
         <v>0</v>
@@ -9132,11 +9132,11 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>liam livingstone</t>
+          <t>lhuan dre pretorius</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C63" t="n">
         <v>0</v>
@@ -9145,11 +9145,11 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>lokesh rahul</t>
+          <t>liam livingstone</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>111</v>
+        <v>15</v>
       </c>
       <c r="C64" t="n">
         <v>0</v>
@@ -9158,89 +9158,89 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>lungi ngidi</t>
+          <t>lokesh rahul</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>3</v>
+        <v>168</v>
       </c>
       <c r="C65" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>manimaran siddharth</t>
+          <t>lungi ngidi</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C66" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>marco jansen</t>
+          <t>manimaran siddharth</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C67" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>marcus stoinis</t>
+          <t>marco jansen</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C68" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>matt henry</t>
+          <t>marcus stoinis</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="C69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>matt short</t>
+          <t>matt henry</t>
         </is>
       </c>
       <c r="B70" t="n">
+        <v>7</v>
+      </c>
+      <c r="C70" t="n">
         <v>2</v>
-      </c>
-      <c r="C70" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>mayank markande</t>
+          <t>matt short</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="C71" t="n">
         <v>0</v>
@@ -9249,7 +9249,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>mayank rawat</t>
+          <t>mayank markande</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -9262,11 +9262,11 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>mitchell marsh</t>
+          <t>mayank rawat</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
@@ -9275,115 +9275,115 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>mitchell santner</t>
+          <t>mitchell marsh</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>26</v>
+        <v>115</v>
       </c>
       <c r="C74" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>mohammed shami</t>
+          <t>mitchell santner</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="C75" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>mohammed siraj</t>
+          <t>mohammed shami</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="C76" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>mohsin khan</t>
+          <t>mohammed siraj</t>
         </is>
       </c>
       <c r="B77" t="n">
         <v>0</v>
       </c>
       <c r="C77" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>mukesh kumar</t>
+          <t>mohsin khan</t>
         </is>
       </c>
       <c r="B78" t="n">
         <v>0</v>
       </c>
       <c r="C78" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>mukul choudhary</t>
+          <t>mukesh choudhary</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>127</v>
+        <v>0</v>
       </c>
       <c r="C79" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>naman dhir</t>
+          <t>mukesh kumar</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="C80" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>nandre burger</t>
+          <t>mukul choudhary</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>3</v>
+        <v>127</v>
       </c>
       <c r="C81" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>navdeep saini</t>
+          <t>naman dhir</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
@@ -9392,24 +9392,24 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>nehal wadhera</t>
+          <t>nandre burger</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="C83" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>nicholas pooran</t>
+          <t>navdeep saini</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="C84" t="n">
         <v>0</v>
@@ -9418,24 +9418,24 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>nitish kumar reddy</t>
+          <t>nehal wadhera</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>124</v>
+        <v>27</v>
       </c>
       <c r="C85" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>nitish rana</t>
+          <t>nicholas pooran</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
@@ -9444,11 +9444,11 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>noor ahmad</t>
+          <t>nitish kumar reddy</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>9</v>
+        <v>136</v>
       </c>
       <c r="C87" t="n">
         <v>4</v>
@@ -9457,11 +9457,11 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>pathum nissanka</t>
+          <t>nitish rana</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>127</v>
+        <v>20</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
@@ -9470,24 +9470,24 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>philip salt</t>
+          <t>noor ahmad</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>139</v>
+        <v>10</v>
       </c>
       <c r="C89" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>prabhsimran singh</t>
+          <t>pathum nissanka</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>211</v>
+        <v>128</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
@@ -9496,24 +9496,24 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>praful hinge</t>
+          <t>philip salt</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0</v>
+        <v>202</v>
       </c>
       <c r="C91" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>prashant veer</t>
+          <t>prabhsimran singh</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>49</v>
+        <v>211</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
@@ -9522,63 +9522,63 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>prasidh krishna</t>
+          <t>praful hinge</t>
         </is>
       </c>
       <c r="B93" t="n">
         <v>0</v>
       </c>
       <c r="C93" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>prince yadav</t>
+          <t>prashant veer</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="C94" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>priyansh arya</t>
+          <t>prasidh krishna</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>118</v>
+        <v>0</v>
       </c>
       <c r="C95" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>quinton de kock</t>
+          <t>prince yadav</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="C96" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>rahul chahar</t>
+          <t>priyansh arya</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="C97" t="n">
         <v>0</v>
@@ -9587,11 +9587,11 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>rahul tewatia</t>
+          <t>quinton de kock</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>41</v>
+        <v>112</v>
       </c>
       <c r="C98" t="n">
         <v>0</v>
@@ -9600,11 +9600,11 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>rajat patidar</t>
+          <t>rahul chahar</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>222</v>
+        <v>0</v>
       </c>
       <c r="C99" t="n">
         <v>0</v>
@@ -9613,115 +9613,115 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ramandeep singh</t>
+          <t>rahul tewatia</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="C100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>rashid khan</t>
+          <t>rajat patidar</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>24</v>
+        <v>230</v>
       </c>
       <c r="C101" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>rasikh salam</t>
+          <t>ramandeep singh</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="C102" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>ravi bishnoi</t>
+          <t>rashid khan</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="C103" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>ravindra jadeja</t>
+          <t>rasikh salam</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="C104" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>rinku singh</t>
+          <t>ravi bishnoi</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="C105" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>rishabh pant</t>
+          <t>ravindra jadeja</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>104</v>
+        <v>76</v>
       </c>
       <c r="C106" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>riyan parag</t>
+          <t>rinku singh</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>49</v>
+        <v>79</v>
       </c>
       <c r="C107" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>rohit sharma</t>
+          <t>rishabh pant</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>137</v>
+        <v>104</v>
       </c>
       <c r="C108" t="n">
         <v>0</v>
@@ -9730,24 +9730,24 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>romario shepherd</t>
+          <t>riyan parag</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="C109" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>rovman powell</t>
+          <t>rohit sharma</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>97</v>
+        <v>137</v>
       </c>
       <c r="C110" t="n">
         <v>0</v>
@@ -9756,24 +9756,24 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ruturaj gaikwad</t>
+          <t>romario shepherd</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="C111" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ryan rickelton</t>
+          <t>rovman powell</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>137</v>
+        <v>97</v>
       </c>
       <c r="C112" t="n">
         <v>0</v>
@@ -9782,24 +9782,24 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>sakib hussain</t>
+          <t>ruturaj gaikwad</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="C113" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>salil arora</t>
+          <t>ryan rickelton</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>42</v>
+        <v>137</v>
       </c>
       <c r="C114" t="n">
         <v>0</v>
@@ -9808,37 +9808,37 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>sameer rizvi</t>
+          <t>sakib hussain</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>166</v>
+        <v>0</v>
       </c>
       <c r="C115" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>sandeep sharma</t>
+          <t>salil arora</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="C116" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>sanju samson</t>
+          <t>sameer rizvi</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>185</v>
+        <v>168</v>
       </c>
       <c r="C117" t="n">
         <v>0</v>
@@ -9847,24 +9847,24 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>sarfaraz khan</t>
+          <t>sandeep sharma</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>122</v>
+        <v>0</v>
       </c>
       <c r="C118" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>shahbaz ahmed</t>
+          <t>sanju samson</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>15</v>
+        <v>192</v>
       </c>
       <c r="C119" t="n">
         <v>0</v>
@@ -9873,11 +9873,11 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>shahrukh khan</t>
+          <t>sarfaraz khan</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="C120" t="n">
         <v>0</v>
@@ -9886,128 +9886,128 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>shardul thakur</t>
+          <t>shahbaz ahmed</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C121" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>shashank singh</t>
+          <t>shahrukh khan</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="C122" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>sherfane rutherford</t>
+          <t>shardul thakur</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>102</v>
+        <v>8</v>
       </c>
       <c r="C123" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>shimron hetmyer</t>
+          <t>shashank singh</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="C124" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>shivam dube</t>
+          <t>sherfane rutherford</t>
         </is>
       </c>
       <c r="B125" t="n">
         <v>102</v>
       </c>
       <c r="C125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>shivang kumar</t>
+          <t>shimron hetmyer</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="C126" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>shreyas iyer</t>
+          <t>shivam dube</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>203</v>
+        <v>123</v>
       </c>
       <c r="C127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>shubman gill</t>
+          <t>shivang kumar</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>251</v>
+        <v>21</v>
       </c>
       <c r="C128" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>sunil narine</t>
+          <t>shreyas iyer</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>36</v>
+        <v>203</v>
       </c>
       <c r="C129" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>suryakumar yadav</t>
+          <t>shubman gill</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>106</v>
+        <v>251</v>
       </c>
       <c r="C130" t="n">
         <v>0</v>
@@ -10016,11 +10016,11 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>suyash sharma</t>
+          <t>sunil narine</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="C131" t="n">
         <v>4</v>
@@ -10029,50 +10029,50 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>t natarajan</t>
+          <t>suryakumar yadav</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>1</v>
+        <v>106</v>
       </c>
       <c r="C132" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>tilak varma</t>
+          <t>suyash sharma</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="C133" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>tim david</t>
+          <t>t natarajan</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>147</v>
+        <v>1</v>
       </c>
       <c r="C134" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>tim seifert</t>
+          <t>tilak varma</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="C135" t="n">
         <v>0</v>
@@ -10081,11 +10081,11 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>travis head</t>
+          <t>tim david</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>120</v>
+        <v>173</v>
       </c>
       <c r="C136" t="n">
         <v>0</v>
@@ -10094,24 +10094,24 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>trent boult</t>
+          <t>tim seifert</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="C137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>tristan stubbs</t>
+          <t>travis head</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>109</v>
+        <v>143</v>
       </c>
       <c r="C138" t="n">
         <v>0</v>
@@ -10120,63 +10120,63 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>tushar deshpande</t>
+          <t>trent boult</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C139" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>vaibhav arora</t>
+          <t>tristan stubbs</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>1</v>
+        <v>169</v>
       </c>
       <c r="C140" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>vaibhav suryavanshi</t>
+          <t>tushar deshpande</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>200</v>
+        <v>25</v>
       </c>
       <c r="C141" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>varun chakravarthy</t>
+          <t>vaibhav arora</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C142" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>venkatesh iyer</t>
+          <t>vaibhav suryavanshi</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>29</v>
+        <v>200</v>
       </c>
       <c r="C143" t="n">
         <v>0</v>
@@ -10185,50 +10185,50 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>vijaykumar vyshak</t>
+          <t>varun chakravarthy</t>
         </is>
       </c>
       <c r="B144" t="n">
         <v>0</v>
       </c>
       <c r="C144" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>vipraj nigam</t>
+          <t>venkatesh iyer</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="C145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>virat kohli</t>
+          <t>vijaykumar vyshak</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>228</v>
+        <v>0</v>
       </c>
       <c r="C146" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>washington sundar</t>
+          <t>vipraj nigam</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>111</v>
+        <v>12</v>
       </c>
       <c r="C147" t="n">
         <v>1</v>
@@ -10237,39 +10237,65 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>xavier bartlett</t>
+          <t>virat kohli</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>11</v>
+        <v>247</v>
       </c>
       <c r="C148" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>yashasvi jaiswal</t>
+          <t>washington sundar</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>184</v>
+        <v>111</v>
       </c>
       <c r="C149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
+          <t>xavier bartlett</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>11</v>
+      </c>
+      <c r="C150" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>yashasvi jaiswal</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>184</v>
+      </c>
+      <c r="C151" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
           <t>yuzvendra chahal</t>
         </is>
       </c>
-      <c r="B150" t="n">
-        <v>0</v>
-      </c>
-      <c r="C150" t="n">
+      <c r="B152" t="n">
+        <v>0</v>
+      </c>
+      <c r="C152" t="n">
         <v>3</v>
       </c>
     </row>
@@ -10284,7 +10310,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K52"/>
+  <dimension ref="A1:K50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10476,7 +10502,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>karun nair</t>
+          <t>jacob bethel</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -10486,13 +10512,13 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>krunal pandya</t>
+          <t>jacob duffy</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -10519,7 +10545,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>jacob bethel</t>
+          <t>Jason Holder</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -10535,7 +10561,7 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>jacob duffy</t>
+          <t>jos buttler</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -10562,7 +10588,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Jason Holder</t>
+          <t>kamindu mendis</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -10572,13 +10598,13 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>jos buttler</t>
+          <t>karun nair</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -10605,7 +10631,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>kamindu mendis</t>
+          <t>Kuldeep sen</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -10621,7 +10647,7 @@
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>naman dhir</t>
+          <t>kuldeep yadav</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -10648,23 +10674,23 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Kuldeep sen</t>
+          <t>Tom Banton</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MEET11</t>
+          <t>VATSAL11</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>kuldeep yadav</t>
+          <t>t natarajan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -10691,7 +10717,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Tom Banton</t>
+          <t>Tim Siefert</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -10707,7 +10733,7 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>t natarajan</t>
+          <t>tim seifert</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -10734,7 +10760,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Tim Siefert</t>
+          <t>Lockie Ferguson</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -10744,13 +10770,13 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>tim seifert</t>
+          <t>lokesh rahul</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -10777,7 +10803,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Lockie Ferguson</t>
+          <t>Adam Milne</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -10793,7 +10819,7 @@
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>lokesh rahul</t>
+          <t>david miller</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -10820,23 +10846,23 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Adam Milne</t>
+          <t>Jos Inglis</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>VATSAL11</t>
+          <t>BABA11</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>david miller</t>
+          <t>marcus stoinis</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -10863,7 +10889,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Jos Inglis</t>
+          <t>Prithvi Shaw</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -10879,7 +10905,7 @@
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>marcus stoinis</t>
+          <t>prasidh krishna</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -10906,7 +10932,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Prithvi Shaw</t>
+          <t>liam livingston</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -10916,13 +10942,13 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>prasidh krishna</t>
+          <t>liam livingstone</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -10949,7 +10975,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>liam livingston</t>
+          <t>rachin ravindra</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -10965,7 +10991,7 @@
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>liam livingstone</t>
+          <t>rashid khan</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -10992,7 +11018,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>rachin ravindra</t>
+          <t>Zeeshan Ansari</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -11002,13 +11028,13 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>rashid khan</t>
+          <t>eshan malinga</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -11035,7 +11061,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Zeeshan Ansari</t>
+          <t>Mitchell Starc</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -11051,7 +11077,7 @@
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>eshan malinga</t>
+          <t>mitchell santner</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -11078,17 +11104,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Mitchell Starc</t>
+          <t>Mitchel Owen</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BABA11</t>
+          <t>DIPESH11</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -11121,7 +11147,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Mitchel Owen</t>
+          <t>Pat Cummins</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -11131,13 +11157,13 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>mitchell santner</t>
+          <t>pathum nissanka</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -11164,7 +11190,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Pat Cummins</t>
+          <t>Auqib Dar</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -11174,13 +11200,13 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>pathum nissanka</t>
+          <t>auqib nabi</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -11207,23 +11233,23 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Auqib Dar</t>
+          <t>Urvil Patel</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>DIPESH11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>auqib nabi</t>
+          <t>axar patel</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -11250,7 +11276,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Urvil Patel</t>
+          <t>Arshin Kulkarni</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -11266,7 +11292,7 @@
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>axar patel</t>
+          <t>shivang kumar</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -11293,7 +11319,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Arshin Kulkarni</t>
+          <t>Nishant Sindhu</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -11303,13 +11329,13 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>shivang kumar</t>
+          <t>shashank singh</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -11336,7 +11362,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Nishant Sindhu</t>
+          <t>Jayant Yadav</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11352,7 +11378,7 @@
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>shashank singh</t>
+          <t>mayank rawat</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -11379,7 +11405,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Jayant Yadav</t>
+          <t>Ajay Mandal</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11395,7 +11421,7 @@
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>mayank rawat</t>
+          <t>rajat patidar</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -11422,7 +11448,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Ajay Mandal</t>
+          <t>Will Jacks</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11438,7 +11464,7 @@
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>rajat patidar</t>
+          <t>mitchell marsh</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -11465,7 +11491,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Will Jacks</t>
+          <t>Kyle Jamieson</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -11475,13 +11501,13 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>mitchell marsh</t>
+          <t>jamie overton</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -11508,7 +11534,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Kyle Jamieson</t>
+          <t>Matheesha Pathirana</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -11524,7 +11550,7 @@
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>jamie overton</t>
+          <t>eshan malinga</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -11551,7 +11577,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Matheesha Pathirana</t>
+          <t>Ben Dwarshuis</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -11567,7 +11593,7 @@
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>eshan malinga</t>
+          <t>b sai sudharshan</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -11594,23 +11620,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Ben Dwarshuis</t>
+          <t>Manish Pandey</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>b sai sudharshan</t>
+          <t>hardik pandya</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -11637,7 +11663,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Manish Pandey</t>
+          <t>Arjun Tendulkar</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -11647,13 +11673,13 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>hardik pandya</t>
+          <t>karun nair</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -11680,7 +11706,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Mukesh Choudhary</t>
+          <t>Kwena Maphaka</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -11696,7 +11722,7 @@
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>mukul choudhary</t>
+          <t>aiden markram</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -11723,23 +11749,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Arjun Tendulkar</t>
+          <t>Ramkrishna Ghosh</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>krunal pandya</t>
+          <t>angkrish raghuvanshi</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -11766,23 +11792,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Kwena Maphaka</t>
+          <t>Azmatullah Omarzai</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>aiden markram</t>
+          <t>mitchell marsh</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -11809,12 +11835,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Ramkrishna Ghosh</t>
+          <t>akshat raghuwanshi</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -11852,23 +11878,23 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Azmatullah Omarzai</t>
+          <t>Himmat Singh</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>mitchell marsh</t>
+          <t>prabhsimran singh</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -11895,7 +11921,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>akshat raghuwanshi</t>
+          <t>Suryansh Shegde</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -11911,7 +11937,7 @@
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>angkrish raghuvanshi</t>
+          <t>suyash sharma</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -11938,7 +11964,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Himmat Singh</t>
+          <t>Tejasvi Singh</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -11981,7 +12007,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Suryansh Shegde</t>
+          <t>Sai Kishor</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -11991,13 +12017,13 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>suyash sharma</t>
+          <t>ishan kishan</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -12024,7 +12050,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Tejasvi Singh</t>
+          <t>Akash Deep</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -12034,13 +12060,13 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>prabhsimran singh</t>
+          <t>arshdeep singh</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -12067,23 +12093,23 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sai Kishor</t>
+          <t>Ben Duckett</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>ishan kishan</t>
+          <t>ryan rickelton</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -12110,23 +12136,23 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Akash Deep</t>
+          <t>Abhishek Porel</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>arshdeep singh</t>
+          <t>abhishek sharma</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -12153,7 +12179,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Ben Duckett</t>
+          <t>Rahul Tripathi</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -12169,7 +12195,7 @@
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>ryan rickelton</t>
+          <t>rahul tewatia</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -12196,7 +12222,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Abhishek Porel</t>
+          <t>Dre Pretorius</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -12212,7 +12238,7 @@
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>abhishek sharma</t>
+          <t>lhuan dre pretorius</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -12239,7 +12265,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Rahul Tripathi</t>
+          <t>Matthew Breetzke</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -12255,7 +12281,7 @@
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>rahul tewatia</t>
+          <t>matt henry</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -12282,7 +12308,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Dre Pretorius</t>
+          <t>Anuj Rawat</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -12298,7 +12324,7 @@
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>lhuan dre pretorius</t>
+          <t>mayank rawat</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -12325,7 +12351,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Matthew Breetzke</t>
+          <t>Wanindu Hasaranga</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -12335,13 +12361,13 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>matt henry</t>
+          <t>sandeep sharma</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -12368,7 +12394,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Anuj Rawat</t>
+          <t>Harpreet Brar</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -12378,13 +12404,13 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>mayank rawat</t>
+          <t>jasprit bumrah</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -12411,7 +12437,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Wanindu Hasaranga</t>
+          <t>Mayank Yadav</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -12421,13 +12447,13 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>sandeep sharma</t>
+          <t>mayank rawat</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -12448,92 +12474,6 @@
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Harpreet Brar</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>BOWL</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>jasprit bumrah</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="G51" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Mayank Yadav</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>BOWL</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>mayank rawat</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="G52" t="n">
-        <v>0</v>
-      </c>
-      <c r="H52" t="n">
-        <v>0</v>
-      </c>
-      <c r="I52" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" t="n">
-        <v>0</v>
-      </c>
-      <c r="K52" t="n">
         <v>0</v>
       </c>
     </row>

--- a/IPL_Fantasy_Points.xlsx
+++ b/IPL_Fantasy_Points.xlsx
@@ -561,19 +561,19 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>104</v>
+        <v>147</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>104</v>
+        <v>147</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>104</v>
+        <v>147</v>
       </c>
     </row>
     <row r="4">
@@ -862,19 +862,19 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>135</v>
+        <v>162</v>
       </c>
       <c r="H10" t="n">
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>135</v>
+        <v>162</v>
       </c>
       <c r="J10" t="n">
         <v>20</v>
       </c>
       <c r="K10" t="n">
-        <v>155</v>
+        <v>182</v>
       </c>
     </row>
     <row r="11">
@@ -948,19 +948,19 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="H12" t="n">
         <v>4</v>
       </c>
       <c r="I12" t="n">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="J12" t="n">
         <v>80</v>
       </c>
       <c r="K12" t="n">
-        <v>90</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13">
@@ -1037,16 +1037,16 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="K14" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15">
@@ -1335,19 +1335,19 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>200</v>
+        <v>246</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>200</v>
+        <v>246</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>200</v>
+        <v>246</v>
       </c>
     </row>
     <row r="22">
@@ -1378,19 +1378,19 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="H22" t="n">
         <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
     </row>
     <row r="23">
@@ -1725,16 +1725,16 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="K30" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
     </row>
     <row r="31">
@@ -2281,19 +2281,19 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H43" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I43" t="n">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="J43" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="K43" t="n">
-        <v>136</v>
+        <v>185</v>
       </c>
     </row>
     <row r="44">
@@ -2367,19 +2367,19 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>19</v>
+        <v>48</v>
       </c>
     </row>
     <row r="46">
@@ -2883,19 +2883,19 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>176</v>
+        <v>181</v>
       </c>
     </row>
     <row r="58">
@@ -2926,19 +2926,19 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>113</v>
+        <v>148</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>113</v>
+        <v>148</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>113</v>
+        <v>148</v>
       </c>
     </row>
     <row r="59">
@@ -3055,19 +3055,19 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>79</v>
+        <v>132</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>79</v>
+        <v>132</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>79</v>
+        <v>132</v>
       </c>
     </row>
     <row r="62">
@@ -3141,19 +3141,19 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>97</v>
+        <v>120</v>
       </c>
     </row>
     <row r="64">
@@ -3359,16 +3359,16 @@
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I68" t="n">
         <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="K68" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
     </row>
     <row r="69">
@@ -3657,19 +3657,19 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>118</v>
+        <v>211</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>118</v>
+        <v>211</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>118</v>
+        <v>211</v>
       </c>
     </row>
     <row r="76">
@@ -3743,19 +3743,19 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
     </row>
     <row r="78">
@@ -3915,19 +3915,19 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>120</v>
+        <v>162</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>120</v>
+        <v>162</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>120</v>
+        <v>162</v>
       </c>
     </row>
     <row r="82">
@@ -4001,19 +4001,19 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>136</v>
+        <v>223</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>136</v>
+        <v>223</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>136</v>
+        <v>223</v>
       </c>
     </row>
     <row r="84">
@@ -4047,16 +4047,16 @@
         <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I84" t="n">
         <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="K84" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
     </row>
     <row r="85">
@@ -4302,19 +4302,19 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>184</v>
+        <v>223</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>184</v>
+        <v>223</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>184</v>
+        <v>223</v>
       </c>
     </row>
     <row r="91">
@@ -4388,19 +4388,19 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>203</v>
+        <v>208</v>
       </c>
     </row>
     <row r="93">
@@ -4732,19 +4732,19 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="H100" t="n">
         <v>2</v>
       </c>
       <c r="I100" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="J100" t="n">
         <v>40</v>
       </c>
       <c r="K100" t="n">
-        <v>89</v>
+        <v>101</v>
       </c>
     </row>
     <row r="101">
@@ -4950,16 +4950,16 @@
         <v>0</v>
       </c>
       <c r="H105" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I105" t="n">
         <v>0</v>
       </c>
       <c r="J105" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="K105" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
     </row>
     <row r="106">
@@ -5036,16 +5036,16 @@
         <v>3</v>
       </c>
       <c r="H107" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I107" t="n">
         <v>0</v>
       </c>
       <c r="J107" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="K107" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
     </row>
     <row r="108">
@@ -5119,19 +5119,19 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>115</v>
+        <v>155</v>
       </c>
       <c r="H109" t="n">
         <v>0</v>
       </c>
       <c r="I109" t="n">
-        <v>115</v>
+        <v>155</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
       </c>
       <c r="K109" t="n">
-        <v>115</v>
+        <v>155</v>
       </c>
     </row>
     <row r="110">
@@ -5205,19 +5205,19 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
       </c>
       <c r="I111" t="n">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
       </c>
       <c r="K111" t="n">
-        <v>24</v>
+        <v>39</v>
       </c>
     </row>
     <row r="112">
@@ -5420,19 +5420,19 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H116" t="n">
         <v>0</v>
       </c>
       <c r="I116" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
       </c>
       <c r="K116" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
     </row>
     <row r="117">
@@ -5509,16 +5509,16 @@
         <v>11</v>
       </c>
       <c r="H118" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I118" t="n">
         <v>0</v>
       </c>
       <c r="J118" t="n">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="K118" t="n">
-        <v>100</v>
+        <v>160</v>
       </c>
     </row>
     <row r="119">
@@ -5595,16 +5595,16 @@
         <v>0</v>
       </c>
       <c r="H120" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I120" t="n">
         <v>0</v>
       </c>
       <c r="J120" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="K120" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
     </row>
     <row r="121">
@@ -6108,19 +6108,19 @@
         </is>
       </c>
       <c r="G132" t="n">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="H132" t="n">
         <v>3</v>
       </c>
       <c r="I132" t="n">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
       </c>
       <c r="K132" t="n">
-        <v>34</v>
+        <v>51</v>
       </c>
     </row>
     <row r="133">
@@ -6194,19 +6194,19 @@
         </is>
       </c>
       <c r="G134" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
       </c>
       <c r="I134" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
       </c>
       <c r="K134" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
     </row>
     <row r="135">
@@ -6541,16 +6541,16 @@
         <v>14</v>
       </c>
       <c r="H142" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I142" t="n">
         <v>0</v>
       </c>
       <c r="J142" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="K142" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="143">
@@ -6710,19 +6710,19 @@
         </is>
       </c>
       <c r="G146" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="H146" t="n">
         <v>0</v>
       </c>
       <c r="I146" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
       </c>
       <c r="K146" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
     </row>
     <row r="147">
@@ -6870,15 +6870,15 @@
           <t>BAT</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr"/>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>prabhsimran singh</t>
-        </is>
-      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>himmat singh</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -7054,19 +7054,19 @@
         </is>
       </c>
       <c r="G154" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="H154" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I154" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="J154" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="K154" t="n">
-        <v>143</v>
+        <v>171</v>
       </c>
     </row>
     <row r="155">
@@ -7143,16 +7143,16 @@
         <v>0</v>
       </c>
       <c r="H156" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I156" t="n">
         <v>0</v>
       </c>
       <c r="J156" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="K156" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
     </row>
     <row r="157">
@@ -7785,19 +7785,19 @@
         </is>
       </c>
       <c r="G171" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H171" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I171" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J171" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="K171" t="n">
-        <v>69</v>
+        <v>110</v>
       </c>
     </row>
     <row r="172">
@@ -7831,16 +7831,16 @@
         <v>36</v>
       </c>
       <c r="H172" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I172" t="n">
         <v>36</v>
       </c>
       <c r="J172" t="n">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="K172" t="n">
-        <v>116</v>
+        <v>156</v>
       </c>
     </row>
     <row r="173">
@@ -8185,7 +8185,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1798</v>
+        <v>2053</v>
       </c>
     </row>
     <row r="3">
@@ -8198,7 +8198,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1680</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="4">
@@ -8211,7 +8211,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1480</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="5">
@@ -8220,11 +8220,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>VATSAL11</t>
+          <t>BABA11</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1394</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="6">
@@ -8233,11 +8233,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BABA11</t>
+          <t>VATSAL11</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1344</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="7">
@@ -8250,7 +8250,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1324</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="8">
@@ -8259,11 +8259,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1198</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="9">
@@ -8272,11 +8272,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1185</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="10">
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1089</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="11">
@@ -8302,7 +8302,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>975</v>
+        <v>1056</v>
       </c>
     </row>
   </sheetData>
@@ -8316,7 +8316,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C152"/>
+  <dimension ref="A1:C154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8382,7 +8382,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>120</v>
+        <v>162</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -8434,7 +8434,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -8486,7 +8486,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="C13" t="n">
         <v>4</v>
@@ -8502,7 +8502,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
@@ -8577,7 +8577,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>113</v>
+        <v>148</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
@@ -8642,7 +8642,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C25" t="n">
         <v>3</v>
@@ -8655,7 +8655,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>135</v>
+        <v>162</v>
       </c>
       <c r="C26" t="n">
         <v>1</v>
@@ -8668,7 +8668,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>136</v>
+        <v>223</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
@@ -8759,7 +8759,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="C34" t="n">
         <v>0</v>
@@ -8785,7 +8785,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
@@ -8911,11 +8911,11 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ishan kishan</t>
+          <t>himmat singh</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>213</v>
+        <v>0</v>
       </c>
       <c r="C46" t="n">
         <v>0</v>
@@ -8924,219 +8924,219 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>jacob duffy</t>
+          <t>ishan kishan</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0</v>
+        <v>213</v>
       </c>
       <c r="C47" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>jamie overton</t>
+          <t>jacob duffy</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>jasprit bumrah</t>
+          <t>jamie overton</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>5</v>
+        <v>103</v>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>jaydev unadkat</t>
+          <t>jasprit bumrah</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C50" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>jitesh sharma</t>
+          <t>jaydev unadkat</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>jofra archer</t>
+          <t>jitesh sharma</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>3</v>
+        <v>52</v>
       </c>
       <c r="C52" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>jos buttler</t>
+          <t>jofra archer</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>201</v>
+        <v>11</v>
       </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>josh hazlewood</t>
+          <t>jos buttler</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0</v>
+        <v>201</v>
       </c>
       <c r="C54" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>kagiso rabada</t>
+          <t>josh hazlewood</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>kartik sharma</t>
+          <t>kagiso rabada</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C56" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>kartik tyagi</t>
+          <t>kartik sharma</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="C57" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>karun nair</t>
+          <t>kartik tyagi</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C58" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>khaleel ahmed</t>
+          <t>karun nair</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C59" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>krunal pandya</t>
+          <t>khaleel ahmed</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C60" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>kuldeep yadav</t>
+          <t>krunal pandya</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C61" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>kumar kushagra</t>
+          <t>kuldeep yadav</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="C62" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>lhuan dre pretorius</t>
+          <t>kumar kushagra</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C63" t="n">
         <v>0</v>
@@ -9145,11 +9145,11 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>liam livingstone</t>
+          <t>lhuan dre pretorius</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="C64" t="n">
         <v>0</v>
@@ -9158,11 +9158,11 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>lokesh rahul</t>
+          <t>liam livingstone</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>168</v>
+        <v>15</v>
       </c>
       <c r="C65" t="n">
         <v>0</v>
@@ -9171,89 +9171,89 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>lungi ngidi</t>
+          <t>lokesh rahul</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>3</v>
+        <v>168</v>
       </c>
       <c r="C66" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>manimaran siddharth</t>
+          <t>lungi ngidi</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C67" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>marco jansen</t>
+          <t>manimaran siddharth</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C68" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>marcus stoinis</t>
+          <t>marco jansen</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C69" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>matt henry</t>
+          <t>marcus stoinis</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="C70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>matt short</t>
+          <t>matt henry</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="C71" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>mayank markande</t>
+          <t>matt short</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="C72" t="n">
         <v>0</v>
@@ -9262,7 +9262,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>mayank rawat</t>
+          <t>mayank markande</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -9275,11 +9275,11 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>mitchell marsh</t>
+          <t>mayank rawat</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="C74" t="n">
         <v>0</v>
@@ -9288,37 +9288,37 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>mitchell santner</t>
+          <t>mitchell marsh</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>26</v>
+        <v>155</v>
       </c>
       <c r="C75" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>mohammed shami</t>
+          <t>mitchell santner</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="C76" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>mohammed siraj</t>
+          <t>mohammed shami</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="C77" t="n">
         <v>5</v>
@@ -9327,20 +9327,20 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>mohsin khan</t>
+          <t>mohammed siraj</t>
         </is>
       </c>
       <c r="B78" t="n">
         <v>0</v>
       </c>
       <c r="C78" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>mukesh choudhary</t>
+          <t>mohsin khan</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -9353,37 +9353,37 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>mukesh kumar</t>
+          <t>mukesh choudhary</t>
         </is>
       </c>
       <c r="B80" t="n">
         <v>0</v>
       </c>
       <c r="C80" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>mukul choudhary</t>
+          <t>mukesh kumar</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>127</v>
+        <v>0</v>
       </c>
       <c r="C81" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>naman dhir</t>
+          <t>mukul choudhary</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>109</v>
+        <v>148</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
@@ -9392,37 +9392,37 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>nandre burger</t>
+          <t>naman dhir</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="C83" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>navdeep saini</t>
+          <t>nandre burger</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C84" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>nehal wadhera</t>
+          <t>navdeep saini</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
@@ -9431,11 +9431,11 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>nicholas pooran</t>
+          <t>nehal wadhera</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
@@ -9444,63 +9444,63 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>nitish kumar reddy</t>
+          <t>nicholas pooran</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>136</v>
+        <v>51</v>
       </c>
       <c r="C87" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>nitish rana</t>
+          <t>nitish kumar reddy</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>20</v>
+        <v>136</v>
       </c>
       <c r="C88" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>noor ahmad</t>
+          <t>nitish rana</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C89" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>pathum nissanka</t>
+          <t>noor ahmad</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>128</v>
+        <v>10</v>
       </c>
       <c r="C90" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>philip salt</t>
+          <t>pathum nissanka</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>202</v>
+        <v>128</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
@@ -9509,11 +9509,11 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>prabhsimran singh</t>
+          <t>philip salt</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
@@ -9522,76 +9522,76 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>praful hinge</t>
+          <t>prabhsimran singh</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0</v>
+        <v>211</v>
       </c>
       <c r="C93" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>prashant veer</t>
+          <t>praful hinge</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="C94" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>prasidh krishna</t>
+          <t>prashant veer</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="C95" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>prince yadav</t>
+          <t>prasidh krishna</t>
         </is>
       </c>
       <c r="B96" t="n">
         <v>0</v>
       </c>
       <c r="C96" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>priyansh arya</t>
+          <t>prince yadav</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>118</v>
+        <v>0</v>
       </c>
       <c r="C97" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>quinton de kock</t>
+          <t>priyansh arya</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>112</v>
+        <v>211</v>
       </c>
       <c r="C98" t="n">
         <v>0</v>
@@ -9600,11 +9600,11 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>rahul chahar</t>
+          <t>quinton de kock</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="C99" t="n">
         <v>0</v>
@@ -9613,11 +9613,11 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>rahul tewatia</t>
+          <t>rahul chahar</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="C100" t="n">
         <v>0</v>
@@ -9626,11 +9626,11 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>rajat patidar</t>
+          <t>rahul tewatia</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>230</v>
+        <v>41</v>
       </c>
       <c r="C101" t="n">
         <v>0</v>
@@ -9639,89 +9639,89 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ramandeep singh</t>
+          <t>rajat patidar</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>66</v>
+        <v>230</v>
       </c>
       <c r="C102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>rashid khan</t>
+          <t>ramandeep singh</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>24</v>
+        <v>76</v>
       </c>
       <c r="C103" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>rasikh salam</t>
+          <t>rashid khan</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="C104" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>ravi bishnoi</t>
+          <t>rasikh salam</t>
         </is>
       </c>
       <c r="B105" t="n">
         <v>0</v>
       </c>
       <c r="C105" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ravindra jadeja</t>
+          <t>ravi bishnoi</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="C106" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>rinku singh</t>
+          <t>ravindra jadeja</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C107" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>rishabh pant</t>
+          <t>rinku singh</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>104</v>
+        <v>132</v>
       </c>
       <c r="C108" t="n">
         <v>0</v>
@@ -9730,63 +9730,63 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>riyan parag</t>
+          <t>rishabh pant</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>49</v>
+        <v>147</v>
       </c>
       <c r="C109" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>rohit sharma</t>
+          <t>riyan parag</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>137</v>
+        <v>61</v>
       </c>
       <c r="C110" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>romario shepherd</t>
+          <t>rohit sharma</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>39</v>
+        <v>137</v>
       </c>
       <c r="C111" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>rovman powell</t>
+          <t>romario shepherd</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>97</v>
+        <v>39</v>
       </c>
       <c r="C112" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ruturaj gaikwad</t>
+          <t>rovman powell</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="C113" t="n">
         <v>0</v>
@@ -9795,11 +9795,11 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ryan rickelton</t>
+          <t>ruturaj gaikwad</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>137</v>
+        <v>82</v>
       </c>
       <c r="C114" t="n">
         <v>0</v>
@@ -9808,37 +9808,37 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>sakib hussain</t>
+          <t>ryan rickelton</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0</v>
+        <v>137</v>
       </c>
       <c r="C115" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>salil arora</t>
+          <t>sakib hussain</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="C116" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>sameer rizvi</t>
+          <t>salil arora</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>168</v>
+        <v>55</v>
       </c>
       <c r="C117" t="n">
         <v>0</v>
@@ -9847,37 +9847,37 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>sandeep sharma</t>
+          <t>sameer rizvi</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="C118" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>sanju samson</t>
+          <t>sandeep sharma</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>192</v>
+        <v>0</v>
       </c>
       <c r="C119" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>sarfaraz khan</t>
+          <t>sanju samson</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>147</v>
+        <v>192</v>
       </c>
       <c r="C120" t="n">
         <v>0</v>
@@ -9886,11 +9886,11 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>shahbaz ahmed</t>
+          <t>sarfaraz khan</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>15</v>
+        <v>147</v>
       </c>
       <c r="C121" t="n">
         <v>0</v>
@@ -9899,11 +9899,11 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>shahrukh khan</t>
+          <t>shahbaz ahmed</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C122" t="n">
         <v>0</v>
@@ -9912,50 +9912,50 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>shardul thakur</t>
+          <t>shahrukh khan</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C123" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>shashank singh</t>
+          <t>shardul thakur</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="C124" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>sherfane rutherford</t>
+          <t>shashank singh</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>102</v>
+        <v>51</v>
       </c>
       <c r="C125" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>shimron hetmyer</t>
+          <t>sherfane rutherford</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>24</v>
+        <v>102</v>
       </c>
       <c r="C126" t="n">
         <v>0</v>
@@ -9964,50 +9964,50 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>shivam dube</t>
+          <t>shimron hetmyer</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>123</v>
+        <v>39</v>
       </c>
       <c r="C127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>shivang kumar</t>
+          <t>shivam dube</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>21</v>
+        <v>123</v>
       </c>
       <c r="C128" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>shreyas iyer</t>
+          <t>shivang kumar</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>203</v>
+        <v>21</v>
       </c>
       <c r="C129" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>shubman gill</t>
+          <t>shreyas iyer</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>251</v>
+        <v>208</v>
       </c>
       <c r="C130" t="n">
         <v>0</v>
@@ -10016,50 +10016,50 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>sunil narine</t>
+          <t>shubman gill</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>36</v>
+        <v>251</v>
       </c>
       <c r="C131" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>suryakumar yadav</t>
+          <t>sunil narine</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>106</v>
+        <v>36</v>
       </c>
       <c r="C132" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>suyash sharma</t>
+          <t>suryakumar yadav</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="C133" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>t natarajan</t>
+          <t>suyash sharma</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C134" t="n">
         <v>4</v>
@@ -10068,24 +10068,24 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>tilak varma</t>
+          <t>t natarajan</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="C135" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>tim david</t>
+          <t>tilak varma</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>173</v>
+        <v>43</v>
       </c>
       <c r="C136" t="n">
         <v>0</v>
@@ -10094,11 +10094,11 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>tim seifert</t>
+          <t>tim david</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>19</v>
+        <v>173</v>
       </c>
       <c r="C137" t="n">
         <v>0</v>
@@ -10107,11 +10107,11 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>travis head</t>
+          <t>tim seifert</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>143</v>
+        <v>19</v>
       </c>
       <c r="C138" t="n">
         <v>0</v>
@@ -10120,183 +10120,209 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>trent boult</t>
+          <t>travis head</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>1</v>
+        <v>143</v>
       </c>
       <c r="C139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>tristan stubbs</t>
+          <t>trent boult</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>169</v>
+        <v>1</v>
       </c>
       <c r="C140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>tushar deshpande</t>
+          <t>tristan stubbs</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>25</v>
+        <v>169</v>
       </c>
       <c r="C141" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>vaibhav arora</t>
+          <t>tushar deshpande</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C142" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>vaibhav suryavanshi</t>
+          <t>vaibhav arora</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>200</v>
+        <v>1</v>
       </c>
       <c r="C143" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>varun chakravarthy</t>
+          <t>vaibhav suryavanshi</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0</v>
+        <v>246</v>
       </c>
       <c r="C144" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>venkatesh iyer</t>
+          <t>varun chakravarthy</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="C145" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>vijaykumar vyshak</t>
+          <t>venkatesh iyer</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="C146" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>vipraj nigam</t>
+          <t>vijaykumar vyshak</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C147" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>virat kohli</t>
+          <t>vipraj nigam</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>247</v>
+        <v>12</v>
       </c>
       <c r="C148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>washington sundar</t>
+          <t>virat kohli</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>111</v>
+        <v>247</v>
       </c>
       <c r="C149" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>xavier bartlett</t>
+          <t>washington sundar</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>11</v>
+        <v>111</v>
       </c>
       <c r="C150" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>yashasvi jaiswal</t>
+          <t>xavier bartlett</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>184</v>
+        <v>11</v>
       </c>
       <c r="C151" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
+          <t>yash raj punja</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>0</v>
+      </c>
+      <c r="C152" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>yashasvi jaiswal</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>223</v>
+      </c>
+      <c r="C153" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
           <t>yuzvendra chahal</t>
         </is>
       </c>
-      <c r="B152" t="n">
-        <v>0</v>
-      </c>
-      <c r="C152" t="n">
-        <v>3</v>
+      <c r="B154" t="n">
+        <v>0</v>
+      </c>
+      <c r="C154" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -10310,7 +10336,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K50"/>
+  <dimension ref="A1:K49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11878,7 +11904,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Himmat Singh</t>
+          <t>Suryansh Shegde</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -11894,7 +11920,7 @@
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>prabhsimran singh</t>
+          <t>suyash sharma</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -11921,7 +11947,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Suryansh Shegde</t>
+          <t>Tejasvi Singh</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -11937,7 +11963,7 @@
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>suyash sharma</t>
+          <t>prabhsimran singh</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -11964,7 +11990,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Tejasvi Singh</t>
+          <t>Sai Kishor</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -11974,13 +12000,13 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>prabhsimran singh</t>
+          <t>ishan kishan</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -12007,7 +12033,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sai Kishor</t>
+          <t>Akash Deep</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -12023,7 +12049,7 @@
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>ishan kishan</t>
+          <t>arshdeep singh</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -12050,23 +12076,23 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Akash Deep</t>
+          <t>Ben Duckett</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>arshdeep singh</t>
+          <t>ryan rickelton</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -12093,7 +12119,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Ben Duckett</t>
+          <t>Abhishek Porel</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -12109,7 +12135,7 @@
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>ryan rickelton</t>
+          <t>abhishek sharma</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -12136,7 +12162,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Abhishek Porel</t>
+          <t>Rahul Tripathi</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -12152,7 +12178,7 @@
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>abhishek sharma</t>
+          <t>rahul tewatia</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -12179,7 +12205,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Rahul Tripathi</t>
+          <t>Dre Pretorius</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -12195,7 +12221,7 @@
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>rahul tewatia</t>
+          <t>lhuan dre pretorius</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -12222,7 +12248,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Dre Pretorius</t>
+          <t>Matthew Breetzke</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -12238,7 +12264,7 @@
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>lhuan dre pretorius</t>
+          <t>matt henry</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -12265,7 +12291,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Matthew Breetzke</t>
+          <t>Anuj Rawat</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -12281,7 +12307,7 @@
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>matt henry</t>
+          <t>mayank rawat</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -12308,7 +12334,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Anuj Rawat</t>
+          <t>Wanindu Hasaranga</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -12318,13 +12344,13 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>mayank rawat</t>
+          <t>sandeep sharma</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -12351,7 +12377,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Wanindu Hasaranga</t>
+          <t>Harpreet Brar</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -12361,13 +12387,13 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>sandeep sharma</t>
+          <t>jasprit bumrah</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -12394,7 +12420,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Harpreet Brar</t>
+          <t>Mayank Yadav</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -12410,7 +12436,7 @@
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>jasprit bumrah</t>
+          <t>mayank rawat</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -12431,49 +12457,6 @@
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Mayank Yadav</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>BOWL</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>mayank rawat</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="G50" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" t="n">
-        <v>0</v>
-      </c>
-      <c r="K50" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12647,19 +12630,19 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>

--- a/IPL_Fantasy_Points.xlsx
+++ b/IPL_Fantasy_Points.xlsx
@@ -819,19 +819,19 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>109</v>
+        <v>154</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>109</v>
+        <v>154</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>109</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10">
@@ -994,16 +994,16 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="K13" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14">
@@ -1249,19 +1249,19 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>251</v>
+        <v>265</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>251</v>
+        <v>265</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>251</v>
+        <v>265</v>
       </c>
     </row>
     <row r="20">
@@ -1550,19 +1550,19 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
     </row>
     <row r="27">
@@ -1811,16 +1811,16 @@
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="K32" t="n">
-        <v>80</v>
+        <v>120</v>
       </c>
     </row>
     <row r="33">
@@ -1980,19 +1980,19 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>112</v>
+        <v>125</v>
       </c>
     </row>
     <row r="37">
@@ -2195,19 +2195,19 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
     </row>
     <row r="42">
@@ -2413,16 +2413,16 @@
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="K46" t="n">
-        <v>220</v>
+        <v>240</v>
       </c>
     </row>
     <row r="47">
@@ -3184,19 +3184,19 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H64" t="n">
         <v>6</v>
       </c>
       <c r="I64" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J64" t="n">
         <v>120</v>
       </c>
       <c r="K64" t="n">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="65">
@@ -3313,19 +3313,19 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="68">
@@ -3488,16 +3488,16 @@
         <v>26</v>
       </c>
       <c r="H71" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I71" t="n">
         <v>0</v>
       </c>
       <c r="J71" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="K71" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
     </row>
     <row r="72">
@@ -4431,19 +4431,19 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>201</v>
+        <v>206</v>
       </c>
     </row>
     <row r="94">
@@ -4508,7 +4508,7 @@
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>shivang kumar</t>
+          <t>ashwani kumar</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -4775,19 +4775,19 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="H101" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I101" t="n">
         <v>0</v>
       </c>
       <c r="J101" t="n">
-        <v>140</v>
+        <v>200</v>
       </c>
       <c r="K101" t="n">
-        <v>140</v>
+        <v>200</v>
       </c>
     </row>
     <row r="102">
@@ -5334,19 +5334,19 @@
         </is>
       </c>
       <c r="G114" t="n">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="H114" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I114" t="n">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="J114" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="K114" t="n">
-        <v>121</v>
+        <v>156</v>
       </c>
     </row>
     <row r="115">
@@ -5979,19 +5979,19 @@
         </is>
       </c>
       <c r="G129" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
       </c>
       <c r="I129" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
       </c>
       <c r="K129" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
     </row>
     <row r="130">
@@ -6065,19 +6065,19 @@
         </is>
       </c>
       <c r="G131" t="n">
-        <v>43</v>
+        <v>144</v>
       </c>
       <c r="H131" t="n">
         <v>0</v>
       </c>
       <c r="I131" t="n">
-        <v>43</v>
+        <v>144</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
       </c>
       <c r="K131" t="n">
-        <v>43</v>
+        <v>144</v>
       </c>
     </row>
     <row r="132">
@@ -6280,19 +6280,19 @@
         </is>
       </c>
       <c r="G136" t="n">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="H136" t="n">
         <v>1</v>
       </c>
       <c r="I136" t="n">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="J136" t="n">
         <v>20</v>
       </c>
       <c r="K136" t="n">
-        <v>131</v>
+        <v>157</v>
       </c>
     </row>
     <row r="137">
@@ -6455,16 +6455,16 @@
         <v>5</v>
       </c>
       <c r="H140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I140" t="n">
         <v>0</v>
       </c>
       <c r="J140" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K140" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="141">
@@ -6667,19 +6667,19 @@
         </is>
       </c>
       <c r="G145" t="n">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
       </c>
       <c r="I145" t="n">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
       </c>
       <c r="K145" t="n">
-        <v>106</v>
+        <v>121</v>
       </c>
     </row>
     <row r="146">
@@ -6882,19 +6882,19 @@
         </is>
       </c>
       <c r="G150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
       </c>
       <c r="I150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
       </c>
       <c r="K150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="151">
@@ -8198,7 +8198,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1756</v>
+        <v>1818</v>
       </c>
     </row>
     <row r="4">
@@ -8211,7 +8211,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1622</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="5">
@@ -8224,7 +8224,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1520</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="6">
@@ -8237,7 +8237,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1472</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="7">
@@ -8246,11 +8246,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1381</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="8">
@@ -8259,11 +8259,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1301</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="9">
@@ -8272,11 +8272,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1245</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="10">
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1208</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="11">
@@ -8316,7 +8316,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C154"/>
+  <dimension ref="A1:C157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8424,7 +8424,7 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -8512,7 +8512,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C15" t="n">
         <v>6</v>
@@ -8534,37 +8534,37 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>auqib nabi</t>
+          <t>ashwani kumar</t>
         </is>
       </c>
       <c r="B17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" t="n">
         <v>4</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>avesh khan</t>
+          <t>auqib nabi</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>axar patel</t>
+          <t>avesh khan</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
         <v>5</v>
@@ -8573,24 +8573,24 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ayush badoni</t>
+          <t>axar patel</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>148</v>
+        <v>29</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ayush mhatre</t>
+          <t>ayush badoni</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>201</v>
+        <v>148</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
@@ -8599,11 +8599,11 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>b sai sudharshan</t>
+          <t>ayush mhatre</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>135</v>
+        <v>201</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
@@ -8612,154 +8612,154 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>bhuvneshwar kumar</t>
+          <t>b sai sudharshan</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>12</v>
+        <v>135</v>
       </c>
       <c r="C23" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>blessing muzarabani</t>
+          <t>bhuvneshwar kumar</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C24" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>brijesh sharma</t>
+          <t>blessing muzarabani</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>cameron green</t>
+          <t>brijesh sharma</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>162</v>
+        <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>cooper connolly</t>
+          <t>cameron green</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>223</v>
+        <v>162</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>corbin bosch</t>
+          <t>cooper connolly</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>11</v>
+        <v>223</v>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>david miller</t>
+          <t>corbin bosch</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>101</v>
+        <v>11</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>david payne</t>
+          <t>danish malewar</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>deepak chahar</t>
+          <t>david miller</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>6</v>
+        <v>101</v>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>devdutt padikkal</t>
+          <t>david payne</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>153</v>
+        <v>6</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>dewald brevis</t>
+          <t>deepak chahar</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>dhruv chand jurel</t>
+          <t>devdutt padikkal</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="C34" t="n">
         <v>0</v>
@@ -8768,24 +8768,24 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>digvesh rathi</t>
+          <t>dewald brevis</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="C35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>donavon ferreira</t>
+          <t>dhruv chand jurel</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>77</v>
+        <v>181</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
@@ -8794,24 +8794,24 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>eshan malinga</t>
+          <t>digvesh rathi</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>0</v>
       </c>
       <c r="C37" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>finn allen</t>
+          <t>donavon ferreira</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -8820,24 +8820,24 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>george linde</t>
+          <t>eshan malinga</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>glenn phillips</t>
+          <t>finn allen</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="C40" t="n">
         <v>0</v>
@@ -8846,76 +8846,76 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>gurjapneet singh</t>
+          <t>george linde</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="C41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>hardik pandya</t>
+          <t>glenn phillips</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="C42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>harsh dubey</t>
+          <t>gurjapneet singh</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C43" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>harshal patel</t>
+          <t>hardik pandya</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4</v>
+        <v>96</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>heinrich klaasen</t>
+          <t>harsh dubey</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>283</v>
+        <v>13</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>himmat singh</t>
+          <t>harshal patel</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C46" t="n">
         <v>0</v>
@@ -8924,11 +8924,11 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ishan kishan</t>
+          <t>heinrich klaasen</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>213</v>
+        <v>283</v>
       </c>
       <c r="C47" t="n">
         <v>0</v>
@@ -8937,89 +8937,89 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>jacob duffy</t>
+          <t>himmat singh</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C48" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>jamie overton</t>
+          <t>ishan kishan</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>103</v>
+        <v>213</v>
       </c>
       <c r="C49" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>jasprit bumrah</t>
+          <t>jacob duffy</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>jaydev unadkat</t>
+          <t>jamie overton</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4</v>
+        <v>103</v>
       </c>
       <c r="C51" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>jitesh sharma</t>
+          <t>jasprit bumrah</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>52</v>
+        <v>5</v>
       </c>
       <c r="C52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>jofra archer</t>
+          <t>jaydev unadkat</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C53" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>jos buttler</t>
+          <t>jitesh sharma</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>201</v>
+        <v>52</v>
       </c>
       <c r="C54" t="n">
         <v>0</v>
@@ -9028,63 +9028,63 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>josh hazlewood</t>
+          <t>jofra archer</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C55" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>kagiso rabada</t>
+          <t>jos buttler</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>23</v>
+        <v>206</v>
       </c>
       <c r="C56" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>kartik sharma</t>
+          <t>josh hazlewood</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="C57" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>kartik tyagi</t>
+          <t>kagiso rabada</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="C58" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>karun nair</t>
+          <t>kartik sharma</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="C59" t="n">
         <v>0</v>
@@ -9093,50 +9093,50 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>khaleel ahmed</t>
+          <t>kartik tyagi</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C60" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>krunal pandya</t>
+          <t>karun nair</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C61" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>kuldeep yadav</t>
+          <t>khaleel ahmed</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C62" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>kumar kushagra</t>
+          <t>krish bhagat</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="C63" t="n">
         <v>0</v>
@@ -9145,37 +9145,37 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>lhuan dre pretorius</t>
+          <t>krunal pandya</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="C64" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>liam livingstone</t>
+          <t>kuldeep yadav</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C65" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>lokesh rahul</t>
+          <t>kumar kushagra</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>168</v>
+        <v>18</v>
       </c>
       <c r="C66" t="n">
         <v>0</v>
@@ -9184,89 +9184,89 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>lungi ngidi</t>
+          <t>lhuan dre pretorius</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C67" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>manimaran siddharth</t>
+          <t>liam livingstone</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C68" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>marco jansen</t>
+          <t>lokesh rahul</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>10</v>
+        <v>168</v>
       </c>
       <c r="C69" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>marcus stoinis</t>
+          <t>lungi ngidi</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>48</v>
+        <v>3</v>
       </c>
       <c r="C70" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>matt henry</t>
+          <t>manimaran siddharth</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C71" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>matt short</t>
+          <t>marco jansen</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="C72" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>mayank markande</t>
+          <t>marcus stoinis</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
@@ -9275,24 +9275,24 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>mayank rawat</t>
+          <t>matt henry</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C74" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>mitchell marsh</t>
+          <t>matt short</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>155</v>
+        <v>36</v>
       </c>
       <c r="C75" t="n">
         <v>0</v>
@@ -9301,128 +9301,128 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>mitchell santner</t>
+          <t>mayank markande</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="C76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>mohammed shami</t>
+          <t>mayank rawat</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C77" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>mohammed siraj</t>
+          <t>mitchell marsh</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="C78" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>mohsin khan</t>
+          <t>mitchell santner</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="C79" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>mukesh choudhary</t>
+          <t>mohammed shami</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="C80" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>mukesh kumar</t>
+          <t>mohammed siraj</t>
         </is>
       </c>
       <c r="B81" t="n">
         <v>0</v>
       </c>
       <c r="C81" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>mukul choudhary</t>
+          <t>mohsin khan</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>148</v>
+        <v>0</v>
       </c>
       <c r="C82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>naman dhir</t>
+          <t>mukesh choudhary</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="C83" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>nandre burger</t>
+          <t>mukesh kumar</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C84" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>navdeep saini</t>
+          <t>mukul choudhary</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
@@ -9431,11 +9431,11 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>nehal wadhera</t>
+          <t>naman dhir</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>40</v>
+        <v>154</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
@@ -9444,37 +9444,37 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>nicholas pooran</t>
+          <t>nandre burger</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="C87" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>nitish kumar reddy</t>
+          <t>navdeep saini</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="C88" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>nitish rana</t>
+          <t>nehal wadhera</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
@@ -9483,37 +9483,37 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>noor ahmad</t>
+          <t>nicholas pooran</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>10</v>
+        <v>51</v>
       </c>
       <c r="C90" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>pathum nissanka</t>
+          <t>nitish kumar reddy</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="C91" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>philip salt</t>
+          <t>nitish rana</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>202</v>
+        <v>20</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
@@ -9522,37 +9522,37 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>prabhsimran singh</t>
+          <t>noor ahmad</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>211</v>
+        <v>10</v>
       </c>
       <c r="C93" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>praful hinge</t>
+          <t>pathum nissanka</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="C94" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>prashant veer</t>
+          <t>philip salt</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>49</v>
+        <v>202</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
@@ -9561,37 +9561,37 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>prasidh krishna</t>
+          <t>prabhsimran singh</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0</v>
+        <v>211</v>
       </c>
       <c r="C96" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>prince yadav</t>
+          <t>praful hinge</t>
         </is>
       </c>
       <c r="B97" t="n">
         <v>0</v>
       </c>
       <c r="C97" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>priyansh arya</t>
+          <t>prashant veer</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>211</v>
+        <v>49</v>
       </c>
       <c r="C98" t="n">
         <v>0</v>
@@ -9600,37 +9600,37 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>quinton de kock</t>
+          <t>prasidh krishna</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="C99" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>rahul chahar</t>
+          <t>prince yadav</t>
         </is>
       </c>
       <c r="B100" t="n">
         <v>0</v>
       </c>
       <c r="C100" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>rahul tewatia</t>
+          <t>priyansh arya</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>41</v>
+        <v>211</v>
       </c>
       <c r="C101" t="n">
         <v>0</v>
@@ -9639,11 +9639,11 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>rajat patidar</t>
+          <t>quinton de kock</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>230</v>
+        <v>125</v>
       </c>
       <c r="C102" t="n">
         <v>0</v>
@@ -9652,115 +9652,115 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>ramandeep singh</t>
+          <t>rahul chahar</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="C103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>rashid khan</t>
+          <t>rahul tewatia</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C104" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>rasikh salam</t>
+          <t>rajat patidar</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="C105" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ravi bishnoi</t>
+          <t>ramandeep singh</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="C106" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ravindra jadeja</t>
+          <t>rashid khan</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>85</v>
+        <v>28</v>
       </c>
       <c r="C107" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>rinku singh</t>
+          <t>rasikh salam</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="C108" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>rishabh pant</t>
+          <t>ravi bishnoi</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>147</v>
+        <v>0</v>
       </c>
       <c r="C109" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>riyan parag</t>
+          <t>ravindra jadeja</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="C110" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>rohit sharma</t>
+          <t>rinku singh</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="C111" t="n">
         <v>0</v>
@@ -9769,37 +9769,37 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>romario shepherd</t>
+          <t>rishabh pant</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>39</v>
+        <v>147</v>
       </c>
       <c r="C112" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>rovman powell</t>
+          <t>riyan parag</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>120</v>
+        <v>61</v>
       </c>
       <c r="C113" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ruturaj gaikwad</t>
+          <t>rohit sharma</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>82</v>
+        <v>137</v>
       </c>
       <c r="C114" t="n">
         <v>0</v>
@@ -9808,37 +9808,37 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ryan rickelton</t>
+          <t>romario shepherd</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>137</v>
+        <v>39</v>
       </c>
       <c r="C115" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>sakib hussain</t>
+          <t>rovman powell</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="C116" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>salil arora</t>
+          <t>ruturaj gaikwad</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>55</v>
+        <v>82</v>
       </c>
       <c r="C117" t="n">
         <v>0</v>
@@ -9847,11 +9847,11 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>sameer rizvi</t>
+          <t>ryan rickelton</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>168</v>
+        <v>137</v>
       </c>
       <c r="C118" t="n">
         <v>0</v>
@@ -9860,7 +9860,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>sandeep sharma</t>
+          <t>sakib hussain</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -9873,11 +9873,11 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>sanju samson</t>
+          <t>salil arora</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>192</v>
+        <v>55</v>
       </c>
       <c r="C120" t="n">
         <v>0</v>
@@ -9886,11 +9886,11 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>sarfaraz khan</t>
+          <t>sameer rizvi</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>147</v>
+        <v>168</v>
       </c>
       <c r="C121" t="n">
         <v>0</v>
@@ -9899,24 +9899,24 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>shahbaz ahmed</t>
+          <t>sandeep sharma</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="C122" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>shahrukh khan</t>
+          <t>sanju samson</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>18</v>
+        <v>192</v>
       </c>
       <c r="C123" t="n">
         <v>0</v>
@@ -9925,37 +9925,37 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>shardul thakur</t>
+          <t>sarfaraz khan</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>8</v>
+        <v>147</v>
       </c>
       <c r="C124" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>shashank singh</t>
+          <t>shahbaz ahmed</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="C125" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>sherfane rutherford</t>
+          <t>shahrukh khan</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>102</v>
+        <v>35</v>
       </c>
       <c r="C126" t="n">
         <v>0</v>
@@ -9964,50 +9964,50 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>shimron hetmyer</t>
+          <t>shardul thakur</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="C127" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>shivam dube</t>
+          <t>shashank singh</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>123</v>
+        <v>51</v>
       </c>
       <c r="C128" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>shivang kumar</t>
+          <t>sherfane rutherford</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>21</v>
+        <v>103</v>
       </c>
       <c r="C129" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>shreyas iyer</t>
+          <t>shimron hetmyer</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>208</v>
+        <v>39</v>
       </c>
       <c r="C130" t="n">
         <v>0</v>
@@ -10016,37 +10016,37 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>shubman gill</t>
+          <t>shivam dube</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>251</v>
+        <v>123</v>
       </c>
       <c r="C131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>sunil narine</t>
+          <t>shivang kumar</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="C132" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>suryakumar yadav</t>
+          <t>shreyas iyer</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>106</v>
+        <v>208</v>
       </c>
       <c r="C133" t="n">
         <v>0</v>
@@ -10055,37 +10055,37 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>suyash sharma</t>
+          <t>shubman gill</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0</v>
+        <v>265</v>
       </c>
       <c r="C134" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>t natarajan</t>
+          <t>sunil narine</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="C135" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>tilak varma</t>
+          <t>suryakumar yadav</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>43</v>
+        <v>121</v>
       </c>
       <c r="C136" t="n">
         <v>0</v>
@@ -10094,37 +10094,37 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>tim david</t>
+          <t>suyash sharma</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>173</v>
+        <v>0</v>
       </c>
       <c r="C137" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>tim seifert</t>
+          <t>t natarajan</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="C138" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>travis head</t>
+          <t>tilak varma</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C139" t="n">
         <v>0</v>
@@ -10133,24 +10133,24 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>trent boult</t>
+          <t>tim david</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>1</v>
+        <v>173</v>
       </c>
       <c r="C140" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>tristan stubbs</t>
+          <t>tim seifert</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>169</v>
+        <v>19</v>
       </c>
       <c r="C141" t="n">
         <v>0</v>
@@ -10159,37 +10159,37 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>tushar deshpande</t>
+          <t>travis head</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>25</v>
+        <v>143</v>
       </c>
       <c r="C142" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>vaibhav arora</t>
+          <t>trent boult</t>
         </is>
       </c>
       <c r="B143" t="n">
         <v>1</v>
       </c>
       <c r="C143" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>vaibhav suryavanshi</t>
+          <t>tristan stubbs</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>246</v>
+        <v>169</v>
       </c>
       <c r="C144" t="n">
         <v>0</v>
@@ -10198,63 +10198,63 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>varun chakravarthy</t>
+          <t>tushar deshpande</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="C145" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>venkatesh iyer</t>
+          <t>vaibhav arora</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C146" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>vijaykumar vyshak</t>
+          <t>vaibhav suryavanshi</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0</v>
+        <v>246</v>
       </c>
       <c r="C147" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>vipraj nigam</t>
+          <t>varun chakravarthy</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C148" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>virat kohli</t>
+          <t>venkatesh iyer</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>247</v>
+        <v>29</v>
       </c>
       <c r="C149" t="n">
         <v>0</v>
@@ -10263,65 +10263,104 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>washington sundar</t>
+          <t>vijaykumar vyshak</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="C150" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>xavier bartlett</t>
+          <t>vipraj nigam</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C151" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>yash raj punja</t>
+          <t>virat kohli</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0</v>
+        <v>247</v>
       </c>
       <c r="C152" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>yashasvi jaiswal</t>
+          <t>washington sundar</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>223</v>
+        <v>137</v>
       </c>
       <c r="C153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
+          <t>xavier bartlett</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>11</v>
+      </c>
+      <c r="C154" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>yash raj punja</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>0</v>
+      </c>
+      <c r="C155" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>yashasvi jaiswal</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>223</v>
+      </c>
+      <c r="C156" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
           <t>yuzvendra chahal</t>
         </is>
       </c>
-      <c r="B154" t="n">
-        <v>0</v>
-      </c>
-      <c r="C154" t="n">
+      <c r="B157" t="n">
+        <v>0</v>
+      </c>
+      <c r="C157" t="n">
         <v>4</v>
       </c>
     </row>
@@ -11318,7 +11357,7 @@
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>shivang kumar</t>
+          <t>ashwani kumar</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">

--- a/IPL_Fantasy_Points.xlsx
+++ b/IPL_Fantasy_Points.xlsx
@@ -604,19 +604,19 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>143</v>
+        <v>180</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>143</v>
+        <v>180</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>143</v>
+        <v>180</v>
       </c>
     </row>
     <row r="5">
@@ -1206,19 +1206,19 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>213</v>
+        <v>238</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>213</v>
+        <v>238</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>213</v>
+        <v>238</v>
       </c>
     </row>
     <row r="19">
@@ -1897,16 +1897,16 @@
         <v>13</v>
       </c>
       <c r="H34" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="K34" t="n">
-        <v>100</v>
+        <v>160</v>
       </c>
     </row>
     <row r="35">
@@ -2023,19 +2023,19 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>283</v>
+        <v>320</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>283</v>
+        <v>320</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>283</v>
+        <v>320</v>
       </c>
     </row>
     <row r="38">
@@ -3786,19 +3786,19 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>169</v>
+        <v>196</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>169</v>
+        <v>196</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>169</v>
+        <v>196</v>
       </c>
     </row>
     <row r="79">
@@ -4345,19 +4345,19 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>168</v>
+        <v>205</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
       </c>
       <c r="I91" t="n">
-        <v>168</v>
+        <v>205</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>168</v>
+        <v>205</v>
       </c>
     </row>
     <row r="92">
@@ -5291,19 +5291,19 @@
         </is>
       </c>
       <c r="G113" t="n">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="H113" t="n">
         <v>0</v>
       </c>
       <c r="I113" t="n">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
       </c>
       <c r="K113" t="n">
-        <v>128</v>
+        <v>136</v>
       </c>
     </row>
     <row r="114">
@@ -6022,19 +6022,19 @@
         </is>
       </c>
       <c r="G130" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
       </c>
       <c r="I130" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
       </c>
       <c r="K130" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="131">
@@ -6151,19 +6151,19 @@
         </is>
       </c>
       <c r="G133" t="n">
-        <v>168</v>
+        <v>209</v>
       </c>
       <c r="H133" t="n">
         <v>0</v>
       </c>
       <c r="I133" t="n">
-        <v>168</v>
+        <v>209</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
       </c>
       <c r="K133" t="n">
-        <v>168</v>
+        <v>209</v>
       </c>
     </row>
     <row r="134">
@@ -6323,19 +6323,19 @@
         </is>
       </c>
       <c r="G137" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H137" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I137" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J137" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="K137" t="n">
-        <v>129</v>
+        <v>151</v>
       </c>
     </row>
     <row r="138">
@@ -6753,19 +6753,19 @@
         </is>
       </c>
       <c r="G147" t="n">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="H147" t="n">
         <v>0</v>
       </c>
       <c r="I147" t="n">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
       </c>
       <c r="K147" t="n">
-        <v>20</v>
+        <v>77</v>
       </c>
     </row>
     <row r="148">
@@ -7398,19 +7398,19 @@
         </is>
       </c>
       <c r="G162" t="n">
-        <v>188</v>
+        <v>323</v>
       </c>
       <c r="H162" t="n">
         <v>0</v>
       </c>
       <c r="I162" t="n">
-        <v>188</v>
+        <v>323</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
       </c>
       <c r="K162" t="n">
-        <v>188</v>
+        <v>323</v>
       </c>
     </row>
     <row r="163">
@@ -8086,7 +8086,7 @@
         </is>
       </c>
       <c r="G178" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H178" t="n">
         <v>5</v>
@@ -8185,7 +8185,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2053</v>
+        <v>2080</v>
       </c>
     </row>
     <row r="3">
@@ -8198,7 +8198,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1818</v>
+        <v>1903</v>
       </c>
     </row>
     <row r="4">
@@ -8211,7 +8211,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1657</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="5">
@@ -8237,7 +8237,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1511</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="7">
@@ -8250,7 +8250,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1409</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="8">
@@ -8263,7 +8263,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1397</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="9">
@@ -8276,7 +8276,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1366</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="10">
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1273</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="11">
@@ -8302,7 +8302,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1056</v>
+        <v>1191</v>
       </c>
     </row>
   </sheetData>
@@ -8316,7 +8316,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C157"/>
+  <dimension ref="A1:C158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8369,7 +8369,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>188</v>
+        <v>323</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -8525,7 +8525,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -8577,10 +8577,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -8807,50 +8807,50 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>donavon ferreira</t>
+          <t>dilshan madushanka</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>eshan malinga</t>
+          <t>donavon ferreira</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="C39" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>finn allen</t>
+          <t>eshan malinga</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>george linde</t>
+          <t>finn allen</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>23</v>
+        <v>81</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
@@ -8859,11 +8859,11 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>glenn phillips</t>
+          <t>george linde</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>67</v>
+        <v>23</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
@@ -8872,63 +8872,63 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>gurjapneet singh</t>
+          <t>glenn phillips</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>hardik pandya</t>
+          <t>gurjapneet singh</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>harsh dubey</t>
+          <t>hardik pandya</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>13</v>
+        <v>96</v>
       </c>
       <c r="C45" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>harshal patel</t>
+          <t>harsh dubey</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>heinrich klaasen</t>
+          <t>harshal patel</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>283</v>
+        <v>4</v>
       </c>
       <c r="C47" t="n">
         <v>0</v>
@@ -8937,11 +8937,11 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>himmat singh</t>
+          <t>heinrich klaasen</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1</v>
+        <v>320</v>
       </c>
       <c r="C48" t="n">
         <v>0</v>
@@ -8950,11 +8950,11 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ishan kishan</t>
+          <t>himmat singh</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>213</v>
+        <v>1</v>
       </c>
       <c r="C49" t="n">
         <v>0</v>
@@ -8963,232 +8963,232 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>jacob duffy</t>
+          <t>ishan kishan</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0</v>
+        <v>238</v>
       </c>
       <c r="C50" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>jamie overton</t>
+          <t>jacob duffy</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>jasprit bumrah</t>
+          <t>jamie overton</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>5</v>
+        <v>103</v>
       </c>
       <c r="C52" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>jaydev unadkat</t>
+          <t>jasprit bumrah</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C53" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>jitesh sharma</t>
+          <t>jaydev unadkat</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="C54" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>jofra archer</t>
+          <t>jitesh sharma</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>11</v>
+        <v>52</v>
       </c>
       <c r="C55" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>jos buttler</t>
+          <t>jofra archer</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>206</v>
+        <v>11</v>
       </c>
       <c r="C56" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>josh hazlewood</t>
+          <t>jos buttler</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0</v>
+        <v>206</v>
       </c>
       <c r="C57" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>kagiso rabada</t>
+          <t>josh hazlewood</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="C58" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>kartik sharma</t>
+          <t>kagiso rabada</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C59" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>kartik tyagi</t>
+          <t>kartik sharma</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="C60" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>karun nair</t>
+          <t>kartik tyagi</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C61" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>khaleel ahmed</t>
+          <t>karun nair</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C62" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>krish bhagat</t>
+          <t>khaleel ahmed</t>
         </is>
       </c>
       <c r="B63" t="n">
         <v>0</v>
       </c>
       <c r="C63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>krunal pandya</t>
+          <t>krish bhagat</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C64" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>kuldeep yadav</t>
+          <t>krunal pandya</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C65" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>kumar kushagra</t>
+          <t>kuldeep yadav</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C66" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>lhuan dre pretorius</t>
+          <t>kumar kushagra</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C67" t="n">
         <v>0</v>
@@ -9197,11 +9197,11 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>liam livingstone</t>
+          <t>lhuan dre pretorius</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="C68" t="n">
         <v>0</v>
@@ -9210,11 +9210,11 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>lokesh rahul</t>
+          <t>liam livingstone</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>168</v>
+        <v>15</v>
       </c>
       <c r="C69" t="n">
         <v>0</v>
@@ -9223,89 +9223,89 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>lungi ngidi</t>
+          <t>lokesh rahul</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>3</v>
+        <v>205</v>
       </c>
       <c r="C70" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>manimaran siddharth</t>
+          <t>lungi ngidi</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C71" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>marco jansen</t>
+          <t>manimaran siddharth</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C72" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>marcus stoinis</t>
+          <t>marco jansen</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="C73" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>matt henry</t>
+          <t>marcus stoinis</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="C74" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>matt short</t>
+          <t>matt henry</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="C75" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>mayank markande</t>
+          <t>matt short</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="C76" t="n">
         <v>0</v>
@@ -9314,7 +9314,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>mayank rawat</t>
+          <t>mayank markande</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -9327,11 +9327,11 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>mitchell marsh</t>
+          <t>mayank rawat</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>155</v>
+        <v>0</v>
       </c>
       <c r="C78" t="n">
         <v>0</v>
@@ -9340,59 +9340,59 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>mitchell santner</t>
+          <t>mitchell marsh</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>26</v>
+        <v>155</v>
       </c>
       <c r="C79" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>mohammed shami</t>
+          <t>mitchell santner</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="C80" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>mohammed siraj</t>
+          <t>mohammed shami</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="C81" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>mohsin khan</t>
+          <t>mohammed siraj</t>
         </is>
       </c>
       <c r="B82" t="n">
         <v>0</v>
       </c>
       <c r="C82" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>mukesh choudhary</t>
+          <t>mohsin khan</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -9405,37 +9405,37 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>mukesh kumar</t>
+          <t>mukesh choudhary</t>
         </is>
       </c>
       <c r="B84" t="n">
         <v>0</v>
       </c>
       <c r="C84" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>mukul choudhary</t>
+          <t>mukesh kumar</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>148</v>
+        <v>0</v>
       </c>
       <c r="C85" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>naman dhir</t>
+          <t>mukul choudhary</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
@@ -9444,37 +9444,37 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>nandre burger</t>
+          <t>naman dhir</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>3</v>
+        <v>154</v>
       </c>
       <c r="C87" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>navdeep saini</t>
+          <t>nandre burger</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C88" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>nehal wadhera</t>
+          <t>navdeep saini</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
@@ -9483,11 +9483,11 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>nicholas pooran</t>
+          <t>nehal wadhera</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
@@ -9496,63 +9496,63 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>nitish kumar reddy</t>
+          <t>nicholas pooran</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>136</v>
+        <v>51</v>
       </c>
       <c r="C91" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>nitish rana</t>
+          <t>nitish kumar reddy</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>20</v>
+        <v>136</v>
       </c>
       <c r="C92" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>noor ahmad</t>
+          <t>nitish rana</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>10</v>
+        <v>77</v>
       </c>
       <c r="C93" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>pathum nissanka</t>
+          <t>noor ahmad</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>128</v>
+        <v>10</v>
       </c>
       <c r="C94" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>philip salt</t>
+          <t>pathum nissanka</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>202</v>
+        <v>136</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
@@ -9561,11 +9561,11 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>prabhsimran singh</t>
+          <t>philip salt</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="C96" t="n">
         <v>0</v>
@@ -9574,76 +9574,76 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>praful hinge</t>
+          <t>prabhsimran singh</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0</v>
+        <v>211</v>
       </c>
       <c r="C97" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>prashant veer</t>
+          <t>praful hinge</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="C98" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>prasidh krishna</t>
+          <t>prashant veer</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="C99" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>prince yadav</t>
+          <t>prasidh krishna</t>
         </is>
       </c>
       <c r="B100" t="n">
         <v>0</v>
       </c>
       <c r="C100" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>priyansh arya</t>
+          <t>prince yadav</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>211</v>
+        <v>0</v>
       </c>
       <c r="C101" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>quinton de kock</t>
+          <t>priyansh arya</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>125</v>
+        <v>211</v>
       </c>
       <c r="C102" t="n">
         <v>0</v>
@@ -9652,11 +9652,11 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>rahul chahar</t>
+          <t>quinton de kock</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="C103" t="n">
         <v>0</v>
@@ -9665,11 +9665,11 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>rahul tewatia</t>
+          <t>rahul chahar</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="C104" t="n">
         <v>0</v>
@@ -9678,11 +9678,11 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>rajat patidar</t>
+          <t>rahul tewatia</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>230</v>
+        <v>49</v>
       </c>
       <c r="C105" t="n">
         <v>0</v>
@@ -9691,89 +9691,89 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ramandeep singh</t>
+          <t>rajat patidar</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>76</v>
+        <v>230</v>
       </c>
       <c r="C106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>rashid khan</t>
+          <t>ramandeep singh</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>28</v>
+        <v>76</v>
       </c>
       <c r="C107" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>rasikh salam</t>
+          <t>rashid khan</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="C108" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>ravi bishnoi</t>
+          <t>rasikh salam</t>
         </is>
       </c>
       <c r="B109" t="n">
         <v>0</v>
       </c>
       <c r="C109" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ravindra jadeja</t>
+          <t>ravi bishnoi</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="C110" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>rinku singh</t>
+          <t>ravindra jadeja</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>132</v>
+        <v>85</v>
       </c>
       <c r="C111" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>rishabh pant</t>
+          <t>rinku singh</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="C112" t="n">
         <v>0</v>
@@ -9782,63 +9782,63 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>riyan parag</t>
+          <t>rishabh pant</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>61</v>
+        <v>147</v>
       </c>
       <c r="C113" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>rohit sharma</t>
+          <t>riyan parag</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>137</v>
+        <v>61</v>
       </c>
       <c r="C114" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>romario shepherd</t>
+          <t>rohit sharma</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>39</v>
+        <v>137</v>
       </c>
       <c r="C115" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>rovman powell</t>
+          <t>romario shepherd</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>120</v>
+        <v>39</v>
       </c>
       <c r="C116" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ruturaj gaikwad</t>
+          <t>rovman powell</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="C117" t="n">
         <v>0</v>
@@ -9847,11 +9847,11 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ryan rickelton</t>
+          <t>ruturaj gaikwad</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>137</v>
+        <v>82</v>
       </c>
       <c r="C118" t="n">
         <v>0</v>
@@ -9860,37 +9860,37 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>sakib hussain</t>
+          <t>ryan rickelton</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0</v>
+        <v>137</v>
       </c>
       <c r="C119" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>salil arora</t>
+          <t>sakib hussain</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="C120" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>sameer rizvi</t>
+          <t>salil arora</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>168</v>
+        <v>55</v>
       </c>
       <c r="C121" t="n">
         <v>0</v>
@@ -9899,37 +9899,37 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>sandeep sharma</t>
+          <t>sameer rizvi</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0</v>
+        <v>209</v>
       </c>
       <c r="C122" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>sanju samson</t>
+          <t>sandeep sharma</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>192</v>
+        <v>0</v>
       </c>
       <c r="C123" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>sarfaraz khan</t>
+          <t>sanju samson</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>147</v>
+        <v>192</v>
       </c>
       <c r="C124" t="n">
         <v>0</v>
@@ -9938,11 +9938,11 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>shahbaz ahmed</t>
+          <t>sarfaraz khan</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>15</v>
+        <v>147</v>
       </c>
       <c r="C125" t="n">
         <v>0</v>
@@ -9951,11 +9951,11 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>shahrukh khan</t>
+          <t>shahbaz ahmed</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="C126" t="n">
         <v>0</v>
@@ -9964,50 +9964,50 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>shardul thakur</t>
+          <t>shahrukh khan</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="C127" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>shashank singh</t>
+          <t>shardul thakur</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="C128" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>sherfane rutherford</t>
+          <t>shashank singh</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>103</v>
+        <v>51</v>
       </c>
       <c r="C129" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>shimron hetmyer</t>
+          <t>sherfane rutherford</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>39</v>
+        <v>103</v>
       </c>
       <c r="C130" t="n">
         <v>0</v>
@@ -10016,50 +10016,50 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>shivam dube</t>
+          <t>shimron hetmyer</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>123</v>
+        <v>39</v>
       </c>
       <c r="C131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>shivang kumar</t>
+          <t>shivam dube</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>21</v>
+        <v>123</v>
       </c>
       <c r="C132" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>shreyas iyer</t>
+          <t>shivang kumar</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>208</v>
+        <v>21</v>
       </c>
       <c r="C133" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>shubman gill</t>
+          <t>shreyas iyer</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>265</v>
+        <v>208</v>
       </c>
       <c r="C134" t="n">
         <v>0</v>
@@ -10068,50 +10068,50 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>sunil narine</t>
+          <t>shubman gill</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>36</v>
+        <v>265</v>
       </c>
       <c r="C135" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>suryakumar yadav</t>
+          <t>sunil narine</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>121</v>
+        <v>36</v>
       </c>
       <c r="C136" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>suyash sharma</t>
+          <t>suryakumar yadav</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="C137" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>t natarajan</t>
+          <t>suyash sharma</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C138" t="n">
         <v>4</v>
@@ -10120,24 +10120,24 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>tilak varma</t>
+          <t>t natarajan</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>144</v>
+        <v>1</v>
       </c>
       <c r="C139" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>tim david</t>
+          <t>tilak varma</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>173</v>
+        <v>144</v>
       </c>
       <c r="C140" t="n">
         <v>0</v>
@@ -10146,11 +10146,11 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>tim seifert</t>
+          <t>tim david</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>19</v>
+        <v>173</v>
       </c>
       <c r="C141" t="n">
         <v>0</v>
@@ -10159,11 +10159,11 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>travis head</t>
+          <t>tim seifert</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>143</v>
+        <v>19</v>
       </c>
       <c r="C142" t="n">
         <v>0</v>
@@ -10172,195 +10172,208 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>trent boult</t>
+          <t>travis head</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>1</v>
+        <v>180</v>
       </c>
       <c r="C143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>tristan stubbs</t>
+          <t>trent boult</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>169</v>
+        <v>1</v>
       </c>
       <c r="C144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>tushar deshpande</t>
+          <t>tristan stubbs</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>25</v>
+        <v>196</v>
       </c>
       <c r="C145" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>vaibhav arora</t>
+          <t>tushar deshpande</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C146" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>vaibhav suryavanshi</t>
+          <t>vaibhav arora</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>246</v>
+        <v>1</v>
       </c>
       <c r="C147" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>varun chakravarthy</t>
+          <t>vaibhav suryavanshi</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0</v>
+        <v>246</v>
       </c>
       <c r="C148" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>venkatesh iyer</t>
+          <t>varun chakravarthy</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="C149" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>vijaykumar vyshak</t>
+          <t>venkatesh iyer</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="C150" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>vipraj nigam</t>
+          <t>vijaykumar vyshak</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C151" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>virat kohli</t>
+          <t>vipraj nigam</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>247</v>
+        <v>12</v>
       </c>
       <c r="C152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>washington sundar</t>
+          <t>virat kohli</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>137</v>
+        <v>247</v>
       </c>
       <c r="C153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>xavier bartlett</t>
+          <t>washington sundar</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>11</v>
+        <v>137</v>
       </c>
       <c r="C154" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>yash raj punja</t>
+          <t>xavier bartlett</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C155" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>yashasvi jaiswal</t>
+          <t>yash raj punja</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>223</v>
+        <v>0</v>
       </c>
       <c r="C156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
+          <t>yashasvi jaiswal</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>223</v>
+      </c>
+      <c r="C157" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
           <t>yuzvendra chahal</t>
         </is>
       </c>
-      <c r="B157" t="n">
-        <v>0</v>
-      </c>
-      <c r="C157" t="n">
+      <c r="B158" t="n">
+        <v>0</v>
+      </c>
+      <c r="C158" t="n">
         <v>4</v>
       </c>
     </row>

--- a/IPL_Fantasy_Points.xlsx
+++ b/IPL_Fantasy_Points.xlsx
@@ -1037,16 +1037,16 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="K14" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15">
@@ -1335,19 +1335,19 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>246</v>
+        <v>254</v>
       </c>
     </row>
     <row r="22">
@@ -1725,16 +1725,16 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="K30" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
     </row>
     <row r="31">
@@ -2281,19 +2281,19 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>85</v>
+        <v>128</v>
       </c>
       <c r="H43" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I43" t="n">
-        <v>85</v>
+        <v>128</v>
       </c>
       <c r="J43" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="K43" t="n">
-        <v>185</v>
+        <v>248</v>
       </c>
     </row>
     <row r="44">
@@ -4302,19 +4302,19 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>223</v>
+        <v>245</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>223</v>
+        <v>245</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>223</v>
+        <v>245</v>
       </c>
     </row>
     <row r="91">
@@ -4594,7 +4594,7 @@
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>mayank rawat</t>
+          <t>mayank yadav</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -4732,19 +4732,19 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="H100" t="n">
         <v>2</v>
       </c>
       <c r="I100" t="n">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="J100" t="n">
         <v>40</v>
       </c>
       <c r="K100" t="n">
-        <v>101</v>
+        <v>121</v>
       </c>
     </row>
     <row r="101">
@@ -5036,16 +5036,16 @@
         <v>3</v>
       </c>
       <c r="H107" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I107" t="n">
         <v>0</v>
       </c>
       <c r="J107" t="n">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="K107" t="n">
-        <v>120</v>
+        <v>160</v>
       </c>
     </row>
     <row r="108">
@@ -5119,19 +5119,19 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>155</v>
+        <v>210</v>
       </c>
       <c r="H109" t="n">
         <v>0</v>
       </c>
       <c r="I109" t="n">
-        <v>155</v>
+        <v>210</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
       </c>
       <c r="K109" t="n">
-        <v>155</v>
+        <v>210</v>
       </c>
     </row>
     <row r="110">
@@ -5205,19 +5205,19 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
       </c>
       <c r="I111" t="n">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
       </c>
       <c r="K111" t="n">
-        <v>39</v>
+        <v>61</v>
       </c>
     </row>
     <row r="112">
@@ -5420,19 +5420,19 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="H116" t="n">
         <v>0</v>
       </c>
       <c r="I116" t="n">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
       </c>
       <c r="K116" t="n">
-        <v>77</v>
+        <v>97</v>
       </c>
     </row>
     <row r="117">
@@ -6538,19 +6538,19 @@
         </is>
       </c>
       <c r="G142" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H142" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I142" t="n">
         <v>0</v>
       </c>
       <c r="J142" t="n">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="K142" t="n">
-        <v>100</v>
+        <v>140</v>
       </c>
     </row>
     <row r="143">
@@ -6710,19 +6710,19 @@
         </is>
       </c>
       <c r="G146" t="n">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="H146" t="n">
         <v>0</v>
       </c>
       <c r="I146" t="n">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
       </c>
       <c r="K146" t="n">
-        <v>51</v>
+        <v>73</v>
       </c>
     </row>
     <row r="147">
@@ -6882,19 +6882,19 @@
         </is>
       </c>
       <c r="G150" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
       </c>
       <c r="I150" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
       </c>
       <c r="K150" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="151">
@@ -7057,16 +7057,16 @@
         <v>11</v>
       </c>
       <c r="H154" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I154" t="n">
         <v>11</v>
       </c>
       <c r="J154" t="n">
-        <v>160</v>
+        <v>220</v>
       </c>
       <c r="K154" t="n">
-        <v>171</v>
+        <v>231</v>
       </c>
     </row>
     <row r="155">
@@ -7945,19 +7945,19 @@
           <t>BOWL</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr"/>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>mayank rawat</t>
-        </is>
-      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>mayank yadav</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="G175" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H175" t="n">
         <v>0</v>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="G177" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H177" t="n">
         <v>3</v>
@@ -8198,7 +8198,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1903</v>
+        <v>1931</v>
       </c>
     </row>
     <row r="4">
@@ -8211,7 +8211,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1665</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="5">
@@ -8220,11 +8220,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BABA11</t>
+          <t>VATSAL11</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1565</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="6">
@@ -8233,11 +8233,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>VATSAL11</t>
+          <t>BABA11</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1548</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="7">
@@ -8246,11 +8246,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1486</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="8">
@@ -8259,11 +8259,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1454</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="9">
@@ -8276,7 +8276,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1403</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="10">
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1310</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="11">
@@ -8316,7 +8316,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C158"/>
+  <dimension ref="A1:C160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8658,7 +8658,7 @@
         <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27">
@@ -8798,7 +8798,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C37" t="n">
         <v>3</v>
@@ -8824,7 +8824,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="C39" t="n">
         <v>0</v>
@@ -8954,7 +8954,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C49" t="n">
         <v>0</v>
@@ -9048,7 +9048,7 @@
         <v>11</v>
       </c>
       <c r="C56" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="57">
@@ -9340,11 +9340,11 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>mitchell marsh</t>
+          <t>mayank yadav</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>155</v>
+        <v>5</v>
       </c>
       <c r="C79" t="n">
         <v>0</v>
@@ -9353,102 +9353,102 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>mitchell santner</t>
+          <t>mitchell marsh</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>26</v>
+        <v>210</v>
       </c>
       <c r="C80" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>mohammed shami</t>
+          <t>mitchell santner</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="C81" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>mohammed siraj</t>
+          <t>mohammed shami</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C82" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>mohsin khan</t>
+          <t>mohammed siraj</t>
         </is>
       </c>
       <c r="B83" t="n">
         <v>0</v>
       </c>
       <c r="C83" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>mukesh choudhary</t>
+          <t>mohsin khan</t>
         </is>
       </c>
       <c r="B84" t="n">
         <v>0</v>
       </c>
       <c r="C84" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>mukesh kumar</t>
+          <t>mukesh choudhary</t>
         </is>
       </c>
       <c r="B85" t="n">
         <v>0</v>
       </c>
       <c r="C85" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>mukul choudhary</t>
+          <t>mukesh kumar</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>148</v>
+        <v>0</v>
       </c>
       <c r="C86" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>naman dhir</t>
+          <t>mukul choudhary</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
@@ -9457,37 +9457,37 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>nandre burger</t>
+          <t>naman dhir</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>3</v>
+        <v>154</v>
       </c>
       <c r="C88" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>navdeep saini</t>
+          <t>nandre burger</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C89" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>nehal wadhera</t>
+          <t>navdeep saini</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
@@ -9496,11 +9496,11 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>nicholas pooran</t>
+          <t>nehal wadhera</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
@@ -9509,63 +9509,63 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>nitish kumar reddy</t>
+          <t>nicholas pooran</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>136</v>
+        <v>73</v>
       </c>
       <c r="C92" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>nitish rana</t>
+          <t>nitish kumar reddy</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>77</v>
+        <v>136</v>
       </c>
       <c r="C93" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>noor ahmad</t>
+          <t>nitish rana</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>10</v>
+        <v>77</v>
       </c>
       <c r="C94" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>pathum nissanka</t>
+          <t>noor ahmad</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>136</v>
+        <v>10</v>
       </c>
       <c r="C95" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>philip salt</t>
+          <t>pathum nissanka</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>202</v>
+        <v>136</v>
       </c>
       <c r="C96" t="n">
         <v>0</v>
@@ -9574,11 +9574,11 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>prabhsimran singh</t>
+          <t>philip salt</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="C97" t="n">
         <v>0</v>
@@ -9587,76 +9587,76 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>praful hinge</t>
+          <t>prabhsimran singh</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0</v>
+        <v>211</v>
       </c>
       <c r="C98" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>prashant veer</t>
+          <t>praful hinge</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="C99" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>prasidh krishna</t>
+          <t>prashant veer</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="C100" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>prince yadav</t>
+          <t>prasidh krishna</t>
         </is>
       </c>
       <c r="B101" t="n">
         <v>0</v>
       </c>
       <c r="C101" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>priyansh arya</t>
+          <t>prince yadav</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>211</v>
+        <v>0</v>
       </c>
       <c r="C102" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>quinton de kock</t>
+          <t>priyansh arya</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>125</v>
+        <v>211</v>
       </c>
       <c r="C103" t="n">
         <v>0</v>
@@ -9665,11 +9665,11 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>rahul chahar</t>
+          <t>quinton de kock</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="C104" t="n">
         <v>0</v>
@@ -9678,11 +9678,11 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>rahul tewatia</t>
+          <t>rahul chahar</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="C105" t="n">
         <v>0</v>
@@ -9691,11 +9691,11 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>rajat patidar</t>
+          <t>rahul tewatia</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>230</v>
+        <v>49</v>
       </c>
       <c r="C106" t="n">
         <v>0</v>
@@ -9704,89 +9704,89 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ramandeep singh</t>
+          <t>rajat patidar</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>76</v>
+        <v>230</v>
       </c>
       <c r="C107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>rashid khan</t>
+          <t>ramandeep singh</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>28</v>
+        <v>76</v>
       </c>
       <c r="C108" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>rasikh salam</t>
+          <t>rashid khan</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="C109" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ravi bishnoi</t>
+          <t>rasikh salam</t>
         </is>
       </c>
       <c r="B110" t="n">
         <v>0</v>
       </c>
       <c r="C110" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ravindra jadeja</t>
+          <t>ravi bishnoi</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="C111" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>rinku singh</t>
+          <t>ravindra jadeja</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C112" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>rishabh pant</t>
+          <t>rinku singh</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="C113" t="n">
         <v>0</v>
@@ -9795,63 +9795,63 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>riyan parag</t>
+          <t>rishabh pant</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>61</v>
+        <v>147</v>
       </c>
       <c r="C114" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>rohit sharma</t>
+          <t>riyan parag</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>137</v>
+        <v>81</v>
       </c>
       <c r="C115" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>romario shepherd</t>
+          <t>rohit sharma</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>39</v>
+        <v>137</v>
       </c>
       <c r="C116" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>rovman powell</t>
+          <t>romario shepherd</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>120</v>
+        <v>39</v>
       </c>
       <c r="C117" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ruturaj gaikwad</t>
+          <t>rovman powell</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="C118" t="n">
         <v>0</v>
@@ -9860,11 +9860,11 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ryan rickelton</t>
+          <t>ruturaj gaikwad</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>137</v>
+        <v>82</v>
       </c>
       <c r="C119" t="n">
         <v>0</v>
@@ -9873,37 +9873,37 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>sakib hussain</t>
+          <t>ryan rickelton</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0</v>
+        <v>137</v>
       </c>
       <c r="C120" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>salil arora</t>
+          <t>sakib hussain</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="C121" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>sameer rizvi</t>
+          <t>salil arora</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>209</v>
+        <v>55</v>
       </c>
       <c r="C122" t="n">
         <v>0</v>
@@ -9912,37 +9912,37 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>sandeep sharma</t>
+          <t>sameer rizvi</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0</v>
+        <v>209</v>
       </c>
       <c r="C123" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>sanju samson</t>
+          <t>sandeep sharma</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>192</v>
+        <v>0</v>
       </c>
       <c r="C124" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>sarfaraz khan</t>
+          <t>sanju samson</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>147</v>
+        <v>192</v>
       </c>
       <c r="C125" t="n">
         <v>0</v>
@@ -9951,11 +9951,11 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>shahbaz ahmed</t>
+          <t>sarfaraz khan</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>15</v>
+        <v>147</v>
       </c>
       <c r="C126" t="n">
         <v>0</v>
@@ -9964,11 +9964,11 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>shahrukh khan</t>
+          <t>shahbaz ahmed</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="C127" t="n">
         <v>0</v>
@@ -9977,50 +9977,50 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>shardul thakur</t>
+          <t>shahrukh khan</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="C128" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>shashank singh</t>
+          <t>shardul thakur</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="C129" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>sherfane rutherford</t>
+          <t>shashank singh</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>103</v>
+        <v>51</v>
       </c>
       <c r="C130" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>shimron hetmyer</t>
+          <t>sherfane rutherford</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>39</v>
+        <v>103</v>
       </c>
       <c r="C131" t="n">
         <v>0</v>
@@ -10029,50 +10029,50 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>shivam dube</t>
+          <t>shimron hetmyer</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>123</v>
+        <v>61</v>
       </c>
       <c r="C132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>shivang kumar</t>
+          <t>shivam dube</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>21</v>
+        <v>123</v>
       </c>
       <c r="C133" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>shreyas iyer</t>
+          <t>shivang kumar</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>208</v>
+        <v>21</v>
       </c>
       <c r="C134" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>shubman gill</t>
+          <t>shreyas iyer</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>265</v>
+        <v>208</v>
       </c>
       <c r="C135" t="n">
         <v>0</v>
@@ -10081,24 +10081,24 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>sunil narine</t>
+          <t>shubham badriprasad dubey</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="C136" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>suryakumar yadav</t>
+          <t>shubman gill</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>121</v>
+        <v>265</v>
       </c>
       <c r="C137" t="n">
         <v>0</v>
@@ -10107,63 +10107,63 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>suyash sharma</t>
+          <t>sunil narine</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="C138" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>t natarajan</t>
+          <t>suryakumar yadav</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>1</v>
+        <v>121</v>
       </c>
       <c r="C139" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>tilak varma</t>
+          <t>suyash sharma</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>144</v>
+        <v>0</v>
       </c>
       <c r="C140" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>tim david</t>
+          <t>t natarajan</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>173</v>
+        <v>1</v>
       </c>
       <c r="C141" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>tim seifert</t>
+          <t>tilak varma</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>19</v>
+        <v>144</v>
       </c>
       <c r="C142" t="n">
         <v>0</v>
@@ -10172,11 +10172,11 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>travis head</t>
+          <t>tim david</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="C143" t="n">
         <v>0</v>
@@ -10185,24 +10185,24 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>trent boult</t>
+          <t>tim seifert</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="C144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>tristan stubbs</t>
+          <t>travis head</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>196</v>
+        <v>180</v>
       </c>
       <c r="C145" t="n">
         <v>0</v>
@@ -10211,63 +10211,63 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>tushar deshpande</t>
+          <t>trent boult</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C146" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>vaibhav arora</t>
+          <t>tristan stubbs</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>1</v>
+        <v>196</v>
       </c>
       <c r="C147" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>vaibhav suryavanshi</t>
+          <t>tushar deshpande</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>246</v>
+        <v>25</v>
       </c>
       <c r="C148" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>varun chakravarthy</t>
+          <t>vaibhav arora</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C149" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>venkatesh iyer</t>
+          <t>vaibhav suryavanshi</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>29</v>
+        <v>254</v>
       </c>
       <c r="C150" t="n">
         <v>0</v>
@@ -10276,50 +10276,50 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>vijaykumar vyshak</t>
+          <t>varun chakravarthy</t>
         </is>
       </c>
       <c r="B151" t="n">
         <v>0</v>
       </c>
       <c r="C151" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>vipraj nigam</t>
+          <t>venkatesh iyer</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="C152" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>virat kohli</t>
+          <t>vijaykumar vyshak</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>247</v>
+        <v>0</v>
       </c>
       <c r="C153" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>washington sundar</t>
+          <t>vipraj nigam</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>137</v>
+        <v>12</v>
       </c>
       <c r="C154" t="n">
         <v>1</v>
@@ -10328,24 +10328,24 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>xavier bartlett</t>
+          <t>virat kohli</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>11</v>
+        <v>247</v>
       </c>
       <c r="C155" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>yash raj punja</t>
+          <t>washington sundar</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0</v>
+        <v>137</v>
       </c>
       <c r="C156" t="n">
         <v>1</v>
@@ -10354,26 +10354,52 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>yashasvi jaiswal</t>
+          <t>xavier bartlett</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>223</v>
+        <v>11</v>
       </c>
       <c r="C157" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
+          <t>yash raj punja</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>0</v>
+      </c>
+      <c r="C158" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>yashasvi jaiswal</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>245</v>
+      </c>
+      <c r="C159" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
           <t>yuzvendra chahal</t>
         </is>
       </c>
-      <c r="B158" t="n">
-        <v>0</v>
-      </c>
-      <c r="C158" t="n">
+      <c r="B160" t="n">
+        <v>0</v>
+      </c>
+      <c r="C160" t="n">
         <v>4</v>
       </c>
     </row>
@@ -10388,7 +10414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K49"/>
+  <dimension ref="A1:K48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11456,7 +11482,7 @@
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>mayank rawat</t>
+          <t>mayank yadav</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -12466,49 +12492,6 @@
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Mayank Yadav</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>BOWL</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>mayank rawat</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="G49" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12682,19 +12665,19 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>77</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>

--- a/IPL_Fantasy_Points.xlsx
+++ b/IPL_Fantasy_Points.xlsx
@@ -733,19 +733,19 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>41</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>25</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9">
@@ -905,19 +905,19 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="K11" t="n">
-        <v>20</v>
+        <v>102</v>
       </c>
     </row>
     <row r="12">
@@ -1811,16 +1811,16 @@
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="K32" t="n">
-        <v>120</v>
+        <v>160</v>
       </c>
     </row>
     <row r="33">
@@ -1854,16 +1854,16 @@
         <v>39</v>
       </c>
       <c r="H33" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="K33" t="n">
-        <v>260</v>
+        <v>280</v>
       </c>
     </row>
     <row r="34">
@@ -1980,19 +1980,19 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>125</v>
+        <v>132</v>
       </c>
     </row>
     <row r="37">
@@ -2324,19 +2324,19 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H44" t="n">
         <v>6</v>
       </c>
       <c r="I44" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J44" t="n">
         <v>120</v>
       </c>
       <c r="K44" t="n">
-        <v>128</v>
+        <v>134</v>
       </c>
     </row>
     <row r="45">
@@ -2754,19 +2754,19 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>192</v>
+        <v>293</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>192</v>
+        <v>293</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>192</v>
+        <v>293</v>
       </c>
     </row>
     <row r="55">
@@ -3098,19 +3098,19 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="H62" t="n">
         <v>1</v>
       </c>
       <c r="I62" t="n">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="63">
@@ -3488,16 +3488,16 @@
         <v>26</v>
       </c>
       <c r="H71" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I71" t="n">
         <v>0</v>
       </c>
       <c r="J71" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="K71" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="72">
@@ -3528,19 +3528,19 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>82</v>
+        <v>104</v>
       </c>
     </row>
     <row r="73">
@@ -3829,19 +3829,19 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="H79" t="n">
         <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>147</v>
+        <v>161</v>
       </c>
     </row>
     <row r="80">
@@ -5334,19 +5334,19 @@
         </is>
       </c>
       <c r="G114" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H114" t="n">
         <v>3</v>
       </c>
       <c r="I114" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J114" t="n">
         <v>60</v>
       </c>
       <c r="K114" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="115">
@@ -5377,19 +5377,19 @@
         </is>
       </c>
       <c r="G115" t="n">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="H115" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I115" t="n">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="J115" t="n">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="K115" t="n">
-        <v>263</v>
+        <v>298</v>
       </c>
     </row>
     <row r="116">
@@ -5638,16 +5638,16 @@
         <v>0</v>
       </c>
       <c r="H121" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I121" t="n">
         <v>0</v>
       </c>
       <c r="J121" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="K121" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="122">
@@ -5681,16 +5681,16 @@
         <v>0</v>
       </c>
       <c r="H122" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I122" t="n">
         <v>0</v>
       </c>
       <c r="J122" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="K122" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="123">
@@ -6065,19 +6065,19 @@
         </is>
       </c>
       <c r="G131" t="n">
-        <v>144</v>
+        <v>181</v>
       </c>
       <c r="H131" t="n">
         <v>0</v>
       </c>
       <c r="I131" t="n">
-        <v>144</v>
+        <v>181</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
       </c>
       <c r="K131" t="n">
-        <v>144</v>
+        <v>181</v>
       </c>
     </row>
     <row r="132">
@@ -6452,19 +6452,19 @@
         </is>
       </c>
       <c r="G140" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H140" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I140" t="n">
         <v>0</v>
       </c>
       <c r="J140" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="K140" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="141">
@@ -6667,19 +6667,19 @@
         </is>
       </c>
       <c r="G145" t="n">
-        <v>121</v>
+        <v>157</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
       </c>
       <c r="I145" t="n">
-        <v>121</v>
+        <v>157</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
       </c>
       <c r="K145" t="n">
-        <v>121</v>
+        <v>157</v>
       </c>
     </row>
     <row r="146">
@@ -8132,16 +8132,16 @@
         <v>10</v>
       </c>
       <c r="H179" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I179" t="n">
         <v>0</v>
       </c>
       <c r="J179" t="n">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="K179" t="n">
-        <v>80</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -8185,7 +8185,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2080</v>
+        <v>2116</v>
       </c>
     </row>
     <row r="3">
@@ -8198,7 +8198,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1931</v>
+        <v>1991</v>
       </c>
     </row>
     <row r="4">
@@ -8211,7 +8211,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1762</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="5">
@@ -8220,11 +8220,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>VATSAL11</t>
+          <t>BABA11</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1611</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="6">
@@ -8233,11 +8233,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BABA11</t>
+          <t>VATSAL11</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1565</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="7">
@@ -8250,7 +8250,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1551</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="8">
@@ -8263,7 +8263,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1526</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="9">
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1350</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="11">
@@ -8302,7 +8302,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1191</v>
+        <v>1231</v>
       </c>
     </row>
   </sheetData>
@@ -8408,10 +8408,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -8424,7 +8424,7 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -8476,7 +8476,7 @@
         <v>39</v>
       </c>
       <c r="C12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13">
@@ -8538,10 +8538,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18">
@@ -8772,7 +8772,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="C35" t="n">
         <v>0</v>
@@ -8892,7 +8892,7 @@
         <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45">
@@ -8902,7 +8902,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C45" t="n">
         <v>3</v>
@@ -8993,10 +8993,10 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="C52" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="53">
@@ -9006,10 +9006,10 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -9097,7 +9097,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="C60" t="n">
         <v>0</v>
@@ -9149,7 +9149,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C64" t="n">
         <v>0</v>
@@ -9373,7 +9373,7 @@
         <v>26</v>
       </c>
       <c r="C81" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="82">
@@ -9425,7 +9425,7 @@
         <v>0</v>
       </c>
       <c r="C85" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="86">
@@ -9555,7 +9555,7 @@
         <v>10</v>
       </c>
       <c r="C95" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="96">
@@ -9669,7 +9669,7 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="C104" t="n">
         <v>0</v>
@@ -9864,7 +9864,7 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="C119" t="n">
         <v>0</v>
@@ -9942,7 +9942,7 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>192</v>
+        <v>293</v>
       </c>
       <c r="C125" t="n">
         <v>0</v>
@@ -9955,7 +9955,7 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="C126" t="n">
         <v>0</v>
@@ -9994,7 +9994,7 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C129" t="n">
         <v>6</v>
@@ -10046,7 +10046,7 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="C133" t="n">
         <v>1</v>
@@ -10124,7 +10124,7 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>121</v>
+        <v>157</v>
       </c>
       <c r="C139" t="n">
         <v>0</v>
@@ -10163,7 +10163,7 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>144</v>
+        <v>181</v>
       </c>
       <c r="C142" t="n">
         <v>0</v>

--- a/IPL_Fantasy_Points.xlsx
+++ b/IPL_Fantasy_Points.xlsx
@@ -647,19 +647,19 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>52</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6">
@@ -690,19 +690,19 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>230</v>
+        <v>238</v>
       </c>
     </row>
     <row r="7">
@@ -994,16 +994,16 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="K13" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
     </row>
     <row r="14">
@@ -1249,19 +1249,19 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>265</v>
+        <v>297</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>265</v>
+        <v>297</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>265</v>
+        <v>297</v>
       </c>
     </row>
     <row r="20">
@@ -1455,7 +1455,7 @@
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>jacob duffy</t>
+          <t>jacob bethell</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1581,31 +1581,31 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>jos buttler</t>
-        </is>
-      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>jason holder</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
     </row>
     <row r="28">
@@ -3187,16 +3187,16 @@
         <v>28</v>
       </c>
       <c r="H64" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I64" t="n">
         <v>28</v>
       </c>
       <c r="J64" t="n">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="K64" t="n">
-        <v>148</v>
+        <v>188</v>
       </c>
     </row>
     <row r="65">
@@ -3571,19 +3571,19 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>135</v>
+        <v>235</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>135</v>
+        <v>235</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>135</v>
+        <v>235</v>
       </c>
     </row>
     <row r="74">
@@ -3958,19 +3958,19 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>173</v>
+        <v>183</v>
       </c>
     </row>
     <row r="83">
@@ -4431,19 +4431,19 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>206</v>
+        <v>231</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>206</v>
+        <v>231</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>206</v>
+        <v>231</v>
       </c>
     </row>
     <row r="94">
@@ -4821,16 +4821,16 @@
         <v>0</v>
       </c>
       <c r="H102" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I102" t="n">
         <v>0</v>
       </c>
       <c r="J102" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="K102" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
     </row>
     <row r="103">
@@ -5850,19 +5850,19 @@
         </is>
       </c>
       <c r="G126" t="n">
-        <v>153</v>
+        <v>208</v>
       </c>
       <c r="H126" t="n">
         <v>0</v>
       </c>
       <c r="I126" t="n">
-        <v>153</v>
+        <v>208</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
       </c>
       <c r="K126" t="n">
-        <v>153</v>
+        <v>208</v>
       </c>
     </row>
     <row r="127">
@@ -6280,19 +6280,19 @@
         </is>
       </c>
       <c r="G136" t="n">
-        <v>137</v>
+        <v>156</v>
       </c>
       <c r="H136" t="n">
         <v>1</v>
       </c>
       <c r="I136" t="n">
-        <v>137</v>
+        <v>156</v>
       </c>
       <c r="J136" t="n">
         <v>20</v>
       </c>
       <c r="K136" t="n">
-        <v>157</v>
+        <v>176</v>
       </c>
     </row>
     <row r="137">
@@ -6624,19 +6624,19 @@
         </is>
       </c>
       <c r="G144" t="n">
-        <v>247</v>
+        <v>328</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
       </c>
       <c r="I144" t="n">
-        <v>247</v>
+        <v>328</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
       </c>
       <c r="K144" t="n">
-        <v>247</v>
+        <v>328</v>
       </c>
     </row>
     <row r="145">
@@ -7011,19 +7011,19 @@
         </is>
       </c>
       <c r="G153" t="n">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="H153" t="n">
         <v>8</v>
       </c>
       <c r="I153" t="n">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="J153" t="n">
         <v>160</v>
       </c>
       <c r="K153" t="n">
-        <v>173</v>
+        <v>196</v>
       </c>
     </row>
     <row r="154">
@@ -7186,16 +7186,16 @@
         <v>12</v>
       </c>
       <c r="H157" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I157" t="n">
         <v>0</v>
       </c>
       <c r="J157" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="K157" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
     </row>
     <row r="158">
@@ -8003,16 +8003,16 @@
         <v>0</v>
       </c>
       <c r="H176" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I176" t="n">
         <v>0</v>
       </c>
       <c r="J176" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="K176" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="177">
@@ -8185,7 +8185,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2116</v>
+        <v>2226</v>
       </c>
     </row>
     <row r="3">
@@ -8198,7 +8198,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1991</v>
+        <v>2066</v>
       </c>
     </row>
     <row r="4">
@@ -8224,7 +8224,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1691</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="6">
@@ -8233,11 +8233,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>VATSAL11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1624</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="7">
@@ -8246,11 +8246,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1587</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="8">
@@ -8259,11 +8259,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>VATSAL11</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1583</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="9">
@@ -8276,7 +8276,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1485</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="10">
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1471</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="11">
@@ -8302,7 +8302,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1231</v>
+        <v>1251</v>
       </c>
     </row>
   </sheetData>
@@ -8316,7 +8316,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C160"/>
+  <dimension ref="A1:C163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8616,7 +8616,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>135</v>
+        <v>235</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
@@ -8632,7 +8632,7 @@
         <v>12</v>
       </c>
       <c r="C24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25">
@@ -8759,7 +8759,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>153</v>
+        <v>208</v>
       </c>
       <c r="C34" t="n">
         <v>0</v>
@@ -8976,89 +8976,89 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>jacob duffy</t>
+          <t>jacob bethell</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="C51" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>jamie overton</t>
+          <t>jacob duffy</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>118</v>
+        <v>0</v>
       </c>
       <c r="C52" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>jasprit bumrah</t>
+          <t>jamie overton</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>7</v>
+        <v>118</v>
       </c>
       <c r="C53" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>jaydev unadkat</t>
+          <t>jason holder</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="C54" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>jitesh sharma</t>
+          <t>jasprit bumrah</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="C55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>jofra archer</t>
+          <t>jaydev unadkat</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C56" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>jos buttler</t>
+          <t>jitesh sharma</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>206</v>
+        <v>62</v>
       </c>
       <c r="C57" t="n">
         <v>0</v>
@@ -9067,63 +9067,63 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>josh hazlewood</t>
+          <t>jofra archer</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C58" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>kagiso rabada</t>
+          <t>jos buttler</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>35</v>
+        <v>231</v>
       </c>
       <c r="C59" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>kartik sharma</t>
+          <t>josh hazlewood</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="C60" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>kartik tyagi</t>
+          <t>kagiso rabada</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="C61" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>karun nair</t>
+          <t>kartik sharma</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>5</v>
+        <v>43</v>
       </c>
       <c r="C62" t="n">
         <v>0</v>
@@ -9132,24 +9132,24 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>khaleel ahmed</t>
+          <t>kartik tyagi</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C63" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>krish bhagat</t>
+          <t>karun nair</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C64" t="n">
         <v>0</v>
@@ -9158,63 +9158,63 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>krunal pandya</t>
+          <t>khaleel ahmed</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C65" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>kuldeep yadav</t>
+          <t>krish bhagat</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C66" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>kumar kushagra</t>
+          <t>krunal pandya</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="C67" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>lhuan dre pretorius</t>
+          <t>kuldeep yadav</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C68" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>liam livingstone</t>
+          <t>kumar kushagra</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C69" t="n">
         <v>0</v>
@@ -9223,11 +9223,11 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>lokesh rahul</t>
+          <t>lhuan dre pretorius</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>205</v>
+        <v>0</v>
       </c>
       <c r="C70" t="n">
         <v>0</v>
@@ -9236,89 +9236,89 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>lungi ngidi</t>
+          <t>liam livingstone</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C71" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>manimaran siddharth</t>
+          <t>lokesh rahul</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0</v>
+        <v>205</v>
       </c>
       <c r="C72" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>marco jansen</t>
+          <t>lungi ngidi</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C73" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>marcus stoinis</t>
+          <t>manav suthar</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="C74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>matt henry</t>
+          <t>manimaran siddharth</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C75" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>matt short</t>
+          <t>marco jansen</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="C76" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>mayank markande</t>
+          <t>marcus stoinis</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="C77" t="n">
         <v>0</v>
@@ -9327,24 +9327,24 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>mayank rawat</t>
+          <t>matt henry</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>mayank yadav</t>
+          <t>matt short</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="C79" t="n">
         <v>0</v>
@@ -9353,11 +9353,11 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>mitchell marsh</t>
+          <t>mayank markande</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="C80" t="n">
         <v>0</v>
@@ -9366,128 +9366,128 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>mitchell santner</t>
+          <t>mayank rawat</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="C81" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>mohammed shami</t>
+          <t>mayank yadav</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="C82" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>mohammed siraj</t>
+          <t>mitchell marsh</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="C83" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>mohsin khan</t>
+          <t>mitchell santner</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="C84" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>mukesh choudhary</t>
+          <t>mohammed shami</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C85" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>mukesh kumar</t>
+          <t>mohammed siraj</t>
         </is>
       </c>
       <c r="B86" t="n">
         <v>0</v>
       </c>
       <c r="C86" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>mukul choudhary</t>
+          <t>mohsin khan</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>155</v>
+        <v>0</v>
       </c>
       <c r="C87" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>naman dhir</t>
+          <t>mukesh choudhary</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>154</v>
+        <v>0</v>
       </c>
       <c r="C88" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>nandre burger</t>
+          <t>mukesh kumar</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C89" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>navdeep saini</t>
+          <t>mukul choudhary</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
@@ -9496,11 +9496,11 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>nehal wadhera</t>
+          <t>naman dhir</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>40</v>
+        <v>154</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
@@ -9509,37 +9509,37 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>nicholas pooran</t>
+          <t>nandre burger</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>73</v>
+        <v>3</v>
       </c>
       <c r="C92" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>nitish kumar reddy</t>
+          <t>navdeep saini</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="C93" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>nitish rana</t>
+          <t>nehal wadhera</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>77</v>
+        <v>40</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
@@ -9548,37 +9548,37 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>noor ahmad</t>
+          <t>nicholas pooran</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>10</v>
+        <v>73</v>
       </c>
       <c r="C95" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>pathum nissanka</t>
+          <t>nitish kumar reddy</t>
         </is>
       </c>
       <c r="B96" t="n">
         <v>136</v>
       </c>
       <c r="C96" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>philip salt</t>
+          <t>nitish rana</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>202</v>
+        <v>77</v>
       </c>
       <c r="C97" t="n">
         <v>0</v>
@@ -9587,37 +9587,37 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>prabhsimran singh</t>
+          <t>noor ahmad</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>211</v>
+        <v>10</v>
       </c>
       <c r="C98" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>praful hinge</t>
+          <t>pathum nissanka</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="C99" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>prashant veer</t>
+          <t>philip salt</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>49</v>
+        <v>202</v>
       </c>
       <c r="C100" t="n">
         <v>0</v>
@@ -9626,37 +9626,37 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>prasidh krishna</t>
+          <t>prabhsimran singh</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0</v>
+        <v>211</v>
       </c>
       <c r="C101" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>prince yadav</t>
+          <t>praful hinge</t>
         </is>
       </c>
       <c r="B102" t="n">
         <v>0</v>
       </c>
       <c r="C102" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>priyansh arya</t>
+          <t>prashant veer</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>211</v>
+        <v>49</v>
       </c>
       <c r="C103" t="n">
         <v>0</v>
@@ -9665,37 +9665,37 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>quinton de kock</t>
+          <t>prasidh krishna</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="C104" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>rahul chahar</t>
+          <t>prince yadav</t>
         </is>
       </c>
       <c r="B105" t="n">
         <v>0</v>
       </c>
       <c r="C105" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>rahul tewatia</t>
+          <t>priyansh arya</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>49</v>
+        <v>211</v>
       </c>
       <c r="C106" t="n">
         <v>0</v>
@@ -9704,11 +9704,11 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>rajat patidar</t>
+          <t>quinton de kock</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>230</v>
+        <v>132</v>
       </c>
       <c r="C107" t="n">
         <v>0</v>
@@ -9717,115 +9717,115 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ramandeep singh</t>
+          <t>rahul chahar</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="C108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>rashid khan</t>
+          <t>rahul tewatia</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="C109" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>rasikh salam</t>
+          <t>rajat patidar</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0</v>
+        <v>238</v>
       </c>
       <c r="C110" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ravi bishnoi</t>
+          <t>ramandeep singh</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="C111" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ravindra jadeja</t>
+          <t>rashid khan</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>128</v>
+        <v>28</v>
       </c>
       <c r="C112" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>rinku singh</t>
+          <t>rasikh salam</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="C113" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>rishabh pant</t>
+          <t>ravi bishnoi</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>147</v>
+        <v>0</v>
       </c>
       <c r="C114" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>riyan parag</t>
+          <t>ravindra jadeja</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>81</v>
+        <v>128</v>
       </c>
       <c r="C115" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>rohit sharma</t>
+          <t>rinku singh</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="C116" t="n">
         <v>0</v>
@@ -9834,37 +9834,37 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>romario shepherd</t>
+          <t>rishabh pant</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>39</v>
+        <v>147</v>
       </c>
       <c r="C117" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>rovman powell</t>
+          <t>riyan parag</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>120</v>
+        <v>81</v>
       </c>
       <c r="C118" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ruturaj gaikwad</t>
+          <t>rohit sharma</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="C119" t="n">
         <v>0</v>
@@ -9873,37 +9873,37 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ryan rickelton</t>
+          <t>romario shepherd</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>137</v>
+        <v>39</v>
       </c>
       <c r="C120" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>sakib hussain</t>
+          <t>rovman powell</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="C121" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>salil arora</t>
+          <t>ruturaj gaikwad</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>55</v>
+        <v>104</v>
       </c>
       <c r="C122" t="n">
         <v>0</v>
@@ -9912,11 +9912,11 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>sameer rizvi</t>
+          <t>ryan rickelton</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>209</v>
+        <v>137</v>
       </c>
       <c r="C123" t="n">
         <v>0</v>
@@ -9925,24 +9925,24 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>sandeep sharma</t>
+          <t>sakib hussain</t>
         </is>
       </c>
       <c r="B124" t="n">
         <v>0</v>
       </c>
       <c r="C124" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>sanju samson</t>
+          <t>salil arora</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>293</v>
+        <v>55</v>
       </c>
       <c r="C125" t="n">
         <v>0</v>
@@ -9951,11 +9951,11 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>sarfaraz khan</t>
+          <t>sameer rizvi</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>161</v>
+        <v>209</v>
       </c>
       <c r="C126" t="n">
         <v>0</v>
@@ -9964,24 +9964,24 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>shahbaz ahmed</t>
+          <t>sandeep sharma</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="C127" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>shahrukh khan</t>
+          <t>sanju samson</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>35</v>
+        <v>293</v>
       </c>
       <c r="C128" t="n">
         <v>0</v>
@@ -9990,37 +9990,37 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>shardul thakur</t>
+          <t>sarfaraz khan</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>14</v>
+        <v>161</v>
       </c>
       <c r="C129" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>shashank singh</t>
+          <t>shahbaz ahmed</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="C130" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>sherfane rutherford</t>
+          <t>shahrukh khan</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>103</v>
+        <v>35</v>
       </c>
       <c r="C131" t="n">
         <v>0</v>
@@ -10029,50 +10029,50 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>shimron hetmyer</t>
+          <t>shardul thakur</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>61</v>
+        <v>14</v>
       </c>
       <c r="C132" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>shivam dube</t>
+          <t>shashank singh</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>128</v>
+        <v>51</v>
       </c>
       <c r="C133" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>shivang kumar</t>
+          <t>sherfane rutherford</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>21</v>
+        <v>103</v>
       </c>
       <c r="C134" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>shreyas iyer</t>
+          <t>shimron hetmyer</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>208</v>
+        <v>61</v>
       </c>
       <c r="C135" t="n">
         <v>0</v>
@@ -10081,50 +10081,50 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>shubham badriprasad dubey</t>
+          <t>shivam dube</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>19</v>
+        <v>128</v>
       </c>
       <c r="C136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>shubman gill</t>
+          <t>shivang kumar</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>265</v>
+        <v>21</v>
       </c>
       <c r="C137" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>sunil narine</t>
+          <t>shreyas iyer</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>36</v>
+        <v>208</v>
       </c>
       <c r="C138" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>suryakumar yadav</t>
+          <t>shubham badriprasad dubey</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>157</v>
+        <v>19</v>
       </c>
       <c r="C139" t="n">
         <v>0</v>
@@ -10133,37 +10133,37 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>suyash sharma</t>
+          <t>shubman gill</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0</v>
+        <v>297</v>
       </c>
       <c r="C140" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>t natarajan</t>
+          <t>sunil narine</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="C141" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>tilak varma</t>
+          <t>suryakumar yadav</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>181</v>
+        <v>157</v>
       </c>
       <c r="C142" t="n">
         <v>0</v>
@@ -10172,37 +10172,37 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>tim david</t>
+          <t>suyash sharma</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>173</v>
+        <v>0</v>
       </c>
       <c r="C143" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>tim seifert</t>
+          <t>t natarajan</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="C144" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>travis head</t>
+          <t>tilak varma</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C145" t="n">
         <v>0</v>
@@ -10211,24 +10211,24 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>trent boult</t>
+          <t>tim david</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>1</v>
+        <v>183</v>
       </c>
       <c r="C146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>tristan stubbs</t>
+          <t>tim seifert</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>196</v>
+        <v>19</v>
       </c>
       <c r="C147" t="n">
         <v>0</v>
@@ -10237,37 +10237,37 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>tushar deshpande</t>
+          <t>travis head</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>25</v>
+        <v>180</v>
       </c>
       <c r="C148" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>vaibhav arora</t>
+          <t>trent boult</t>
         </is>
       </c>
       <c r="B149" t="n">
         <v>1</v>
       </c>
       <c r="C149" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>vaibhav suryavanshi</t>
+          <t>tristan stubbs</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>254</v>
+        <v>196</v>
       </c>
       <c r="C150" t="n">
         <v>0</v>
@@ -10276,63 +10276,63 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>varun chakravarthy</t>
+          <t>tushar deshpande</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="C151" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>venkatesh iyer</t>
+          <t>vaibhav arora</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C152" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>vijaykumar vyshak</t>
+          <t>vaibhav suryavanshi</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0</v>
+        <v>254</v>
       </c>
       <c r="C153" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>vipraj nigam</t>
+          <t>varun chakravarthy</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C154" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>virat kohli</t>
+          <t>venkatesh iyer</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>247</v>
+        <v>29</v>
       </c>
       <c r="C155" t="n">
         <v>0</v>
@@ -10341,65 +10341,104 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>washington sundar</t>
+          <t>vijaykumar vyshak</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="C156" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>xavier bartlett</t>
+          <t>vipraj nigam</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C157" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>yash raj punja</t>
+          <t>virat kohli</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>0</v>
+        <v>328</v>
       </c>
       <c r="C158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>yashasvi jaiswal</t>
+          <t>washington sundar</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>245</v>
+        <v>156</v>
       </c>
       <c r="C159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
+          <t>xavier bartlett</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>11</v>
+      </c>
+      <c r="C160" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>yash raj punja</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>0</v>
+      </c>
+      <c r="C161" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>yashasvi jaiswal</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>245</v>
+      </c>
+      <c r="C162" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
           <t>yuzvendra chahal</t>
         </is>
       </c>
-      <c r="B160" t="n">
-        <v>0</v>
-      </c>
-      <c r="C160" t="n">
+      <c r="B163" t="n">
+        <v>0</v>
+      </c>
+      <c r="C163" t="n">
         <v>4</v>
       </c>
     </row>
@@ -10414,7 +10453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K48"/>
+  <dimension ref="A1:K47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10622,7 +10661,7 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>jacob duffy</t>
+          <t>jacob bethell</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -10649,7 +10688,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Jason Holder</t>
+          <t>kamindu mendis</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -10659,13 +10698,13 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>jos buttler</t>
+          <t>karun nair</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -10692,7 +10731,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>kamindu mendis</t>
+          <t>Kuldeep sen</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -10708,7 +10747,7 @@
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>karun nair</t>
+          <t>kuldeep yadav</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -10735,23 +10774,23 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Kuldeep sen</t>
+          <t>Tom Banton</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MEET11</t>
+          <t>VATSAL11</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>kuldeep yadav</t>
+          <t>t natarajan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -10778,7 +10817,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Tom Banton</t>
+          <t>Tim Siefert</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -10794,7 +10833,7 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>t natarajan</t>
+          <t>tim seifert</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -10821,7 +10860,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Tim Siefert</t>
+          <t>Lockie Ferguson</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -10831,13 +10870,13 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>tim seifert</t>
+          <t>lokesh rahul</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -10864,7 +10903,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Lockie Ferguson</t>
+          <t>Adam Milne</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -10880,7 +10919,7 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>lokesh rahul</t>
+          <t>david miller</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -10907,23 +10946,23 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Adam Milne</t>
+          <t>Jos Inglis</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>VATSAL11</t>
+          <t>BABA11</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>david miller</t>
+          <t>marcus stoinis</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -10950,7 +10989,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Jos Inglis</t>
+          <t>Prithvi Shaw</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -10966,7 +11005,7 @@
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>marcus stoinis</t>
+          <t>prasidh krishna</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -10993,7 +11032,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Prithvi Shaw</t>
+          <t>liam livingston</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -11003,13 +11042,13 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>prasidh krishna</t>
+          <t>liam livingstone</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -11036,7 +11075,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>liam livingston</t>
+          <t>rachin ravindra</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -11052,7 +11091,7 @@
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>liam livingstone</t>
+          <t>rashid khan</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -11079,7 +11118,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>rachin ravindra</t>
+          <t>Zeeshan Ansari</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -11089,13 +11128,13 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>rashid khan</t>
+          <t>eshan malinga</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -11122,7 +11161,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Zeeshan Ansari</t>
+          <t>Mitchell Starc</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -11138,7 +11177,7 @@
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>eshan malinga</t>
+          <t>mitchell santner</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -11165,17 +11204,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Mitchell Starc</t>
+          <t>Mitchel Owen</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BABA11</t>
+          <t>DIPESH11</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -11208,7 +11247,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Mitchel Owen</t>
+          <t>Pat Cummins</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -11218,13 +11257,13 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>mitchell santner</t>
+          <t>pathum nissanka</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -11251,7 +11290,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Pat Cummins</t>
+          <t>Auqib Dar</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -11261,13 +11300,13 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>pathum nissanka</t>
+          <t>auqib nabi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -11294,23 +11333,23 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Auqib Dar</t>
+          <t>Urvil Patel</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DIPESH11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>auqib nabi</t>
+          <t>axar patel</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -11337,7 +11376,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Urvil Patel</t>
+          <t>Arshin Kulkarni</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -11353,7 +11392,7 @@
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>axar patel</t>
+          <t>ashwani kumar</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -11380,7 +11419,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Arshin Kulkarni</t>
+          <t>Nishant Sindhu</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -11390,13 +11429,13 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ashwani kumar</t>
+          <t>shashank singh</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -11423,7 +11462,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Nishant Sindhu</t>
+          <t>Jayant Yadav</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -11439,7 +11478,7 @@
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>shashank singh</t>
+          <t>mayank yadav</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -11466,7 +11505,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Jayant Yadav</t>
+          <t>Ajay Mandal</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11482,7 +11521,7 @@
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>mayank yadav</t>
+          <t>rajat patidar</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -11509,7 +11548,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Ajay Mandal</t>
+          <t>Will Jacks</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11525,7 +11564,7 @@
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>rajat patidar</t>
+          <t>mitchell marsh</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -11552,7 +11591,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Will Jacks</t>
+          <t>Kyle Jamieson</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11562,13 +11601,13 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>mitchell marsh</t>
+          <t>jamie overton</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -11595,7 +11634,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Kyle Jamieson</t>
+          <t>Matheesha Pathirana</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -11611,7 +11650,7 @@
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>jamie overton</t>
+          <t>eshan malinga</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -11638,7 +11677,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Matheesha Pathirana</t>
+          <t>Ben Dwarshuis</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -11654,7 +11693,7 @@
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>eshan malinga</t>
+          <t>b sai sudharshan</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -11681,23 +11720,23 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Ben Dwarshuis</t>
+          <t>Manish Pandey</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>b sai sudharshan</t>
+          <t>hardik pandya</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -11724,7 +11763,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Manish Pandey</t>
+          <t>Arjun Tendulkar</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -11734,13 +11773,13 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>hardik pandya</t>
+          <t>karun nair</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -11767,7 +11806,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Arjun Tendulkar</t>
+          <t>Kwena Maphaka</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -11783,7 +11822,7 @@
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>karun nair</t>
+          <t>aiden markram</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -11810,23 +11849,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Kwena Maphaka</t>
+          <t>Ramkrishna Ghosh</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>aiden markram</t>
+          <t>angkrish raghuvanshi</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -11853,7 +11892,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Ramkrishna Ghosh</t>
+          <t>Azmatullah Omarzai</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -11863,13 +11902,13 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>angkrish raghuvanshi</t>
+          <t>mitchell marsh</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -11896,23 +11935,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Azmatullah Omarzai</t>
+          <t>akshat raghuwanshi</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>mitchell marsh</t>
+          <t>angkrish raghuvanshi</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -11939,7 +11978,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>akshat raghuwanshi</t>
+          <t>Suryansh Shegde</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -11955,7 +11994,7 @@
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>angkrish raghuvanshi</t>
+          <t>suyash sharma</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -11982,7 +12021,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Suryansh Shegde</t>
+          <t>Tejasvi Singh</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -11998,7 +12037,7 @@
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>suyash sharma</t>
+          <t>prabhsimran singh</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -12025,7 +12064,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Tejasvi Singh</t>
+          <t>Sai Kishor</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -12035,13 +12074,13 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>prabhsimran singh</t>
+          <t>ishan kishan</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -12068,7 +12107,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sai Kishor</t>
+          <t>Akash Deep</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -12084,7 +12123,7 @@
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>ishan kishan</t>
+          <t>arshdeep singh</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -12111,23 +12150,23 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Akash Deep</t>
+          <t>Ben Duckett</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>arshdeep singh</t>
+          <t>ryan rickelton</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -12154,7 +12193,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Ben Duckett</t>
+          <t>Abhishek Porel</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -12170,7 +12209,7 @@
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>ryan rickelton</t>
+          <t>abhishek sharma</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -12197,7 +12236,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Abhishek Porel</t>
+          <t>Rahul Tripathi</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -12213,7 +12252,7 @@
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>abhishek sharma</t>
+          <t>rahul tewatia</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -12240,7 +12279,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Rahul Tripathi</t>
+          <t>Dre Pretorius</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -12256,7 +12295,7 @@
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>rahul tewatia</t>
+          <t>lhuan dre pretorius</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -12283,7 +12322,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Dre Pretorius</t>
+          <t>Matthew Breetzke</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -12299,7 +12338,7 @@
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>lhuan dre pretorius</t>
+          <t>matt henry</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -12326,7 +12365,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Matthew Breetzke</t>
+          <t>Anuj Rawat</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -12342,7 +12381,7 @@
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>matt henry</t>
+          <t>mayank rawat</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -12369,7 +12408,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Anuj Rawat</t>
+          <t>Wanindu Hasaranga</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -12379,13 +12418,13 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>mayank rawat</t>
+          <t>sandeep sharma</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -12412,7 +12451,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Wanindu Hasaranga</t>
+          <t>Harpreet Brar</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -12422,13 +12461,13 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>sandeep sharma</t>
+          <t>jasprit bumrah</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -12449,49 +12488,6 @@
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Harpreet Brar</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>BOWL</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>jasprit bumrah</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="G48" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" t="n">
         <v>0</v>
       </c>
     </row>

--- a/IPL_Fantasy_Points.xlsx
+++ b/IPL_Fantasy_Points.xlsx
@@ -604,19 +604,19 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>180</v>
+        <v>186</v>
       </c>
     </row>
     <row r="5">
@@ -1206,19 +1206,19 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>238</v>
+        <v>312</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>238</v>
+        <v>312</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>238</v>
+        <v>312</v>
       </c>
     </row>
     <row r="19">
@@ -1335,19 +1335,19 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>254</v>
+        <v>357</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>254</v>
+        <v>357</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>254</v>
+        <v>357</v>
       </c>
     </row>
     <row r="22">
@@ -1510,16 +1510,16 @@
         <v>12</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I25" t="n">
         <v>12</v>
       </c>
       <c r="J25" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="K25" t="n">
-        <v>32</v>
+        <v>52</v>
       </c>
     </row>
     <row r="26">
@@ -2023,19 +2023,19 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>320</v>
+        <v>349</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>320</v>
+        <v>349</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>320</v>
+        <v>349</v>
       </c>
     </row>
     <row r="38">
@@ -2109,19 +2109,19 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>136</v>
+        <v>172</v>
       </c>
       <c r="H39" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I39" t="n">
-        <v>136</v>
+        <v>172</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>136</v>
+        <v>172</v>
       </c>
     </row>
     <row r="40">
@@ -2281,19 +2281,19 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="H43" t="n">
         <v>6</v>
       </c>
       <c r="I43" t="n">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="J43" t="n">
         <v>120</v>
       </c>
       <c r="K43" t="n">
-        <v>248</v>
+        <v>252</v>
       </c>
     </row>
     <row r="44">
@@ -2840,19 +2840,19 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="57">
@@ -2883,19 +2883,19 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>181</v>
+        <v>232</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>181</v>
+        <v>232</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>181</v>
+        <v>232</v>
       </c>
     </row>
     <row r="58">
@@ -3614,19 +3614,19 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>211</v>
+        <v>287</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>211</v>
+        <v>287</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>211</v>
+        <v>287</v>
       </c>
     </row>
     <row r="75">
@@ -3657,19 +3657,19 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>211</v>
+        <v>254</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>211</v>
+        <v>254</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>211</v>
+        <v>254</v>
       </c>
     </row>
     <row r="76">
@@ -3743,19 +3743,19 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
     </row>
     <row r="78">
@@ -3860,31 +3860,31 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>pathum nissanka</t>
-        </is>
-      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>pat cummins</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="G80" t="n">
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I80" t="n">
         <v>0</v>
       </c>
       <c r="J80" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K80" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="81">
@@ -4001,19 +4001,19 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>223</v>
+        <v>240</v>
       </c>
     </row>
     <row r="84">
@@ -4047,16 +4047,16 @@
         <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I84" t="n">
         <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="K84" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
     </row>
     <row r="85">
@@ -4262,16 +4262,16 @@
         <v>11</v>
       </c>
       <c r="H89" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I89" t="n">
         <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="K89" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="90">
@@ -4302,19 +4302,19 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>245</v>
+        <v>255</v>
       </c>
     </row>
     <row r="91">
@@ -4345,19 +4345,19 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>205</v>
+        <v>357</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
       </c>
       <c r="I91" t="n">
-        <v>205</v>
+        <v>357</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>205</v>
+        <v>357</v>
       </c>
     </row>
     <row r="92">
@@ -4388,19 +4388,19 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>208</v>
+        <v>279</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>208</v>
+        <v>279</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>208</v>
+        <v>279</v>
       </c>
     </row>
     <row r="93">
@@ -4732,19 +4732,19 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="H100" t="n">
         <v>2</v>
       </c>
       <c r="I100" t="n">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="J100" t="n">
         <v>40</v>
       </c>
       <c r="K100" t="n">
-        <v>121</v>
+        <v>128</v>
       </c>
     </row>
     <row r="101">
@@ -5205,19 +5205,19 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
       </c>
       <c r="I111" t="n">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
       </c>
       <c r="K111" t="n">
-        <v>61</v>
+        <v>72</v>
       </c>
     </row>
     <row r="112">
@@ -5291,19 +5291,19 @@
         </is>
       </c>
       <c r="G113" t="n">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="H113" t="n">
         <v>0</v>
       </c>
       <c r="I113" t="n">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
       </c>
       <c r="K113" t="n">
-        <v>136</v>
+        <v>147</v>
       </c>
     </row>
     <row r="114">
@@ -5420,19 +5420,19 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>97</v>
+        <v>130</v>
       </c>
       <c r="H116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I116" t="n">
-        <v>97</v>
+        <v>130</v>
       </c>
       <c r="J116" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K116" t="n">
-        <v>97</v>
+        <v>150</v>
       </c>
     </row>
     <row r="117">
@@ -6108,19 +6108,19 @@
         </is>
       </c>
       <c r="G132" t="n">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="H132" t="n">
         <v>3</v>
       </c>
       <c r="I132" t="n">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
       </c>
       <c r="K132" t="n">
-        <v>51</v>
+        <v>70</v>
       </c>
     </row>
     <row r="133">
@@ -6326,16 +6326,16 @@
         <v>31</v>
       </c>
       <c r="H137" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I137" t="n">
         <v>31</v>
       </c>
       <c r="J137" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="K137" t="n">
-        <v>151</v>
+        <v>171</v>
       </c>
     </row>
     <row r="138">
@@ -6409,19 +6409,19 @@
         </is>
       </c>
       <c r="G139" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="H139" t="n">
         <v>0</v>
       </c>
       <c r="I139" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
       </c>
       <c r="K139" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
     </row>
     <row r="140">
@@ -6753,19 +6753,19 @@
         </is>
       </c>
       <c r="G147" t="n">
-        <v>77</v>
+        <v>168</v>
       </c>
       <c r="H147" t="n">
         <v>0</v>
       </c>
       <c r="I147" t="n">
-        <v>77</v>
+        <v>168</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
       </c>
       <c r="K147" t="n">
-        <v>77</v>
+        <v>168</v>
       </c>
     </row>
     <row r="148">
@@ -6796,19 +6796,19 @@
         </is>
       </c>
       <c r="G148" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H148" t="n">
         <v>0</v>
       </c>
       <c r="I148" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
       </c>
       <c r="K148" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="149">
@@ -7054,19 +7054,19 @@
         </is>
       </c>
       <c r="G154" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H154" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I154" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J154" t="n">
-        <v>220</v>
+        <v>260</v>
       </c>
       <c r="K154" t="n">
-        <v>231</v>
+        <v>273</v>
       </c>
     </row>
     <row r="155">
@@ -7398,19 +7398,19 @@
         </is>
       </c>
       <c r="G162" t="n">
-        <v>323</v>
+        <v>380</v>
       </c>
       <c r="H162" t="n">
         <v>0</v>
       </c>
       <c r="I162" t="n">
-        <v>323</v>
+        <v>380</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
       </c>
       <c r="K162" t="n">
-        <v>323</v>
+        <v>380</v>
       </c>
     </row>
     <row r="163">
@@ -8089,16 +8089,16 @@
         <v>6</v>
       </c>
       <c r="H178" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I178" t="n">
         <v>0</v>
       </c>
       <c r="J178" t="n">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="K178" t="n">
-        <v>100</v>
+        <v>140</v>
       </c>
     </row>
     <row r="179">
@@ -8185,7 +8185,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2226</v>
+        <v>2447</v>
       </c>
     </row>
     <row r="3">
@@ -8198,7 +8198,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2066</v>
+        <v>2263</v>
       </c>
     </row>
     <row r="4">
@@ -8211,7 +8211,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1838</v>
+        <v>1913</v>
       </c>
     </row>
     <row r="5">
@@ -8220,11 +8220,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BABA11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1731</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="6">
@@ -8233,11 +8233,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>BABA11</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1711</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="7">
@@ -8246,11 +8246,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1657</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="8">
@@ -8259,11 +8259,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>VATSAL11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1624</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="9">
@@ -8272,11 +8272,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>VATSAL11</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1530</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="10">
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1509</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="11">
@@ -8302,7 +8302,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1251</v>
+        <v>1348</v>
       </c>
     </row>
   </sheetData>
@@ -8316,7 +8316,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C163"/>
+  <dimension ref="A1:C164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8369,7 +8369,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>323</v>
+        <v>380</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -8502,7 +8502,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
@@ -8580,7 +8580,7 @@
         <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21">
@@ -8658,7 +8658,7 @@
         <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27">
@@ -8681,7 +8681,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
@@ -8720,7 +8720,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
@@ -8785,7 +8785,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>181</v>
+        <v>232</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
@@ -8824,10 +8824,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>97</v>
+        <v>130</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -8840,7 +8840,7 @@
         <v>0</v>
       </c>
       <c r="C40" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="41">
@@ -8941,7 +8941,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>320</v>
+        <v>349</v>
       </c>
       <c r="C48" t="n">
         <v>0</v>
@@ -8967,7 +8967,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>238</v>
+        <v>312</v>
       </c>
       <c r="C50" t="n">
         <v>0</v>
@@ -9071,10 +9071,10 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C58" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="59">
@@ -9204,7 +9204,7 @@
         <v>6</v>
       </c>
       <c r="C68" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="69">
@@ -9253,7 +9253,7 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>205</v>
+        <v>357</v>
       </c>
       <c r="C72" t="n">
         <v>0</v>
@@ -9539,7 +9539,7 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
@@ -9565,10 +9565,10 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>136</v>
+        <v>172</v>
       </c>
       <c r="C96" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="97">
@@ -9578,7 +9578,7 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>77</v>
+        <v>168</v>
       </c>
       <c r="C97" t="n">
         <v>0</v>
@@ -9600,24 +9600,24 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>pathum nissanka</t>
+          <t>pat cummins</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="C99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>philip salt</t>
+          <t>pathum nissanka</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>202</v>
+        <v>147</v>
       </c>
       <c r="C100" t="n">
         <v>0</v>
@@ -9626,11 +9626,11 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>prabhsimran singh</t>
+          <t>philip salt</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="C101" t="n">
         <v>0</v>
@@ -9639,76 +9639,76 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>praful hinge</t>
+          <t>prabhsimran singh</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0</v>
+        <v>287</v>
       </c>
       <c r="C102" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>prashant veer</t>
+          <t>praful hinge</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="C103" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>prasidh krishna</t>
+          <t>prashant veer</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="C104" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>prince yadav</t>
+          <t>prasidh krishna</t>
         </is>
       </c>
       <c r="B105" t="n">
         <v>0</v>
       </c>
       <c r="C105" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>priyansh arya</t>
+          <t>prince yadav</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>211</v>
+        <v>0</v>
       </c>
       <c r="C106" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>quinton de kock</t>
+          <t>priyansh arya</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>132</v>
+        <v>254</v>
       </c>
       <c r="C107" t="n">
         <v>0</v>
@@ -9717,11 +9717,11 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>rahul chahar</t>
+          <t>quinton de kock</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="C108" t="n">
         <v>0</v>
@@ -9730,11 +9730,11 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>rahul tewatia</t>
+          <t>rahul chahar</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="C109" t="n">
         <v>0</v>
@@ -9743,11 +9743,11 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>rajat patidar</t>
+          <t>rahul tewatia</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>238</v>
+        <v>49</v>
       </c>
       <c r="C110" t="n">
         <v>0</v>
@@ -9756,89 +9756,89 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ramandeep singh</t>
+          <t>rajat patidar</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>76</v>
+        <v>238</v>
       </c>
       <c r="C111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>rashid khan</t>
+          <t>ramandeep singh</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>28</v>
+        <v>76</v>
       </c>
       <c r="C112" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>rasikh salam</t>
+          <t>rashid khan</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="C113" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ravi bishnoi</t>
+          <t>rasikh salam</t>
         </is>
       </c>
       <c r="B114" t="n">
         <v>0</v>
       </c>
       <c r="C114" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ravindra jadeja</t>
+          <t>ravi bishnoi</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="C115" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>rinku singh</t>
+          <t>ravindra jadeja</t>
         </is>
       </c>
       <c r="B116" t="n">
         <v>132</v>
       </c>
       <c r="C116" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>rishabh pant</t>
+          <t>rinku singh</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="C117" t="n">
         <v>0</v>
@@ -9847,63 +9847,63 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>riyan parag</t>
+          <t>rishabh pant</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>81</v>
+        <v>147</v>
       </c>
       <c r="C118" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>rohit sharma</t>
+          <t>riyan parag</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>137</v>
+        <v>88</v>
       </c>
       <c r="C119" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>romario shepherd</t>
+          <t>rohit sharma</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>39</v>
+        <v>137</v>
       </c>
       <c r="C120" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>rovman powell</t>
+          <t>romario shepherd</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>120</v>
+        <v>39</v>
       </c>
       <c r="C121" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ruturaj gaikwad</t>
+          <t>rovman powell</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="C122" t="n">
         <v>0</v>
@@ -9912,11 +9912,11 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ryan rickelton</t>
+          <t>ruturaj gaikwad</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>137</v>
+        <v>104</v>
       </c>
       <c r="C123" t="n">
         <v>0</v>
@@ -9925,37 +9925,37 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>sakib hussain</t>
+          <t>ryan rickelton</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0</v>
+        <v>137</v>
       </c>
       <c r="C124" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>salil arora</t>
+          <t>sakib hussain</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="C125" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>sameer rizvi</t>
+          <t>salil arora</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>209</v>
+        <v>63</v>
       </c>
       <c r="C126" t="n">
         <v>0</v>
@@ -9964,37 +9964,37 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>sandeep sharma</t>
+          <t>sameer rizvi</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0</v>
+        <v>209</v>
       </c>
       <c r="C127" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>sanju samson</t>
+          <t>sandeep sharma</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>293</v>
+        <v>0</v>
       </c>
       <c r="C128" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>sarfaraz khan</t>
+          <t>sanju samson</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>161</v>
+        <v>293</v>
       </c>
       <c r="C129" t="n">
         <v>0</v>
@@ -10003,11 +10003,11 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>shahbaz ahmed</t>
+          <t>sarfaraz khan</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>15</v>
+        <v>161</v>
       </c>
       <c r="C130" t="n">
         <v>0</v>
@@ -10016,11 +10016,11 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>shahrukh khan</t>
+          <t>shahbaz ahmed</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="C131" t="n">
         <v>0</v>
@@ -10029,50 +10029,50 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>shardul thakur</t>
+          <t>shahrukh khan</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="C132" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>shashank singh</t>
+          <t>shardul thakur</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="C133" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>sherfane rutherford</t>
+          <t>shashank singh</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>103</v>
+        <v>70</v>
       </c>
       <c r="C134" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>shimron hetmyer</t>
+          <t>sherfane rutherford</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>61</v>
+        <v>103</v>
       </c>
       <c r="C135" t="n">
         <v>0</v>
@@ -10081,50 +10081,50 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>shivam dube</t>
+          <t>shimron hetmyer</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>128</v>
+        <v>72</v>
       </c>
       <c r="C136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>shivang kumar</t>
+          <t>shivam dube</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>21</v>
+        <v>128</v>
       </c>
       <c r="C137" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>shreyas iyer</t>
+          <t>shivang kumar</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>208</v>
+        <v>21</v>
       </c>
       <c r="C138" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>shubham badriprasad dubey</t>
+          <t>shreyas iyer</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>19</v>
+        <v>279</v>
       </c>
       <c r="C139" t="n">
         <v>0</v>
@@ -10133,11 +10133,11 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>shubman gill</t>
+          <t>shubham badriprasad dubey</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>297</v>
+        <v>19</v>
       </c>
       <c r="C140" t="n">
         <v>0</v>
@@ -10146,76 +10146,76 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>sunil narine</t>
+          <t>shubman gill</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>36</v>
+        <v>297</v>
       </c>
       <c r="C141" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>suryakumar yadav</t>
+          <t>sunil narine</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>157</v>
+        <v>36</v>
       </c>
       <c r="C142" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>suyash sharma</t>
+          <t>suryakumar yadav</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0</v>
+        <v>157</v>
       </c>
       <c r="C143" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>t natarajan</t>
+          <t>suyash sharma</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C144" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>tilak varma</t>
+          <t>t natarajan</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>181</v>
+        <v>1</v>
       </c>
       <c r="C145" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>tim david</t>
+          <t>tilak varma</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C146" t="n">
         <v>0</v>
@@ -10224,11 +10224,11 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>tim seifert</t>
+          <t>tim david</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>19</v>
+        <v>183</v>
       </c>
       <c r="C147" t="n">
         <v>0</v>
@@ -10237,11 +10237,11 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>travis head</t>
+          <t>tim seifert</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>180</v>
+        <v>19</v>
       </c>
       <c r="C148" t="n">
         <v>0</v>
@@ -10250,195 +10250,208 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>trent boult</t>
+          <t>travis head</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>1</v>
+        <v>186</v>
       </c>
       <c r="C149" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>tristan stubbs</t>
+          <t>trent boult</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>196</v>
+        <v>1</v>
       </c>
       <c r="C150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>tushar deshpande</t>
+          <t>tristan stubbs</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>25</v>
+        <v>196</v>
       </c>
       <c r="C151" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>vaibhav arora</t>
+          <t>tushar deshpande</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C152" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>vaibhav suryavanshi</t>
+          <t>vaibhav arora</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>254</v>
+        <v>1</v>
       </c>
       <c r="C153" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>varun chakravarthy</t>
+          <t>vaibhav suryavanshi</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0</v>
+        <v>357</v>
       </c>
       <c r="C154" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>venkatesh iyer</t>
+          <t>varun chakravarthy</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="C155" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>vijaykumar vyshak</t>
+          <t>venkatesh iyer</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="C156" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>vipraj nigam</t>
+          <t>vijaykumar vyshak</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C157" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>virat kohli</t>
+          <t>vipraj nigam</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>328</v>
+        <v>12</v>
       </c>
       <c r="C158" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>washington sundar</t>
+          <t>virat kohli</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>156</v>
+        <v>328</v>
       </c>
       <c r="C159" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>xavier bartlett</t>
+          <t>washington sundar</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>11</v>
+        <v>156</v>
       </c>
       <c r="C160" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>yash raj punja</t>
+          <t>xavier bartlett</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C161" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>yashasvi jaiswal</t>
+          <t>yash raj punja</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>245</v>
+        <v>0</v>
       </c>
       <c r="C162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
+          <t>yashasvi jaiswal</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>255</v>
+      </c>
+      <c r="C163" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
           <t>yuzvendra chahal</t>
         </is>
       </c>
-      <c r="B163" t="n">
-        <v>0</v>
-      </c>
-      <c r="C163" t="n">
+      <c r="B164" t="n">
+        <v>0</v>
+      </c>
+      <c r="C164" t="n">
         <v>4</v>
       </c>
     </row>
@@ -10453,7 +10466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K47"/>
+  <dimension ref="A1:K46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11247,7 +11260,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Pat Cummins</t>
+          <t>Auqib Dar</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -11257,13 +11270,13 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>pathum nissanka</t>
+          <t>auqib nabi</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -11290,23 +11303,23 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Auqib Dar</t>
+          <t>Urvil Patel</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DIPESH11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>auqib nabi</t>
+          <t>axar patel</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -11333,7 +11346,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Urvil Patel</t>
+          <t>Arshin Kulkarni</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -11349,7 +11362,7 @@
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>axar patel</t>
+          <t>ashwani kumar</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -11376,7 +11389,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Arshin Kulkarni</t>
+          <t>Nishant Sindhu</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -11386,13 +11399,13 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ashwani kumar</t>
+          <t>shashank singh</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -11419,7 +11432,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Nishant Sindhu</t>
+          <t>Jayant Yadav</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -11435,7 +11448,7 @@
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>shashank singh</t>
+          <t>mayank yadav</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -11462,7 +11475,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Jayant Yadav</t>
+          <t>Ajay Mandal</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -11478,7 +11491,7 @@
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>mayank yadav</t>
+          <t>rajat patidar</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -11505,7 +11518,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Ajay Mandal</t>
+          <t>Will Jacks</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11521,7 +11534,7 @@
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>rajat patidar</t>
+          <t>mitchell marsh</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -11548,7 +11561,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Will Jacks</t>
+          <t>Kyle Jamieson</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11558,13 +11571,13 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>mitchell marsh</t>
+          <t>jamie overton</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -11591,7 +11604,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Kyle Jamieson</t>
+          <t>Matheesha Pathirana</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11607,7 +11620,7 @@
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>jamie overton</t>
+          <t>eshan malinga</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -11634,7 +11647,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Matheesha Pathirana</t>
+          <t>Ben Dwarshuis</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -11650,7 +11663,7 @@
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>eshan malinga</t>
+          <t>b sai sudharshan</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -11677,23 +11690,23 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Ben Dwarshuis</t>
+          <t>Manish Pandey</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>b sai sudharshan</t>
+          <t>hardik pandya</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -11720,7 +11733,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Manish Pandey</t>
+          <t>Arjun Tendulkar</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -11730,13 +11743,13 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>hardik pandya</t>
+          <t>karun nair</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -11763,7 +11776,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Arjun Tendulkar</t>
+          <t>Kwena Maphaka</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -11779,7 +11792,7 @@
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>karun nair</t>
+          <t>aiden markram</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -11806,23 +11819,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Kwena Maphaka</t>
+          <t>Ramkrishna Ghosh</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>aiden markram</t>
+          <t>angkrish raghuvanshi</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -11849,7 +11862,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Ramkrishna Ghosh</t>
+          <t>Azmatullah Omarzai</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -11859,13 +11872,13 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>angkrish raghuvanshi</t>
+          <t>mitchell marsh</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -11892,23 +11905,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Azmatullah Omarzai</t>
+          <t>akshat raghuwanshi</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>mitchell marsh</t>
+          <t>angkrish raghuvanshi</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -11935,7 +11948,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>akshat raghuwanshi</t>
+          <t>Suryansh Shegde</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -11951,7 +11964,7 @@
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>angkrish raghuvanshi</t>
+          <t>suyash sharma</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -11978,7 +11991,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Suryansh Shegde</t>
+          <t>Tejasvi Singh</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -11994,7 +12007,7 @@
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>suyash sharma</t>
+          <t>prabhsimran singh</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -12021,7 +12034,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Tejasvi Singh</t>
+          <t>Sai Kishor</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -12031,13 +12044,13 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>prabhsimran singh</t>
+          <t>ishan kishan</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -12064,7 +12077,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sai Kishor</t>
+          <t>Akash Deep</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -12080,7 +12093,7 @@
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>ishan kishan</t>
+          <t>arshdeep singh</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -12107,23 +12120,23 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Akash Deep</t>
+          <t>Ben Duckett</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>arshdeep singh</t>
+          <t>ryan rickelton</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -12150,7 +12163,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Ben Duckett</t>
+          <t>Abhishek Porel</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -12166,7 +12179,7 @@
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>ryan rickelton</t>
+          <t>abhishek sharma</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -12193,7 +12206,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Abhishek Porel</t>
+          <t>Rahul Tripathi</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -12209,7 +12222,7 @@
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>abhishek sharma</t>
+          <t>rahul tewatia</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -12236,7 +12249,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Rahul Tripathi</t>
+          <t>Dre Pretorius</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -12252,7 +12265,7 @@
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>rahul tewatia</t>
+          <t>lhuan dre pretorius</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -12279,7 +12292,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Dre Pretorius</t>
+          <t>Matthew Breetzke</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -12295,7 +12308,7 @@
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>lhuan dre pretorius</t>
+          <t>matt henry</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -12322,7 +12335,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Matthew Breetzke</t>
+          <t>Anuj Rawat</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -12338,7 +12351,7 @@
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>matt henry</t>
+          <t>mayank rawat</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -12365,7 +12378,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Anuj Rawat</t>
+          <t>Wanindu Hasaranga</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -12375,13 +12388,13 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>mayank rawat</t>
+          <t>sandeep sharma</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -12408,7 +12421,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Wanindu Hasaranga</t>
+          <t>Harpreet Brar</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -12418,13 +12431,13 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>sandeep sharma</t>
+          <t>jasprit bumrah</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -12445,49 +12458,6 @@
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Harpreet Brar</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>BOWL</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>jasprit bumrah</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="G47" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" t="n">
-        <v>0</v>
-      </c>
-      <c r="K47" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12661,19 +12631,19 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>97</v>
+        <v>130</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>97</v>
+        <v>130</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K2" t="n">
-        <v>97</v>
+        <v>150</v>
       </c>
     </row>
   </sheetData>

--- a/IPL_Fantasy_Points.xlsx
+++ b/IPL_Fantasy_Points.xlsx
@@ -561,19 +561,19 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>147</v>
+        <v>189</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>147</v>
+        <v>189</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>147</v>
+        <v>189</v>
       </c>
     </row>
     <row r="4">
@@ -733,19 +733,19 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>43</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9">
@@ -862,19 +862,19 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>162</v>
+        <v>196</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I10" t="n">
-        <v>162</v>
+        <v>196</v>
       </c>
       <c r="J10" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="K10" t="n">
-        <v>182</v>
+        <v>236</v>
       </c>
     </row>
     <row r="11">
@@ -908,16 +908,16 @@
         <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I11" t="n">
         <v>2</v>
       </c>
       <c r="J11" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="K11" t="n">
-        <v>102</v>
+        <v>122</v>
       </c>
     </row>
     <row r="12">
@@ -951,16 +951,16 @@
         <v>39</v>
       </c>
       <c r="H12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I12" t="n">
         <v>39</v>
       </c>
       <c r="J12" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="K12" t="n">
-        <v>119</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13">
@@ -994,16 +994,16 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="K13" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14">
@@ -1037,16 +1037,16 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>80</v>
+        <v>180</v>
       </c>
       <c r="K14" t="n">
-        <v>80</v>
+        <v>180</v>
       </c>
     </row>
     <row r="15">
@@ -1249,19 +1249,19 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>297</v>
+        <v>330</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>297</v>
+        <v>330</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>297</v>
+        <v>330</v>
       </c>
     </row>
     <row r="20">
@@ -1292,19 +1292,19 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>152</v>
+        <v>162</v>
       </c>
     </row>
     <row r="21">
@@ -1378,19 +1378,19 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H22" t="n">
         <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
     </row>
     <row r="23">
@@ -2754,19 +2754,19 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>293</v>
+        <v>304</v>
       </c>
     </row>
     <row r="55">
@@ -2926,19 +2926,19 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>148</v>
+        <v>172</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>148</v>
+        <v>172</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>148</v>
+        <v>172</v>
       </c>
     </row>
     <row r="59">
@@ -3055,19 +3055,19 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>132</v>
+        <v>215</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>132</v>
+        <v>215</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>132</v>
+        <v>215</v>
       </c>
     </row>
     <row r="62">
@@ -3098,19 +3098,19 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>128</v>
+        <v>150</v>
       </c>
       <c r="H62" t="n">
         <v>1</v>
       </c>
       <c r="I62" t="n">
-        <v>128</v>
+        <v>150</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>128</v>
+        <v>150</v>
       </c>
     </row>
     <row r="63">
@@ -3141,19 +3141,19 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="64">
@@ -3359,16 +3359,16 @@
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I68" t="n">
         <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="K68" t="n">
-        <v>100</v>
+        <v>140</v>
       </c>
     </row>
     <row r="69">
@@ -3528,19 +3528,19 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>104</v>
+        <v>178</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>104</v>
+        <v>178</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>104</v>
+        <v>178</v>
       </c>
     </row>
     <row r="73">
@@ -3571,19 +3571,19 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>235</v>
+        <v>322</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>235</v>
+        <v>322</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>235</v>
+        <v>322</v>
       </c>
     </row>
     <row r="74">
@@ -3915,19 +3915,19 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>162</v>
+        <v>193</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>162</v>
+        <v>193</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>162</v>
+        <v>193</v>
       </c>
     </row>
     <row r="82">
@@ -4431,19 +4431,19 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>231</v>
+        <v>270</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>231</v>
+        <v>270</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>231</v>
+        <v>270</v>
       </c>
     </row>
     <row r="94">
@@ -4462,31 +4462,31 @@
           <t>BAT</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>axar patel</t>
-        </is>
-      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>urvil patel</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="G94" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H94" t="n">
         <v>0</v>
       </c>
       <c r="I94" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="95">
@@ -4778,16 +4778,16 @@
         <v>35</v>
       </c>
       <c r="H101" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I101" t="n">
         <v>0</v>
       </c>
       <c r="J101" t="n">
-        <v>200</v>
+        <v>260</v>
       </c>
       <c r="K101" t="n">
-        <v>200</v>
+        <v>260</v>
       </c>
     </row>
     <row r="102">
@@ -5119,19 +5119,19 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="H109" t="n">
         <v>0</v>
       </c>
       <c r="I109" t="n">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
       </c>
       <c r="K109" t="n">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="110">
@@ -5377,19 +5377,19 @@
         </is>
       </c>
       <c r="G115" t="n">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="H115" t="n">
         <v>9</v>
       </c>
       <c r="I115" t="n">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="J115" t="n">
         <v>180</v>
       </c>
       <c r="K115" t="n">
-        <v>298</v>
+        <v>316</v>
       </c>
     </row>
     <row r="116">
@@ -5509,16 +5509,16 @@
         <v>11</v>
       </c>
       <c r="H118" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I118" t="n">
         <v>0</v>
       </c>
       <c r="J118" t="n">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="K118" t="n">
-        <v>160</v>
+        <v>180</v>
       </c>
     </row>
     <row r="119">
@@ -6194,19 +6194,19 @@
         </is>
       </c>
       <c r="G134" t="n">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
       </c>
       <c r="I134" t="n">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
       </c>
       <c r="K134" t="n">
-        <v>200</v>
+        <v>209</v>
       </c>
     </row>
     <row r="135">
@@ -6280,19 +6280,19 @@
         </is>
       </c>
       <c r="G136" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H136" t="n">
         <v>1</v>
       </c>
       <c r="I136" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J136" t="n">
         <v>20</v>
       </c>
       <c r="K136" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="137">
@@ -6538,7 +6538,7 @@
         </is>
       </c>
       <c r="G142" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="H142" t="n">
         <v>7</v>
@@ -6710,19 +6710,19 @@
         </is>
       </c>
       <c r="G146" t="n">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="H146" t="n">
         <v>0</v>
       </c>
       <c r="I146" t="n">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
       </c>
       <c r="K146" t="n">
-        <v>73</v>
+        <v>82</v>
       </c>
     </row>
     <row r="147">
@@ -6882,19 +6882,19 @@
         </is>
       </c>
       <c r="G150" t="n">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
       </c>
       <c r="I150" t="n">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
       </c>
       <c r="K150" t="n">
-        <v>16</v>
+        <v>35</v>
       </c>
     </row>
     <row r="151">
@@ -7229,16 +7229,16 @@
         <v>1</v>
       </c>
       <c r="H158" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I158" t="n">
         <v>0</v>
       </c>
       <c r="J158" t="n">
-        <v>140</v>
+        <v>180</v>
       </c>
       <c r="K158" t="n">
-        <v>140</v>
+        <v>180</v>
       </c>
     </row>
     <row r="159">
@@ -7828,19 +7828,19 @@
         </is>
       </c>
       <c r="G172" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H172" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I172" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J172" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="K172" t="n">
-        <v>156</v>
+        <v>180</v>
       </c>
     </row>
     <row r="173">
@@ -8132,16 +8132,16 @@
         <v>10</v>
       </c>
       <c r="H179" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I179" t="n">
         <v>0</v>
       </c>
       <c r="J179" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="K179" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -8185,7 +8185,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2447</v>
+        <v>2639</v>
       </c>
     </row>
     <row r="3">
@@ -8198,7 +8198,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2263</v>
+        <v>2312</v>
       </c>
     </row>
     <row r="4">
@@ -8207,11 +8207,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>BABA11</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1913</v>
+        <v>1966</v>
       </c>
     </row>
     <row r="5">
@@ -8220,11 +8220,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1845</v>
+        <v>1953</v>
       </c>
     </row>
     <row r="6">
@@ -8233,11 +8233,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BABA11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1785</v>
+        <v>1913</v>
       </c>
     </row>
     <row r="7">
@@ -8250,7 +8250,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1770</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="8">
@@ -8259,11 +8259,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>NIRAV11</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1704</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="9">
@@ -8272,11 +8272,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>VATSAL11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1693</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="10">
@@ -8285,11 +8285,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NIRAV11</t>
+          <t>VATSAL11</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1515</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="11">
@@ -8302,7 +8302,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1348</v>
+        <v>1392</v>
       </c>
     </row>
   </sheetData>
@@ -8316,7 +8316,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C164"/>
+  <dimension ref="A1:C166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8382,7 +8382,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>162</v>
+        <v>193</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -8395,7 +8395,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -8411,7 +8411,7 @@
         <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -8434,7 +8434,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -8489,121 +8489,121 @@
         <v>39</v>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>arshdeep singh</t>
+          <t>arshad khan</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ashok sharma</t>
+          <t>arshdeep singh</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ashutosh sharma</t>
+          <t>ashok sharma</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ashwani kumar</t>
+          <t>ashutosh sharma</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="C17" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>auqib nabi</t>
+          <t>ashwani kumar</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>avesh khan</t>
+          <t>auqib nabi</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>axar patel</t>
+          <t>avesh khan</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ayush badoni</t>
+          <t>axar patel</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>148</v>
+        <v>31</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ayush mhatre</t>
+          <t>ayush badoni</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>201</v>
+        <v>172</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
@@ -8612,11 +8612,11 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>b sai sudharshan</t>
+          <t>ayush mhatre</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>235</v>
+        <v>201</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
@@ -8625,102 +8625,102 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>bhuvneshwar kumar</t>
+          <t>b sai sudharshan</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>12</v>
+        <v>322</v>
       </c>
       <c r="C24" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>blessing muzarabani</t>
+          <t>bhuvneshwar kumar</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C25" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>brijesh sharma</t>
+          <t>blessing muzarabani</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>cameron green</t>
+          <t>brijesh sharma</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>162</v>
+        <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>cooper connolly</t>
+          <t>cameron green</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>240</v>
+        <v>196</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>corbin bosch</t>
+          <t>cooper connolly</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>11</v>
+        <v>240</v>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>danish malewar</t>
+          <t>corbin bosch</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>david miller</t>
+          <t>danish malewar</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>104</v>
+        <v>2</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
@@ -8729,50 +8729,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>david payne</t>
+          <t>david miller</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>6</v>
+        <v>104</v>
       </c>
       <c r="C32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>deepak chahar</t>
+          <t>david payne</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>6</v>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>devdutt padikkal</t>
+          <t>deepak chahar</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>208</v>
+        <v>6</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>dewald brevis</t>
+          <t>devdutt padikkal</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>62</v>
+        <v>208</v>
       </c>
       <c r="C35" t="n">
         <v>0</v>
@@ -8781,11 +8781,11 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>dhruv chand jurel</t>
+          <t>dewald brevis</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>232</v>
+        <v>64</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
@@ -8794,37 +8794,37 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>digvesh rathi</t>
+          <t>dhruv chand jurel</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2</v>
+        <v>232</v>
       </c>
       <c r="C37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>dilshan madushanka</t>
+          <t>digvesh rathi</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>donavon ferreira</t>
+          <t>dilshan madushanka</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="C39" t="n">
         <v>1</v>
@@ -8833,37 +8833,37 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>eshan malinga</t>
+          <t>donavon ferreira</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="C40" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>finn allen</t>
+          <t>eshan malinga</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>george linde</t>
+          <t>finn allen</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>23</v>
+        <v>81</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
@@ -8872,37 +8872,37 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>glenn phillips</t>
+          <t>george linde</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>67</v>
+        <v>31</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>gurjapneet singh</t>
+          <t>glenn phillips</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="C44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>hardik pandya</t>
+          <t>gurjapneet singh</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="C45" t="n">
         <v>3</v>
@@ -8911,37 +8911,37 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>harsh dubey</t>
+          <t>hardik pandya</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>13</v>
+        <v>97</v>
       </c>
       <c r="C46" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>harshal patel</t>
+          <t>harsh dubey</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>heinrich klaasen</t>
+          <t>harshal patel</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>349</v>
+        <v>4</v>
       </c>
       <c r="C48" t="n">
         <v>0</v>
@@ -8950,11 +8950,11 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>himmat singh</t>
+          <t>heinrich klaasen</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>16</v>
+        <v>349</v>
       </c>
       <c r="C49" t="n">
         <v>0</v>
@@ -8963,11 +8963,11 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ishan kishan</t>
+          <t>himmat singh</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>312</v>
+        <v>35</v>
       </c>
       <c r="C50" t="n">
         <v>0</v>
@@ -8976,11 +8976,11 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>jacob bethell</t>
+          <t>ishan kishan</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>14</v>
+        <v>312</v>
       </c>
       <c r="C51" t="n">
         <v>0</v>
@@ -8989,245 +8989,245 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>jacob duffy</t>
+          <t>jacob bethell</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="C52" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>jamie overton</t>
+          <t>jacob duffy</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>118</v>
+        <v>0</v>
       </c>
       <c r="C53" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>jason holder</t>
+          <t>jamie overton</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>23</v>
+        <v>136</v>
       </c>
       <c r="C54" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>jasprit bumrah</t>
+          <t>jason holder</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="C55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>jaydev unadkat</t>
+          <t>jasprit bumrah</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C56" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>jitesh sharma</t>
+          <t>jaydev unadkat</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>62</v>
+        <v>4</v>
       </c>
       <c r="C57" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>jofra archer</t>
+          <t>jitesh sharma</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>13</v>
+        <v>62</v>
       </c>
       <c r="C58" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>jos buttler</t>
+          <t>jofra archer</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>231</v>
+        <v>13</v>
       </c>
       <c r="C59" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>josh hazlewood</t>
+          <t>jos buttler</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="C60" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>kagiso rabada</t>
+          <t>josh hazlewood</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="C61" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>kartik sharma</t>
+          <t>kagiso rabada</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C62" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>kartik tyagi</t>
+          <t>kartik sharma</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>11</v>
+        <v>58</v>
       </c>
       <c r="C63" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>karun nair</t>
+          <t>kartik tyagi</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C64" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>khaleel ahmed</t>
+          <t>karun nair</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C65" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>krish bhagat</t>
+          <t>khaleel ahmed</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>krunal pandya</t>
+          <t>krish bhagat</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="C67" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>kuldeep yadav</t>
+          <t>krunal pandya</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="C68" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>kumar kushagra</t>
+          <t>kuldeep yadav</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C69" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>lhuan dre pretorius</t>
+          <t>kumar kushagra</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C70" t="n">
         <v>0</v>
@@ -9236,11 +9236,11 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>liam livingstone</t>
+          <t>lhuan dre pretorius</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="C71" t="n">
         <v>0</v>
@@ -9249,11 +9249,11 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>lokesh rahul</t>
+          <t>liam livingstone</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>357</v>
+        <v>15</v>
       </c>
       <c r="C72" t="n">
         <v>0</v>
@@ -9262,102 +9262,102 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>lungi ngidi</t>
+          <t>lokesh rahul</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>3</v>
+        <v>357</v>
       </c>
       <c r="C73" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>manav suthar</t>
+          <t>lungi ngidi</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C74" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>manimaran siddharth</t>
+          <t>manav suthar</t>
         </is>
       </c>
       <c r="B75" t="n">
         <v>0</v>
       </c>
       <c r="C75" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>marco jansen</t>
+          <t>manimaran siddharth</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C76" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>marcus stoinis</t>
+          <t>marco jansen</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="C77" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>matt henry</t>
+          <t>marcus stoinis</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="C78" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>matt short</t>
+          <t>matt henry</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="C79" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>mayank markande</t>
+          <t>matt short</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="C80" t="n">
         <v>0</v>
@@ -9366,7 +9366,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>mayank rawat</t>
+          <t>mayank markande</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -9379,11 +9379,11 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>mayank yadav</t>
+          <t>mayank rawat</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
@@ -9392,11 +9392,11 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>mitchell marsh</t>
+          <t>mayank yadav</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>210</v>
+        <v>5</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
@@ -9405,37 +9405,37 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>mitchell santner</t>
+          <t>mitchell marsh</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>26</v>
+        <v>212</v>
       </c>
       <c r="C84" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>mohammed shami</t>
+          <t>mitchell santner</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C85" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>mohammed siraj</t>
+          <t>mohammed shami</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="C86" t="n">
         <v>7</v>
@@ -9444,63 +9444,63 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>mohsin khan</t>
+          <t>mohammed siraj</t>
         </is>
       </c>
       <c r="B87" t="n">
         <v>0</v>
       </c>
       <c r="C87" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>mukesh choudhary</t>
+          <t>mohsin khan</t>
         </is>
       </c>
       <c r="B88" t="n">
         <v>0</v>
       </c>
       <c r="C88" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>mukesh kumar</t>
+          <t>mukesh choudhary</t>
         </is>
       </c>
       <c r="B89" t="n">
         <v>0</v>
       </c>
       <c r="C89" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>mukul choudhary</t>
+          <t>mukesh kumar</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>155</v>
+        <v>0</v>
       </c>
       <c r="C90" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>naman dhir</t>
+          <t>mukul choudhary</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
@@ -9509,37 +9509,37 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>nandre burger</t>
+          <t>naman dhir</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>3</v>
+        <v>154</v>
       </c>
       <c r="C92" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>navdeep saini</t>
+          <t>nandre burger</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C93" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>nehal wadhera</t>
+          <t>navdeep saini</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
@@ -9548,11 +9548,11 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>nicholas pooran</t>
+          <t>nehal wadhera</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
@@ -9561,76 +9561,76 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>nitish kumar reddy</t>
+          <t>nicholas pooran</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>172</v>
+        <v>82</v>
       </c>
       <c r="C96" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>nitish rana</t>
+          <t>nitish kumar reddy</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C97" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>noor ahmad</t>
+          <t>nitish rana</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>10</v>
+        <v>168</v>
       </c>
       <c r="C98" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>pat cummins</t>
+          <t>noor ahmad</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C99" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>pathum nissanka</t>
+          <t>pat cummins</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>147</v>
+        <v>0</v>
       </c>
       <c r="C100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>philip salt</t>
+          <t>pathum nissanka</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>202</v>
+        <v>147</v>
       </c>
       <c r="C101" t="n">
         <v>0</v>
@@ -9639,11 +9639,11 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>prabhsimran singh</t>
+          <t>philip salt</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>287</v>
+        <v>202</v>
       </c>
       <c r="C102" t="n">
         <v>0</v>
@@ -9652,76 +9652,76 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>praful hinge</t>
+          <t>prabhsimran singh</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0</v>
+        <v>287</v>
       </c>
       <c r="C103" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>prashant veer</t>
+          <t>praful hinge</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="C104" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>prasidh krishna</t>
+          <t>prashant veer</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="C105" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>prince yadav</t>
+          <t>prasidh krishna</t>
         </is>
       </c>
       <c r="B106" t="n">
         <v>0</v>
       </c>
       <c r="C106" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>priyansh arya</t>
+          <t>prince yadav</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>254</v>
+        <v>0</v>
       </c>
       <c r="C107" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>quinton de kock</t>
+          <t>priyansh arya</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>132</v>
+        <v>254</v>
       </c>
       <c r="C108" t="n">
         <v>0</v>
@@ -9730,11 +9730,11 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>rahul chahar</t>
+          <t>quinton de kock</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="C109" t="n">
         <v>0</v>
@@ -9743,11 +9743,11 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>rahul tewatia</t>
+          <t>rahul chahar</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="C110" t="n">
         <v>0</v>
@@ -9756,11 +9756,11 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>rajat patidar</t>
+          <t>rahul tewatia</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>238</v>
+        <v>49</v>
       </c>
       <c r="C111" t="n">
         <v>0</v>
@@ -9769,89 +9769,89 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ramandeep singh</t>
+          <t>rajat patidar</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>76</v>
+        <v>238</v>
       </c>
       <c r="C112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>rashid khan</t>
+          <t>ramandeep singh</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>28</v>
+        <v>82</v>
       </c>
       <c r="C113" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>rasikh salam</t>
+          <t>rashid khan</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="C114" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ravi bishnoi</t>
+          <t>rasikh salam</t>
         </is>
       </c>
       <c r="B115" t="n">
         <v>0</v>
       </c>
       <c r="C115" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ravindra jadeja</t>
+          <t>ravi bishnoi</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="C116" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>rinku singh</t>
+          <t>ravindra jadeja</t>
         </is>
       </c>
       <c r="B117" t="n">
         <v>132</v>
       </c>
       <c r="C117" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>rishabh pant</t>
+          <t>rinku singh</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>147</v>
+        <v>215</v>
       </c>
       <c r="C118" t="n">
         <v>0</v>
@@ -9860,63 +9860,63 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>riyan parag</t>
+          <t>rishabh pant</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>88</v>
+        <v>189</v>
       </c>
       <c r="C119" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>rohit sharma</t>
+          <t>riyan parag</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>137</v>
+        <v>88</v>
       </c>
       <c r="C120" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>romario shepherd</t>
+          <t>rohit sharma</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>39</v>
+        <v>137</v>
       </c>
       <c r="C121" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>rovman powell</t>
+          <t>romario shepherd</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>120</v>
+        <v>39</v>
       </c>
       <c r="C122" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ruturaj gaikwad</t>
+          <t>rovman powell</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="C123" t="n">
         <v>0</v>
@@ -9925,11 +9925,11 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ryan rickelton</t>
+          <t>ruturaj gaikwad</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>137</v>
+        <v>178</v>
       </c>
       <c r="C124" t="n">
         <v>0</v>
@@ -9938,37 +9938,37 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>sakib hussain</t>
+          <t>ryan rickelton</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0</v>
+        <v>137</v>
       </c>
       <c r="C125" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>salil arora</t>
+          <t>sakib hussain</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="C126" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>sameer rizvi</t>
+          <t>salil arora</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>209</v>
+        <v>63</v>
       </c>
       <c r="C127" t="n">
         <v>0</v>
@@ -9977,37 +9977,37 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>sandeep sharma</t>
+          <t>sameer rizvi</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0</v>
+        <v>209</v>
       </c>
       <c r="C128" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>sanju samson</t>
+          <t>sandeep sharma</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>293</v>
+        <v>0</v>
       </c>
       <c r="C129" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>sarfaraz khan</t>
+          <t>sanju samson</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>161</v>
+        <v>304</v>
       </c>
       <c r="C130" t="n">
         <v>0</v>
@@ -10016,11 +10016,11 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>shahbaz ahmed</t>
+          <t>sarfaraz khan</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>15</v>
+        <v>161</v>
       </c>
       <c r="C131" t="n">
         <v>0</v>
@@ -10029,11 +10029,11 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>shahrukh khan</t>
+          <t>shahbaz ahmed</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="C132" t="n">
         <v>0</v>
@@ -10042,50 +10042,50 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>shardul thakur</t>
+          <t>shahrukh khan</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="C133" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>shashank singh</t>
+          <t>shardul thakur</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>70</v>
+        <v>14</v>
       </c>
       <c r="C134" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>sherfane rutherford</t>
+          <t>shashank singh</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>103</v>
+        <v>70</v>
       </c>
       <c r="C135" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>shimron hetmyer</t>
+          <t>sherfane rutherford</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>72</v>
+        <v>103</v>
       </c>
       <c r="C136" t="n">
         <v>0</v>
@@ -10094,50 +10094,50 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>shivam dube</t>
+          <t>shimron hetmyer</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>128</v>
+        <v>72</v>
       </c>
       <c r="C137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>shivang kumar</t>
+          <t>shivam dube</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>21</v>
+        <v>150</v>
       </c>
       <c r="C138" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>shreyas iyer</t>
+          <t>shivang kumar</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>279</v>
+        <v>21</v>
       </c>
       <c r="C139" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>shubham badriprasad dubey</t>
+          <t>shreyas iyer</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>19</v>
+        <v>279</v>
       </c>
       <c r="C140" t="n">
         <v>0</v>
@@ -10146,11 +10146,11 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>shubman gill</t>
+          <t>shubham badriprasad dubey</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>297</v>
+        <v>19</v>
       </c>
       <c r="C141" t="n">
         <v>0</v>
@@ -10159,76 +10159,76 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>sunil narine</t>
+          <t>shubman gill</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>36</v>
+        <v>330</v>
       </c>
       <c r="C142" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>suryakumar yadav</t>
+          <t>sunil narine</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>157</v>
+        <v>40</v>
       </c>
       <c r="C143" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>suyash sharma</t>
+          <t>suryakumar yadav</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0</v>
+        <v>157</v>
       </c>
       <c r="C144" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>t natarajan</t>
+          <t>suyash sharma</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C145" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>tilak varma</t>
+          <t>t natarajan</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>181</v>
+        <v>1</v>
       </c>
       <c r="C146" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>tim david</t>
+          <t>tilak varma</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C147" t="n">
         <v>0</v>
@@ -10237,11 +10237,11 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>tim seifert</t>
+          <t>tim david</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>19</v>
+        <v>183</v>
       </c>
       <c r="C148" t="n">
         <v>0</v>
@@ -10250,11 +10250,11 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>travis head</t>
+          <t>tim seifert</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>186</v>
+        <v>19</v>
       </c>
       <c r="C149" t="n">
         <v>0</v>
@@ -10263,63 +10263,63 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>trent boult</t>
+          <t>travis head</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>1</v>
+        <v>186</v>
       </c>
       <c r="C150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>tristan stubbs</t>
+          <t>trent boult</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>196</v>
+        <v>1</v>
       </c>
       <c r="C151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>tushar deshpande</t>
+          <t>tristan stubbs</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>25</v>
+        <v>196</v>
       </c>
       <c r="C152" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>vaibhav arora</t>
+          <t>tushar deshpande</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C153" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>vaibhav suryavanshi</t>
+          <t>urvil patel</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>357</v>
+        <v>4</v>
       </c>
       <c r="C154" t="n">
         <v>0</v>
@@ -10328,24 +10328,24 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>varun chakravarthy</t>
+          <t>vaibhav arora</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C155" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>venkatesh iyer</t>
+          <t>vaibhav suryavanshi</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>29</v>
+        <v>357</v>
       </c>
       <c r="C156" t="n">
         <v>0</v>
@@ -10354,76 +10354,76 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>vijaykumar vyshak</t>
+          <t>varun chakravarthy</t>
         </is>
       </c>
       <c r="B157" t="n">
         <v>0</v>
       </c>
       <c r="C157" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>vipraj nigam</t>
+          <t>venkatesh iyer</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="C158" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>virat kohli</t>
+          <t>vijaykumar vyshak</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>328</v>
+        <v>0</v>
       </c>
       <c r="C159" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>washington sundar</t>
+          <t>vipraj nigam</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>156</v>
+        <v>12</v>
       </c>
       <c r="C160" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>xavier bartlett</t>
+          <t>virat kohli</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>11</v>
+        <v>328</v>
       </c>
       <c r="C161" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>yash raj punja</t>
+          <t>washington sundar</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>0</v>
+        <v>157</v>
       </c>
       <c r="C162" t="n">
         <v>1</v>
@@ -10432,26 +10432,52 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>yashasvi jaiswal</t>
+          <t>xavier bartlett</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>255</v>
+        <v>11</v>
       </c>
       <c r="C163" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
+          <t>yash raj punja</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>0</v>
+      </c>
+      <c r="C164" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>yashasvi jaiswal</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>255</v>
+      </c>
+      <c r="C165" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
           <t>yuzvendra chahal</t>
         </is>
       </c>
-      <c r="B164" t="n">
-        <v>0</v>
-      </c>
-      <c r="C164" t="n">
+      <c r="B166" t="n">
+        <v>0</v>
+      </c>
+      <c r="C166" t="n">
         <v>4</v>
       </c>
     </row>
@@ -10466,7 +10492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K46"/>
+  <dimension ref="A1:K45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11303,7 +11329,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Urvil Patel</t>
+          <t>Arshin Kulkarni</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -11319,7 +11345,7 @@
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>axar patel</t>
+          <t>ashwani kumar</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -11346,7 +11372,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Arshin Kulkarni</t>
+          <t>Nishant Sindhu</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -11356,13 +11382,13 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ashwani kumar</t>
+          <t>shashank singh</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -11389,7 +11415,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Nishant Sindhu</t>
+          <t>Jayant Yadav</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -11405,7 +11431,7 @@
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>shashank singh</t>
+          <t>mayank yadav</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -11432,7 +11458,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Jayant Yadav</t>
+          <t>Ajay Mandal</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -11448,7 +11474,7 @@
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>mayank yadav</t>
+          <t>rajat patidar</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -11475,7 +11501,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Ajay Mandal</t>
+          <t>Will Jacks</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -11491,7 +11517,7 @@
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>rajat patidar</t>
+          <t>mitchell marsh</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -11518,7 +11544,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Will Jacks</t>
+          <t>Kyle Jamieson</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11528,13 +11554,13 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>mitchell marsh</t>
+          <t>jamie overton</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -11561,7 +11587,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Kyle Jamieson</t>
+          <t>Matheesha Pathirana</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11577,7 +11603,7 @@
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>jamie overton</t>
+          <t>eshan malinga</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -11604,7 +11630,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Matheesha Pathirana</t>
+          <t>Ben Dwarshuis</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11620,7 +11646,7 @@
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>eshan malinga</t>
+          <t>b sai sudharshan</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -11647,23 +11673,23 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Ben Dwarshuis</t>
+          <t>Manish Pandey</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>b sai sudharshan</t>
+          <t>hardik pandya</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -11690,7 +11716,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Manish Pandey</t>
+          <t>Arjun Tendulkar</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -11700,13 +11726,13 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>hardik pandya</t>
+          <t>karun nair</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -11733,7 +11759,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Arjun Tendulkar</t>
+          <t>Kwena Maphaka</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -11749,7 +11775,7 @@
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>karun nair</t>
+          <t>aiden markram</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -11776,23 +11802,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Kwena Maphaka</t>
+          <t>Ramkrishna Ghosh</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>aiden markram</t>
+          <t>angkrish raghuvanshi</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -11819,7 +11845,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Ramkrishna Ghosh</t>
+          <t>Azmatullah Omarzai</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -11829,13 +11855,13 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>angkrish raghuvanshi</t>
+          <t>mitchell marsh</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -11862,23 +11888,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Azmatullah Omarzai</t>
+          <t>akshat raghuwanshi</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>mitchell marsh</t>
+          <t>angkrish raghuvanshi</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -11905,7 +11931,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>akshat raghuwanshi</t>
+          <t>Suryansh Shegde</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -11921,7 +11947,7 @@
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>angkrish raghuvanshi</t>
+          <t>suyash sharma</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -11948,7 +11974,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Suryansh Shegde</t>
+          <t>Tejasvi Singh</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -11964,7 +11990,7 @@
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>suyash sharma</t>
+          <t>prabhsimran singh</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -11991,7 +12017,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Tejasvi Singh</t>
+          <t>Sai Kishor</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -12001,13 +12027,13 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>prabhsimran singh</t>
+          <t>ishan kishan</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -12034,7 +12060,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sai Kishor</t>
+          <t>Akash Deep</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -12050,7 +12076,7 @@
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>ishan kishan</t>
+          <t>arshdeep singh</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -12077,23 +12103,23 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Akash Deep</t>
+          <t>Ben Duckett</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>arshdeep singh</t>
+          <t>ryan rickelton</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -12120,7 +12146,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Ben Duckett</t>
+          <t>Abhishek Porel</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -12136,7 +12162,7 @@
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>ryan rickelton</t>
+          <t>abhishek sharma</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -12163,7 +12189,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Abhishek Porel</t>
+          <t>Rahul Tripathi</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -12179,7 +12205,7 @@
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>abhishek sharma</t>
+          <t>rahul tewatia</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -12206,7 +12232,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Rahul Tripathi</t>
+          <t>Dre Pretorius</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -12222,7 +12248,7 @@
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>rahul tewatia</t>
+          <t>lhuan dre pretorius</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -12249,7 +12275,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Dre Pretorius</t>
+          <t>Matthew Breetzke</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -12265,7 +12291,7 @@
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>lhuan dre pretorius</t>
+          <t>matt henry</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -12292,7 +12318,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Matthew Breetzke</t>
+          <t>Anuj Rawat</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -12308,7 +12334,7 @@
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>matt henry</t>
+          <t>mayank rawat</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -12335,7 +12361,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Anuj Rawat</t>
+          <t>Wanindu Hasaranga</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -12345,13 +12371,13 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>mayank rawat</t>
+          <t>sandeep sharma</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -12378,7 +12404,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Wanindu Hasaranga</t>
+          <t>Harpreet Brar</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -12388,13 +12414,13 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>sandeep sharma</t>
+          <t>jasprit bumrah</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -12415,49 +12441,6 @@
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Harpreet Brar</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>BOWL</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>jasprit bumrah</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="G46" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" t="n">
         <v>0</v>
       </c>
     </row>

--- a/IPL_Fantasy_Points.xlsx
+++ b/IPL_Fantasy_Points.xlsx
@@ -2840,19 +2840,19 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>104</v>
+        <v>123</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>104</v>
+        <v>123</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>104</v>
+        <v>123</v>
       </c>
     </row>
     <row r="57">
@@ -3786,19 +3786,19 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>196</v>
+        <v>201</v>
       </c>
     </row>
     <row r="79">
@@ -4219,16 +4219,16 @@
         <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I88" t="n">
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="K88" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
     </row>
     <row r="89">
@@ -4345,19 +4345,19 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
       </c>
       <c r="I91" t="n">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="92">
@@ -4821,16 +4821,16 @@
         <v>0</v>
       </c>
       <c r="H102" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I102" t="n">
         <v>0</v>
       </c>
       <c r="J102" t="n">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="K102" t="n">
-        <v>80</v>
+        <v>160</v>
       </c>
     </row>
     <row r="103">
@@ -4849,31 +4849,31 @@
           <t>BOWL</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>jamie overton</t>
-        </is>
-      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>kyle jamieson</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="G103" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I103" t="n">
         <v>0</v>
       </c>
       <c r="J103" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K103" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="104">
@@ -5850,19 +5850,19 @@
         </is>
       </c>
       <c r="G126" t="n">
-        <v>208</v>
+        <v>242</v>
       </c>
       <c r="H126" t="n">
         <v>0</v>
       </c>
       <c r="I126" t="n">
-        <v>208</v>
+        <v>242</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
       </c>
       <c r="K126" t="n">
-        <v>208</v>
+        <v>242</v>
       </c>
     </row>
     <row r="127">
@@ -6624,19 +6624,19 @@
         </is>
       </c>
       <c r="G144" t="n">
-        <v>328</v>
+        <v>351</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
       </c>
       <c r="I144" t="n">
-        <v>328</v>
+        <v>351</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
       </c>
       <c r="K144" t="n">
-        <v>328</v>
+        <v>351</v>
       </c>
     </row>
     <row r="145">
@@ -6753,19 +6753,19 @@
         </is>
       </c>
       <c r="G147" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H147" t="n">
         <v>0</v>
       </c>
       <c r="I147" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
       </c>
       <c r="K147" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="148">
@@ -7014,16 +7014,16 @@
         <v>36</v>
       </c>
       <c r="H153" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I153" t="n">
         <v>36</v>
       </c>
       <c r="J153" t="n">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="K153" t="n">
-        <v>196</v>
+        <v>216</v>
       </c>
     </row>
     <row r="154">
@@ -7186,16 +7186,16 @@
         <v>12</v>
       </c>
       <c r="H157" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I157" t="n">
         <v>0</v>
       </c>
       <c r="J157" t="n">
-        <v>220</v>
+        <v>280</v>
       </c>
       <c r="K157" t="n">
-        <v>220</v>
+        <v>280</v>
       </c>
     </row>
     <row r="158">
@@ -7472,31 +7472,31 @@
           <t>BAT</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr"/>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>abhishek sharma</t>
-        </is>
-      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>abishek porel</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>ai_structured</t>
         </is>
       </c>
       <c r="G164" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H164" t="n">
         <v>0</v>
       </c>
       <c r="I164" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
       </c>
       <c r="K164" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="165">
@@ -8003,16 +8003,16 @@
         <v>0</v>
       </c>
       <c r="H176" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I176" t="n">
         <v>0</v>
       </c>
       <c r="J176" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="K176" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
     </row>
     <row r="177">
@@ -8086,7 +8086,7 @@
         </is>
       </c>
       <c r="G178" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H178" t="n">
         <v>7</v>
@@ -8185,7 +8185,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2639</v>
+        <v>2664</v>
       </c>
     </row>
     <row r="3">
@@ -8207,11 +8207,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BABA11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1966</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="5">
@@ -8220,11 +8220,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>BABA11</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1953</v>
+        <v>1985</v>
       </c>
     </row>
     <row r="6">
@@ -8233,11 +8233,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1913</v>
+        <v>1974</v>
       </c>
     </row>
     <row r="7">
@@ -8246,11 +8246,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1873</v>
+        <v>1953</v>
       </c>
     </row>
     <row r="8">
@@ -8276,7 +8276,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1714</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="10">
@@ -8302,7 +8302,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1392</v>
+        <v>1442</v>
       </c>
     </row>
   </sheetData>
@@ -8316,7 +8316,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C166"/>
+  <dimension ref="A1:C170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8378,11 +8378,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>aiden markram</t>
+          <t>abishek porel</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>30</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -8391,11 +8391,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ajinkya rahane</t>
+          <t>aiden markram</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>162</v>
+        <v>193</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -8404,50 +8404,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>akeal hosein</t>
+          <t>ajinkya rahane</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>162</v>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>am ghazanfar</t>
+          <t>akeal hosein</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>angkrish raghuvanshi</t>
+          <t>am ghazanfar</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>209</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>aniket verma</t>
+          <t>angkrish raghuvanshi</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>73</v>
+        <v>209</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -8456,11 +8456,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>anrich nortje</t>
+          <t>aniket verma</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -8469,154 +8469,154 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>anshul kamboj</t>
+          <t>anrich nortje</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>anukul roy</t>
+          <t>anshul kamboj</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>39</v>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>arshad khan</t>
+          <t>anukul roy</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>arshdeep singh</t>
+          <t>arshad khan</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ashok sharma</t>
+          <t>arshdeep singh</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ashutosh sharma</t>
+          <t>ashok sharma</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ashwani kumar</t>
+          <t>ashutosh sharma</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="C18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>auqib nabi</t>
+          <t>ashwani kumar</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>avesh khan</t>
+          <t>auqib nabi</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C20" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>axar patel</t>
+          <t>avesh khan</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="C21" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ayush badoni</t>
+          <t>axar patel</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>172</v>
+        <v>31</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ayush mhatre</t>
+          <t>ayush badoni</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>201</v>
+        <v>172</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
@@ -8625,11 +8625,11 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>b sai sudharshan</t>
+          <t>ayush mhatre</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>322</v>
+        <v>201</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
@@ -8638,102 +8638,102 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>bhuvneshwar kumar</t>
+          <t>b sai sudharshan</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>12</v>
+        <v>322</v>
       </c>
       <c r="C25" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>blessing muzarabani</t>
+          <t>bhuvneshwar kumar</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C26" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>brijesh sharma</t>
+          <t>blessing muzarabani</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>cameron green</t>
+          <t>brijesh sharma</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>196</v>
+        <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>cooper connolly</t>
+          <t>cameron green</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>240</v>
+        <v>196</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>corbin bosch</t>
+          <t>cooper connolly</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>11</v>
+        <v>240</v>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>danish malewar</t>
+          <t>corbin bosch</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>david miller</t>
+          <t>danish malewar</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>104</v>
+        <v>2</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
@@ -8742,50 +8742,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>david payne</t>
+          <t>david miller</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>6</v>
+        <v>123</v>
       </c>
       <c r="C33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>deepak chahar</t>
+          <t>david payne</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>6</v>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>devdutt padikkal</t>
+          <t>deepak chahar</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>208</v>
+        <v>6</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>dewald brevis</t>
+          <t>devdutt padikkal</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>64</v>
+        <v>242</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
@@ -8794,11 +8794,11 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>dhruv chand jurel</t>
+          <t>dewald brevis</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>232</v>
+        <v>64</v>
       </c>
       <c r="C37" t="n">
         <v>0</v>
@@ -8807,37 +8807,37 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>digvesh rathi</t>
+          <t>dhruv chand jurel</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2</v>
+        <v>232</v>
       </c>
       <c r="C38" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>dilshan madushanka</t>
+          <t>digvesh rathi</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C39" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>donavon ferreira</t>
+          <t>dilshan madushanka</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="C40" t="n">
         <v>1</v>
@@ -8846,24 +8846,24 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>eshan malinga</t>
+          <t>donavon ferreira</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="C41" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>finn allen</t>
+          <t>dushmantha chameera</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
@@ -8872,24 +8872,24 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>george linde</t>
+          <t>eshan malinga</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="C43" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>glenn phillips</t>
+          <t>finn allen</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
@@ -8898,76 +8898,76 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>gurjapneet singh</t>
+          <t>george linde</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="C45" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>hardik pandya</t>
+          <t>glenn phillips</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>97</v>
+        <v>67</v>
       </c>
       <c r="C46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>harsh dubey</t>
+          <t>gurjapneet singh</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C47" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>harshal patel</t>
+          <t>hardik pandya</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>4</v>
+        <v>97</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>heinrich klaasen</t>
+          <t>harsh dubey</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>349</v>
+        <v>13</v>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>himmat singh</t>
+          <t>harshal patel</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="C50" t="n">
         <v>0</v>
@@ -8976,11 +8976,11 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ishan kishan</t>
+          <t>heinrich klaasen</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>312</v>
+        <v>349</v>
       </c>
       <c r="C51" t="n">
         <v>0</v>
@@ -8989,11 +8989,11 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>jacob bethell</t>
+          <t>himmat singh</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="C52" t="n">
         <v>0</v>
@@ -9002,102 +9002,102 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>jacob duffy</t>
+          <t>ishan kishan</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0</v>
+        <v>312</v>
       </c>
       <c r="C53" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>jamie overton</t>
+          <t>jacob bethell</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>136</v>
+        <v>34</v>
       </c>
       <c r="C54" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>jason holder</t>
+          <t>jacob duffy</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>jasprit bumrah</t>
+          <t>jamie overton</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>7</v>
+        <v>136</v>
       </c>
       <c r="C56" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>jaydev unadkat</t>
+          <t>jason holder</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="C57" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>jitesh sharma</t>
+          <t>jasprit bumrah</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>62</v>
+        <v>7</v>
       </c>
       <c r="C58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>jofra archer</t>
+          <t>jaydev unadkat</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C59" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>jos buttler</t>
+          <t>jitesh sharma</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>270</v>
+        <v>62</v>
       </c>
       <c r="C60" t="n">
         <v>0</v>
@@ -9106,63 +9106,63 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>josh hazlewood</t>
+          <t>jofra archer</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="C61" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>kagiso rabada</t>
+          <t>jos buttler</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>35</v>
+        <v>270</v>
       </c>
       <c r="C62" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>kartik sharma</t>
+          <t>josh hazlewood</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="C63" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>kartik tyagi</t>
+          <t>kagiso rabada</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="C64" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>karun nair</t>
+          <t>kartik sharma</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>5</v>
+        <v>58</v>
       </c>
       <c r="C65" t="n">
         <v>0</v>
@@ -9171,24 +9171,24 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>khaleel ahmed</t>
+          <t>kartik tyagi</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C66" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>krish bhagat</t>
+          <t>karun nair</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C67" t="n">
         <v>0</v>
@@ -9197,63 +9197,63 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>krunal pandya</t>
+          <t>khaleel ahmed</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="C68" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>kuldeep yadav</t>
+          <t>krish bhagat</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C69" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>kumar kushagra</t>
+          <t>krunal pandya</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="C70" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>lhuan dre pretorius</t>
+          <t>kuldeep yadav</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C71" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>liam livingstone</t>
+          <t>kumar kushagra</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C72" t="n">
         <v>0</v>
@@ -9262,115 +9262,115 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>lokesh rahul</t>
+          <t>kyle jamieson</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>357</v>
+        <v>12</v>
       </c>
       <c r="C73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>lungi ngidi</t>
+          <t>lhuan dre pretorius</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C74" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>manav suthar</t>
+          <t>liam livingstone</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C75" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>manimaran siddharth</t>
+          <t>lokesh rahul</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0</v>
+        <v>358</v>
       </c>
       <c r="C76" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>marco jansen</t>
+          <t>lungi ngidi</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C77" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>marcus stoinis</t>
+          <t>manav suthar</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="C78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>matt henry</t>
+          <t>manimaran siddharth</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C79" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>matt short</t>
+          <t>marco jansen</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="C80" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>mayank markande</t>
+          <t>marcus stoinis</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="C81" t="n">
         <v>0</v>
@@ -9379,24 +9379,24 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>mayank rawat</t>
+          <t>matt henry</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>mayank yadav</t>
+          <t>matt short</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
@@ -9405,11 +9405,11 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>mitchell marsh</t>
+          <t>mayank markande</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>212</v>
+        <v>0</v>
       </c>
       <c r="C84" t="n">
         <v>0</v>
@@ -9418,128 +9418,128 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>mitchell santner</t>
+          <t>mayank rawat</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="C85" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>mohammed shami</t>
+          <t>mayank yadav</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="C86" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>mohammed siraj</t>
+          <t>mitchell marsh</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0</v>
+        <v>212</v>
       </c>
       <c r="C87" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>mohsin khan</t>
+          <t>mitchell santner</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="C88" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>mukesh choudhary</t>
+          <t>mohammed shami</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="C89" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>mukesh kumar</t>
+          <t>mohammed siraj</t>
         </is>
       </c>
       <c r="B90" t="n">
         <v>0</v>
       </c>
       <c r="C90" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>mukul choudhary</t>
+          <t>mohsin khan</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="C91" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>naman dhir</t>
+          <t>mukesh choudhary</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>154</v>
+        <v>0</v>
       </c>
       <c r="C92" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>nandre burger</t>
+          <t>mukesh kumar</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C93" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>navdeep saini</t>
+          <t>mukul choudhary</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
@@ -9548,11 +9548,11 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>nehal wadhera</t>
+          <t>naman dhir</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>65</v>
+        <v>154</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
@@ -9561,37 +9561,37 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>nicholas pooran</t>
+          <t>nandre burger</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>82</v>
+        <v>3</v>
       </c>
       <c r="C96" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>nitish kumar reddy</t>
+          <t>navdeep saini</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>172</v>
+        <v>0</v>
       </c>
       <c r="C97" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>nitish rana</t>
+          <t>nehal wadhera</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>168</v>
+        <v>65</v>
       </c>
       <c r="C98" t="n">
         <v>0</v>
@@ -9600,37 +9600,37 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>noor ahmad</t>
+          <t>nicholas pooran</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>10</v>
+        <v>82</v>
       </c>
       <c r="C99" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>pat cummins</t>
+          <t>nitish kumar reddy</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0</v>
+        <v>172</v>
       </c>
       <c r="C100" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>pathum nissanka</t>
+          <t>nitish rana</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>147</v>
+        <v>169</v>
       </c>
       <c r="C101" t="n">
         <v>0</v>
@@ -9639,50 +9639,50 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>philip salt</t>
+          <t>noor ahmad</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>202</v>
+        <v>10</v>
       </c>
       <c r="C102" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>prabhsimran singh</t>
+          <t>pat cummins</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>287</v>
+        <v>0</v>
       </c>
       <c r="C103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>praful hinge</t>
+          <t>pathum nissanka</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0</v>
+        <v>147</v>
       </c>
       <c r="C104" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>prashant veer</t>
+          <t>philip salt</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>49</v>
+        <v>202</v>
       </c>
       <c r="C105" t="n">
         <v>0</v>
@@ -9691,37 +9691,37 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>prasidh krishna</t>
+          <t>prabhsimran singh</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0</v>
+        <v>287</v>
       </c>
       <c r="C106" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>prince yadav</t>
+          <t>praful hinge</t>
         </is>
       </c>
       <c r="B107" t="n">
         <v>0</v>
       </c>
       <c r="C107" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>priyansh arya</t>
+          <t>prashant veer</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>254</v>
+        <v>49</v>
       </c>
       <c r="C108" t="n">
         <v>0</v>
@@ -9730,37 +9730,37 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>quinton de kock</t>
+          <t>prasidh krishna</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="C109" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>rahul chahar</t>
+          <t>prince yadav</t>
         </is>
       </c>
       <c r="B110" t="n">
         <v>0</v>
       </c>
       <c r="C110" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>rahul tewatia</t>
+          <t>priyansh arya</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>49</v>
+        <v>254</v>
       </c>
       <c r="C111" t="n">
         <v>0</v>
@@ -9769,11 +9769,11 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>rajat patidar</t>
+          <t>quinton de kock</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>238</v>
+        <v>132</v>
       </c>
       <c r="C112" t="n">
         <v>0</v>
@@ -9782,115 +9782,115 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ramandeep singh</t>
+          <t>rahul chahar</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="C113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>rashid khan</t>
+          <t>rahul tewatia</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="C114" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>rasikh salam</t>
+          <t>rajat patidar</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0</v>
+        <v>238</v>
       </c>
       <c r="C115" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ravi bishnoi</t>
+          <t>ramandeep singh</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="C116" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ravindra jadeja</t>
+          <t>rashid khan</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>132</v>
+        <v>28</v>
       </c>
       <c r="C117" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>rinku singh</t>
+          <t>rasikh salam</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="C118" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>rishabh pant</t>
+          <t>ravi bishnoi</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>189</v>
+        <v>0</v>
       </c>
       <c r="C119" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>riyan parag</t>
+          <t>ravindra jadeja</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>88</v>
+        <v>132</v>
       </c>
       <c r="C120" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>rohit sharma</t>
+          <t>rinku singh</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="C121" t="n">
         <v>0</v>
@@ -9899,37 +9899,37 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>romario shepherd</t>
+          <t>rishabh pant</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>39</v>
+        <v>189</v>
       </c>
       <c r="C122" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>rovman powell</t>
+          <t>riyan parag</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>121</v>
+        <v>88</v>
       </c>
       <c r="C123" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ruturaj gaikwad</t>
+          <t>rohit sharma</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>178</v>
+        <v>137</v>
       </c>
       <c r="C124" t="n">
         <v>0</v>
@@ -9938,37 +9938,37 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>ryan rickelton</t>
+          <t>romario shepherd</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>137</v>
+        <v>39</v>
       </c>
       <c r="C125" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>sakib hussain</t>
+          <t>rovman powell</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="C126" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>salil arora</t>
+          <t>ruturaj gaikwad</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>63</v>
+        <v>178</v>
       </c>
       <c r="C127" t="n">
         <v>0</v>
@@ -9977,11 +9977,11 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>sameer rizvi</t>
+          <t>ryan rickelton</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>209</v>
+        <v>137</v>
       </c>
       <c r="C128" t="n">
         <v>0</v>
@@ -9990,37 +9990,37 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>sandeep sharma</t>
+          <t>sahil parakh</t>
         </is>
       </c>
       <c r="B129" t="n">
         <v>0</v>
       </c>
       <c r="C129" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>sanju samson</t>
+          <t>sakib hussain</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>304</v>
+        <v>0</v>
       </c>
       <c r="C130" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>sarfaraz khan</t>
+          <t>salil arora</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>161</v>
+        <v>63</v>
       </c>
       <c r="C131" t="n">
         <v>0</v>
@@ -10029,11 +10029,11 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>shahbaz ahmed</t>
+          <t>sameer rizvi</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>15</v>
+        <v>209</v>
       </c>
       <c r="C132" t="n">
         <v>0</v>
@@ -10042,50 +10042,50 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>shahrukh khan</t>
+          <t>sandeep sharma</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="C133" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>shardul thakur</t>
+          <t>sanju samson</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>14</v>
+        <v>304</v>
       </c>
       <c r="C134" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>shashank singh</t>
+          <t>sarfaraz khan</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>70</v>
+        <v>161</v>
       </c>
       <c r="C135" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>sherfane rutherford</t>
+          <t>shahbaz ahmed</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>103</v>
+        <v>15</v>
       </c>
       <c r="C136" t="n">
         <v>0</v>
@@ -10094,11 +10094,11 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>shimron hetmyer</t>
+          <t>shahrukh khan</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>72</v>
+        <v>35</v>
       </c>
       <c r="C137" t="n">
         <v>0</v>
@@ -10107,37 +10107,37 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>shivam dube</t>
+          <t>shardul thakur</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>150</v>
+        <v>14</v>
       </c>
       <c r="C138" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>shivang kumar</t>
+          <t>shashank singh</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>21</v>
+        <v>70</v>
       </c>
       <c r="C139" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>shreyas iyer</t>
+          <t>sherfane rutherford</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>279</v>
+        <v>103</v>
       </c>
       <c r="C140" t="n">
         <v>0</v>
@@ -10146,11 +10146,11 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>shubham badriprasad dubey</t>
+          <t>shimron hetmyer</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>19</v>
+        <v>72</v>
       </c>
       <c r="C141" t="n">
         <v>0</v>
@@ -10159,37 +10159,37 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>shubman gill</t>
+          <t>shivam dube</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>330</v>
+        <v>150</v>
       </c>
       <c r="C142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>sunil narine</t>
+          <t>shivang kumar</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="C143" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>suryakumar yadav</t>
+          <t>shreyas iyer</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>157</v>
+        <v>279</v>
       </c>
       <c r="C144" t="n">
         <v>0</v>
@@ -10198,50 +10198,50 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>suyash sharma</t>
+          <t>shubham badriprasad dubey</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="C145" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>t natarajan</t>
+          <t>shubman gill</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>1</v>
+        <v>330</v>
       </c>
       <c r="C146" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>tilak varma</t>
+          <t>sunil narine</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>181</v>
+        <v>40</v>
       </c>
       <c r="C147" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>tim david</t>
+          <t>suryakumar yadav</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>183</v>
+        <v>157</v>
       </c>
       <c r="C148" t="n">
         <v>0</v>
@@ -10250,50 +10250,50 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>tim seifert</t>
+          <t>suyash sharma</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="C149" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>travis head</t>
+          <t>t natarajan</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>186</v>
+        <v>1</v>
       </c>
       <c r="C150" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>trent boult</t>
+          <t>tilak varma</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>1</v>
+        <v>181</v>
       </c>
       <c r="C151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>tristan stubbs</t>
+          <t>tim david</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="C152" t="n">
         <v>0</v>
@@ -10302,24 +10302,24 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>tushar deshpande</t>
+          <t>tim seifert</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C153" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>urvil patel</t>
+          <t>travis head</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>4</v>
+        <v>186</v>
       </c>
       <c r="C154" t="n">
         <v>0</v>
@@ -10328,24 +10328,24 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>vaibhav arora</t>
+          <t>trent boult</t>
         </is>
       </c>
       <c r="B155" t="n">
         <v>1</v>
       </c>
       <c r="C155" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>vaibhav suryavanshi</t>
+          <t>tristan stubbs</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>357</v>
+        <v>201</v>
       </c>
       <c r="C156" t="n">
         <v>0</v>
@@ -10354,24 +10354,24 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>varun chakravarthy</t>
+          <t>tushar deshpande</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="C157" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>venkatesh iyer</t>
+          <t>urvil patel</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="C158" t="n">
         <v>0</v>
@@ -10380,89 +10380,89 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>vijaykumar vyshak</t>
+          <t>vaibhav arora</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C159" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>vipraj nigam</t>
+          <t>vaibhav suryavanshi</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>12</v>
+        <v>357</v>
       </c>
       <c r="C160" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>virat kohli</t>
+          <t>varun chakravarthy</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>328</v>
+        <v>0</v>
       </c>
       <c r="C161" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>washington sundar</t>
+          <t>venkatesh iyer</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>157</v>
+        <v>29</v>
       </c>
       <c r="C162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>xavier bartlett</t>
+          <t>vijaykumar vyshak</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C163" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>yash raj punja</t>
+          <t>vipraj nigam</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C164" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>yashasvi jaiswal</t>
+          <t>virat kohli</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>255</v>
+        <v>351</v>
       </c>
       <c r="C165" t="n">
         <v>0</v>
@@ -10471,13 +10471,65 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
+          <t>washington sundar</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>157</v>
+      </c>
+      <c r="C166" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>xavier bartlett</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>11</v>
+      </c>
+      <c r="C167" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>yash raj punja</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>0</v>
+      </c>
+      <c r="C168" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>yashasvi jaiswal</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>255</v>
+      </c>
+      <c r="C169" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
           <t>yuzvendra chahal</t>
         </is>
       </c>
-      <c r="B166" t="n">
-        <v>0</v>
-      </c>
-      <c r="C166" t="n">
+      <c r="B170" t="n">
+        <v>0</v>
+      </c>
+      <c r="C170" t="n">
         <v>4</v>
       </c>
     </row>
@@ -10492,7 +10544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K45"/>
+  <dimension ref="A1:K43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11544,7 +11596,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Kyle Jamieson</t>
+          <t>Matheesha Pathirana</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11560,7 +11612,7 @@
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>jamie overton</t>
+          <t>eshan malinga</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -11587,7 +11639,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Matheesha Pathirana</t>
+          <t>Ben Dwarshuis</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11603,7 +11655,7 @@
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>eshan malinga</t>
+          <t>b sai sudharshan</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -11630,23 +11682,23 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Ben Dwarshuis</t>
+          <t>Manish Pandey</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>b sai sudharshan</t>
+          <t>hardik pandya</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -11673,7 +11725,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Manish Pandey</t>
+          <t>Arjun Tendulkar</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -11683,13 +11735,13 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>hardik pandya</t>
+          <t>karun nair</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -11716,7 +11768,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Arjun Tendulkar</t>
+          <t>Kwena Maphaka</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -11732,7 +11784,7 @@
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>karun nair</t>
+          <t>aiden markram</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -11759,23 +11811,23 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Kwena Maphaka</t>
+          <t>Ramkrishna Ghosh</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>aiden markram</t>
+          <t>angkrish raghuvanshi</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -11802,7 +11854,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Ramkrishna Ghosh</t>
+          <t>Azmatullah Omarzai</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -11812,13 +11864,13 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>angkrish raghuvanshi</t>
+          <t>mitchell marsh</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -11845,23 +11897,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Azmatullah Omarzai</t>
+          <t>akshat raghuwanshi</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>mitchell marsh</t>
+          <t>angkrish raghuvanshi</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -11888,7 +11940,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>akshat raghuwanshi</t>
+          <t>Suryansh Shegde</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -11904,7 +11956,7 @@
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>angkrish raghuvanshi</t>
+          <t>suyash sharma</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -11931,7 +11983,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Suryansh Shegde</t>
+          <t>Tejasvi Singh</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -11947,7 +11999,7 @@
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>suyash sharma</t>
+          <t>prabhsimran singh</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -11974,7 +12026,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Tejasvi Singh</t>
+          <t>Sai Kishor</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -11984,13 +12036,13 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>prabhsimran singh</t>
+          <t>ishan kishan</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -12017,7 +12069,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sai Kishor</t>
+          <t>Akash Deep</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -12033,7 +12085,7 @@
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ishan kishan</t>
+          <t>arshdeep singh</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -12060,23 +12112,23 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Akash Deep</t>
+          <t>Ben Duckett</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>arshdeep singh</t>
+          <t>ryan rickelton</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -12103,7 +12155,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Ben Duckett</t>
+          <t>Rahul Tripathi</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -12119,7 +12171,7 @@
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>ryan rickelton</t>
+          <t>rahul tewatia</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -12146,7 +12198,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Abhishek Porel</t>
+          <t>Dre Pretorius</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -12162,7 +12214,7 @@
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>abhishek sharma</t>
+          <t>lhuan dre pretorius</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -12189,7 +12241,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rahul Tripathi</t>
+          <t>Matthew Breetzke</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -12205,7 +12257,7 @@
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>rahul tewatia</t>
+          <t>matt henry</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -12232,7 +12284,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Dre Pretorius</t>
+          <t>Anuj Rawat</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -12248,7 +12300,7 @@
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>lhuan dre pretorius</t>
+          <t>mayank rawat</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -12275,7 +12327,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Matthew Breetzke</t>
+          <t>Wanindu Hasaranga</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -12285,13 +12337,13 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>matt henry</t>
+          <t>sandeep sharma</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -12318,7 +12370,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Anuj Rawat</t>
+          <t>Harpreet Brar</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -12328,13 +12380,13 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>mayank rawat</t>
+          <t>jasprit bumrah</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -12355,92 +12407,6 @@
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Wanindu Hasaranga</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>AR</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>sandeep sharma</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="G44" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Harpreet Brar</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>BOWL</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>jasprit bumrah</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="G45" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12526,7 +12492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12629,6 +12595,49 @@
         <v>150</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Abhishek Porel</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>PRATIK11</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>BAT</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>abishek porel</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>ai_structured</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>30</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>30</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
